--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Trade" sheetId="4" r:id="rId3"/>
     <sheet name="references" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="358">
   <si>
     <t>parameter</t>
   </si>
@@ -1114,6 +1114,12 @@
   </si>
   <si>
     <t>for 2019</t>
+  </si>
+  <si>
+    <t>temp add 303000</t>
+  </si>
+  <si>
+    <t>temp add 246000</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N386"/>
+  <dimension ref="A1:R386"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -3295,7 +3301,7 @@
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>295</v>
       </c>
@@ -3321,7 +3327,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>296</v>
       </c>
@@ -3335,7 +3341,8 @@
         <v>300</v>
       </c>
       <c r="K98" s="33">
-        <v>304650.40000000002</v>
+        <f>304650.4+303000</f>
+        <v>607650.4</v>
       </c>
       <c r="L98" t="s">
         <v>196</v>
@@ -3346,8 +3353,11 @@
       <c r="N98" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="R98" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>297</v>
       </c>
@@ -3373,7 +3383,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>298</v>
       </c>
@@ -3387,7 +3397,8 @@
         <v>300</v>
       </c>
       <c r="K100" s="33">
-        <v>177249.6</v>
+        <f>177249.6+246000</f>
+        <v>423249.6</v>
       </c>
       <c r="L100" t="s">
         <v>196</v>
@@ -3398,8 +3409,11 @@
       <c r="N100" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="R100" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>208</v>
       </c>
@@ -3425,7 +3439,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -3451,7 +3465,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>34</v>
       </c>
@@ -3469,7 +3483,7 @@
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>26</v>
       </c>
@@ -3486,7 +3500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>26</v>
       </c>
@@ -3503,7 +3517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>26</v>
       </c>
@@ -3523,7 +3537,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>103</v>
       </c>
@@ -3540,7 +3554,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>103</v>
       </c>
@@ -3557,7 +3571,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>103</v>
       </c>
@@ -3577,7 +3591,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>108</v>
       </c>
@@ -3594,7 +3608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>108</v>
       </c>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="9870"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="7170"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="374">
   <si>
     <t>parameter</t>
   </si>
@@ -384,21 +384,6 @@
     <t>~75% water content. 20% of produced beer</t>
   </si>
   <si>
-    <t>wheat bran</t>
-  </si>
-  <si>
-    <t>wheat germ</t>
-  </si>
-  <si>
-    <t>barley bran</t>
-  </si>
-  <si>
-    <t>barley hulls</t>
-  </si>
-  <si>
-    <t>rye bran</t>
-  </si>
-  <si>
     <t>potatoe offals</t>
   </si>
   <si>
@@ -600,9 +585,6 @@
     <t>Share conventional is calculated as what remains (value should be -100). Do not specify per food</t>
   </si>
   <si>
-    <t>oat hulls</t>
-  </si>
-  <si>
     <t>Wheat and products, refined</t>
   </si>
   <si>
@@ -969,9 +951,6 @@
     <t>Other</t>
   </si>
   <si>
-    <t>Raw commodity</t>
-  </si>
-  <si>
     <t>Adjusted to ~1/2 of prod. used in paper industry</t>
   </si>
   <si>
@@ -1077,12 +1056,6 @@
     <t>2.1 kg DM wheat --&gt; 1 L bioethanol + 0.8 kg DM distillers grain. Wheat 86% DM, distillers grain 90% DM. Bioethanol 21.3 MJ/L and 27.8 MJ/kg --&gt; 0.766 kg/L</t>
   </si>
   <si>
-    <t>havrekli??</t>
-  </si>
-  <si>
-    <t>oat bran</t>
-  </si>
-  <si>
     <t>161 kg WS/t SB</t>
   </si>
   <si>
@@ -1102,15 +1075,6 @@
   </si>
   <si>
     <t>https://fransverige.se/aktuellt/nya-siffror-visar-sveriges-sjalvforsorjningsgrad/</t>
-  </si>
-  <si>
-    <t>43.6% 2019. Adjusted to match slaughter statistics</t>
-  </si>
-  <si>
-    <t>23.3% 2019. Adjusted to match slaughter statistics</t>
-  </si>
-  <si>
-    <t>28.4% 2019. Adjusted to match slaughter statistics</t>
   </si>
   <si>
     <t>for 2019</t>
@@ -1173,6 +1137,57 @@
       </rPr>
       <t xml:space="preserve"> No demand for the number of 'other sheep'. Their number is instead controlled by setting 'max_share_in_sub_system' parameter</t>
     </r>
+  </si>
+  <si>
+    <t>SOURCE?</t>
+  </si>
+  <si>
+    <t>milling by-products from wheat, barley or rye</t>
+  </si>
+  <si>
+    <t>bran?</t>
+  </si>
+  <si>
+    <t>19% bran + 2% germ</t>
+  </si>
+  <si>
+    <t>19% bran + 9% hulls</t>
+  </si>
+  <si>
+    <t>hulls</t>
+  </si>
+  <si>
+    <t>bran</t>
+  </si>
+  <si>
+    <t>20% offals + 27% hulls</t>
+  </si>
+  <si>
+    <t>milling by-products from oats</t>
+  </si>
+  <si>
+    <t>27% hulls</t>
+  </si>
+  <si>
+    <t>Unprocessed commodity</t>
+  </si>
+  <si>
+    <t>adjusted from 73% to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>adjusted from 71% to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>Clune et al</t>
+  </si>
+  <si>
+    <t>adjusted from 77% (= bone free) to match slaughter statistics. Large change needed, potentially cons./imp./waste wrong</t>
+  </si>
+  <si>
+    <t>changed from 2.9 g/day to match slaughter statistics</t>
+  </si>
+  <si>
+    <t>chnaged from 66% to match slaughter statistics</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1358,6 +1373,8 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1742,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R397"/>
+  <dimension ref="A1:R395"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -1874,7 +1891,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1890,15 +1907,15 @@
         <v>19</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="N7" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1916,7 +1933,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1932,15 +1949,15 @@
         <v>19</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N9" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -1959,7 +1976,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1975,12 +1992,12 @@
         <v>19</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -2016,7 +2033,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
@@ -2032,12 +2049,12 @@
         <v>19</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -2056,7 +2073,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -2072,12 +2089,12 @@
         <v>19</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -2096,7 +2113,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -2112,12 +2129,12 @@
         <v>19</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
@@ -2188,7 +2205,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
         <v>103</v>
@@ -2225,7 +2242,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2243,7 +2260,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
         <v>108</v>
@@ -2260,7 +2277,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B27" t="s">
         <v>108</v>
@@ -2277,7 +2294,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
         <v>108</v>
@@ -2294,7 +2311,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
         <v>108</v>
@@ -2311,7 +2328,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -2328,7 +2345,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B31" t="s">
         <v>108</v>
@@ -2379,7 +2396,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B34" t="s">
         <v>108</v>
@@ -2396,7 +2413,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B35" t="s">
         <v>108</v>
@@ -2412,7 +2429,7 @@
         <v>19</v>
       </c>
       <c r="M35" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -2421,7 +2438,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2439,10 +2456,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
@@ -2456,10 +2473,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -2473,10 +2490,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
@@ -2490,10 +2507,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -2507,10 +2524,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2523,15 +2540,15 @@
         <v>19</v>
       </c>
       <c r="M42" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -2545,10 +2562,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C44" s="9"/>
       <c r="J44" t="s">
@@ -2561,15 +2578,15 @@
         <v>19</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B45" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J45" t="s">
         <v>18</v>
@@ -2582,7 +2599,7 @@
         <v>19</v>
       </c>
       <c r="M45" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -2822,7 +2839,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
@@ -2830,16 +2847,19 @@
       <c r="J59" t="s">
         <v>18</v>
       </c>
-      <c r="K59">
-        <v>2.9</v>
+      <c r="K59" s="6">
+        <v>2.1</v>
       </c>
       <c r="L59" t="s">
         <v>19</v>
       </c>
+      <c r="M59" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s">
         <v>55</v>
@@ -2877,7 +2897,7 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="J62" t="s">
         <v>18</v>
@@ -2890,7 +2910,7 @@
         <v>19</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -2931,10 +2951,10 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J65" t="s">
         <v>18</v>
@@ -2948,10 +2968,10 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J66" t="s">
         <v>18</v>
@@ -2965,10 +2985,10 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J67" t="s">
         <v>18</v>
@@ -2982,10 +3002,10 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J68" t="s">
         <v>18</v>
@@ -2999,10 +3019,10 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J69" t="s">
         <v>18</v>
@@ -3052,10 +3072,10 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J72" t="s">
         <v>18</v>
@@ -3068,15 +3088,15 @@
         <v>19</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J73" t="s">
         <v>18</v>
@@ -3089,15 +3109,15 @@
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J74" t="s">
         <v>18</v>
@@ -3110,7 +3130,7 @@
         <v>19</v>
       </c>
       <c r="M74" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -3133,10 +3153,10 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J76" t="s">
         <v>18</v>
@@ -3150,10 +3170,10 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B77" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J77" t="s">
         <v>18</v>
@@ -3165,15 +3185,15 @@
         <v>19</v>
       </c>
       <c r="M77" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J78" t="s">
         <v>18</v>
@@ -3205,7 +3225,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B80" t="s">
         <v>112</v>
@@ -3222,7 +3242,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B81" t="s">
         <v>112</v>
@@ -3239,7 +3259,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B82" t="s">
         <v>112</v>
@@ -3254,12 +3274,12 @@
         <v>19</v>
       </c>
       <c r="M82" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
@@ -3274,7 +3294,7 @@
         <v>19</v>
       </c>
       <c r="M83" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -3351,7 +3371,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3369,50 +3389,50 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" t="s">
         <v>200</v>
-      </c>
-      <c r="B90" t="s">
-        <v>206</v>
       </c>
       <c r="H90" t="s">
         <v>45</v>
       </c>
       <c r="J90" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K90" s="33">
-        <f>600000*(K389/100)</f>
+        <f>600000*(K387/100)</f>
         <v>188217.14285714284</v>
       </c>
       <c r="L90" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M90" s="17" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N90" s="21"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H91" t="s">
         <v>45</v>
       </c>
       <c r="J91" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K91" s="33">
         <v>10000</v>
       </c>
       <c r="L91" t="s">
+        <v>190</v>
+      </c>
+      <c r="M91" t="s">
         <v>196</v>
-      </c>
-      <c r="M91" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -3423,25 +3443,25 @@
         <v>101</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H93" t="s">
         <v>45</v>
       </c>
       <c r="J93" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K93" s="33">
         <v>34000</v>
       </c>
       <c r="L93" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M93" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N93" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -3449,39 +3469,39 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H95" t="s">
         <v>45</v>
       </c>
       <c r="J95" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K95" s="37">
         <v>355.5</v>
       </c>
       <c r="L95" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M95" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="45" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="K96" s="37"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H97" t="s">
         <v>45</v>
@@ -3492,18 +3512,18 @@
         <v>90.068160000000006</v>
       </c>
       <c r="L97" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M97" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B98" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H98" t="s">
         <v>43</v>
@@ -3514,7 +3534,7 @@
         <v>25.403839999999999</v>
       </c>
       <c r="L98" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
@@ -3522,7 +3542,7 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -3540,140 +3560,140 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B101" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H101" t="s">
         <v>45</v>
       </c>
       <c r="J101" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K101" s="33">
         <v>558249.80000000005</v>
       </c>
       <c r="L101" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M101" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N101" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B102" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H102" t="s">
         <v>45</v>
       </c>
       <c r="J102" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K102" s="33">
         <f>304650.4+303000</f>
         <v>607650.4</v>
       </c>
       <c r="L102" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M102" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N102" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B103" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H103" t="s">
         <v>45</v>
       </c>
       <c r="J103" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K103" s="33">
         <v>32965.800000000003</v>
       </c>
       <c r="L103" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M103" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="N103" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B104" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H104" t="s">
         <v>45</v>
       </c>
       <c r="J104" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K104" s="33">
         <f>177249.6+246000</f>
         <v>423249.6</v>
       </c>
       <c r="L104" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M104" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N104" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B105" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H105" t="s">
         <v>45</v>
       </c>
       <c r="J105" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K105" s="33">
         <v>22062.799999999999</v>
       </c>
       <c r="L105" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M105" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N105" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -3681,25 +3701,25 @@
         <v>101</v>
       </c>
       <c r="B106" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H106" t="s">
         <v>45</v>
       </c>
       <c r="J106" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K106" s="33">
         <v>25000</v>
       </c>
       <c r="L106" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M106" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="N106" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
@@ -3884,7 +3904,7 @@
     </row>
     <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I118" t="s">
         <v>50</v>
@@ -3901,7 +3921,7 @@
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I119" t="s">
         <v>51</v>
@@ -3918,7 +3938,7 @@
     </row>
     <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I120" t="s">
         <v>52</v>
@@ -4047,7 +4067,7 @@
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I127" t="s">
         <v>50</v>
@@ -4064,7 +4084,7 @@
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I128" t="s">
         <v>51</v>
@@ -4081,7 +4101,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I129" t="s">
         <v>52</v>
@@ -4101,7 +4121,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I130" t="s">
         <v>50</v>
@@ -4118,7 +4138,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I131" t="s">
         <v>51</v>
@@ -4135,7 +4155,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I132" t="s">
         <v>52</v>
@@ -4155,7 +4175,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I133" t="s">
         <v>50</v>
@@ -4172,7 +4192,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I134" t="s">
         <v>51</v>
@@ -4189,7 +4209,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I135" t="s">
         <v>52</v>
@@ -4209,7 +4229,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I136" t="s">
         <v>50</v>
@@ -4226,7 +4246,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I137" t="s">
         <v>51</v>
@@ -4243,7 +4263,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I138" t="s">
         <v>52</v>
@@ -4371,7 +4391,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J146" t="s">
         <v>40</v>
@@ -4385,7 +4405,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J147" t="s">
         <v>40</v>
@@ -4398,12 +4418,12 @@
         <v>38</v>
       </c>
       <c r="M147" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J148" t="s">
         <v>40</v>
@@ -4417,7 +4437,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J149" t="s">
         <v>40</v>
@@ -4430,12 +4450,12 @@
         <v>38</v>
       </c>
       <c r="M149" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J150" t="s">
         <v>40</v>
@@ -4449,7 +4469,7 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J151" t="s">
         <v>40</v>
@@ -4462,7 +4482,7 @@
         <v>38</v>
       </c>
       <c r="M151" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
@@ -4481,7 +4501,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J153" t="s">
         <v>40</v>
@@ -4495,7 +4515,7 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J154" t="s">
         <v>40</v>
@@ -4508,12 +4528,12 @@
         <v>38</v>
       </c>
       <c r="M154" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J155" t="s">
         <v>40</v>
@@ -4527,7 +4547,7 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J156" t="s">
         <v>40</v>
@@ -4540,12 +4560,12 @@
         <v>38</v>
       </c>
       <c r="M156" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J157" t="s">
         <v>40</v>
@@ -4557,12 +4577,12 @@
         <v>38</v>
       </c>
       <c r="M157" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="J158" t="s">
         <v>40</v>
@@ -4575,7 +4595,7 @@
         <v>38</v>
       </c>
       <c r="M158" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
@@ -4626,7 +4646,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J162" t="s">
         <v>40</v>
@@ -4672,7 +4692,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J165" t="s">
         <v>40</v>
@@ -4686,7 +4706,7 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J166" t="s">
         <v>40</v>
@@ -4700,7 +4720,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J167" t="s">
         <v>40</v>
@@ -4714,7 +4734,7 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J168" t="s">
         <v>40</v>
@@ -4728,7 +4748,7 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J169" t="s">
         <v>40</v>
@@ -4740,12 +4760,12 @@
         <v>38</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="17" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J170" t="s">
         <v>40</v>
@@ -4759,7 +4779,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C171" s="9"/>
       <c r="J171" t="s">
@@ -4772,12 +4792,12 @@
         <v>38</v>
       </c>
       <c r="M171" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J172" t="s">
         <v>40</v>
@@ -4789,7 +4809,7 @@
         <v>38</v>
       </c>
       <c r="M172" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -4812,7 +4832,7 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J174" t="s">
         <v>40</v>
@@ -4826,7 +4846,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J175" t="s">
         <v>40</v>
@@ -4840,7 +4860,7 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="17" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J176" t="s">
         <v>40</v>
@@ -4854,7 +4874,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J177" t="s">
         <v>40</v>
@@ -4869,7 +4889,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J178" t="s">
         <v>40</v>
@@ -4881,12 +4901,12 @@
         <v>38</v>
       </c>
       <c r="M178" s="6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J179" t="s">
         <v>40</v>
@@ -4928,7 +4948,7 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J182" t="s">
         <v>40</v>
@@ -4942,7 +4962,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J183" t="s">
         <v>40</v>
@@ -4954,7 +4974,7 @@
         <v>38</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -4972,7 +4992,7 @@
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
       <c r="L184" s="5" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M184" s="41">
         <v>0.81799999999999995</v>
@@ -5139,18 +5159,13 @@
       <c r="J195" t="s">
         <v>40</v>
       </c>
-      <c r="K195" s="6">
-        <v>37.5</v>
+      <c r="K195" s="17">
+        <v>36.909999999999997</v>
       </c>
       <c r="L195" t="s">
         <v>38</v>
       </c>
-      <c r="M195" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="N195" t="s">
-        <v>351</v>
-      </c>
+      <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
@@ -5159,28 +5174,23 @@
       <c r="J196" t="s">
         <v>40</v>
       </c>
-      <c r="K196" s="6">
-        <v>48.1</v>
+      <c r="K196" s="17">
+        <v>43.11</v>
       </c>
       <c r="L196" t="s">
         <v>38</v>
       </c>
-      <c r="M196" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="N196" t="s">
-        <v>351</v>
-      </c>
+      <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="J197" t="s">
         <v>40</v>
       </c>
       <c r="K197" s="17">
-        <v>64</v>
+        <v>63.94</v>
       </c>
       <c r="L197" s="17" t="s">
         <v>38</v>
@@ -5189,23 +5199,18 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J198" t="s">
         <v>40</v>
       </c>
-      <c r="K198" s="6">
-        <v>46.1</v>
+      <c r="K198" s="17">
+        <v>36.49</v>
       </c>
       <c r="L198" t="s">
         <v>38</v>
       </c>
-      <c r="M198" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="N198" t="s">
-        <v>351</v>
-      </c>
+      <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
@@ -5240,10 +5245,10 @@
         <v>38</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="N200" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -5266,7 +5271,7 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J202" t="s">
         <v>40</v>
@@ -5280,7 +5285,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="26" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J203" t="s">
         <v>40</v>
@@ -5294,7 +5299,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="J204" t="s">
         <v>40</v>
@@ -5306,12 +5311,12 @@
         <v>38</v>
       </c>
       <c r="M204" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="26" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="J205" t="s">
         <v>40</v>
@@ -5325,7 +5330,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="26" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -5367,7 +5372,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J208" t="s">
         <v>40</v>
@@ -5400,7 +5405,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="J210" t="s">
         <v>40</v>
@@ -5412,12 +5417,12 @@
         <v>38</v>
       </c>
       <c r="M210" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="J211" t="s">
         <v>40</v>
@@ -5430,12 +5435,12 @@
         <v>38</v>
       </c>
       <c r="M211" s="27" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J212" t="s">
         <v>40</v>
@@ -5467,7 +5472,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J214" t="s">
         <v>40</v>
@@ -5481,7 +5486,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J215" t="s">
         <v>40</v>
@@ -5498,7 +5503,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J216" t="s">
         <v>40</v>
@@ -5510,12 +5515,12 @@
         <v>38</v>
       </c>
       <c r="M216" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J217" t="s">
         <v>40</v>
@@ -5527,12 +5532,12 @@
         <v>38</v>
       </c>
       <c r="M217" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -5564,7 +5569,7 @@
         <v>46</v>
       </c>
       <c r="M220" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
@@ -5606,7 +5611,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G223" t="s">
         <v>87</v>
@@ -5624,7 +5629,7 @@
         <v>38</v>
       </c>
       <c r="M223" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N223" t="s">
         <v>98</v>
@@ -5632,7 +5637,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G224" t="s">
         <v>87</v>
@@ -5653,7 +5658,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G225" t="s">
         <v>87</v>
@@ -5671,7 +5676,7 @@
         <v>38</v>
       </c>
       <c r="M225" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N225" t="s">
         <v>98</v>
@@ -5679,7 +5684,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G226" t="s">
         <v>87</v>
@@ -5700,7 +5705,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G227" t="s">
         <v>87</v>
@@ -5718,7 +5723,7 @@
         <v>38</v>
       </c>
       <c r="M227" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N227" t="s">
         <v>98</v>
@@ -5726,7 +5731,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G228" t="s">
         <v>87</v>
@@ -5747,7 +5752,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G229" t="s">
         <v>87</v>
@@ -5765,15 +5770,15 @@
         <v>38</v>
       </c>
       <c r="M229" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="N229" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G230" t="s">
         <v>87</v>
@@ -5795,7 +5800,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G231" t="s">
         <v>87</v>
@@ -5815,7 +5820,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G232" t="s">
         <v>87</v>
@@ -5872,7 +5877,7 @@
         <v>38</v>
       </c>
       <c r="N234" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
@@ -5895,12 +5900,12 @@
         <v>38</v>
       </c>
       <c r="N235" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="17" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G236" t="s">
         <v>87</v>
@@ -5958,7 +5963,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G239" t="s">
         <v>87</v>
@@ -5976,15 +5981,15 @@
         <v>38</v>
       </c>
       <c r="M239" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="N239" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G240" t="s">
         <v>87</v>
@@ -6002,15 +6007,15 @@
         <v>38</v>
       </c>
       <c r="M240" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="N240" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G241" t="s">
         <v>87</v>
@@ -6028,10 +6033,10 @@
         <v>38</v>
       </c>
       <c r="M241" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="N241" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
@@ -6054,10 +6059,10 @@
         <v>38</v>
       </c>
       <c r="M242" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="N242" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
@@ -6080,15 +6085,15 @@
         <v>38</v>
       </c>
       <c r="M243" s="26" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="N243" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G244" t="s">
         <v>87</v>
@@ -6129,7 +6134,7 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H246" t="s">
         <v>43</v>
@@ -6144,15 +6149,15 @@
         <v>38</v>
       </c>
       <c r="M246" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N246" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H247" t="s">
         <v>43</v>
@@ -6167,15 +6172,15 @@
         <v>38</v>
       </c>
       <c r="M247" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N247" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="17" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H248" t="s">
         <v>43</v>
@@ -6190,15 +6195,15 @@
         <v>38</v>
       </c>
       <c r="M248" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N248" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H249" t="s">
         <v>43</v>
@@ -6213,10 +6218,10 @@
         <v>38</v>
       </c>
       <c r="M249" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N249" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
@@ -6258,7 +6263,7 @@
         <v>38</v>
       </c>
       <c r="M251" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N251" t="s">
         <v>94</v>
@@ -6302,7 +6307,7 @@
         <v>38</v>
       </c>
       <c r="M253" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
@@ -6325,12 +6330,12 @@
         <v>38</v>
       </c>
       <c r="M254" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="G255" t="s">
         <v>87</v>
@@ -6348,12 +6353,12 @@
         <v>38</v>
       </c>
       <c r="M255" s="6" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G256" t="s">
         <v>87</v>
@@ -6371,7 +6376,7 @@
         <v>38</v>
       </c>
       <c r="M256" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
@@ -6412,10 +6417,10 @@
         <v>38</v>
       </c>
       <c r="M258" s="6" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="N258" s="26" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
@@ -6438,7 +6443,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H260" t="s">
         <v>43</v>
@@ -6453,10 +6458,10 @@
         <v>38</v>
       </c>
       <c r="M260" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N260" s="26" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
@@ -6479,7 +6484,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G262" t="s">
         <v>87</v>
@@ -6517,7 +6522,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H264" t="s">
         <v>43</v>
@@ -6532,15 +6537,15 @@
         <v>38</v>
       </c>
       <c r="M264" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N264" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H265" t="s">
         <v>43</v>
@@ -6555,15 +6560,15 @@
         <v>38</v>
       </c>
       <c r="M265" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N265" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H266" t="s">
         <v>43</v>
@@ -6578,15 +6583,15 @@
         <v>38</v>
       </c>
       <c r="M266" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N266" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H267" t="s">
         <v>43</v>
@@ -6601,10 +6606,10 @@
         <v>38</v>
       </c>
       <c r="M267" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N267" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
@@ -6673,7 +6678,7 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C274" t="s">
         <v>37</v>
@@ -6693,22 +6698,26 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C275" t="s">
         <v>37</v>
       </c>
       <c r="F275" t="s">
-        <v>116</v>
+        <v>358</v>
       </c>
       <c r="J275" t="s">
         <v>86</v>
       </c>
       <c r="K275">
-        <v>19</v>
+        <f>19+2</f>
+        <v>21</v>
       </c>
       <c r="L275" t="s">
         <v>38</v>
+      </c>
+      <c r="M275" t="s">
+        <v>360</v>
       </c>
       <c r="N275" t="s">
         <v>92</v>
@@ -6716,50 +6725,53 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C276" t="s">
         <v>37</v>
       </c>
-      <c r="F276" t="s">
-        <v>117</v>
-      </c>
       <c r="J276" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K276">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="L276" t="s">
         <v>38</v>
       </c>
-      <c r="N276" t="s">
-        <v>92</v>
+      <c r="N276" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C277" t="s">
         <v>37</v>
       </c>
+      <c r="F277" t="s">
+        <v>358</v>
+      </c>
       <c r="J277" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K277">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L277" t="s">
         <v>38</v>
       </c>
-      <c r="N277" t="s">
-        <v>92</v>
+      <c r="M277" t="s">
+        <v>359</v>
+      </c>
+      <c r="N277" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8" t="s">
@@ -6787,7 +6799,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8" t="s">
@@ -6795,8 +6807,8 @@
       </c>
       <c r="D279" s="8"/>
       <c r="E279" s="8"/>
-      <c r="F279" s="8" t="s">
-        <v>118</v>
+      <c r="F279" t="s">
+        <v>358</v>
       </c>
       <c r="G279" s="8"/>
       <c r="H279" s="8"/>
@@ -6810,14 +6822,16 @@
       <c r="L279" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M279" s="8"/>
+      <c r="M279" s="8" t="s">
+        <v>361</v>
+      </c>
       <c r="N279" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8" t="s">
@@ -6825,17 +6839,15 @@
       </c>
       <c r="D280" s="8"/>
       <c r="E280" s="8"/>
-      <c r="F280" s="8" t="s">
-        <v>119</v>
-      </c>
+      <c r="F280" s="8"/>
       <c r="G280" s="8"/>
       <c r="H280" s="8"/>
       <c r="I280" s="8"/>
       <c r="J280" t="s">
-        <v>86</v>
-      </c>
-      <c r="K280" s="8">
-        <v>9</v>
+        <v>85</v>
+      </c>
+      <c r="K280" s="9">
+        <v>91</v>
       </c>
       <c r="L280" s="8" t="s">
         <v>38</v>
@@ -6847,7 +6859,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8" t="s">
@@ -6855,45 +6867,47 @@
       </c>
       <c r="D281" s="8"/>
       <c r="E281" s="8"/>
-      <c r="F281" s="8"/>
+      <c r="F281" t="s">
+        <v>358</v>
+      </c>
       <c r="G281" s="8"/>
       <c r="H281" s="8"/>
       <c r="I281" s="8"/>
       <c r="J281" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K281" s="9">
-        <v>91</v>
-      </c>
-      <c r="L281" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M281" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="L281" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M281" s="8" t="s">
+        <v>362</v>
+      </c>
       <c r="N281" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="8" t="s">
-        <v>191</v>
+      <c r="A282" t="s">
+        <v>181</v>
       </c>
       <c r="B282" s="8"/>
-      <c r="C282" s="8" t="s">
-        <v>48</v>
+      <c r="C282" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="D282" s="8"/>
       <c r="E282" s="8"/>
-      <c r="F282" s="8" t="s">
-        <v>119</v>
-      </c>
+      <c r="F282" s="8"/>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
       <c r="I282" s="8"/>
       <c r="J282" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K282" s="9">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="L282" s="9" t="s">
         <v>38</v>
@@ -6905,7 +6919,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="9" t="s">
@@ -6913,27 +6927,31 @@
       </c>
       <c r="D283" s="8"/>
       <c r="E283" s="8"/>
-      <c r="F283" s="8"/>
+      <c r="F283" t="s">
+        <v>358</v>
+      </c>
       <c r="G283" s="8"/>
       <c r="H283" s="8"/>
       <c r="I283" s="8"/>
       <c r="J283" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K283" s="9">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="L283" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M283" s="8"/>
+      <c r="M283" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="N283" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="9" t="s">
@@ -6941,17 +6959,15 @@
       </c>
       <c r="D284" s="8"/>
       <c r="E284" s="8"/>
-      <c r="F284" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="F284" s="9"/>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
       <c r="I284" s="8"/>
       <c r="J284" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K284" s="9">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L284" s="9" t="s">
         <v>38</v>
@@ -6963,15 +6979,15 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D285" s="8"/>
       <c r="E285" s="8"/>
-      <c r="F285" s="9"/>
+      <c r="F285" s="8"/>
       <c r="G285" s="8"/>
       <c r="H285" s="8"/>
       <c r="I285" s="8"/>
@@ -6979,7 +6995,7 @@
         <v>85</v>
       </c>
       <c r="K285" s="9">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="L285" s="9" t="s">
         <v>38</v>
@@ -6991,7 +7007,7 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="9" t="s">
@@ -6999,27 +7015,32 @@
       </c>
       <c r="D286" s="8"/>
       <c r="E286" s="8"/>
-      <c r="F286" s="8"/>
+      <c r="F286" t="s">
+        <v>365</v>
+      </c>
       <c r="G286" s="8"/>
       <c r="H286" s="8"/>
       <c r="I286" s="8"/>
       <c r="J286" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K286" s="9">
-        <v>53</v>
+        <f>20+27</f>
+        <v>47</v>
       </c>
       <c r="L286" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M286" s="8"/>
+      <c r="M286" s="19" t="s">
+        <v>364</v>
+      </c>
       <c r="N286" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B287" s="8"/>
       <c r="C287" s="9" t="s">
@@ -7027,31 +7048,27 @@
       </c>
       <c r="D287" s="8"/>
       <c r="E287" s="8"/>
-      <c r="F287" s="9" t="s">
-        <v>344</v>
-      </c>
+      <c r="F287" s="9"/>
       <c r="G287" s="8"/>
       <c r="H287" s="8"/>
       <c r="I287" s="8"/>
       <c r="J287" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K287" s="9">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="L287" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M287" s="10" t="s">
-        <v>343</v>
-      </c>
+      <c r="M287" s="8"/>
       <c r="N287" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B288" s="8"/>
       <c r="C288" s="9" t="s">
@@ -7059,8 +7076,8 @@
       </c>
       <c r="D288" s="8"/>
       <c r="E288" s="8"/>
-      <c r="F288" s="9" t="s">
-        <v>184</v>
+      <c r="F288" t="s">
+        <v>365</v>
       </c>
       <c r="G288" s="8"/>
       <c r="H288" s="8"/>
@@ -7074,76 +7091,76 @@
       <c r="L288" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M288" s="8"/>
+      <c r="M288" s="8" t="s">
+        <v>366</v>
+      </c>
       <c r="N288" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>193</v>
-      </c>
-      <c r="B289" s="8"/>
+        <v>289</v>
+      </c>
+      <c r="B289" s="10"/>
       <c r="C289" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D289" s="8"/>
-      <c r="E289" s="8"/>
-      <c r="F289" s="9"/>
-      <c r="G289" s="8"/>
-      <c r="H289" s="8"/>
-      <c r="I289" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="D289" s="10"/>
+      <c r="E289" s="10"/>
+      <c r="F289" s="10"/>
+      <c r="G289" s="10"/>
+      <c r="H289" s="10"/>
+      <c r="I289" s="10"/>
       <c r="J289" t="s">
         <v>85</v>
       </c>
-      <c r="K289" s="9">
-        <v>73</v>
+      <c r="K289" s="20">
+        <v>100</v>
       </c>
       <c r="L289" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M289" s="8"/>
-      <c r="N289" t="s">
-        <v>92</v>
-      </c>
+      <c r="M289" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N289" s="8"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>193</v>
-      </c>
-      <c r="B290" s="8"/>
-      <c r="C290" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D290" s="8"/>
-      <c r="E290" s="8"/>
-      <c r="F290" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="G290" s="8"/>
-      <c r="H290" s="8"/>
-      <c r="I290" s="8"/>
+        <v>290</v>
+      </c>
+      <c r="B290" s="10"/>
+      <c r="C290" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D290" s="10"/>
+      <c r="E290" s="10"/>
+      <c r="F290" s="10"/>
+      <c r="G290" s="10"/>
+      <c r="H290" s="10"/>
+      <c r="I290" s="10"/>
       <c r="J290" t="s">
-        <v>86</v>
-      </c>
-      <c r="K290" s="9">
-        <v>27</v>
+        <v>85</v>
+      </c>
+      <c r="K290" s="20">
+        <v>100</v>
       </c>
       <c r="L290" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M290" s="8"/>
-      <c r="N290" t="s">
-        <v>92</v>
-      </c>
+      <c r="M290" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N290" s="8"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B291" s="10"/>
       <c r="C291" s="9" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="D291" s="10"/>
       <c r="E291" s="10"/>
@@ -7161,17 +7178,17 @@
         <v>38</v>
       </c>
       <c r="M291" s="8" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="N291" s="8"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B292" s="10"/>
-      <c r="C292" s="8" t="s">
-        <v>48</v>
+      <c r="C292" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="D292" s="10"/>
       <c r="E292" s="10"/>
@@ -7189,87 +7206,83 @@
         <v>38</v>
       </c>
       <c r="M292" s="8" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="N292" s="8"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>297</v>
-      </c>
-      <c r="B293" s="10"/>
-      <c r="C293" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D293" s="10"/>
-      <c r="E293" s="10"/>
-      <c r="F293" s="10"/>
-      <c r="G293" s="10"/>
-      <c r="H293" s="10"/>
-      <c r="I293" s="10"/>
-      <c r="J293" t="s">
-        <v>85</v>
-      </c>
-      <c r="K293" s="20">
-        <v>100</v>
-      </c>
-      <c r="L293" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M293" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="N293" s="8"/>
+      <c r="A293" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B293" s="4"/>
+      <c r="C293" s="4"/>
+      <c r="D293" s="4"/>
+      <c r="E293" s="4"/>
+      <c r="F293" s="4"/>
+      <c r="G293" s="4"/>
+      <c r="H293" s="4"/>
+      <c r="I293" s="4"/>
+      <c r="J293" s="5"/>
+      <c r="K293" s="5"/>
+      <c r="L293" s="5"/>
+      <c r="M293" s="5"/>
+      <c r="N293" s="5"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>298</v>
-      </c>
-      <c r="B294" s="10"/>
+      <c r="A294" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B294" s="8"/>
       <c r="C294" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D294" s="10"/>
-      <c r="E294" s="10"/>
-      <c r="F294" s="10"/>
-      <c r="G294" s="10"/>
-      <c r="H294" s="10"/>
-      <c r="I294" s="10"/>
+        <v>105</v>
+      </c>
+      <c r="D294" s="8"/>
+      <c r="E294" s="8"/>
+      <c r="F294" s="9"/>
+      <c r="G294" s="8"/>
+      <c r="H294" s="8"/>
+      <c r="I294" s="8"/>
       <c r="J294" t="s">
         <v>85</v>
       </c>
-      <c r="K294" s="20">
+      <c r="K294" s="11">
         <v>100</v>
       </c>
       <c r="L294" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M294" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="N294" s="8"/>
+      <c r="M294" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A295" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B295" s="4"/>
-      <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4"/>
-      <c r="G295" s="4"/>
-      <c r="H295" s="4"/>
-      <c r="I295" s="4"/>
-      <c r="J295" s="5"/>
-      <c r="K295" s="5"/>
-      <c r="L295" s="5"/>
-      <c r="M295" s="5"/>
-      <c r="N295" s="5"/>
+      <c r="A295" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B295" s="8"/>
+      <c r="C295" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D295" s="8"/>
+      <c r="E295" s="8"/>
+      <c r="F295" s="9"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="8"/>
+      <c r="J295" t="s">
+        <v>85</v>
+      </c>
+      <c r="K295" s="9">
+        <v>50</v>
+      </c>
+      <c r="L295" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M295" s="8"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B296" s="8"/>
       <c r="C296" s="9" t="s">
@@ -7277,30 +7290,30 @@
       </c>
       <c r="D296" s="8"/>
       <c r="E296" s="8"/>
-      <c r="F296" s="9"/>
+      <c r="F296" s="9" t="s">
+        <v>116</v>
+      </c>
       <c r="G296" s="8"/>
       <c r="H296" s="8"/>
       <c r="I296" s="8"/>
       <c r="J296" t="s">
-        <v>85</v>
-      </c>
-      <c r="K296" s="11">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K296" s="9">
+        <v>50</v>
       </c>
       <c r="L296" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M296" s="10" t="s">
-        <v>104</v>
-      </c>
+      <c r="M296" s="8"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="B297" s="8"/>
-      <c r="C297" s="9" t="s">
-        <v>105</v>
+      <c r="C297" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="D297" s="8"/>
       <c r="E297" s="8"/>
@@ -7311,150 +7324,132 @@
       <c r="J297" t="s">
         <v>85</v>
       </c>
-      <c r="K297" s="9">
-        <v>50</v>
+      <c r="K297" s="18">
+        <v>20</v>
       </c>
       <c r="L297" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M297" s="8"/>
+      <c r="M297" s="10" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B298" s="8"/>
       <c r="C298" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D298" s="8"/>
       <c r="E298" s="8"/>
-      <c r="F298" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="F298" s="9"/>
       <c r="G298" s="8"/>
       <c r="H298" s="8"/>
       <c r="I298" s="8"/>
       <c r="J298" t="s">
-        <v>86</v>
-      </c>
-      <c r="K298" s="9">
-        <v>50</v>
+        <v>85</v>
+      </c>
+      <c r="K298" s="18">
+        <v>19</v>
       </c>
       <c r="L298" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M298" s="8"/>
+      <c r="M298" s="19"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>215</v>
+        <v>101</v>
       </c>
       <c r="B299" s="8"/>
-      <c r="C299" s="11" t="s">
+      <c r="C299" s="9" t="s">
         <v>106</v>
       </c>
       <c r="D299" s="8"/>
       <c r="E299" s="8"/>
-      <c r="F299" s="9"/>
+      <c r="F299" t="s">
+        <v>191</v>
+      </c>
       <c r="G299" s="8"/>
       <c r="H299" s="8"/>
       <c r="I299" s="8"/>
       <c r="J299" t="s">
-        <v>85</v>
-      </c>
-      <c r="K299" s="18">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="K299" s="28">
+        <f>0.02*0.5*100/(844/1000)/0.9</f>
+        <v>1.3164823591363877</v>
       </c>
       <c r="L299" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M299" s="10" t="s">
-        <v>216</v>
+      <c r="M299" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="N299" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A300" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B300" s="8"/>
-      <c r="C300" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D300" s="8"/>
-      <c r="E300" s="8"/>
-      <c r="F300" s="9"/>
-      <c r="G300" s="8"/>
-      <c r="H300" s="8"/>
-      <c r="I300" s="8"/>
-      <c r="J300" t="s">
-        <v>85</v>
-      </c>
-      <c r="K300" s="18">
-        <v>19</v>
-      </c>
-      <c r="L300" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M300" s="19"/>
+      <c r="A300" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B300" s="4"/>
+      <c r="C300" s="4"/>
+      <c r="D300" s="4"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4"/>
+      <c r="G300" s="4"/>
+      <c r="H300" s="4"/>
+      <c r="I300" s="4"/>
+      <c r="J300" s="5"/>
+      <c r="K300" s="5"/>
+      <c r="L300" s="5"/>
+      <c r="M300" s="5"/>
+      <c r="N300" s="5"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B301" s="8"/>
+        <v>135</v>
+      </c>
       <c r="C301" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D301" s="8"/>
-      <c r="E301" s="8"/>
-      <c r="F301" t="s">
-        <v>197</v>
-      </c>
-      <c r="G301" s="8"/>
-      <c r="H301" s="8"/>
-      <c r="I301" s="8"/>
+        <v>136</v>
+      </c>
       <c r="J301" t="s">
-        <v>86</v>
-      </c>
-      <c r="K301" s="28">
-        <f>0.02*0.5*100/(844/1000)/0.9</f>
-        <v>1.3164823591363877</v>
-      </c>
-      <c r="L301" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M301" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="N301" s="9" t="s">
-        <v>199</v>
+        <v>85</v>
+      </c>
+      <c r="K301" s="18">
+        <v>100</v>
+      </c>
+      <c r="L301" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A302" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B302" s="4"/>
-      <c r="C302" s="4"/>
-      <c r="D302" s="4"/>
-      <c r="E302" s="4"/>
-      <c r="F302" s="4"/>
-      <c r="G302" s="4"/>
-      <c r="H302" s="4"/>
-      <c r="I302" s="4"/>
-      <c r="J302" s="5"/>
-      <c r="K302" s="5"/>
-      <c r="L302" s="5"/>
-      <c r="M302" s="5"/>
-      <c r="N302" s="5"/>
+      <c r="A302" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J302" t="s">
+        <v>85</v>
+      </c>
+      <c r="K302" s="18">
+        <v>100</v>
+      </c>
+      <c r="L302" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J303" t="s">
         <v>85</v>
@@ -7468,10 +7463,10 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" s="17" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="J304" t="s">
         <v>85</v>
@@ -7485,10 +7480,10 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J305" t="s">
         <v>85</v>
@@ -7502,10 +7497,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="J306" t="s">
         <v>85</v>
@@ -7519,11 +7514,18 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="17" t="s">
-        <v>144</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B307" s="8"/>
       <c r="C307" s="9" t="s">
-        <v>150</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D307" s="8"/>
+      <c r="E307" s="8"/>
+      <c r="F307" s="9"/>
+      <c r="G307" s="8"/>
+      <c r="H307" s="8"/>
+      <c r="I307" s="8"/>
       <c r="J307" t="s">
         <v>85</v>
       </c>
@@ -7533,14 +7535,22 @@
       <c r="L307" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M307" s="10"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="17" t="s">
-        <v>145</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B308" s="8"/>
       <c r="C308" s="9" t="s">
-        <v>147</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D308" s="8"/>
+      <c r="E308" s="8"/>
+      <c r="F308" s="9"/>
+      <c r="G308" s="8"/>
+      <c r="H308" s="8"/>
+      <c r="I308" s="8"/>
       <c r="J308" t="s">
         <v>85</v>
       </c>
@@ -7550,14 +7560,15 @@
       <c r="L308" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M308" s="10"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="17" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B309" s="8"/>
       <c r="C309" s="9" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D309" s="8"/>
       <c r="E309" s="8"/>
@@ -7577,102 +7588,95 @@
       <c r="M309" s="10"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A310" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B310" s="8"/>
-      <c r="C310" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D310" s="8"/>
-      <c r="E310" s="8"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="8"/>
-      <c r="H310" s="8"/>
-      <c r="I310" s="8"/>
-      <c r="J310" t="s">
-        <v>85</v>
-      </c>
-      <c r="K310" s="18">
-        <v>100</v>
-      </c>
-      <c r="L310" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M310" s="10"/>
+      <c r="A310" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B310" s="4"/>
+      <c r="C310" s="4"/>
+      <c r="D310" s="4"/>
+      <c r="E310" s="4"/>
+      <c r="F310" s="4"/>
+      <c r="G310" s="4"/>
+      <c r="H310" s="4"/>
+      <c r="I310" s="4"/>
+      <c r="J310" s="5"/>
+      <c r="K310" s="5"/>
+      <c r="L310" s="5"/>
+      <c r="M310" s="5"/>
+      <c r="N310" s="5"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B311" s="8"/>
+        <v>241</v>
+      </c>
       <c r="C311" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D311" s="8"/>
-      <c r="E311" s="8"/>
-      <c r="F311" s="9"/>
-      <c r="G311" s="8"/>
-      <c r="H311" s="8"/>
-      <c r="I311" s="8"/>
+        <v>238</v>
+      </c>
       <c r="J311" t="s">
         <v>85</v>
       </c>
-      <c r="K311" s="18">
+      <c r="K311" s="17">
         <v>100</v>
       </c>
       <c r="L311" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M311" s="10"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A312" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B312" s="4"/>
-      <c r="C312" s="4"/>
-      <c r="D312" s="4"/>
-      <c r="E312" s="4"/>
-      <c r="F312" s="4"/>
-      <c r="G312" s="4"/>
-      <c r="H312" s="4"/>
-      <c r="I312" s="4"/>
-      <c r="J312" s="5"/>
-      <c r="K312" s="5"/>
-      <c r="L312" s="5"/>
-      <c r="M312" s="5"/>
-      <c r="N312" s="5"/>
+      <c r="A312" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J312" t="s">
+        <v>85</v>
+      </c>
+      <c r="K312" s="17">
+        <v>65</v>
+      </c>
+      <c r="L312" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N312" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="17" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>244</v>
+        <v>238</v>
+      </c>
+      <c r="F313" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="J313" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K313" s="17">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L313" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="N313" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" s="17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J314" t="s">
         <v>85</v>
       </c>
       <c r="K314" s="17">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="L314" s="17" t="s">
         <v>38</v>
@@ -7683,13 +7687,13 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C315" s="9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F315" s="19" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J315" t="s">
         <v>86</v>
@@ -7706,53 +7710,44 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" s="17" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J316" t="s">
         <v>85</v>
       </c>
       <c r="K316" s="17">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="L316" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N316" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" s="17" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="F317" s="19" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J317" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K317" s="17">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L317" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N317" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="17" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="J318" t="s">
         <v>85</v>
@@ -7766,10 +7761,10 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J319" t="s">
         <v>85</v>
@@ -7783,10 +7778,10 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="17" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J320" t="s">
         <v>85</v>
@@ -7799,60 +7794,91 @@
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A321" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="C321" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="J321" t="s">
-        <v>85</v>
-      </c>
-      <c r="K321" s="17">
-        <v>100</v>
-      </c>
-      <c r="L321" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A321" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B321" s="4"/>
+      <c r="C321" s="4"/>
+      <c r="D321" s="4"/>
+      <c r="E321" s="4"/>
+      <c r="F321" s="4"/>
+      <c r="G321" s="4"/>
+      <c r="H321" s="4"/>
+      <c r="I321" s="4"/>
+      <c r="J321" s="5"/>
+      <c r="K321" s="5"/>
+      <c r="L321" s="5"/>
+      <c r="M321" s="5"/>
+      <c r="N321" s="5"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="C322" s="9" t="s">
-        <v>269</v>
-      </c>
+      <c r="A322" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B322" s="10"/>
+      <c r="C322" s="10"/>
+      <c r="D322" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E322" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F322" s="10"/>
+      <c r="G322" s="10"/>
+      <c r="H322" s="10"/>
+      <c r="I322" s="10"/>
       <c r="J322" t="s">
         <v>85</v>
       </c>
-      <c r="K322" s="17">
-        <v>100</v>
-      </c>
-      <c r="L322" s="17" t="s">
-        <v>38</v>
+      <c r="K322" s="12">
+        <f>100-K323</f>
+        <v>90.75</v>
+      </c>
+      <c r="L322" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M322" t="s">
+        <v>71</v>
+      </c>
+      <c r="N322" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B323" s="4"/>
-      <c r="C323" s="4"/>
-      <c r="D323" s="4"/>
-      <c r="E323" s="4"/>
-      <c r="F323" s="4"/>
-      <c r="G323" s="4"/>
-      <c r="H323" s="4"/>
-      <c r="I323" s="4"/>
-      <c r="J323" s="5"/>
-      <c r="K323" s="5"/>
-      <c r="L323" s="5"/>
-      <c r="M323" s="5"/>
-      <c r="N323" s="5"/>
+      <c r="A323" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B323" s="10"/>
+      <c r="C323" s="10"/>
+      <c r="D323" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E323" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F323" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G323" s="10"/>
+      <c r="H323" s="10"/>
+      <c r="I323" s="10"/>
+      <c r="J323" t="s">
+        <v>86</v>
+      </c>
+      <c r="K323" s="12">
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
+      </c>
+      <c r="L323" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N323" s="8" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B324" s="10"/>
       <c r="C324" s="10"/>
@@ -7871,13 +7897,13 @@
       </c>
       <c r="K324" s="12">
         <f>100-K325</f>
-        <v>90.75</v>
+        <v>93.25</v>
       </c>
       <c r="L324" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M324" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N324" s="8" t="s">
         <v>93</v>
@@ -7885,7 +7911,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B325" s="10"/>
       <c r="C325" s="10"/>
@@ -7905,8 +7931,8 @@
         <v>86</v>
       </c>
       <c r="K325" s="12">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L325" s="10" t="s">
         <v>38</v>
@@ -7917,7 +7943,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B326" s="10"/>
       <c r="C326" s="10"/>
@@ -7936,13 +7962,13 @@
       </c>
       <c r="K326" s="12">
         <f>100-K327</f>
-        <v>93.25</v>
+        <v>97</v>
       </c>
       <c r="L326" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M326" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N326" s="8" t="s">
         <v>93</v>
@@ -7950,7 +7976,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B327" s="10"/>
       <c r="C327" s="10"/>
@@ -7970,8 +7996,8 @@
         <v>86</v>
       </c>
       <c r="K327" s="12">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="L327" s="10" t="s">
         <v>38</v>
@@ -7982,7 +8008,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B328" s="10"/>
       <c r="C328" s="10"/>
@@ -8000,14 +8026,14 @@
         <v>85</v>
       </c>
       <c r="K328" s="12">
-        <f>100-K329</f>
-        <v>97</v>
+        <f>(100-K329)*0.1</f>
+        <v>9.7000000000000011</v>
       </c>
       <c r="L328" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M328" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="N328" s="8" t="s">
         <v>93</v>
@@ -8015,7 +8041,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B329" s="10"/>
       <c r="C329" s="10"/>
@@ -8057,22 +8083,21 @@
       <c r="E330" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F330" s="10"/>
+      <c r="F330" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="G330" s="10"/>
       <c r="H330" s="10"/>
       <c r="I330" s="10"/>
       <c r="J330" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K330" s="12">
-        <f>(100-K331)*0.1</f>
-        <v>9.7000000000000011</v>
+        <f>(100-K329)*0.9</f>
+        <v>87.3</v>
       </c>
       <c r="L330" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M330" t="s">
-        <v>80</v>
       </c>
       <c r="N330" s="8" t="s">
         <v>93</v>
@@ -8080,7 +8105,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B331" s="10"/>
       <c r="C331" s="10"/>
@@ -8088,31 +8113,32 @@
         <v>79</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F331" s="10" t="s">
         <v>60</v>
       </c>
+      <c r="F331" s="10"/>
       <c r="G331" s="10"/>
       <c r="H331" s="10"/>
       <c r="I331" s="10"/>
       <c r="J331" t="s">
-        <v>86</v>
-      </c>
-      <c r="K331" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
+        <v>85</v>
+      </c>
+      <c r="K331" s="10">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
       </c>
       <c r="L331" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M331" t="s">
+        <v>78</v>
       </c>
       <c r="N331" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A332" s="10" t="s">
-        <v>64</v>
+      <c r="A332" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="B332" s="10"/>
       <c r="C332" s="10"/>
@@ -8120,23 +8146,24 @@
         <v>79</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F332" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F332" s="10"/>
       <c r="G332" s="10"/>
       <c r="H332" s="10"/>
       <c r="I332" s="10"/>
       <c r="J332" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K332" s="12">
-        <f>(100-K331)*0.9</f>
-        <v>87.3</v>
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
       </c>
       <c r="L332" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M332" t="s">
+        <v>74</v>
       </c>
       <c r="N332" s="8" t="s">
         <v>93</v>
@@ -8144,7 +8171,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B333" s="10"/>
       <c r="C333" s="10"/>
@@ -8161,23 +8188,23 @@
       <c r="J333" t="s">
         <v>85</v>
       </c>
-      <c r="K333" s="10">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+      <c r="K333" s="12">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
       </c>
       <c r="L333" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M333" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N333" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="11" t="s">
-        <v>69</v>
+      <c r="A334" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="B334" s="10"/>
       <c r="C334" s="10"/>
@@ -8194,15 +8221,15 @@
       <c r="J334" t="s">
         <v>85</v>
       </c>
-      <c r="K334" s="12">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+      <c r="K334" s="10">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
       </c>
       <c r="L334" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M334" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N334" s="8" t="s">
         <v>93</v>
@@ -8210,7 +8237,7 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B335" s="10"/>
       <c r="C335" s="10"/>
@@ -8228,14 +8255,14 @@
         <v>85</v>
       </c>
       <c r="K335" s="12">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
+        <v>49.367088607594937</v>
       </c>
       <c r="L335" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M335" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N335" s="8" t="s">
         <v>93</v>
@@ -8243,122 +8270,123 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B336" s="10"/>
-      <c r="C336" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="B336" s="8"/>
+      <c r="C336" s="8"/>
       <c r="D336" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E336" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F336" s="10"/>
-      <c r="G336" s="10"/>
-      <c r="H336" s="10"/>
-      <c r="I336" s="10"/>
+      <c r="F336" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G336" s="8"/>
+      <c r="H336" s="8"/>
+      <c r="I336" s="8"/>
       <c r="J336" t="s">
-        <v>85</v>
-      </c>
-      <c r="K336" s="10">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K336" s="14">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
       </c>
       <c r="L336" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="M336" t="s">
-        <v>76</v>
+      <c r="M336" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="N336" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A337" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B337" s="10"/>
-      <c r="C337" s="10"/>
-      <c r="D337" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E337" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F337" s="10"/>
-      <c r="G337" s="10"/>
-      <c r="H337" s="10"/>
-      <c r="I337" s="10"/>
-      <c r="J337" t="s">
-        <v>85</v>
-      </c>
-      <c r="K337" s="12">
-        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
-        <v>49.367088607594937</v>
-      </c>
-      <c r="L337" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M337" t="s">
-        <v>77</v>
-      </c>
-      <c r="N337" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="A337" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" s="4"/>
+      <c r="C337" s="4"/>
+      <c r="D337" s="4"/>
+      <c r="E337" s="4"/>
+      <c r="F337" s="4"/>
+      <c r="G337" s="4"/>
+      <c r="H337" s="4"/>
+      <c r="I337" s="4"/>
+      <c r="J337" s="5"/>
+      <c r="K337" s="5"/>
+      <c r="L337" s="5"/>
+      <c r="M337" s="5"/>
+      <c r="N337" s="5"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="10" t="s">
-        <v>65</v>
+      <c r="A338" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B338" s="8"/>
       <c r="C338" s="8"/>
-      <c r="D338" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E338" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F338" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="D338" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E338" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F338" s="8"/>
       <c r="G338" s="8"/>
       <c r="H338" s="8"/>
       <c r="I338" s="8"/>
       <c r="J338" t="s">
+        <v>85</v>
+      </c>
+      <c r="K338" s="11">
+        <v>73.5</v>
+      </c>
+      <c r="L338" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M338" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N338" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A339" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B339" s="8"/>
+      <c r="C339" s="8"/>
+      <c r="D339" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E339" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F339" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="8"/>
+      <c r="J339" t="s">
         <v>86</v>
       </c>
-      <c r="K338" s="14">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
-      </c>
-      <c r="L338" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M338" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N338" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A339" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B339" s="4"/>
-      <c r="C339" s="4"/>
-      <c r="D339" s="4"/>
-      <c r="E339" s="4"/>
-      <c r="F339" s="4"/>
-      <c r="G339" s="4"/>
-      <c r="H339" s="4"/>
-      <c r="I339" s="4"/>
-      <c r="J339" s="5"/>
-      <c r="K339" s="5"/>
-      <c r="L339" s="5"/>
-      <c r="M339" s="5"/>
-      <c r="N339" s="5"/>
+      <c r="K339" s="16">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="L339" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M339" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="N339" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
@@ -8372,20 +8400,25 @@
       <c r="E340" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F340" s="8"/>
+      <c r="F340" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
       <c r="I340" s="8"/>
       <c r="J340" t="s">
-        <v>85</v>
-      </c>
-      <c r="K340" s="9">
-        <v>73</v>
+        <v>86</v>
+      </c>
+      <c r="K340" s="16">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
       </c>
       <c r="L340" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M340" s="8"/>
+      <c r="M340" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="N340" s="8" t="s">
         <v>92</v>
       </c>
@@ -8403,7 +8436,7 @@
         <v>55</v>
       </c>
       <c r="F341" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G341" s="8"/>
       <c r="H341" s="8"/>
@@ -8412,8 +8445,8 @@
         <v>86</v>
       </c>
       <c r="K341" s="16">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
       </c>
       <c r="L341" s="8" t="s">
         <v>38</v>
@@ -8438,7 +8471,7 @@
         <v>55</v>
       </c>
       <c r="F342" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
@@ -8446,69 +8479,63 @@
       <c r="J342" t="s">
         <v>86</v>
       </c>
-      <c r="K342" s="16">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
+      <c r="K342" s="9">
+        <v>18</v>
       </c>
       <c r="L342" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M342" s="9" t="s">
-        <v>96</v>
-      </c>
+      <c r="M342" s="8"/>
       <c r="N342" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" s="8" t="s">
-        <v>54</v>
+      <c r="A343" t="s">
+        <v>95</v>
       </c>
       <c r="B343" s="8"/>
       <c r="C343" s="8"/>
-      <c r="D343" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E343" s="8" t="s">
+      <c r="D343" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E343" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F343" s="8" t="s">
-        <v>124</v>
-      </c>
+      <c r="F343" s="8"/>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
       <c r="I343" s="8"/>
       <c r="J343" t="s">
-        <v>86</v>
-      </c>
-      <c r="K343" s="16">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
-      </c>
-      <c r="L343" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K343" s="11">
+        <v>77.7</v>
+      </c>
+      <c r="L343" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M343" s="9" t="s">
-        <v>96</v>
+        <v>369</v>
       </c>
       <c r="N343" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A344" s="8" t="s">
-        <v>54</v>
+      <c r="A344" t="s">
+        <v>95</v>
       </c>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
-      <c r="D344" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E344" s="8" t="s">
+      <c r="D344" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E344" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F344" s="8" t="s">
-        <v>125</v>
+      <c r="F344" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="G344" s="8"/>
       <c r="H344" s="8"/>
@@ -8516,13 +8543,16 @@
       <c r="J344" t="s">
         <v>86</v>
       </c>
-      <c r="K344" s="9">
-        <v>18</v>
-      </c>
-      <c r="L344" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M344" s="8"/>
+      <c r="K344" s="16">
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
+      </c>
+      <c r="L344" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M344" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="N344" s="8" t="s">
         <v>92</v>
       </c>
@@ -8539,20 +8569,25 @@
       <c r="E345" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F345" s="8"/>
+      <c r="F345" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G345" s="8"/>
       <c r="H345" s="8"/>
       <c r="I345" s="8"/>
       <c r="J345" t="s">
-        <v>85</v>
-      </c>
-      <c r="K345" s="9">
-        <v>71</v>
+        <v>86</v>
+      </c>
+      <c r="K345" s="16">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
       </c>
       <c r="L345" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M345" s="8"/>
+      <c r="M345" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="N345" s="8" t="s">
         <v>92</v>
       </c>
@@ -8570,7 +8605,7 @@
         <v>55</v>
       </c>
       <c r="F346" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G346" s="8"/>
       <c r="H346" s="8"/>
@@ -8579,8 +8614,8 @@
         <v>86</v>
       </c>
       <c r="K346" s="16">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
       </c>
       <c r="L346" s="9" t="s">
         <v>38</v>
@@ -8605,7 +8640,7 @@
         <v>55</v>
       </c>
       <c r="F347" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G347" s="8"/>
       <c r="H347" s="8"/>
@@ -8613,139 +8648,141 @@
       <c r="J347" t="s">
         <v>86</v>
       </c>
-      <c r="K347" s="16">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
+      <c r="K347" s="9">
+        <v>12</v>
       </c>
       <c r="L347" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M347" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="M347" s="8"/>
       <c r="N347" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>95</v>
+        <v>346</v>
       </c>
       <c r="B348" s="8"/>
       <c r="C348" s="8"/>
       <c r="D348" s="9" t="s">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="E348" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F348" s="9" t="s">
-        <v>128</v>
-      </c>
+      <c r="F348" s="8"/>
       <c r="G348" s="8"/>
       <c r="H348" s="8"/>
       <c r="I348" s="8"/>
       <c r="J348" t="s">
-        <v>86</v>
-      </c>
-      <c r="K348" s="16">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
+        <v>85</v>
+      </c>
+      <c r="K348" s="11">
+        <v>69</v>
       </c>
       <c r="L348" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M348" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="N348" s="8" t="s">
-        <v>92</v>
+        <v>373</v>
+      </c>
+      <c r="N348" s="26" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>95</v>
+        <v>346</v>
       </c>
       <c r="B349" s="8"/>
       <c r="C349" s="8"/>
       <c r="D349" s="9" t="s">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="E349" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F349" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G349" s="8"/>
-      <c r="H349" s="8"/>
-      <c r="I349" s="8"/>
+      <c r="F349" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="G349" s="26"/>
+      <c r="H349" s="26"/>
+      <c r="I349" s="26"/>
       <c r="J349" t="s">
         <v>86</v>
       </c>
-      <c r="K349" s="9">
-        <v>12</v>
+      <c r="K349" s="16">
+        <f>(1/0.5)*8</f>
+        <v>16</v>
       </c>
       <c r="L349" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M349" s="8"/>
-      <c r="N349" s="8" t="s">
-        <v>92</v>
+      <c r="M349" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="N349" s="26" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B350" s="8"/>
       <c r="C350" s="8"/>
       <c r="D350" s="9" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="E350" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F350" s="8"/>
+      <c r="F350" s="26" t="s">
+        <v>352</v>
+      </c>
       <c r="G350" s="8"/>
       <c r="H350" s="8"/>
       <c r="I350" s="8"/>
       <c r="J350" t="s">
-        <v>85</v>
-      </c>
-      <c r="K350" s="9">
-        <v>66</v>
+        <v>86</v>
+      </c>
+      <c r="K350" s="16">
+        <f>(1/0.5)*3</f>
+        <v>6</v>
       </c>
       <c r="L350" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M350" s="8"/>
+      <c r="M350" s="9" t="s">
+        <v>354</v>
+      </c>
       <c r="N350" s="26" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B351" s="8"/>
       <c r="C351" s="8"/>
       <c r="D351" s="9" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="E351" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F351" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="G351" s="26"/>
-      <c r="H351" s="26"/>
-      <c r="I351" s="26"/>
+        <v>351</v>
+      </c>
+      <c r="G351" s="8"/>
+      <c r="H351" s="8"/>
+      <c r="I351" s="8"/>
       <c r="J351" t="s">
         <v>86</v>
       </c>
-      <c r="K351" s="16">
+      <c r="K351" s="9">
         <f>(1/0.5)*8</f>
         <v>16</v>
       </c>
@@ -8753,136 +8790,116 @@
         <v>38</v>
       </c>
       <c r="M351" s="9" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="N351" s="26" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>358</v>
+        <v>267</v>
       </c>
       <c r="B352" s="8"/>
       <c r="C352" s="8"/>
       <c r="D352" s="9" t="s">
-        <v>361</v>
+        <v>268</v>
       </c>
       <c r="E352" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F352" s="26" t="s">
-        <v>364</v>
-      </c>
+      <c r="F352" s="8"/>
       <c r="G352" s="8"/>
       <c r="H352" s="8"/>
       <c r="I352" s="8"/>
       <c r="J352" t="s">
-        <v>86</v>
-      </c>
-      <c r="K352" s="16">
-        <f>(1/0.5)*3</f>
-        <v>6</v>
+        <v>85</v>
+      </c>
+      <c r="K352" s="11">
+        <v>90</v>
       </c>
       <c r="L352" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M352" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N352" s="26" t="s">
-        <v>362</v>
+        <v>371</v>
+      </c>
+      <c r="N352" s="47" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>358</v>
-      </c>
-      <c r="B353" s="8"/>
-      <c r="C353" s="8"/>
-      <c r="D353" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="E353" s="9" t="s">
+      <c r="A353" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B353" s="10"/>
+      <c r="C353" s="10"/>
+      <c r="D353" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E353" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F353" s="26" t="s">
-        <v>363</v>
+      <c r="F353" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="G353" s="8"/>
       <c r="H353" s="8"/>
       <c r="I353" s="8"/>
-      <c r="J353" t="s">
-        <v>86</v>
-      </c>
-      <c r="K353" s="9">
-        <f>(1/0.5)*8</f>
-        <v>16</v>
-      </c>
-      <c r="L353" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M353" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N353" s="26" t="s">
-        <v>362</v>
-      </c>
+      <c r="K353" s="9"/>
+      <c r="L353" s="9"/>
+      <c r="M353" s="8"/>
+      <c r="N353" s="8"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>273</v>
-      </c>
-      <c r="B354" s="8"/>
-      <c r="C354" s="8"/>
-      <c r="D354" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="E354" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F354" s="8"/>
-      <c r="G354" s="8"/>
-      <c r="H354" s="8"/>
-      <c r="I354" s="8"/>
-      <c r="J354" t="s">
-        <v>85</v>
-      </c>
-      <c r="K354" s="9">
-        <v>77</v>
-      </c>
-      <c r="L354" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M354" s="8"/>
-      <c r="N354" s="8"/>
+      <c r="A354" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B354" s="4"/>
+      <c r="C354" s="4"/>
+      <c r="D354" s="4"/>
+      <c r="E354" s="4"/>
+      <c r="F354" s="4"/>
+      <c r="G354" s="4"/>
+      <c r="H354" s="4"/>
+      <c r="I354" s="4"/>
+      <c r="J354" s="5"/>
+      <c r="K354" s="5"/>
+      <c r="L354" s="5"/>
+      <c r="M354" s="5"/>
+      <c r="N354" s="5"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A355" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B355" s="10"/>
-      <c r="C355" s="10"/>
-      <c r="D355" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="E355" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F355" s="11" t="s">
-        <v>275</v>
-      </c>
+      <c r="A355" t="s">
+        <v>15</v>
+      </c>
+      <c r="B355" s="8"/>
+      <c r="C355" s="8"/>
+      <c r="D355" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E355" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F355" s="8"/>
       <c r="G355" s="8"/>
       <c r="H355" s="8"/>
       <c r="I355" s="8"/>
-      <c r="K355" s="9"/>
-      <c r="L355" s="9"/>
+      <c r="J355" t="s">
+        <v>85</v>
+      </c>
+      <c r="K355" s="9">
+        <v>100</v>
+      </c>
+      <c r="L355" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="M355" s="8"/>
       <c r="N355" s="8"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -8900,56 +8917,44 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>15</v>
-      </c>
-      <c r="B357" s="8"/>
-      <c r="C357" s="8"/>
-      <c r="D357" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="E357" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="F357" s="8"/>
-      <c r="G357" s="8"/>
-      <c r="H357" s="8"/>
-      <c r="I357" s="8"/>
+        <v>202</v>
+      </c>
+      <c r="C357" t="s">
+        <v>211</v>
+      </c>
       <c r="J357" t="s">
         <v>85</v>
       </c>
-      <c r="K357" s="9">
+      <c r="K357">
         <v>100</v>
       </c>
-      <c r="L357" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M357" s="8"/>
-      <c r="N357" s="8"/>
+      <c r="L357" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A358" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B358" s="4"/>
-      <c r="C358" s="4"/>
-      <c r="D358" s="4"/>
-      <c r="E358" s="4"/>
-      <c r="F358" s="4"/>
-      <c r="G358" s="4"/>
-      <c r="H358" s="4"/>
-      <c r="I358" s="4"/>
-      <c r="J358" s="5"/>
-      <c r="K358" s="5"/>
-      <c r="L358" s="5"/>
-      <c r="M358" s="5"/>
-      <c r="N358" s="5"/>
+      <c r="A358" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C358" t="s">
+        <v>212</v>
+      </c>
+      <c r="J358" t="s">
+        <v>85</v>
+      </c>
+      <c r="K358">
+        <v>100</v>
+      </c>
+      <c r="L358" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
-        <v>208</v>
+      <c r="A359" s="26" t="s">
+        <v>204</v>
       </c>
       <c r="C359" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J359" t="s">
         <v>85</v>
@@ -8962,472 +8967,496 @@
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A360" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C360" t="s">
-        <v>218</v>
-      </c>
-      <c r="J360" t="s">
+      <c r="A360" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B361" s="8"/>
+      <c r="C361" s="8"/>
+      <c r="D361" s="9"/>
+      <c r="E361" s="9"/>
+      <c r="F361" s="8"/>
+      <c r="G361" s="8"/>
+      <c r="H361" s="8"/>
+      <c r="I361" s="8"/>
+      <c r="M361" s="8"/>
+      <c r="N361" s="8"/>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B362" s="4"/>
+      <c r="C362" s="4"/>
+      <c r="D362" s="4"/>
+      <c r="E362" s="4"/>
+      <c r="F362" s="4"/>
+      <c r="G362" s="4"/>
+      <c r="H362" s="4"/>
+      <c r="I362" s="4"/>
+      <c r="J362" s="5"/>
+      <c r="K362" s="5"/>
+      <c r="L362" s="5"/>
+      <c r="M362" s="5"/>
+      <c r="N362" s="5"/>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>126</v>
+      </c>
+      <c r="C363" t="s">
+        <v>128</v>
+      </c>
+      <c r="H363" t="s">
+        <v>45</v>
+      </c>
+      <c r="J363" t="s">
         <v>85</v>
       </c>
-      <c r="K360">
-        <v>100</v>
-      </c>
-      <c r="L360" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A361" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="C361" t="s">
-        <v>219</v>
-      </c>
-      <c r="J361" t="s">
-        <v>85</v>
-      </c>
-      <c r="K361">
-        <v>100</v>
-      </c>
-      <c r="L361" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A363" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B363" s="8"/>
-      <c r="C363" s="8"/>
-      <c r="D363" s="9"/>
-      <c r="E363" s="9"/>
-      <c r="F363" s="8"/>
-      <c r="G363" s="8"/>
-      <c r="H363" s="8"/>
-      <c r="I363" s="8"/>
-      <c r="M363" s="8"/>
-      <c r="N363" s="8"/>
+      <c r="K363" s="21">
+        <v>38</v>
+      </c>
+      <c r="L363" t="s">
+        <v>38</v>
+      </c>
+      <c r="M363" s="11"/>
+      <c r="N363" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A364" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B364" s="4"/>
-      <c r="C364" s="4"/>
-      <c r="D364" s="4"/>
-      <c r="E364" s="4"/>
-      <c r="F364" s="4"/>
-      <c r="G364" s="4"/>
-      <c r="H364" s="4"/>
-      <c r="I364" s="4"/>
-      <c r="J364" s="5"/>
-      <c r="K364" s="5"/>
-      <c r="L364" s="5"/>
-      <c r="M364" s="5"/>
-      <c r="N364" s="5"/>
+      <c r="A364" t="s">
+        <v>126</v>
+      </c>
+      <c r="C364" t="s">
+        <v>128</v>
+      </c>
+      <c r="F364" t="s">
+        <v>129</v>
+      </c>
+      <c r="H364" t="s">
+        <v>45</v>
+      </c>
+      <c r="J364" t="s">
+        <v>86</v>
+      </c>
+      <c r="K364" s="21">
+        <v>60</v>
+      </c>
+      <c r="L364" t="s">
+        <v>38</v>
+      </c>
+      <c r="N364" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C365" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H365" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J365" t="s">
         <v>85</v>
       </c>
       <c r="K365" s="21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L365" t="s">
         <v>38</v>
       </c>
-      <c r="M365" s="11"/>
-      <c r="N365" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="M365" t="s">
+        <v>131</v>
+      </c>
+      <c r="N365" s="8"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C366" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F366" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H366" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J366" t="s">
         <v>86</v>
       </c>
       <c r="K366" s="21">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L366" t="s">
         <v>38</v>
       </c>
-      <c r="N366" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="N366" s="8"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>131</v>
-      </c>
-      <c r="C367" t="s">
-        <v>133</v>
-      </c>
-      <c r="H367" t="s">
-        <v>43</v>
-      </c>
-      <c r="J367" t="s">
-        <v>85</v>
-      </c>
-      <c r="K367" s="21">
-        <v>32</v>
-      </c>
-      <c r="L367" t="s">
-        <v>38</v>
-      </c>
-      <c r="M367" t="s">
-        <v>136</v>
-      </c>
-      <c r="N367" s="8"/>
+      <c r="A367" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B367" s="4"/>
+      <c r="C367" s="4"/>
+      <c r="D367" s="4"/>
+      <c r="E367" s="4"/>
+      <c r="F367" s="4"/>
+      <c r="G367" s="4"/>
+      <c r="H367" s="4"/>
+      <c r="I367" s="4"/>
+      <c r="J367" s="5"/>
+      <c r="K367" s="5"/>
+      <c r="L367" s="5"/>
+      <c r="M367" s="5"/>
+      <c r="N367" s="5"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="C368" t="s">
-        <v>133</v>
-      </c>
-      <c r="F368" t="s">
-        <v>135</v>
-      </c>
-      <c r="H368" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="J368" t="s">
+        <v>85</v>
+      </c>
+      <c r="K368" s="22">
+        <f>161/1000*100</f>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="L368" t="s">
+        <v>38</v>
+      </c>
+      <c r="M368" t="s">
+        <v>336</v>
+      </c>
+      <c r="N368" s="17" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>217</v>
+      </c>
+      <c r="C369" t="s">
+        <v>224</v>
+      </c>
+      <c r="F369" t="s">
+        <v>225</v>
+      </c>
+      <c r="J369" t="s">
         <v>86</v>
       </c>
-      <c r="K368" s="21">
-        <v>68</v>
-      </c>
-      <c r="L368" t="s">
-        <v>38</v>
-      </c>
-      <c r="N368" s="8"/>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A369" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B369" s="4"/>
-      <c r="C369" s="4"/>
-      <c r="D369" s="4"/>
-      <c r="E369" s="4"/>
-      <c r="F369" s="4"/>
-      <c r="G369" s="4"/>
-      <c r="H369" s="4"/>
-      <c r="I369" s="4"/>
-      <c r="J369" s="5"/>
-      <c r="K369" s="5"/>
-      <c r="L369" s="5"/>
-      <c r="M369" s="5"/>
-      <c r="N369" s="5"/>
+      <c r="K369" s="22">
+        <f>(6.4+25.2)/1000/0.9*100</f>
+        <v>3.5111111111111115</v>
+      </c>
+      <c r="L369" t="s">
+        <v>38</v>
+      </c>
+      <c r="M369" t="s">
+        <v>339</v>
+      </c>
+      <c r="N369" s="17" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C370" t="s">
-        <v>230</v>
+        <v>224</v>
+      </c>
+      <c r="F370" t="s">
+        <v>226</v>
       </c>
       <c r="J370" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K370" s="22">
-        <f>161/1000*100</f>
-        <v>16.100000000000001</v>
+        <f>19/1000/0.76*100</f>
+        <v>2.5</v>
       </c>
       <c r="L370" t="s">
         <v>38</v>
       </c>
       <c r="M370" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N370" s="17" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C371" t="s">
-        <v>230</v>
-      </c>
-      <c r="F371" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J371" t="s">
-        <v>86</v>
-      </c>
-      <c r="K371" s="22">
-        <f>(6.4+25.2)/1000/0.9*100</f>
-        <v>3.5111111111111115</v>
+        <v>85</v>
+      </c>
+      <c r="K371" s="43">
+        <f>K368/0.8</f>
+        <v>20.125</v>
       </c>
       <c r="L371" t="s">
         <v>38</v>
       </c>
-      <c r="M371" t="s">
-        <v>348</v>
-      </c>
-      <c r="N371" s="17" t="s">
-        <v>347</v>
+      <c r="M371" s="17" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C372" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F372" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J372" t="s">
         <v>86</v>
       </c>
-      <c r="K372" s="22">
-        <f>19/1000/0.76*100</f>
-        <v>2.5</v>
+      <c r="K372" s="43">
+        <f>K369</f>
+        <v>3.5111111111111115</v>
       </c>
       <c r="L372" t="s">
         <v>38</v>
-      </c>
-      <c r="M372" t="s">
-        <v>349</v>
-      </c>
-      <c r="N372" s="17" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C373" t="s">
+        <v>224</v>
+      </c>
+      <c r="F373" t="s">
+        <v>226</v>
+      </c>
+      <c r="J373" t="s">
+        <v>86</v>
+      </c>
+      <c r="K373" s="43">
+        <f>K370</f>
+        <v>2.5</v>
+      </c>
+      <c r="L373" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B375" s="4"/>
+      <c r="C375" s="4"/>
+      <c r="D375" s="4"/>
+      <c r="E375" s="4"/>
+      <c r="F375" s="4"/>
+      <c r="G375" s="4"/>
+      <c r="H375" s="4"/>
+      <c r="I375" s="4"/>
+      <c r="J375" s="5"/>
+      <c r="K375" s="5"/>
+      <c r="L375" s="5"/>
+      <c r="M375" s="5"/>
+      <c r="N375" s="5"/>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>227</v>
+      </c>
+      <c r="B376" s="10"/>
+      <c r="C376" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D376" s="10"/>
+      <c r="E376" s="10"/>
+      <c r="F376" s="10"/>
+      <c r="G376" s="10"/>
+      <c r="H376" s="10"/>
+      <c r="I376" s="10"/>
+      <c r="J376" t="s">
+        <v>85</v>
+      </c>
+      <c r="K376" s="20">
+        <v>70</v>
+      </c>
+      <c r="L376" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M376" s="8"/>
+      <c r="N376" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
         <v>230</v>
       </c>
-      <c r="J373" t="s">
+      <c r="B377" s="10"/>
+      <c r="C377" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D377" s="10"/>
+      <c r="E377" s="10"/>
+      <c r="F377" s="10"/>
+      <c r="G377" s="10"/>
+      <c r="H377" s="10"/>
+      <c r="I377" s="10"/>
+      <c r="J377" t="s">
         <v>85</v>
       </c>
-      <c r="K373" s="43">
-        <f>K370/0.8</f>
-        <v>20.125</v>
-      </c>
-      <c r="L373" t="s">
-        <v>38</v>
-      </c>
-      <c r="M373" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>225</v>
-      </c>
-      <c r="C374" t="s">
-        <v>230</v>
-      </c>
-      <c r="F374" t="s">
-        <v>231</v>
-      </c>
-      <c r="J374" t="s">
-        <v>86</v>
-      </c>
-      <c r="K374" s="43">
-        <f>K371</f>
-        <v>3.5111111111111115</v>
-      </c>
-      <c r="L374" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
-        <v>225</v>
-      </c>
-      <c r="C375" t="s">
-        <v>230</v>
-      </c>
-      <c r="F375" t="s">
-        <v>232</v>
-      </c>
-      <c r="J375" t="s">
-        <v>86</v>
-      </c>
-      <c r="K375" s="43">
-        <f>K372</f>
-        <v>2.5</v>
-      </c>
-      <c r="L375" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A377" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B377" s="4"/>
-      <c r="C377" s="4"/>
-      <c r="D377" s="4"/>
-      <c r="E377" s="4"/>
-      <c r="F377" s="4"/>
-      <c r="G377" s="4"/>
-      <c r="H377" s="4"/>
-      <c r="I377" s="4"/>
-      <c r="J377" s="5"/>
-      <c r="K377" s="5"/>
-      <c r="L377" s="5"/>
-      <c r="M377" s="5"/>
-      <c r="N377" s="5"/>
+      <c r="K377" s="20">
+        <f>655*0.7</f>
+        <v>458.49999999999994</v>
+      </c>
+      <c r="L377" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M377" s="8"/>
+      <c r="N377" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B378" s="10"/>
       <c r="C378" s="8" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="D378" s="10"/>
       <c r="E378" s="10"/>
-      <c r="F378" s="10"/>
+      <c r="F378" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="G378" s="10"/>
       <c r="H378" s="10"/>
       <c r="I378" s="10"/>
       <c r="J378" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K378" s="20">
-        <v>70</v>
+        <f>1*(K377/100)*0.2*100</f>
+        <v>91.699999999999989</v>
       </c>
       <c r="L378" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M378" s="8"/>
+      <c r="M378" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="N378" s="8" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
-        <v>236</v>
-      </c>
       <c r="B379" s="10"/>
-      <c r="C379" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="C379" s="8"/>
       <c r="D379" s="10"/>
       <c r="E379" s="10"/>
-      <c r="F379" s="10"/>
+      <c r="F379" s="10" t="s">
+        <v>176</v>
+      </c>
       <c r="G379" s="10"/>
       <c r="H379" s="10"/>
       <c r="I379" s="10"/>
-      <c r="J379" t="s">
-        <v>85</v>
-      </c>
-      <c r="K379" s="20">
-        <f>655*0.7</f>
-        <v>458.49999999999994</v>
-      </c>
-      <c r="L379" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M379" s="8"/>
-      <c r="N379" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="K379" s="20"/>
+      <c r="L379" s="9"/>
+      <c r="M379" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="N379" s="8"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B380" s="10"/>
-      <c r="C380" s="8" t="s">
-        <v>48</v>
+      <c r="C380" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="D380" s="10"/>
       <c r="E380" s="10"/>
-      <c r="F380" s="19" t="s">
-        <v>130</v>
-      </c>
+      <c r="F380" s="19"/>
       <c r="G380" s="10"/>
       <c r="H380" s="10"/>
       <c r="I380" s="10"/>
       <c r="J380" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K380" s="20">
-        <f>1*(K379/100)*0.2*100</f>
-        <v>91.699999999999989</v>
+        <v>65</v>
       </c>
       <c r="L380" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M380" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="M380" s="8"/>
       <c r="N380" s="8" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>228</v>
+      </c>
       <c r="B381" s="10"/>
-      <c r="C381" s="8"/>
+      <c r="C381" s="9" t="s">
+        <v>238</v>
+      </c>
       <c r="D381" s="10"/>
       <c r="E381" s="10"/>
-      <c r="F381" s="10" t="s">
-        <v>181</v>
+      <c r="F381" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="G381" s="10"/>
       <c r="H381" s="10"/>
       <c r="I381" s="10"/>
-      <c r="K381" s="20"/>
-      <c r="L381" s="9"/>
-      <c r="M381" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="N381" s="8"/>
+      <c r="J381" t="s">
+        <v>86</v>
+      </c>
+      <c r="K381" s="20">
+        <v>35</v>
+      </c>
+      <c r="L381" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M381" s="8"/>
+      <c r="N381" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B382" s="10"/>
       <c r="C382" s="9" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="D382" s="10"/>
       <c r="E382" s="10"/>
@@ -9439,7 +9468,7 @@
         <v>85</v>
       </c>
       <c r="K382" s="20">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="L382" s="9" t="s">
         <v>38</v>
@@ -9451,337 +9480,279 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B383" s="10"/>
       <c r="C383" s="9" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="D383" s="10"/>
       <c r="E383" s="10"/>
-      <c r="F383" s="19" t="s">
-        <v>245</v>
+      <c r="F383" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="G383" s="10"/>
       <c r="H383" s="10"/>
       <c r="I383" s="10"/>
-      <c r="J383" t="s">
+      <c r="J383" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K383" s="20">
-        <v>35</v>
-      </c>
-      <c r="L383" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M383" s="8"/>
-      <c r="N383" s="8" t="s">
+      <c r="K383" s="12">
+        <v>11</v>
+      </c>
+      <c r="L383" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M383" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="N383" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
-        <v>237</v>
-      </c>
-      <c r="B384" s="10"/>
-      <c r="C384" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D384" s="10"/>
-      <c r="E384" s="10"/>
-      <c r="F384" s="19"/>
-      <c r="G384" s="10"/>
-      <c r="H384" s="10"/>
-      <c r="I384" s="10"/>
-      <c r="J384" t="s">
-        <v>85</v>
-      </c>
-      <c r="K384" s="20">
-        <v>30</v>
-      </c>
-      <c r="L384" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M384" s="8"/>
-      <c r="N384" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="A384" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B384" s="4"/>
+      <c r="C384" s="4"/>
+      <c r="D384" s="4"/>
+      <c r="E384" s="4"/>
+      <c r="F384" s="4"/>
+      <c r="G384" s="4"/>
+      <c r="H384" s="4"/>
+      <c r="I384" s="4"/>
+      <c r="J384" s="5"/>
+      <c r="K384" s="5"/>
+      <c r="L384" s="5"/>
+      <c r="M384" s="5"/>
+      <c r="N384" s="5"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B385" s="10"/>
-      <c r="C385" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D385" s="10"/>
-      <c r="E385" s="10"/>
-      <c r="F385" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="G385" s="10"/>
-      <c r="H385" s="10"/>
-      <c r="I385" s="10"/>
-      <c r="J385" s="6" t="s">
+      <c r="C385" t="s">
+        <v>128</v>
+      </c>
+      <c r="J385" t="s">
+        <v>85</v>
+      </c>
+      <c r="K385" s="21">
+        <v>38</v>
+      </c>
+      <c r="L385" t="s">
+        <v>38</v>
+      </c>
+      <c r="M385" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="N385" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>195</v>
+      </c>
+      <c r="B386" s="10"/>
+      <c r="C386" t="s">
+        <v>128</v>
+      </c>
+      <c r="F386" t="s">
+        <v>129</v>
+      </c>
+      <c r="J386" t="s">
         <v>86</v>
       </c>
-      <c r="K385" s="12">
-        <v>11</v>
-      </c>
-      <c r="L385" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M385" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="N385" s="10" t="s">
+      <c r="K386" s="21">
+        <v>60</v>
+      </c>
+      <c r="L386" t="s">
+        <v>38</v>
+      </c>
+      <c r="N386" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A386" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B386" s="4"/>
-      <c r="C386" s="4"/>
-      <c r="D386" s="4"/>
-      <c r="E386" s="4"/>
-      <c r="F386" s="4"/>
-      <c r="G386" s="4"/>
-      <c r="H386" s="4"/>
-      <c r="I386" s="4"/>
-      <c r="J386" s="5"/>
-      <c r="K386" s="5"/>
-      <c r="L386" s="5"/>
-      <c r="M386" s="5"/>
-      <c r="N386" s="5"/>
-    </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>201</v>
+      <c r="A387" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="B387" s="10"/>
       <c r="C387" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="J387" t="s">
         <v>85</v>
       </c>
-      <c r="K387" s="21">
-        <v>38</v>
-      </c>
-      <c r="L387" t="s">
-        <v>38</v>
-      </c>
-      <c r="M387" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="N387" s="8" t="s">
-        <v>92</v>
+      <c r="K387" s="15">
+        <f>(1*0.766) / (2.1/0.86) * 100</f>
+        <v>31.369523809523809</v>
+      </c>
+      <c r="L387" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M387" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="N387" s="9" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>201</v>
+      <c r="A388" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="B388" s="10"/>
       <c r="C388" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="F388" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="J388" t="s">
         <v>86</v>
       </c>
-      <c r="K388" s="21">
-        <v>60</v>
-      </c>
-      <c r="L388" t="s">
-        <v>38</v>
-      </c>
-      <c r="N388" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A389" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B389" s="10"/>
-      <c r="C389" t="s">
-        <v>37</v>
-      </c>
-      <c r="J389" t="s">
-        <v>85</v>
-      </c>
-      <c r="K389" s="15">
-        <f>(1*0.766) / (2.1/0.86) * 100</f>
-        <v>31.369523809523809</v>
-      </c>
-      <c r="L389" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M389" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="N389" s="9" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A390" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B390" s="10"/>
-      <c r="C390" t="s">
-        <v>37</v>
-      </c>
-      <c r="F390" t="s">
-        <v>318</v>
-      </c>
-      <c r="J390" t="s">
-        <v>86</v>
-      </c>
-      <c r="K390" s="15">
+      <c r="K388" s="15">
         <f>(0.8/0.9) / (2.1/0.86) * 100</f>
         <v>36.402116402116405</v>
       </c>
-      <c r="L390" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M390" s="42" t="s">
-        <v>338</v>
-      </c>
-      <c r="N390" s="9" t="s">
-        <v>340</v>
-      </c>
+      <c r="L388" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M388" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="N388" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" s="6"/>
+      <c r="B389" s="10"/>
+      <c r="F389" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="K389" s="23"/>
+      <c r="L389" s="6"/>
+      <c r="M389" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="N389" s="9"/>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B390" s="4"/>
+      <c r="C390" s="4"/>
+      <c r="D390" s="4"/>
+      <c r="E390" s="4"/>
+      <c r="F390" s="4"/>
+      <c r="G390" s="4"/>
+      <c r="H390" s="4"/>
+      <c r="I390" s="4"/>
+      <c r="J390" s="5"/>
+      <c r="K390" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="L390" s="5"/>
+      <c r="M390" s="5"/>
+      <c r="N390" s="5"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A391" s="6"/>
+      <c r="A391" t="s">
+        <v>272</v>
+      </c>
       <c r="B391" s="10"/>
-      <c r="F391" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="K391" s="23"/>
-      <c r="L391" s="6"/>
-      <c r="M391" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="N391" s="9"/>
+      <c r="C391" s="10"/>
+      <c r="D391" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E391" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="F391" s="10"/>
+      <c r="G391" s="10"/>
+      <c r="H391" s="10"/>
+      <c r="I391" s="10"/>
+      <c r="J391" t="s">
+        <v>85</v>
+      </c>
+      <c r="K391" s="19">
+        <v>100</v>
+      </c>
+      <c r="L391" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M391" s="8"/>
+      <c r="N391" s="8"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B392" s="4"/>
-      <c r="C392" s="4"/>
-      <c r="D392" s="4"/>
-      <c r="E392" s="4"/>
-      <c r="F392" s="4"/>
-      <c r="G392" s="4"/>
-      <c r="H392" s="4"/>
-      <c r="I392" s="4"/>
-      <c r="J392" s="5"/>
-      <c r="K392" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="L392" s="5"/>
-      <c r="M392" s="5"/>
-      <c r="N392" s="5"/>
+      <c r="A392" t="s">
+        <v>347</v>
+      </c>
+      <c r="B392" s="10"/>
+      <c r="C392" s="10"/>
+      <c r="D392" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="E392" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="F392" s="10"/>
+      <c r="G392" s="10"/>
+      <c r="H392" s="10"/>
+      <c r="I392" s="10"/>
+      <c r="J392" t="s">
+        <v>85</v>
+      </c>
+      <c r="K392" s="19">
+        <v>100</v>
+      </c>
+      <c r="L392" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M392" s="8"/>
+      <c r="N392" s="8"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>278</v>
-      </c>
       <c r="B393" s="10"/>
       <c r="C393" s="10"/>
-      <c r="D393" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="E393" s="19" t="s">
-        <v>277</v>
-      </c>
+      <c r="D393" s="19"/>
+      <c r="E393" s="19"/>
       <c r="F393" s="10"/>
       <c r="G393" s="10"/>
       <c r="H393" s="10"/>
       <c r="I393" s="10"/>
-      <c r="J393" t="s">
-        <v>85</v>
-      </c>
-      <c r="K393" s="19">
-        <v>100</v>
-      </c>
-      <c r="L393" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="K393" s="19"/>
+      <c r="L393" s="8"/>
       <c r="M393" s="8"/>
       <c r="N393" s="8"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
-        <v>359</v>
-      </c>
-      <c r="B394" s="10"/>
-      <c r="C394" s="10"/>
-      <c r="D394" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="E394" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="F394" s="10"/>
-      <c r="G394" s="10"/>
-      <c r="H394" s="10"/>
-      <c r="I394" s="10"/>
-      <c r="J394" t="s">
-        <v>85</v>
-      </c>
-      <c r="K394" s="19">
-        <v>100</v>
-      </c>
-      <c r="L394" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M394" s="8"/>
-      <c r="N394" s="8"/>
+      <c r="A394" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B394" s="2"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
+      <c r="E394" s="2"/>
+      <c r="F394" s="2"/>
+      <c r="G394" s="2"/>
+      <c r="H394" s="2"/>
+      <c r="I394" s="2"/>
+      <c r="J394" s="2"/>
+      <c r="K394" s="2"/>
+      <c r="L394" s="2"/>
+      <c r="M394" s="2"/>
+      <c r="N394" s="2"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B395" s="10"/>
-      <c r="C395" s="10"/>
-      <c r="D395" s="19"/>
-      <c r="E395" s="19"/>
-      <c r="F395" s="10"/>
-      <c r="G395" s="10"/>
-      <c r="H395" s="10"/>
-      <c r="I395" s="10"/>
-      <c r="K395" s="19"/>
-      <c r="L395" s="8"/>
-      <c r="M395" s="8"/>
-      <c r="N395" s="8"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A396" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B396" s="2"/>
-      <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
-      <c r="E396" s="2"/>
-      <c r="F396" s="2"/>
-      <c r="G396" s="2"/>
-      <c r="H396" s="2"/>
-      <c r="I396" s="2"/>
-      <c r="J396" s="2"/>
-      <c r="K396" s="2"/>
-      <c r="L396" s="2"/>
-      <c r="M396" s="2"/>
-      <c r="N396" s="2"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A397" s="6" t="s">
-        <v>323</v>
+      <c r="A395" s="6" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -9798,72 +9769,72 @@
   <sheetData>
     <row r="8" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E8" s="25" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E15" s="25" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="25" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E23" s="25" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -9882,23 +9853,23 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -9906,18 +9877,18 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C5" s="25" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -9937,7 +9908,7 @@
         <v>2020</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I7">
         <v>2016</v>
@@ -9955,7 +9926,7 @@
         <v>2020</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="O7">
         <v>2016</v>
@@ -9973,15 +9944,15 @@
         <v>2020</v>
       </c>
       <c r="T7" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C8" s="34">
         <v>142352</v>
@@ -10048,10 +10019,10 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C9" s="33">
         <v>11521</v>
@@ -10118,10 +10089,10 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C10" s="33">
         <v>77862</v>
@@ -10188,10 +10159,10 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C11" s="33">
         <v>2564</v>
@@ -10258,10 +10229,10 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C12" s="33">
         <v>32168</v>
@@ -10328,18 +10299,18 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C14" s="25" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -10359,7 +10330,7 @@
         <v>2020</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I16">
         <v>2016</v>
@@ -10377,7 +10348,7 @@
         <v>2020</v>
       </c>
       <c r="N16" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="O16">
         <v>2016</v>
@@ -10395,15 +10366,15 @@
         <v>2020</v>
       </c>
       <c r="T16" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C17" s="33">
         <v>9962</v>
@@ -10484,12 +10455,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="382">
   <si>
     <t>parameter</t>
   </si>
@@ -1203,6 +1203,15 @@
   </si>
   <si>
     <t>DemandAndConversions-population.csv</t>
+  </si>
+  <si>
+    <t>fodder</t>
+  </si>
+  <si>
+    <t>Ley, biogas feedstock</t>
+  </si>
+  <si>
+    <t>tonnes DM</t>
   </si>
 </sst>
 </file>
@@ -1774,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R396"/>
+  <dimension ref="A1:R400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -3433,7 +3442,7 @@
         <v>197</v>
       </c>
       <c r="K91" s="33">
-        <f>600000*(K388/100)</f>
+        <f>600000*(K391/100)</f>
         <v>188217.14285714284</v>
       </c>
       <c r="L91" t="s">
@@ -3570,265 +3579,241 @@
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K100" s="33"/>
+      <c r="J100" s="44"/>
+      <c r="K100" s="37"/>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="36"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3"/>
+      <c r="J101" s="44"/>
+      <c r="K101" s="37"/>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>289</v>
+      <c r="A102" s="17" t="s">
+        <v>380</v>
       </c>
       <c r="B102" t="s">
-        <v>293</v>
+        <v>200</v>
       </c>
       <c r="H102" t="s">
         <v>45</v>
       </c>
       <c r="J102" t="s">
+        <v>197</v>
+      </c>
+      <c r="K102" s="15">
+        <v>1000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>381</v>
+      </c>
+      <c r="M102" s="6"/>
+      <c r="N102" s="9"/>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K103" s="33"/>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="36"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>289</v>
+      </c>
+      <c r="B105" t="s">
+        <v>293</v>
+      </c>
+      <c r="H105" t="s">
+        <v>45</v>
+      </c>
+      <c r="J105" t="s">
         <v>294</v>
       </c>
-      <c r="K102" s="33">
+      <c r="K105" s="33">
         <v>558249.80000000005</v>
       </c>
-      <c r="L102" t="s">
+      <c r="L105" t="s">
         <v>190</v>
       </c>
-      <c r="M102" t="s">
+      <c r="M105" t="s">
         <v>297</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N105" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>290</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B106" t="s">
         <v>293</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H106" t="s">
         <v>45</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J106" t="s">
         <v>294</v>
       </c>
-      <c r="K103" s="33">
+      <c r="K106" s="33">
         <f>304650.4+303000</f>
         <v>607650.4</v>
       </c>
-      <c r="L103" t="s">
+      <c r="L106" t="s">
         <v>190</v>
       </c>
-      <c r="M103" t="s">
+      <c r="M106" t="s">
         <v>297</v>
       </c>
-      <c r="N103" t="s">
+      <c r="N106" t="s">
         <v>295</v>
       </c>
-      <c r="R103" s="6" t="s">
+      <c r="R106" s="6" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>291</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B107" t="s">
         <v>293</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H107" t="s">
         <v>45</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J107" t="s">
         <v>294</v>
       </c>
-      <c r="K104" s="33">
+      <c r="K107" s="33">
         <v>32965.800000000003</v>
       </c>
-      <c r="L104" t="s">
+      <c r="L107" t="s">
         <v>190</v>
       </c>
-      <c r="M104" t="s">
+      <c r="M107" t="s">
         <v>309</v>
       </c>
-      <c r="N104" t="s">
+      <c r="N107" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>292</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B108" t="s">
         <v>293</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H108" t="s">
         <v>45</v>
       </c>
-      <c r="J105" t="s">
+      <c r="J108" t="s">
         <v>294</v>
       </c>
-      <c r="K105" s="33">
+      <c r="K108" s="33">
         <f>177249.6+246000</f>
         <v>423249.6</v>
       </c>
-      <c r="L105" t="s">
+      <c r="L108" t="s">
         <v>190</v>
       </c>
-      <c r="M105" t="s">
+      <c r="M108" t="s">
         <v>297</v>
       </c>
-      <c r="N105" t="s">
+      <c r="N108" t="s">
         <v>295</v>
       </c>
-      <c r="R105" s="6" t="s">
+      <c r="R108" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>202</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B109" t="s">
         <v>293</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H109" t="s">
         <v>45</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J109" t="s">
         <v>294</v>
       </c>
-      <c r="K106" s="33">
+      <c r="K109" s="33">
         <v>22062.799999999999</v>
       </c>
-      <c r="L106" t="s">
+      <c r="L109" t="s">
         <v>190</v>
       </c>
-      <c r="M106" t="s">
+      <c r="M109" t="s">
         <v>297</v>
       </c>
-      <c r="N106" t="s">
+      <c r="N109" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>101</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B110" t="s">
         <v>293</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H110" t="s">
         <v>45</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J110" t="s">
         <v>294</v>
       </c>
-      <c r="K107" s="33">
+      <c r="K110" s="33">
         <v>25000</v>
       </c>
-      <c r="L107" t="s">
+      <c r="L110" t="s">
         <v>190</v>
       </c>
-      <c r="M107" t="s">
+      <c r="M110" t="s">
         <v>299</v>
       </c>
-      <c r="N107" t="s">
+      <c r="N110" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>26</v>
-      </c>
-      <c r="I110" t="s">
-        <v>50</v>
-      </c>
-      <c r="J110" t="s">
-        <v>53</v>
-      </c>
-      <c r="K110">
-        <v>25</v>
-      </c>
-      <c r="L110" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
-        <v>26</v>
-      </c>
-      <c r="I111" t="s">
-        <v>51</v>
-      </c>
-      <c r="J111" t="s">
-        <v>53</v>
-      </c>
-      <c r="K111">
-        <v>2</v>
-      </c>
-      <c r="L111" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>26</v>
-      </c>
-      <c r="I112" t="s">
-        <v>52</v>
-      </c>
-      <c r="J112" t="s">
-        <v>53</v>
-      </c>
-      <c r="K112" s="6">
-        <v>10.5</v>
-      </c>
-      <c r="L112" t="s">
-        <v>38</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
     </row>
     <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="I113" t="s">
         <v>50</v>
@@ -3837,7 +3822,7 @@
         <v>53</v>
       </c>
       <c r="K113">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L113" t="s">
         <v>38</v>
@@ -3845,7 +3830,7 @@
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="I114" t="s">
         <v>51</v>
@@ -3854,7 +3839,7 @@
         <v>53</v>
       </c>
       <c r="K114">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L114" t="s">
         <v>38</v>
@@ -3862,7 +3847,7 @@
     </row>
     <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="I115" t="s">
         <v>52</v>
@@ -3871,7 +3856,7 @@
         <v>53</v>
       </c>
       <c r="K115" s="6">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="L115" t="s">
         <v>38</v>
@@ -3882,7 +3867,7 @@
     </row>
     <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I116" t="s">
         <v>50</v>
@@ -3891,7 +3876,7 @@
         <v>53</v>
       </c>
       <c r="K116">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L116" t="s">
         <v>38</v>
@@ -3899,7 +3884,7 @@
     </row>
     <row r="117" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I117" t="s">
         <v>51</v>
@@ -3908,7 +3893,7 @@
         <v>53</v>
       </c>
       <c r="K117">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L117" t="s">
         <v>38</v>
@@ -3916,7 +3901,7 @@
     </row>
     <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I118" t="s">
         <v>52</v>
@@ -3925,7 +3910,7 @@
         <v>53</v>
       </c>
       <c r="K118" s="6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L118" t="s">
         <v>38</v>
@@ -3936,7 +3921,7 @@
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="I119" t="s">
         <v>50</v>
@@ -3953,7 +3938,7 @@
     </row>
     <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="I120" t="s">
         <v>51</v>
@@ -3970,7 +3955,7 @@
     </row>
     <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="I121" t="s">
         <v>52</v>
@@ -3990,7 +3975,7 @@
     </row>
     <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="I122" t="s">
         <v>50</v>
@@ -3999,7 +3984,7 @@
         <v>53</v>
       </c>
       <c r="K122">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L122" t="s">
         <v>38</v>
@@ -4007,7 +3992,7 @@
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="I123" t="s">
         <v>51</v>
@@ -4016,70 +4001,70 @@
         <v>53</v>
       </c>
       <c r="K123">
+        <v>10</v>
+      </c>
+      <c r="L123" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>244</v>
+      </c>
+      <c r="I124" t="s">
+        <v>52</v>
+      </c>
+      <c r="J124" t="s">
+        <v>53</v>
+      </c>
+      <c r="K124" s="6">
+        <v>2</v>
+      </c>
+      <c r="L124" t="s">
+        <v>38</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>81</v>
+      </c>
+      <c r="I125" t="s">
+        <v>50</v>
+      </c>
+      <c r="J125" t="s">
+        <v>53</v>
+      </c>
+      <c r="K125">
+        <v>11</v>
+      </c>
+      <c r="L125" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>81</v>
+      </c>
+      <c r="I126" t="s">
+        <v>51</v>
+      </c>
+      <c r="J126" t="s">
+        <v>53</v>
+      </c>
+      <c r="K126">
         <f>0.5</f>
         <v>0.5</v>
       </c>
-      <c r="L123" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>81</v>
-      </c>
-      <c r="I124" t="s">
-        <v>52</v>
-      </c>
-      <c r="J124" t="s">
-        <v>53</v>
-      </c>
-      <c r="K124" s="6">
-        <v>1</v>
-      </c>
-      <c r="L124" t="s">
-        <v>38</v>
-      </c>
-      <c r="M124" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
-        <v>55</v>
-      </c>
-      <c r="I125" t="s">
-        <v>50</v>
-      </c>
-      <c r="J125" t="s">
-        <v>53</v>
-      </c>
-      <c r="K125">
-        <v>11</v>
-      </c>
-      <c r="L125" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>55</v>
-      </c>
-      <c r="I126" t="s">
-        <v>51</v>
-      </c>
-      <c r="J126" t="s">
-        <v>53</v>
-      </c>
-      <c r="K126">
-        <v>4</v>
-      </c>
       <c r="L126" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="I127" t="s">
         <v>52</v>
@@ -4088,7 +4073,7 @@
         <v>53</v>
       </c>
       <c r="K127" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L127" t="s">
         <v>38</v>
@@ -4099,7 +4084,7 @@
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>325</v>
+        <v>55</v>
       </c>
       <c r="I128" t="s">
         <v>50</v>
@@ -4114,9 +4099,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>325</v>
+        <v>55</v>
       </c>
       <c r="I129" t="s">
         <v>51</v>
@@ -4131,9 +4116,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>325</v>
+        <v>55</v>
       </c>
       <c r="I130" t="s">
         <v>52</v>
@@ -4151,9 +4136,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="I131" t="s">
         <v>50</v>
@@ -4162,15 +4147,15 @@
         <v>53</v>
       </c>
       <c r="K131">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L131" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="I132" t="s">
         <v>51</v>
@@ -4179,15 +4164,15 @@
         <v>53</v>
       </c>
       <c r="K132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L132" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="I133" t="s">
         <v>52</v>
@@ -4205,9 +4190,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="I134" t="s">
         <v>50</v>
@@ -4222,9 +4207,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="I135" t="s">
         <v>51</v>
@@ -4239,9 +4224,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="I136" t="s">
         <v>52</v>
@@ -4259,9 +4244,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="I137" t="s">
         <v>50</v>
@@ -4270,15 +4255,15 @@
         <v>53</v>
       </c>
       <c r="K137">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L137" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="I138" t="s">
         <v>51</v>
@@ -4287,15 +4272,15 @@
         <v>53</v>
       </c>
       <c r="K138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L138" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="I139" t="s">
         <v>52</v>
@@ -4313,9 +4298,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="I140" t="s">
         <v>50</v>
@@ -4324,15 +4309,15 @@
         <v>53</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L140" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="I141" t="s">
         <v>51</v>
@@ -4347,9 +4332,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="I142" t="s">
         <v>52</v>
@@ -4367,179 +4352,187 @@
         <v>89</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K143" s="6"/>
-      <c r="M143" s="6"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>112</v>
+      </c>
+      <c r="I143" t="s">
+        <v>50</v>
+      </c>
+      <c r="J143" t="s">
+        <v>53</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="144" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>112</v>
+      </c>
+      <c r="I144" t="s">
+        <v>51</v>
+      </c>
+      <c r="J144" t="s">
+        <v>53</v>
+      </c>
+      <c r="K144">
+        <v>5</v>
+      </c>
+      <c r="L144" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>112</v>
+      </c>
+      <c r="I145" t="s">
+        <v>52</v>
+      </c>
+      <c r="J145" t="s">
+        <v>53</v>
+      </c>
+      <c r="K145" s="6">
+        <v>5</v>
+      </c>
+      <c r="L145" t="s">
+        <v>38</v>
+      </c>
+      <c r="M145" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K146" s="6"/>
+      <c r="M146" s="6"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-      <c r="H144" s="2"/>
-      <c r="I144" s="2"/>
-      <c r="J144" s="3"/>
-      <c r="K144" s="3"/>
-      <c r="L144" s="3"/>
-      <c r="M144" s="3"/>
-      <c r="N144" s="3"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J145" s="7" t="s">
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J148" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K145" s="7">
+      <c r="K148" s="7">
         <v>100</v>
       </c>
-      <c r="L145" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M145" s="7" t="s">
+      <c r="L148" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M148" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="5"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="5"/>
-      <c r="M146" s="5"/>
-      <c r="N146" s="5"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>179</v>
-      </c>
-      <c r="J147" t="s">
-        <v>40</v>
-      </c>
-      <c r="K147">
-        <v>22</v>
-      </c>
-      <c r="L147" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>184</v>
-      </c>
-      <c r="J148" t="s">
-        <v>40</v>
-      </c>
-      <c r="K148" s="27">
-        <f>K147</f>
-        <v>22</v>
-      </c>
-      <c r="L148" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M148" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>317</v>
-      </c>
-      <c r="J149" t="s">
-        <v>40</v>
-      </c>
-      <c r="K149">
-        <v>100</v>
-      </c>
-      <c r="L149" t="s">
-        <v>38</v>
-      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="5"/>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="J150" t="s">
         <v>40</v>
       </c>
-      <c r="K150" s="27">
-        <f>K149</f>
-        <v>100</v>
-      </c>
-      <c r="L150" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M150" s="27" t="s">
-        <v>216</v>
+      <c r="K150">
+        <v>22</v>
+      </c>
+      <c r="L150" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J151" t="s">
         <v>40</v>
       </c>
-      <c r="K151">
-        <v>4</v>
-      </c>
-      <c r="L151" t="s">
-        <v>38</v>
+      <c r="K151" s="27">
+        <f>K150</f>
+        <v>22</v>
+      </c>
+      <c r="L151" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M151" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="J152" t="s">
         <v>40</v>
       </c>
-      <c r="K152" s="27">
-        <f>K151</f>
-        <v>4</v>
-      </c>
-      <c r="L152" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M152" s="27" t="s">
-        <v>216</v>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>88</v>
+        <v>318</v>
       </c>
       <c r="J153" t="s">
         <v>40</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="27">
+        <f>K152</f>
         <v>100</v>
       </c>
-      <c r="L153" t="s">
-        <v>38</v>
+      <c r="L153" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M153" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J154" t="s">
         <v>40</v>
       </c>
       <c r="K154">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L154" t="s">
         <v>38</v>
@@ -4547,14 +4540,14 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J155" t="s">
         <v>40</v>
       </c>
       <c r="K155" s="27">
         <f>K154</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L155" s="27" t="s">
         <v>38</v>
@@ -4565,13 +4558,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="J156" t="s">
         <v>40</v>
       </c>
       <c r="K156">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L156" t="s">
         <v>38</v>
@@ -4579,120 +4572,124 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J157" t="s">
         <v>40</v>
       </c>
-      <c r="K157" s="27">
-        <f>K156</f>
-        <v>1</v>
-      </c>
-      <c r="L157" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M157" s="27" t="s">
-        <v>216</v>
+      <c r="K157">
+        <v>8</v>
+      </c>
+      <c r="L157" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J158" t="s">
         <v>40</v>
       </c>
-      <c r="K158" s="6">
-        <v>22</v>
-      </c>
-      <c r="L158" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M158" t="s">
-        <v>149</v>
+      <c r="K158" s="27">
+        <f>K157</f>
+        <v>8</v>
+      </c>
+      <c r="L158" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M158" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J159" t="s">
         <v>40</v>
       </c>
-      <c r="K159" s="27">
-        <f>K158</f>
-        <v>22</v>
-      </c>
-      <c r="L159" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M159" s="27" t="s">
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>187</v>
+      </c>
+      <c r="J160" t="s">
+        <v>40</v>
+      </c>
+      <c r="K160" s="27">
+        <f>K159</f>
+        <v>1</v>
+      </c>
+      <c r="L160" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M160" s="27" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
-      <c r="L160" s="5"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="5"/>
-    </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A161" s="17" t="s">
-        <v>99</v>
+      <c r="A161" t="s">
+        <v>183</v>
       </c>
       <c r="J161" t="s">
         <v>40</v>
       </c>
-      <c r="K161" s="17">
-        <v>16</v>
+      <c r="K161" s="6">
+        <v>22</v>
       </c>
       <c r="L161" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M161" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" s="17" t="s">
-        <v>100</v>
+      <c r="A162" t="s">
+        <v>188</v>
       </c>
       <c r="J162" t="s">
         <v>40</v>
       </c>
-      <c r="K162" s="17">
-        <v>16</v>
-      </c>
-      <c r="L162" s="17" t="s">
-        <v>38</v>
+      <c r="K162" s="27">
+        <f>K161</f>
+        <v>22</v>
+      </c>
+      <c r="L162" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M162" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="J163" t="s">
-        <v>40</v>
-      </c>
-      <c r="K163" s="17">
-        <v>16</v>
-      </c>
-      <c r="L163" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
+      <c r="I163" s="4"/>
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
+      <c r="L163" s="5"/>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J164" t="s">
         <v>40</v>
@@ -4705,32 +4702,28 @@
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="5"/>
-      <c r="K165" s="5"/>
-      <c r="L165" s="5"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="5"/>
+      <c r="A165" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="J165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K165" s="17">
+        <v>16</v>
+      </c>
+      <c r="L165" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="17" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="J166" t="s">
         <v>40</v>
       </c>
       <c r="K166" s="17">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L166" s="17" t="s">
         <v>38</v>
@@ -4738,41 +4731,45 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>242</v>
+        <v>101</v>
       </c>
       <c r="J167" t="s">
         <v>40</v>
       </c>
       <c r="K167" s="17">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="L167" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A168" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="J168" t="s">
-        <v>40</v>
-      </c>
-      <c r="K168" s="17">
-        <v>85</v>
-      </c>
-      <c r="L168" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A168" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="5"/>
+      <c r="K168" s="5"/>
+      <c r="L168" s="5"/>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J169" t="s">
         <v>40</v>
       </c>
       <c r="K169" s="17">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L169" s="17" t="s">
         <v>38</v>
@@ -4780,30 +4777,27 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="17" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="J170" t="s">
         <v>40</v>
       </c>
-      <c r="K170" s="6">
-        <v>97</v>
+      <c r="K170" s="17">
+        <v>85</v>
       </c>
       <c r="L170" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M170" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="J171" t="s">
         <v>40</v>
       </c>
       <c r="K171" s="17">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="L171" s="17" t="s">
         <v>38</v>
@@ -4811,140 +4805,139 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="C172" s="9"/>
+        <v>245</v>
+      </c>
       <c r="J172" t="s">
         <v>40</v>
       </c>
-      <c r="K172" s="6">
-        <v>50</v>
+      <c r="K172" s="17">
+        <v>95</v>
       </c>
       <c r="L172" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M172" s="6" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J173" t="s">
         <v>40</v>
       </c>
       <c r="K173" s="6">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L173" s="17" t="s">
         <v>38</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="5"/>
-      <c r="K174" s="5"/>
-      <c r="L174" s="5"/>
-      <c r="M174" s="5"/>
-      <c r="N174" s="5"/>
+      <c r="A174" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="J174" t="s">
+        <v>40</v>
+      </c>
+      <c r="K174" s="17">
+        <v>29</v>
+      </c>
+      <c r="L174" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>135</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C175" s="9"/>
       <c r="J175" t="s">
         <v>40</v>
       </c>
-      <c r="K175">
-        <v>7</v>
+      <c r="K175" s="6">
+        <v>50</v>
       </c>
       <c r="L175" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="M175" s="6" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="17" t="s">
-        <v>141</v>
+        <v>256</v>
       </c>
       <c r="J176" t="s">
         <v>40</v>
       </c>
-      <c r="K176" s="17">
-        <v>35</v>
+      <c r="K176" s="6">
+        <v>90</v>
       </c>
       <c r="L176" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M176" s="6" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J177" t="s">
-        <v>40</v>
-      </c>
-      <c r="K177" s="17">
-        <v>63</v>
-      </c>
-      <c r="L177" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="A177" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4"/>
+      <c r="J177" s="5"/>
+      <c r="K177" s="5"/>
+      <c r="L177" s="5"/>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J178" t="s">
         <v>40</v>
       </c>
-      <c r="K178" s="17">
-        <v>54</v>
+      <c r="K178">
+        <v>7</v>
       </c>
       <c r="L178" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J179" t="s">
         <v>40</v>
       </c>
-      <c r="K179" s="6">
-        <v>75</v>
+      <c r="K179" s="17">
+        <v>35</v>
       </c>
       <c r="L179" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="M179" s="6" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J180" t="s">
         <v>40</v>
       </c>
       <c r="K180" s="17">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="L180" s="17" t="s">
         <v>38</v>
@@ -4952,41 +4945,45 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="J181" t="s">
         <v>40</v>
       </c>
       <c r="K181" s="17">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="L181" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="J182" t="s">
         <v>40</v>
       </c>
-      <c r="K182" s="17">
-        <v>46</v>
+      <c r="K182" s="6">
+        <v>75</v>
       </c>
       <c r="L182" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="M182" s="6" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="J183" t="s">
         <v>40</v>
       </c>
       <c r="K183" s="17">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L183" s="17" t="s">
         <v>38</v>
@@ -4994,98 +4991,95 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="J184" t="s">
         <v>40</v>
       </c>
-      <c r="K184" s="6">
+      <c r="K184" s="17">
         <v>90</v>
       </c>
       <c r="L184" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M184" s="6" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-      <c r="D185" s="4"/>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="5"/>
-      <c r="K185" s="5"/>
-      <c r="L185" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="M185" s="41">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="N185" s="5"/>
+      <c r="A185" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J185" t="s">
+        <v>40</v>
+      </c>
+      <c r="K185" s="17">
+        <v>46</v>
+      </c>
+      <c r="L185" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
-        <v>62</v>
+      <c r="A186" s="17" t="s">
+        <v>249</v>
       </c>
       <c r="J186" t="s">
         <v>40</v>
       </c>
-      <c r="K186" s="13">
-        <f>8.5*20/(29.5+8.5)*$M$185</f>
-        <v>3.6594736842105262</v>
-      </c>
-      <c r="L186" t="s">
+      <c r="K186" s="17">
+        <v>100</v>
+      </c>
+      <c r="L186" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
-        <v>61</v>
+      <c r="A187" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="J187" t="s">
         <v>40</v>
       </c>
-      <c r="K187" s="13">
-        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)*$M$185</f>
-        <v>2.438757763975155</v>
-      </c>
-      <c r="L187" t="s">
-        <v>38</v>
+      <c r="K187" s="6">
+        <v>90</v>
+      </c>
+      <c r="L187" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M187" s="6" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J188" t="s">
-        <v>40</v>
-      </c>
-      <c r="K188" s="13">
-        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)*$M$185</f>
-        <v>6.317653239929947</v>
-      </c>
-      <c r="L188" t="s">
-        <v>38</v>
-      </c>
+      <c r="A188" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" s="4"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
+      <c r="I188" s="4"/>
+      <c r="J188" s="5"/>
+      <c r="K188" s="5"/>
+      <c r="L188" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="M188" s="41">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="N188" s="5"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J189" t="s">
         <v>40</v>
       </c>
-      <c r="K189">
-        <f>60*$M$185</f>
-        <v>49.08</v>
+      <c r="K189" s="13">
+        <f>8.5*20/(29.5+8.5)*$M$188</f>
+        <v>3.6594736842105262</v>
       </c>
       <c r="L189" t="s">
         <v>38</v>
@@ -5093,14 +5087,14 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J190" t="s">
         <v>40</v>
       </c>
-      <c r="K190">
-        <f>0*$M$185</f>
-        <v>0</v>
+      <c r="K190" s="13">
+        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)*$M$188</f>
+        <v>2.438757763975155</v>
       </c>
       <c r="L190" t="s">
         <v>38</v>
@@ -5108,14 +5102,14 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J191" t="s">
         <v>40</v>
       </c>
-      <c r="K191">
-        <f>20*$M$185</f>
-        <v>16.36</v>
+      <c r="K191" s="13">
+        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)*$M$188</f>
+        <v>6.317653239929947</v>
       </c>
       <c r="L191" t="s">
         <v>38</v>
@@ -5123,14 +5117,14 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J192" t="s">
         <v>40</v>
       </c>
       <c r="K192">
-        <f>20*$M$185</f>
-        <v>16.36</v>
+        <f>60*$M$188</f>
+        <v>49.08</v>
       </c>
       <c r="L192" t="s">
         <v>38</v>
@@ -5138,14 +5132,14 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J193" t="s">
         <v>40</v>
       </c>
       <c r="K193">
-        <f>20*$M$185</f>
-        <v>16.36</v>
+        <f>0*$M$188</f>
+        <v>0</v>
       </c>
       <c r="L193" t="s">
         <v>38</v>
@@ -5153,91 +5147,91 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J194" t="s">
         <v>40</v>
       </c>
       <c r="K194">
-        <f>43*$M$185</f>
-        <v>35.173999999999999</v>
+        <f>20*$M$188</f>
+        <v>16.36</v>
       </c>
       <c r="L194" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="5"/>
-      <c r="K195" s="5"/>
-      <c r="L195" s="5"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="5"/>
+      <c r="A195" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J195" t="s">
+        <v>40</v>
+      </c>
+      <c r="K195">
+        <f>20*$M$188</f>
+        <v>16.36</v>
+      </c>
+      <c r="L195" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>54</v>
+      <c r="A196" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="J196" t="s">
         <v>40</v>
       </c>
-      <c r="K196" s="17">
-        <v>36.909999999999997</v>
+      <c r="K196">
+        <f>20*$M$188</f>
+        <v>16.36</v>
       </c>
       <c r="L196" t="s">
         <v>38</v>
       </c>
-      <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>95</v>
+      <c r="A197" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="J197" t="s">
         <v>40</v>
       </c>
-      <c r="K197" s="17">
-        <v>43.11</v>
+      <c r="K197">
+        <f>43*$M$188</f>
+        <v>35.173999999999999</v>
       </c>
       <c r="L197" t="s">
         <v>38</v>
       </c>
-      <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>346</v>
-      </c>
-      <c r="J198" t="s">
-        <v>40</v>
-      </c>
-      <c r="K198" s="17">
-        <v>63.94</v>
-      </c>
-      <c r="L198" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M198" s="6"/>
+      <c r="A198" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+      <c r="H198" s="4"/>
+      <c r="I198" s="4"/>
+      <c r="J198" s="5"/>
+      <c r="K198" s="5"/>
+      <c r="L198" s="5"/>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>267</v>
+        <v>54</v>
       </c>
       <c r="J199" t="s">
         <v>40</v>
       </c>
       <c r="K199" s="17">
-        <v>36.49</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="L199" t="s">
         <v>38</v>
@@ -5245,116 +5239,116 @@
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
-      <c r="J200" s="5"/>
-      <c r="K200" s="5"/>
-      <c r="L200" s="5"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="5"/>
+      <c r="A200" t="s">
+        <v>95</v>
+      </c>
+      <c r="J200" t="s">
+        <v>40</v>
+      </c>
+      <c r="K200" s="17">
+        <v>43.11</v>
+      </c>
+      <c r="L200" t="s">
+        <v>38</v>
+      </c>
+      <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="J201" t="s">
         <v>40</v>
       </c>
       <c r="K201" s="17">
+        <v>63.94</v>
+      </c>
+      <c r="L201" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M201" s="6"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>267</v>
+      </c>
+      <c r="J202" t="s">
+        <v>40</v>
+      </c>
+      <c r="K202" s="17">
+        <v>36.49</v>
+      </c>
+      <c r="L202" t="s">
+        <v>38</v>
+      </c>
+      <c r="M202" s="6"/>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="4"/>
+      <c r="D203" s="4"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4"/>
+      <c r="G203" s="4"/>
+      <c r="H203" s="4"/>
+      <c r="I203" s="4"/>
+      <c r="J203" s="5"/>
+      <c r="K203" s="5"/>
+      <c r="L203" s="5"/>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>15</v>
+      </c>
+      <c r="J204" t="s">
+        <v>40</v>
+      </c>
+      <c r="K204" s="17">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="L201" t="s">
-        <v>38</v>
-      </c>
-      <c r="M201" s="17" t="s">
+      <c r="L204" t="s">
+        <v>38</v>
+      </c>
+      <c r="M204" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="N201" t="s">
+      <c r="N204" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
-      <c r="I202" s="4"/>
-      <c r="J202" s="5"/>
-      <c r="K202" s="5"/>
-      <c r="L202" s="5"/>
-      <c r="M202" s="5"/>
-      <c r="N202" s="5"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="B205" s="4"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4"/>
+      <c r="G205" s="4"/>
+      <c r="H205" s="4"/>
+      <c r="I205" s="4"/>
+      <c r="J205" s="5"/>
+      <c r="K205" s="5"/>
+      <c r="L205" s="5"/>
+      <c r="M205" s="5"/>
+      <c r="N205" s="5"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>202</v>
-      </c>
-      <c r="J203" t="s">
-        <v>40</v>
-      </c>
-      <c r="K203">
-        <v>5</v>
-      </c>
-      <c r="L203" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="J204" t="s">
-        <v>40</v>
-      </c>
-      <c r="K204">
-        <v>0.4</v>
-      </c>
-      <c r="L204" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="J205" t="s">
-        <v>40</v>
-      </c>
-      <c r="K205" s="6">
-        <v>95</v>
-      </c>
-      <c r="L205" t="s">
-        <v>38</v>
-      </c>
-      <c r="M205" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="26" t="s">
-        <v>205</v>
       </c>
       <c r="J206" t="s">
         <v>40</v>
       </c>
       <c r="K206">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L206" t="s">
         <v>38</v>
@@ -5362,361 +5356,333 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="8"/>
-      <c r="G207" s="8"/>
-      <c r="H207" s="8"/>
-      <c r="I207" s="8"/>
+        <v>203</v>
+      </c>
       <c r="J207" t="s">
         <v>40</v>
       </c>
       <c r="K207">
-        <v>100</v>
+        <v>0.4</v>
       </c>
       <c r="L207" t="s">
         <v>38</v>
       </c>
-      <c r="M207" s="8"/>
-      <c r="N207" s="8"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-      <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
-      <c r="I208" s="4"/>
-      <c r="J208" s="5"/>
-      <c r="K208" s="5"/>
-      <c r="L208" s="5"/>
-      <c r="M208" s="5"/>
-      <c r="N208" s="5"/>
+      <c r="A208" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="J208" t="s">
+        <v>40</v>
+      </c>
+      <c r="K208" s="6">
+        <v>95</v>
+      </c>
+      <c r="L208" t="s">
+        <v>38</v>
+      </c>
+      <c r="M208" s="6" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>126</v>
+      <c r="A209" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="J209" t="s">
         <v>40</v>
       </c>
-      <c r="K209" s="15">
-        <v>52</v>
+      <c r="K209">
+        <v>100</v>
       </c>
       <c r="L209" t="s">
         <v>38</v>
       </c>
-      <c r="M209" s="24"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A210" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-      <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
-      <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
-      <c r="I210" s="4"/>
-      <c r="J210" s="5"/>
-      <c r="K210" s="5"/>
-      <c r="L210" s="5"/>
-      <c r="M210" s="5"/>
-      <c r="N210" s="5"/>
+      <c r="A210" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B210" s="8"/>
+      <c r="C210" s="8"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
+      <c r="F210" s="8"/>
+      <c r="G210" s="8"/>
+      <c r="H210" s="8"/>
+      <c r="I210" s="8"/>
+      <c r="J210" t="s">
+        <v>40</v>
+      </c>
+      <c r="K210">
+        <v>100</v>
+      </c>
+      <c r="L210" t="s">
+        <v>38</v>
+      </c>
+      <c r="M210" s="8"/>
+      <c r="N210" s="8"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>217</v>
-      </c>
-      <c r="J211" t="s">
-        <v>40</v>
-      </c>
-      <c r="K211" s="6">
-        <v>24</v>
-      </c>
-      <c r="L211" t="s">
-        <v>38</v>
-      </c>
-      <c r="M211" s="6" t="s">
-        <v>222</v>
-      </c>
+      <c r="A211" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4"/>
+      <c r="G211" s="4"/>
+      <c r="H211" s="4"/>
+      <c r="I211" s="4"/>
+      <c r="J211" s="5"/>
+      <c r="K211" s="5"/>
+      <c r="L211" s="5"/>
+      <c r="M211" s="5"/>
+      <c r="N211" s="5"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="J212" t="s">
         <v>40</v>
       </c>
-      <c r="K212" s="27">
-        <f>K211</f>
+      <c r="K212" s="15">
+        <v>52</v>
+      </c>
+      <c r="L212" t="s">
+        <v>38</v>
+      </c>
+      <c r="M212" s="24"/>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L212" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="M212" s="27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>218</v>
-      </c>
-      <c r="J213" t="s">
+      <c r="B213" s="4"/>
+      <c r="C213" s="4"/>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4"/>
+      <c r="G213" s="4"/>
+      <c r="H213" s="4"/>
+      <c r="I213" s="4"/>
+      <c r="J213" s="5"/>
+      <c r="K213" s="5"/>
+      <c r="L213" s="5"/>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>217</v>
+      </c>
+      <c r="J214" t="s">
         <v>40</v>
       </c>
-      <c r="K213">
-        <v>61</v>
-      </c>
-      <c r="L213" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A214" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
-      <c r="I214" s="4"/>
-      <c r="J214" s="5"/>
-      <c r="K214" s="5"/>
-      <c r="L214" s="5"/>
-      <c r="M214" s="5"/>
-      <c r="N214" s="5"/>
+      <c r="K214" s="6">
+        <v>24</v>
+      </c>
+      <c r="L214" t="s">
+        <v>38</v>
+      </c>
+      <c r="M214" s="6" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="J215" t="s">
         <v>40</v>
       </c>
-      <c r="K215">
-        <v>100</v>
-      </c>
-      <c r="L215" t="s">
-        <v>38</v>
+      <c r="K215" s="27">
+        <f>K214</f>
+        <v>24</v>
+      </c>
+      <c r="L215" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="M215" s="27" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="J216" t="s">
         <v>40</v>
       </c>
       <c r="K216">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="L216" t="s">
         <v>38</v>
       </c>
-      <c r="M216" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>228</v>
-      </c>
-      <c r="J217" t="s">
-        <v>40</v>
-      </c>
-      <c r="K217">
-        <v>85</v>
-      </c>
-      <c r="L217" t="s">
-        <v>38</v>
-      </c>
-      <c r="M217" t="s">
-        <v>233</v>
-      </c>
+      <c r="A217" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="5"/>
+      <c r="K217" s="5"/>
+      <c r="L217" s="5"/>
+      <c r="M217" s="5"/>
+      <c r="N217" s="5"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J218" t="s">
         <v>40</v>
       </c>
       <c r="K218">
+        <v>100</v>
+      </c>
+      <c r="L218" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>230</v>
+      </c>
+      <c r="J219" t="s">
+        <v>40</v>
+      </c>
+      <c r="K219">
+        <v>4</v>
+      </c>
+      <c r="L219" t="s">
+        <v>38</v>
+      </c>
+      <c r="M219" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>228</v>
+      </c>
+      <c r="J220" t="s">
+        <v>40</v>
+      </c>
+      <c r="K220">
+        <v>85</v>
+      </c>
+      <c r="L220" t="s">
+        <v>38</v>
+      </c>
+      <c r="M220" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>231</v>
+      </c>
+      <c r="J221" t="s">
+        <v>40</v>
+      </c>
+      <c r="K221">
         <v>22</v>
       </c>
-      <c r="L218" t="s">
-        <v>38</v>
-      </c>
-      <c r="M218" t="s">
+      <c r="L221" t="s">
+        <v>38</v>
+      </c>
+      <c r="M221" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B220" s="2"/>
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
-      <c r="J220" s="3"/>
-      <c r="K220" s="3"/>
-      <c r="L220" s="3"/>
-      <c r="M220" s="3"/>
-      <c r="N220" s="3"/>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G221" s="7"/>
-      <c r="H221" s="7" t="s">
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="3"/>
+      <c r="K223" s="3"/>
+      <c r="L223" s="3"/>
+      <c r="M223" s="3"/>
+      <c r="N223" s="3"/>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G224" s="7"/>
+      <c r="H224" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7" t="s">
+      <c r="I224" s="7"/>
+      <c r="J224" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K221" s="7">
+      <c r="K224" s="7">
         <v>-100</v>
       </c>
-      <c r="L221" s="7" t="s">
+      <c r="L224" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M221" s="7" t="s">
+      <c r="M224" s="7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G222" s="7"/>
-      <c r="H222" s="7" t="s">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G225" s="7"/>
+      <c r="H225" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7" t="s">
+      <c r="I225" s="7"/>
+      <c r="J225" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K222" s="7">
+      <c r="K225" s="7">
         <v>0</v>
       </c>
-      <c r="L222" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M222" s="7" t="s">
+      <c r="L225" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M225" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" s="4" t="s">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
-      <c r="D223" s="4"/>
-      <c r="E223" s="4"/>
-      <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
-      <c r="I223" s="4"/>
-      <c r="J223" s="5"/>
-      <c r="K223" s="5"/>
-      <c r="L223" s="5"/>
-      <c r="M223" s="5"/>
-      <c r="N223" s="5"/>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>179</v>
-      </c>
-      <c r="G224" t="s">
-        <v>87</v>
-      </c>
-      <c r="H224" t="s">
-        <v>43</v>
-      </c>
-      <c r="J224" t="s">
-        <v>41</v>
-      </c>
-      <c r="K224" s="17">
-        <v>5.3</v>
-      </c>
-      <c r="L224" t="s">
-        <v>38</v>
-      </c>
-      <c r="M224" t="s">
-        <v>169</v>
-      </c>
-      <c r="N224" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>184</v>
-      </c>
-      <c r="G225" t="s">
-        <v>87</v>
-      </c>
-      <c r="H225" t="s">
-        <v>43</v>
-      </c>
-      <c r="J225" t="s">
-        <v>41</v>
-      </c>
-      <c r="K225" s="40">
-        <f>K224</f>
-        <v>5.3</v>
-      </c>
-      <c r="L225" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>180</v>
-      </c>
-      <c r="G226" t="s">
-        <v>87</v>
-      </c>
-      <c r="H226" t="s">
-        <v>43</v>
-      </c>
-      <c r="J226" t="s">
-        <v>41</v>
-      </c>
-      <c r="K226" s="17">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L226" t="s">
-        <v>38</v>
-      </c>
-      <c r="M226" t="s">
-        <v>169</v>
-      </c>
-      <c r="N226" t="s">
-        <v>98</v>
-      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="4"/>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4"/>
+      <c r="G226" s="4"/>
+      <c r="H226" s="4"/>
+      <c r="I226" s="4"/>
+      <c r="J226" s="5"/>
+      <c r="K226" s="5"/>
+      <c r="L226" s="5"/>
+      <c r="M226" s="5"/>
+      <c r="N226" s="5"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G227" t="s">
         <v>87</v>
@@ -5727,17 +5693,22 @@
       <c r="J227" t="s">
         <v>41</v>
       </c>
-      <c r="K227" s="40">
-        <f>K226</f>
-        <v>4.9000000000000004</v>
+      <c r="K227" s="17">
+        <v>5.3</v>
       </c>
       <c r="L227" t="s">
         <v>38</v>
+      </c>
+      <c r="M227" t="s">
+        <v>169</v>
+      </c>
+      <c r="N227" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G228" t="s">
         <v>87</v>
@@ -5748,22 +5719,17 @@
       <c r="J228" t="s">
         <v>41</v>
       </c>
-      <c r="K228" s="17">
-        <v>12.7</v>
+      <c r="K228" s="40">
+        <f>K227</f>
+        <v>5.3</v>
       </c>
       <c r="L228" t="s">
         <v>38</v>
-      </c>
-      <c r="M228" t="s">
-        <v>169</v>
-      </c>
-      <c r="N228" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G229" t="s">
         <v>87</v>
@@ -5774,17 +5740,22 @@
       <c r="J229" t="s">
         <v>41</v>
       </c>
-      <c r="K229" s="40">
-        <f>K228</f>
-        <v>12.7</v>
+      <c r="K229" s="17">
+        <v>4.9000000000000004</v>
       </c>
       <c r="L229" t="s">
         <v>38</v>
+      </c>
+      <c r="M229" t="s">
+        <v>169</v>
+      </c>
+      <c r="N229" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G230" t="s">
         <v>87</v>
@@ -5795,22 +5766,17 @@
       <c r="J230" t="s">
         <v>41</v>
       </c>
-      <c r="K230" s="17">
-        <v>24</v>
+      <c r="K230" s="40">
+        <f>K229</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L230" t="s">
         <v>38</v>
-      </c>
-      <c r="M230" t="s">
-        <v>170</v>
-      </c>
-      <c r="N230" s="26" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G231" t="s">
         <v>87</v>
@@ -5821,18 +5787,22 @@
       <c r="J231" t="s">
         <v>41</v>
       </c>
-      <c r="K231" s="40">
-        <f>K230</f>
-        <v>24</v>
+      <c r="K231" s="17">
+        <v>12.7</v>
       </c>
       <c r="L231" t="s">
         <v>38</v>
       </c>
-      <c r="N231" s="26"/>
+      <c r="M231" t="s">
+        <v>169</v>
+      </c>
+      <c r="N231" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G232" t="s">
         <v>87</v>
@@ -5843,8 +5813,9 @@
       <c r="J232" t="s">
         <v>41</v>
       </c>
-      <c r="K232" s="6">
-        <v>10</v>
+      <c r="K232" s="40">
+        <f>K231</f>
+        <v>12.7</v>
       </c>
       <c r="L232" t="s">
         <v>38</v>
@@ -5852,7 +5823,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G233" t="s">
         <v>87</v>
@@ -5863,35 +5834,44 @@
       <c r="J233" t="s">
         <v>41</v>
       </c>
-      <c r="K233" s="40">
-        <f>K232</f>
-        <v>10</v>
+      <c r="K233" s="17">
+        <v>24</v>
       </c>
       <c r="L233" t="s">
         <v>38</v>
       </c>
+      <c r="M233" t="s">
+        <v>170</v>
+      </c>
+      <c r="N233" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="4"/>
-      <c r="J234" s="5"/>
-      <c r="K234" s="5"/>
-      <c r="L234" s="5"/>
-      <c r="M234" s="5"/>
-      <c r="N234" s="5"/>
+      <c r="A234" t="s">
+        <v>187</v>
+      </c>
+      <c r="G234" t="s">
+        <v>87</v>
+      </c>
+      <c r="H234" t="s">
+        <v>43</v>
+      </c>
+      <c r="J234" t="s">
+        <v>41</v>
+      </c>
+      <c r="K234" s="40">
+        <f>K233</f>
+        <v>24</v>
+      </c>
+      <c r="L234" t="s">
+        <v>38</v>
+      </c>
+      <c r="N234" s="26"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" s="17" t="s">
-        <v>99</v>
+      <c r="A235" t="s">
+        <v>183</v>
       </c>
       <c r="G235" t="s">
         <v>87</v>
@@ -5902,19 +5882,16 @@
       <c r="J235" t="s">
         <v>41</v>
       </c>
-      <c r="K235" s="17">
-        <v>12</v>
+      <c r="K235" s="6">
+        <v>10</v>
       </c>
       <c r="L235" t="s">
         <v>38</v>
       </c>
-      <c r="N235" s="26" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" s="17" t="s">
-        <v>100</v>
+      <c r="A236" t="s">
+        <v>188</v>
       </c>
       <c r="G236" t="s">
         <v>87</v>
@@ -5925,39 +5902,35 @@
       <c r="J236" t="s">
         <v>41</v>
       </c>
-      <c r="K236" s="17">
-        <v>12</v>
+      <c r="K236" s="40">
+        <f>K235</f>
+        <v>10</v>
       </c>
       <c r="L236" t="s">
         <v>38</v>
       </c>
-      <c r="N236" s="26" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="G237" t="s">
-        <v>87</v>
-      </c>
-      <c r="H237" t="s">
-        <v>43</v>
-      </c>
-      <c r="J237" t="s">
-        <v>41</v>
-      </c>
-      <c r="K237" s="17">
-        <v>0</v>
-      </c>
-      <c r="L237" t="s">
-        <v>38</v>
-      </c>
+      <c r="A237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4"/>
+      <c r="G237" s="4"/>
+      <c r="H237" s="4"/>
+      <c r="I237" s="4"/>
+      <c r="J237" s="5"/>
+      <c r="K237" s="5"/>
+      <c r="L237" s="5"/>
+      <c r="M237" s="5"/>
+      <c r="N237" s="5"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G238" t="s">
         <v>87</v>
@@ -5969,33 +5942,41 @@
         <v>41</v>
       </c>
       <c r="K238" s="17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L238" t="s">
         <v>38</v>
       </c>
+      <c r="N238" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" s="4" t="s">
+      <c r="A239" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="G239" t="s">
+        <v>87</v>
+      </c>
+      <c r="H239" t="s">
+        <v>43</v>
+      </c>
+      <c r="J239" t="s">
+        <v>41</v>
+      </c>
+      <c r="K239" s="17">
         <v>12</v>
       </c>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-      <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
-      <c r="H239" s="4"/>
-      <c r="I239" s="4"/>
-      <c r="J239" s="5"/>
-      <c r="K239" s="5"/>
-      <c r="L239" s="5"/>
-      <c r="M239" s="5"/>
-      <c r="N239" s="5"/>
+      <c r="L239" t="s">
+        <v>38</v>
+      </c>
+      <c r="N239" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="17" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="G240" t="s">
         <v>87</v>
@@ -6007,21 +5988,15 @@
         <v>41</v>
       </c>
       <c r="K240" s="17">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L240" t="s">
         <v>38</v>
-      </c>
-      <c r="M240" t="s">
-        <v>172</v>
-      </c>
-      <c r="N240" s="26" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="G241" t="s">
         <v>87</v>
@@ -6033,47 +6008,33 @@
         <v>41</v>
       </c>
       <c r="K241" s="17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L241" t="s">
         <v>38</v>
       </c>
-      <c r="M241" t="s">
-        <v>173</v>
-      </c>
-      <c r="N241" s="26" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G242" t="s">
-        <v>87</v>
-      </c>
-      <c r="H242" t="s">
-        <v>43</v>
-      </c>
-      <c r="J242" t="s">
-        <v>41</v>
-      </c>
-      <c r="K242" s="17">
-        <v>19</v>
-      </c>
-      <c r="L242" t="s">
-        <v>38</v>
-      </c>
-      <c r="M242" t="s">
-        <v>171</v>
-      </c>
-      <c r="N242" s="26" t="s">
-        <v>167</v>
-      </c>
+      <c r="A242" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242" s="4"/>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4"/>
+      <c r="G242" s="4"/>
+      <c r="H242" s="4"/>
+      <c r="I242" s="4"/>
+      <c r="J242" s="5"/>
+      <c r="K242" s="5"/>
+      <c r="L242" s="5"/>
+      <c r="M242" s="5"/>
+      <c r="N242" s="5"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="G243" t="s">
         <v>87</v>
@@ -6085,13 +6046,13 @@
         <v>41</v>
       </c>
       <c r="K243" s="17">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L243" t="s">
         <v>38</v>
       </c>
       <c r="M243" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N243" s="26" t="s">
         <v>167</v>
@@ -6099,7 +6060,7 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G244" t="s">
         <v>87</v>
@@ -6111,13 +6072,13 @@
         <v>41</v>
       </c>
       <c r="K244" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L244" t="s">
         <v>38</v>
       </c>
-      <c r="M244" s="26" t="s">
-        <v>174</v>
+      <c r="M244" t="s">
+        <v>173</v>
       </c>
       <c r="N244" s="26" t="s">
         <v>167</v>
@@ -6125,7 +6086,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G245" t="s">
         <v>87</v>
@@ -6136,37 +6097,51 @@
       <c r="J245" t="s">
         <v>41</v>
       </c>
-      <c r="K245" s="6">
-        <f>AVERAGE(K241:K244)</f>
-        <v>13</v>
+      <c r="K245" s="17">
+        <v>19</v>
       </c>
       <c r="L245" t="s">
         <v>38</v>
       </c>
-      <c r="M245" s="26"/>
-      <c r="N245" s="26"/>
+      <c r="M245" t="s">
+        <v>171</v>
+      </c>
+      <c r="N245" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A246" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
-      <c r="I246" s="4"/>
-      <c r="J246" s="5"/>
-      <c r="K246" s="5"/>
-      <c r="L246" s="5"/>
-      <c r="M246" s="5"/>
-      <c r="N246" s="5"/>
+      <c r="A246" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G246" t="s">
+        <v>87</v>
+      </c>
+      <c r="H246" t="s">
+        <v>43</v>
+      </c>
+      <c r="J246" t="s">
+        <v>41</v>
+      </c>
+      <c r="K246" s="17">
+        <v>9</v>
+      </c>
+      <c r="L246" t="s">
+        <v>38</v>
+      </c>
+      <c r="M246" t="s">
+        <v>175</v>
+      </c>
+      <c r="N246" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>241</v>
+        <v>110</v>
+      </c>
+      <c r="G247" t="s">
+        <v>87</v>
       </c>
       <c r="H247" t="s">
         <v>43</v>
@@ -6175,21 +6150,24 @@
         <v>41</v>
       </c>
       <c r="K247" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L247" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M247" t="s">
-        <v>246</v>
-      </c>
-      <c r="N247" t="s">
+        <v>11</v>
+      </c>
+      <c r="L247" t="s">
+        <v>38</v>
+      </c>
+      <c r="M247" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="N247" s="26" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="17" t="s">
-        <v>242</v>
+        <v>148</v>
+      </c>
+      <c r="G248" t="s">
+        <v>87</v>
       </c>
       <c r="H248" t="s">
         <v>43</v>
@@ -6197,45 +6175,37 @@
       <c r="J248" t="s">
         <v>41</v>
       </c>
-      <c r="K248" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L248" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M248" t="s">
-        <v>246</v>
-      </c>
-      <c r="N248" t="s">
-        <v>167</v>
-      </c>
+      <c r="K248" s="6">
+        <f>AVERAGE(K244:K247)</f>
+        <v>13</v>
+      </c>
+      <c r="L248" t="s">
+        <v>38</v>
+      </c>
+      <c r="M248" s="26"/>
+      <c r="N248" s="26"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="H249" t="s">
-        <v>43</v>
-      </c>
-      <c r="J249" t="s">
-        <v>41</v>
-      </c>
-      <c r="K249" s="17">
-        <v>7.9</v>
-      </c>
-      <c r="L249" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M249" t="s">
-        <v>246</v>
-      </c>
-      <c r="N249" t="s">
-        <v>167</v>
-      </c>
+      <c r="A249" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B249" s="4"/>
+      <c r="C249" s="4"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4"/>
+      <c r="G249" s="4"/>
+      <c r="H249" s="4"/>
+      <c r="I249" s="4"/>
+      <c r="J249" s="5"/>
+      <c r="K249" s="5"/>
+      <c r="L249" s="5"/>
+      <c r="M249" s="5"/>
+      <c r="N249" s="5"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H250" t="s">
         <v>43</v>
@@ -6257,30 +6227,31 @@
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B251" s="4"/>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
-      <c r="H251" s="4"/>
-      <c r="I251" s="4"/>
-      <c r="J251" s="5"/>
-      <c r="K251" s="5"/>
-      <c r="L251" s="5"/>
-      <c r="M251" s="5"/>
-      <c r="N251" s="5"/>
+      <c r="A251" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="H251" t="s">
+        <v>43</v>
+      </c>
+      <c r="J251" t="s">
+        <v>41</v>
+      </c>
+      <c r="K251" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L251" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M251" t="s">
+        <v>246</v>
+      </c>
+      <c r="N251" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" s="6"/>
-      <c r="B252" t="s">
-        <v>81</v>
-      </c>
-      <c r="G252" t="s">
-        <v>87</v>
+      <c r="A252" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="H252" t="s">
         <v>43</v>
@@ -6288,63 +6259,64 @@
       <c r="J252" t="s">
         <v>41</v>
       </c>
-      <c r="K252" s="29">
-        <v>15.75</v>
-      </c>
-      <c r="L252" t="s">
+      <c r="K252" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L252" s="17" t="s">
         <v>38</v>
       </c>
       <c r="M252" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="N252" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B253" s="4"/>
-      <c r="C253" s="4"/>
-      <c r="D253" s="4"/>
-      <c r="E253" s="4"/>
-      <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
-      <c r="H253" s="4"/>
-      <c r="I253" s="4"/>
-      <c r="J253" s="5"/>
-      <c r="K253" s="5"/>
-      <c r="L253" s="5"/>
-      <c r="M253" s="5"/>
-      <c r="N253" s="5"/>
+      <c r="A253" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="H253" t="s">
+        <v>43</v>
+      </c>
+      <c r="J253" t="s">
+        <v>41</v>
+      </c>
+      <c r="K253" s="17">
+        <v>7.9</v>
+      </c>
+      <c r="L253" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M253" t="s">
+        <v>246</v>
+      </c>
+      <c r="N253" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>54</v>
-      </c>
-      <c r="G254" t="s">
-        <v>87</v>
-      </c>
-      <c r="H254" t="s">
-        <v>43</v>
-      </c>
-      <c r="J254" t="s">
-        <v>41</v>
-      </c>
-      <c r="K254" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="L254" t="s">
-        <v>38</v>
-      </c>
-      <c r="M254" t="s">
-        <v>326</v>
-      </c>
+      <c r="A254" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="4"/>
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4"/>
+      <c r="G254" s="4"/>
+      <c r="H254" s="4"/>
+      <c r="I254" s="4"/>
+      <c r="J254" s="5"/>
+      <c r="K254" s="5"/>
+      <c r="L254" s="5"/>
+      <c r="M254" s="5"/>
+      <c r="N254" s="5"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>95</v>
+      <c r="A255" s="6"/>
+      <c r="B255" t="s">
+        <v>81</v>
       </c>
       <c r="G255" t="s">
         <v>87</v>
@@ -6355,42 +6327,40 @@
       <c r="J255" t="s">
         <v>41</v>
       </c>
-      <c r="K255" s="6">
-        <v>18.100000000000001</v>
+      <c r="K255" s="29">
+        <v>15.75</v>
       </c>
       <c r="L255" t="s">
         <v>38</v>
       </c>
       <c r="M255" t="s">
-        <v>326</v>
+        <v>168</v>
+      </c>
+      <c r="N255" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>346</v>
-      </c>
-      <c r="G256" t="s">
-        <v>87</v>
-      </c>
-      <c r="H256" t="s">
-        <v>43</v>
-      </c>
-      <c r="J256" t="s">
-        <v>41</v>
-      </c>
-      <c r="K256" s="6">
-        <v>20</v>
-      </c>
-      <c r="L256" t="s">
-        <v>38</v>
-      </c>
-      <c r="M256" s="6" t="s">
-        <v>355</v>
-      </c>
+      <c r="A256" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="4"/>
+      <c r="D256" s="4"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="4"/>
+      <c r="G256" s="4"/>
+      <c r="H256" s="4"/>
+      <c r="I256" s="4"/>
+      <c r="J256" s="5"/>
+      <c r="K256" s="5"/>
+      <c r="L256" s="5"/>
+      <c r="M256" s="5"/>
+      <c r="N256" s="5"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>267</v>
+        <v>54</v>
       </c>
       <c r="G257" t="s">
         <v>87</v>
@@ -6402,7 +6372,7 @@
         <v>41</v>
       </c>
       <c r="K257" s="6">
-        <v>0.95</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="L257" t="s">
         <v>38</v>
@@ -6412,26 +6382,31 @@
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A258" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
-      <c r="I258" s="4"/>
-      <c r="J258" s="5"/>
-      <c r="K258" s="5"/>
-      <c r="L258" s="5"/>
-      <c r="M258" s="5"/>
-      <c r="N258" s="5"/>
+      <c r="A258" t="s">
+        <v>95</v>
+      </c>
+      <c r="G258" t="s">
+        <v>87</v>
+      </c>
+      <c r="H258" t="s">
+        <v>43</v>
+      </c>
+      <c r="J258" t="s">
+        <v>41</v>
+      </c>
+      <c r="K258" s="6">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L258" t="s">
+        <v>38</v>
+      </c>
+      <c r="M258" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="G259" t="s">
         <v>87</v>
@@ -6443,141 +6418,147 @@
         <v>41</v>
       </c>
       <c r="K259" s="6">
+        <v>20</v>
+      </c>
+      <c r="L259" t="s">
+        <v>38</v>
+      </c>
+      <c r="M259" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>267</v>
+      </c>
+      <c r="G260" t="s">
+        <v>87</v>
+      </c>
+      <c r="H260" t="s">
+        <v>43</v>
+      </c>
+      <c r="J260" t="s">
+        <v>41</v>
+      </c>
+      <c r="K260" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="L260" t="s">
+        <v>38</v>
+      </c>
+      <c r="M260" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B261" s="4"/>
+      <c r="C261" s="4"/>
+      <c r="D261" s="4"/>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4"/>
+      <c r="G261" s="4"/>
+      <c r="H261" s="4"/>
+      <c r="I261" s="4"/>
+      <c r="J261" s="5"/>
+      <c r="K261" s="5"/>
+      <c r="L261" s="5"/>
+      <c r="M261" s="5"/>
+      <c r="N261" s="5"/>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>15</v>
+      </c>
+      <c r="G262" t="s">
+        <v>87</v>
+      </c>
+      <c r="H262" t="s">
+        <v>43</v>
+      </c>
+      <c r="J262" t="s">
+        <v>41</v>
+      </c>
+      <c r="K262" s="6">
         <v>16.5</v>
       </c>
-      <c r="L259" t="s">
-        <v>38</v>
-      </c>
-      <c r="M259" s="6" t="s">
+      <c r="L262" t="s">
+        <v>38</v>
+      </c>
+      <c r="M262" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="N259" s="26" t="s">
+      <c r="N262" s="26" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A260" s="4" t="s">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
-      <c r="G260" s="4"/>
-      <c r="H260" s="4"/>
-      <c r="I260" s="4"/>
-      <c r="J260" s="5"/>
-      <c r="K260" s="5"/>
-      <c r="L260" s="5"/>
-      <c r="M260" s="5"/>
-      <c r="N260" s="5"/>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B261" t="s">
+      <c r="B263" s="4"/>
+      <c r="C263" s="4"/>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4"/>
+      <c r="G263" s="4"/>
+      <c r="H263" s="4"/>
+      <c r="I263" s="4"/>
+      <c r="J263" s="5"/>
+      <c r="K263" s="5"/>
+      <c r="L263" s="5"/>
+      <c r="M263" s="5"/>
+      <c r="N263" s="5"/>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
         <v>207</v>
       </c>
-      <c r="H261" t="s">
+      <c r="H264" t="s">
         <v>43</v>
       </c>
-      <c r="J261" t="s">
+      <c r="J264" t="s">
         <v>41</v>
       </c>
-      <c r="K261">
+      <c r="K264">
         <v>34.200000000000003</v>
       </c>
-      <c r="L261" t="s">
-        <v>38</v>
-      </c>
-      <c r="M261" t="s">
+      <c r="L264" t="s">
+        <v>38</v>
+      </c>
+      <c r="M264" t="s">
         <v>214</v>
       </c>
-      <c r="N261" s="26" t="s">
+      <c r="N264" s="26" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A262" s="4" t="s">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B262" s="4"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-      <c r="E262" s="4"/>
-      <c r="F262" s="4"/>
-      <c r="G262" s="4"/>
-      <c r="H262" s="4"/>
-      <c r="I262" s="4"/>
-      <c r="J262" s="5"/>
-      <c r="K262" s="5"/>
-      <c r="L262" s="5"/>
-      <c r="M262" s="5"/>
-      <c r="N262" s="5"/>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>126</v>
-      </c>
-      <c r="G263" t="s">
-        <v>87</v>
-      </c>
-      <c r="H263" t="s">
-        <v>43</v>
-      </c>
-      <c r="J263" t="s">
-        <v>41</v>
-      </c>
-      <c r="K263" s="23">
-        <v>1</v>
-      </c>
-      <c r="L263" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
-      <c r="H264" s="4"/>
-      <c r="I264" s="4"/>
-      <c r="J264" s="5"/>
-      <c r="K264" s="5"/>
-      <c r="L264" s="5"/>
-      <c r="M264" s="5"/>
-      <c r="N264" s="5"/>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>227</v>
-      </c>
-      <c r="H265" t="s">
-        <v>43</v>
-      </c>
-      <c r="J265" t="s">
-        <v>41</v>
-      </c>
-      <c r="K265" s="17">
-        <v>24.7</v>
-      </c>
-      <c r="L265" t="s">
-        <v>38</v>
-      </c>
-      <c r="M265" t="s">
-        <v>235</v>
-      </c>
-      <c r="N265" s="26" t="s">
-        <v>167</v>
-      </c>
+      <c r="B265" s="4"/>
+      <c r="C265" s="4"/>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="4"/>
+      <c r="G265" s="4"/>
+      <c r="H265" s="4"/>
+      <c r="I265" s="4"/>
+      <c r="J265" s="5"/>
+      <c r="K265" s="5"/>
+      <c r="L265" s="5"/>
+      <c r="M265" s="5"/>
+      <c r="N265" s="5"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>230</v>
+        <v>126</v>
+      </c>
+      <c r="G266" t="s">
+        <v>87</v>
       </c>
       <c r="H266" t="s">
         <v>43</v>
@@ -6585,45 +6566,34 @@
       <c r="J266" t="s">
         <v>41</v>
       </c>
-      <c r="K266" s="17">
-        <v>8</v>
+      <c r="K266" s="23">
+        <v>1</v>
       </c>
       <c r="L266" t="s">
         <v>38</v>
       </c>
-      <c r="M266" t="s">
-        <v>166</v>
-      </c>
-      <c r="N266" s="26" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>228</v>
-      </c>
-      <c r="H267" t="s">
-        <v>43</v>
-      </c>
-      <c r="J267" t="s">
-        <v>41</v>
-      </c>
-      <c r="K267">
-        <v>7.9</v>
-      </c>
-      <c r="L267" t="s">
-        <v>38</v>
-      </c>
-      <c r="M267" t="s">
-        <v>248</v>
-      </c>
-      <c r="N267" s="26" t="s">
-        <v>167</v>
-      </c>
+      <c r="A267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="4"/>
+      <c r="H267" s="4"/>
+      <c r="I267" s="4"/>
+      <c r="J267" s="5"/>
+      <c r="K267" s="5"/>
+      <c r="L267" s="5"/>
+      <c r="M267" s="5"/>
+      <c r="N267" s="5"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H268" t="s">
         <v>43</v>
@@ -6631,267 +6601,248 @@
       <c r="J268" t="s">
         <v>41</v>
       </c>
-      <c r="K268">
-        <v>4.7</v>
+      <c r="K268" s="17">
+        <v>24.7</v>
       </c>
       <c r="L268" t="s">
         <v>38</v>
       </c>
       <c r="M268" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N268" s="26" t="s">
         <v>167</v>
       </c>
     </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>230</v>
+      </c>
+      <c r="H269" t="s">
+        <v>43</v>
+      </c>
+      <c r="J269" t="s">
+        <v>41</v>
+      </c>
+      <c r="K269" s="17">
+        <v>8</v>
+      </c>
+      <c r="L269" t="s">
+        <v>38</v>
+      </c>
+      <c r="M269" t="s">
+        <v>166</v>
+      </c>
+      <c r="N269" s="26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>228</v>
+      </c>
+      <c r="H270" t="s">
+        <v>43</v>
+      </c>
+      <c r="J270" t="s">
+        <v>41</v>
+      </c>
+      <c r="K270">
+        <v>7.9</v>
+      </c>
+      <c r="L270" t="s">
+        <v>38</v>
+      </c>
+      <c r="M270" t="s">
+        <v>248</v>
+      </c>
+      <c r="N270" s="26" t="s">
+        <v>167</v>
+      </c>
+    </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
+      <c r="A271" t="s">
+        <v>231</v>
+      </c>
+      <c r="H271" t="s">
+        <v>43</v>
+      </c>
+      <c r="J271" t="s">
+        <v>41</v>
+      </c>
+      <c r="K271">
+        <v>4.7</v>
+      </c>
+      <c r="L271" t="s">
+        <v>38</v>
+      </c>
+      <c r="M271" t="s">
+        <v>236</v>
+      </c>
+      <c r="N271" s="26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B271" s="2"/>
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-      <c r="H271" s="2"/>
-      <c r="I271" s="2"/>
-      <c r="J271" s="3"/>
-      <c r="K271" s="3"/>
-      <c r="L271" s="3"/>
-      <c r="M271" s="3"/>
-      <c r="N271" s="3"/>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J272" s="7" t="s">
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+      <c r="H274" s="2"/>
+      <c r="I274" s="2"/>
+      <c r="J274" s="3"/>
+      <c r="K274" s="3"/>
+      <c r="L274" s="3"/>
+      <c r="M274" s="3"/>
+      <c r="N274" s="3"/>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J275" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K272" s="7">
+      <c r="K275" s="7">
         <v>0</v>
       </c>
-      <c r="L272" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M272" s="7" t="s">
+      <c r="L275" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M275" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J273" s="7" t="s">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J276" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K273" s="7">
+      <c r="K276" s="7">
         <v>0</v>
       </c>
-      <c r="L273" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M273" s="7" t="s">
+      <c r="L276" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M276" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" s="4" t="s">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B274" s="4"/>
-      <c r="C274" s="4"/>
-      <c r="D274" s="4"/>
-      <c r="E274" s="4"/>
-      <c r="F274" s="4"/>
-      <c r="G274" s="4"/>
-      <c r="H274" s="4"/>
-      <c r="I274" s="4"/>
-      <c r="J274" s="5"/>
-      <c r="K274" s="5"/>
-      <c r="L274" s="5"/>
-      <c r="M274" s="5"/>
-      <c r="N274" s="5"/>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="B277" s="4"/>
+      <c r="C277" s="4"/>
+      <c r="D277" s="4"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="4"/>
+      <c r="G277" s="4"/>
+      <c r="H277" s="4"/>
+      <c r="I277" s="4"/>
+      <c r="J277" s="5"/>
+      <c r="K277" s="5"/>
+      <c r="L277" s="5"/>
+      <c r="M277" s="5"/>
+      <c r="N277" s="5"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
         <v>179</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C278" t="s">
         <v>37</v>
       </c>
-      <c r="J275" t="s">
+      <c r="J278" t="s">
         <v>85</v>
       </c>
-      <c r="K275">
+      <c r="K278">
         <v>79</v>
       </c>
-      <c r="L275" t="s">
-        <v>38</v>
-      </c>
-      <c r="N275" t="s">
+      <c r="L278" t="s">
+        <v>38</v>
+      </c>
+      <c r="N278" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
         <v>179</v>
       </c>
-      <c r="C276" t="s">
+      <c r="C279" t="s">
         <v>37</v>
       </c>
-      <c r="F276" t="s">
+      <c r="F279" t="s">
         <v>358</v>
       </c>
-      <c r="J276" t="s">
+      <c r="J279" t="s">
         <v>86</v>
       </c>
-      <c r="K276">
+      <c r="K279">
         <f>19+2</f>
         <v>21</v>
       </c>
-      <c r="L276" t="s">
-        <v>38</v>
-      </c>
-      <c r="M276" t="s">
+      <c r="L279" t="s">
+        <v>38</v>
+      </c>
+      <c r="M279" t="s">
         <v>360</v>
       </c>
-      <c r="N276" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>184</v>
-      </c>
-      <c r="C277" t="s">
-        <v>37</v>
-      </c>
-      <c r="J277" t="s">
-        <v>85</v>
-      </c>
-      <c r="K277">
-        <v>95</v>
-      </c>
-      <c r="L277" t="s">
-        <v>38</v>
-      </c>
-      <c r="N277" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>184</v>
-      </c>
-      <c r="C278" t="s">
-        <v>37</v>
-      </c>
-      <c r="F278" t="s">
-        <v>358</v>
-      </c>
-      <c r="J278" t="s">
-        <v>86</v>
-      </c>
-      <c r="K278">
-        <v>5</v>
-      </c>
-      <c r="L278" t="s">
-        <v>38</v>
-      </c>
-      <c r="M278" t="s">
-        <v>359</v>
-      </c>
-      <c r="N278" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D279" s="8"/>
-      <c r="E279" s="8"/>
-      <c r="F279" s="8"/>
-      <c r="G279" s="8"/>
-      <c r="H279" s="8"/>
-      <c r="I279" s="8"/>
-      <c r="J279" t="s">
-        <v>85</v>
-      </c>
-      <c r="K279" s="8">
-        <v>72</v>
-      </c>
-      <c r="L279" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M279" s="8"/>
       <c r="N279" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B280" s="8"/>
-      <c r="C280" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D280" s="8"/>
-      <c r="E280" s="8"/>
-      <c r="F280" t="s">
+      <c r="A280" t="s">
+        <v>184</v>
+      </c>
+      <c r="C280" t="s">
+        <v>37</v>
+      </c>
+      <c r="J280" t="s">
+        <v>85</v>
+      </c>
+      <c r="K280">
+        <v>95</v>
+      </c>
+      <c r="L280" t="s">
+        <v>38</v>
+      </c>
+      <c r="N280" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>184</v>
+      </c>
+      <c r="C281" t="s">
+        <v>37</v>
+      </c>
+      <c r="F281" t="s">
         <v>358</v>
       </c>
-      <c r="G280" s="8"/>
-      <c r="H280" s="8"/>
-      <c r="I280" s="8"/>
-      <c r="J280" t="s">
+      <c r="J281" t="s">
         <v>86</v>
       </c>
-      <c r="K280" s="8">
-        <v>19</v>
-      </c>
-      <c r="L280" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M280" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="N280" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D281" s="8"/>
-      <c r="E281" s="8"/>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
-      <c r="H281" s="8"/>
-      <c r="I281" s="8"/>
-      <c r="J281" t="s">
-        <v>85</v>
-      </c>
-      <c r="K281" s="9">
-        <v>91</v>
-      </c>
-      <c r="L281" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M281" s="8"/>
-      <c r="N281" t="s">
-        <v>92</v>
+      <c r="K281">
+        <v>5</v>
+      </c>
+      <c r="L281" t="s">
+        <v>38</v>
+      </c>
+      <c r="M281" t="s">
+        <v>359</v>
+      </c>
+      <c r="N281" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8" t="s">
@@ -6899,123 +6850,123 @@
       </c>
       <c r="D282" s="8"/>
       <c r="E282" s="8"/>
-      <c r="F282" t="s">
-        <v>358</v>
-      </c>
+      <c r="F282" s="8"/>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
       <c r="I282" s="8"/>
       <c r="J282" t="s">
-        <v>86</v>
-      </c>
-      <c r="K282" s="9">
-        <v>9</v>
-      </c>
-      <c r="L282" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M282" s="8" t="s">
-        <v>362</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="K282" s="8">
+        <v>72</v>
+      </c>
+      <c r="L282" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M282" s="8"/>
       <c r="N282" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>181</v>
+      <c r="A283" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="B283" s="8"/>
-      <c r="C283" s="9" t="s">
-        <v>90</v>
+      <c r="C283" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D283" s="8"/>
       <c r="E283" s="8"/>
-      <c r="F283" s="8"/>
+      <c r="F283" t="s">
+        <v>358</v>
+      </c>
       <c r="G283" s="8"/>
       <c r="H283" s="8"/>
       <c r="I283" s="8"/>
       <c r="J283" t="s">
-        <v>85</v>
-      </c>
-      <c r="K283" s="9">
-        <v>80</v>
-      </c>
-      <c r="L283" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M283" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="K283" s="8">
+        <v>19</v>
+      </c>
+      <c r="L283" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M283" s="8" t="s">
+        <v>361</v>
+      </c>
       <c r="N283" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>181</v>
+      <c r="A284" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="B284" s="8"/>
-      <c r="C284" s="9" t="s">
-        <v>90</v>
+      <c r="C284" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D284" s="8"/>
       <c r="E284" s="8"/>
-      <c r="F284" t="s">
-        <v>358</v>
-      </c>
+      <c r="F284" s="8"/>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
       <c r="I284" s="8"/>
       <c r="J284" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K284" s="9">
-        <v>20</v>
-      </c>
-      <c r="L284" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M284" s="8" t="s">
-        <v>363</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="L284" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M284" s="8"/>
       <c r="N284" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>186</v>
+      <c r="A285" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="B285" s="8"/>
-      <c r="C285" s="9" t="s">
-        <v>90</v>
+      <c r="C285" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D285" s="8"/>
       <c r="E285" s="8"/>
-      <c r="F285" s="9"/>
+      <c r="F285" t="s">
+        <v>358</v>
+      </c>
       <c r="G285" s="8"/>
       <c r="H285" s="8"/>
       <c r="I285" s="8"/>
       <c r="J285" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K285" s="9">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="L285" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M285" s="8"/>
+      <c r="M285" s="8" t="s">
+        <v>362</v>
+      </c>
       <c r="N285" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D286" s="8"/>
       <c r="E286" s="8"/>
@@ -7027,7 +6978,7 @@
         <v>85</v>
       </c>
       <c r="K286" s="9">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="L286" s="9" t="s">
         <v>38</v>
@@ -7039,16 +6990,16 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B287" s="8"/>
       <c r="C287" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D287" s="8"/>
       <c r="E287" s="8"/>
       <c r="F287" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="G287" s="8"/>
       <c r="H287" s="8"/>
@@ -7057,14 +7008,13 @@
         <v>86</v>
       </c>
       <c r="K287" s="9">
-        <f>20+27</f>
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L287" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M287" s="19" t="s">
-        <v>364</v>
+      <c r="M287" s="8" t="s">
+        <v>363</v>
       </c>
       <c r="N287" t="s">
         <v>92</v>
@@ -7072,11 +7022,11 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B288" s="8"/>
       <c r="C288" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D288" s="8"/>
       <c r="E288" s="8"/>
@@ -7088,7 +7038,7 @@
         <v>85</v>
       </c>
       <c r="K288" s="9">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="L288" s="9" t="s">
         <v>38</v>
@@ -7100,7 +7050,7 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B289" s="8"/>
       <c r="C289" s="9" t="s">
@@ -7108,119 +7058,124 @@
       </c>
       <c r="D289" s="8"/>
       <c r="E289" s="8"/>
-      <c r="F289" t="s">
-        <v>365</v>
-      </c>
+      <c r="F289" s="8"/>
       <c r="G289" s="8"/>
       <c r="H289" s="8"/>
       <c r="I289" s="8"/>
       <c r="J289" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K289" s="9">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L289" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M289" s="8" t="s">
-        <v>366</v>
-      </c>
+      <c r="M289" s="8"/>
       <c r="N289" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>289</v>
-      </c>
-      <c r="B290" s="10"/>
+        <v>182</v>
+      </c>
+      <c r="B290" s="8"/>
       <c r="C290" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D290" s="10"/>
-      <c r="E290" s="10"/>
-      <c r="F290" s="10"/>
-      <c r="G290" s="10"/>
-      <c r="H290" s="10"/>
-      <c r="I290" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="D290" s="8"/>
+      <c r="E290" s="8"/>
+      <c r="F290" t="s">
+        <v>365</v>
+      </c>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="8"/>
       <c r="J290" t="s">
-        <v>85</v>
-      </c>
-      <c r="K290" s="20">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K290" s="9">
+        <f>20+27</f>
+        <v>47</v>
       </c>
       <c r="L290" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M290" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="N290" s="8"/>
+      <c r="M290" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="N290" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>290</v>
-      </c>
-      <c r="B291" s="10"/>
-      <c r="C291" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D291" s="10"/>
-      <c r="E291" s="10"/>
-      <c r="F291" s="10"/>
-      <c r="G291" s="10"/>
-      <c r="H291" s="10"/>
-      <c r="I291" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="B291" s="8"/>
+      <c r="C291" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D291" s="8"/>
+      <c r="E291" s="8"/>
+      <c r="F291" s="9"/>
+      <c r="G291" s="8"/>
+      <c r="H291" s="8"/>
+      <c r="I291" s="8"/>
       <c r="J291" t="s">
         <v>85</v>
       </c>
-      <c r="K291" s="20">
-        <v>100</v>
+      <c r="K291" s="9">
+        <v>73</v>
       </c>
       <c r="L291" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M291" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="N291" s="8"/>
+      <c r="M291" s="8"/>
+      <c r="N291" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>291</v>
-      </c>
-      <c r="B292" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="B292" s="8"/>
       <c r="C292" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D292" s="10"/>
-      <c r="E292" s="10"/>
-      <c r="F292" s="10"/>
-      <c r="G292" s="10"/>
-      <c r="H292" s="10"/>
-      <c r="I292" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="D292" s="8"/>
+      <c r="E292" s="8"/>
+      <c r="F292" t="s">
+        <v>365</v>
+      </c>
+      <c r="G292" s="8"/>
+      <c r="H292" s="8"/>
+      <c r="I292" s="8"/>
       <c r="J292" t="s">
-        <v>85</v>
-      </c>
-      <c r="K292" s="20">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="K292" s="9">
+        <v>27</v>
       </c>
       <c r="L292" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M292" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="N292" s="8"/>
+        <v>366</v>
+      </c>
+      <c r="N292" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B293" s="10"/>
       <c r="C293" s="9" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="D293" s="10"/>
       <c r="E293" s="10"/>
@@ -7243,109 +7198,114 @@
       <c r="N293" s="8"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A294" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B294" s="4"/>
-      <c r="C294" s="4"/>
-      <c r="D294" s="4"/>
-      <c r="E294" s="4"/>
-      <c r="F294" s="4"/>
-      <c r="G294" s="4"/>
-      <c r="H294" s="4"/>
-      <c r="I294" s="4"/>
-      <c r="J294" s="5"/>
-      <c r="K294" s="5"/>
-      <c r="L294" s="5"/>
-      <c r="M294" s="5"/>
-      <c r="N294" s="5"/>
+      <c r="A294" t="s">
+        <v>290</v>
+      </c>
+      <c r="B294" s="10"/>
+      <c r="C294" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D294" s="10"/>
+      <c r="E294" s="10"/>
+      <c r="F294" s="10"/>
+      <c r="G294" s="10"/>
+      <c r="H294" s="10"/>
+      <c r="I294" s="10"/>
+      <c r="J294" t="s">
+        <v>85</v>
+      </c>
+      <c r="K294" s="20">
+        <v>100</v>
+      </c>
+      <c r="L294" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M294" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N294" s="8"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A295" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B295" s="8"/>
+      <c r="A295" t="s">
+        <v>291</v>
+      </c>
+      <c r="B295" s="10"/>
       <c r="C295" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D295" s="8"/>
-      <c r="E295" s="8"/>
-      <c r="F295" s="9"/>
-      <c r="G295" s="8"/>
-      <c r="H295" s="8"/>
-      <c r="I295" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="D295" s="10"/>
+      <c r="E295" s="10"/>
+      <c r="F295" s="10"/>
+      <c r="G295" s="10"/>
+      <c r="H295" s="10"/>
+      <c r="I295" s="10"/>
       <c r="J295" t="s">
         <v>85</v>
       </c>
-      <c r="K295" s="11">
+      <c r="K295" s="20">
         <v>100</v>
       </c>
       <c r="L295" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M295" s="10" t="s">
-        <v>104</v>
-      </c>
+      <c r="M295" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N295" s="8"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A296" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B296" s="8"/>
+      <c r="A296" t="s">
+        <v>292</v>
+      </c>
+      <c r="B296" s="10"/>
       <c r="C296" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D296" s="8"/>
-      <c r="E296" s="8"/>
-      <c r="F296" s="9"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="D296" s="10"/>
+      <c r="E296" s="10"/>
+      <c r="F296" s="10"/>
+      <c r="G296" s="10"/>
+      <c r="H296" s="10"/>
+      <c r="I296" s="10"/>
       <c r="J296" t="s">
         <v>85</v>
       </c>
-      <c r="K296" s="9">
-        <v>50</v>
+      <c r="K296" s="20">
+        <v>100</v>
       </c>
       <c r="L296" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M296" s="8"/>
+      <c r="M296" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N296" s="8"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A297" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B297" s="8"/>
-      <c r="C297" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D297" s="8"/>
-      <c r="E297" s="8"/>
-      <c r="F297" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G297" s="8"/>
-      <c r="H297" s="8"/>
-      <c r="I297" s="8"/>
-      <c r="J297" t="s">
-        <v>86</v>
-      </c>
-      <c r="K297" s="9">
-        <v>50</v>
-      </c>
-      <c r="L297" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M297" s="8"/>
+      <c r="A297" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" s="4"/>
+      <c r="C297" s="4"/>
+      <c r="D297" s="4"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="4"/>
+      <c r="G297" s="4"/>
+      <c r="H297" s="4"/>
+      <c r="I297" s="4"/>
+      <c r="J297" s="5"/>
+      <c r="K297" s="5"/>
+      <c r="L297" s="5"/>
+      <c r="M297" s="5"/>
+      <c r="N297" s="5"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" s="17" t="s">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="B298" s="8"/>
-      <c r="C298" s="11" t="s">
-        <v>106</v>
+      <c r="C298" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="D298" s="8"/>
       <c r="E298" s="8"/>
@@ -7356,23 +7316,23 @@
       <c r="J298" t="s">
         <v>85</v>
       </c>
-      <c r="K298" s="18">
-        <v>20</v>
+      <c r="K298" s="11">
+        <v>100</v>
       </c>
       <c r="L298" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M298" s="10" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B299" s="8"/>
       <c r="C299" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D299" s="8"/>
       <c r="E299" s="8"/>
@@ -7383,26 +7343,26 @@
       <c r="J299" t="s">
         <v>85</v>
       </c>
-      <c r="K299" s="18">
-        <v>19</v>
+      <c r="K299" s="9">
+        <v>50</v>
       </c>
       <c r="L299" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M299" s="19"/>
+      <c r="M299" s="8"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B300" s="8"/>
       <c r="C300" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D300" s="8"/>
       <c r="E300" s="8"/>
-      <c r="F300" t="s">
-        <v>191</v>
+      <c r="F300" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G300" s="8"/>
       <c r="H300" s="8"/>
@@ -7410,95 +7370,123 @@
       <c r="J300" t="s">
         <v>86</v>
       </c>
-      <c r="K300" s="28">
+      <c r="K300" s="9">
+        <v>50</v>
+      </c>
+      <c r="L300" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M300" s="8"/>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A301" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B301" s="8"/>
+      <c r="C301" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D301" s="8"/>
+      <c r="E301" s="8"/>
+      <c r="F301" s="9"/>
+      <c r="G301" s="8"/>
+      <c r="H301" s="8"/>
+      <c r="I301" s="8"/>
+      <c r="J301" t="s">
+        <v>85</v>
+      </c>
+      <c r="K301" s="18">
+        <v>20</v>
+      </c>
+      <c r="L301" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M301" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A302" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B302" s="8"/>
+      <c r="C302" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D302" s="8"/>
+      <c r="E302" s="8"/>
+      <c r="F302" s="9"/>
+      <c r="G302" s="8"/>
+      <c r="H302" s="8"/>
+      <c r="I302" s="8"/>
+      <c r="J302" t="s">
+        <v>85</v>
+      </c>
+      <c r="K302" s="18">
+        <v>19</v>
+      </c>
+      <c r="L302" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M302" s="19"/>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A303" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B303" s="8"/>
+      <c r="C303" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D303" s="8"/>
+      <c r="E303" s="8"/>
+      <c r="F303" t="s">
+        <v>191</v>
+      </c>
+      <c r="G303" s="8"/>
+      <c r="H303" s="8"/>
+      <c r="I303" s="8"/>
+      <c r="J303" t="s">
+        <v>86</v>
+      </c>
+      <c r="K303" s="28">
         <f>0.02*0.5*100/(844/1000)/0.9</f>
         <v>1.3164823591363877</v>
       </c>
-      <c r="L300" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M300" s="19" t="s">
+      <c r="L303" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M303" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="N300" s="9" t="s">
+      <c r="N303" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A301" s="4" t="s">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B301" s="4"/>
-      <c r="C301" s="4"/>
-      <c r="D301" s="4"/>
-      <c r="E301" s="4"/>
-      <c r="F301" s="4"/>
-      <c r="G301" s="4"/>
-      <c r="H301" s="4"/>
-      <c r="I301" s="4"/>
-      <c r="J301" s="5"/>
-      <c r="K301" s="5"/>
-      <c r="L301" s="5"/>
-      <c r="M301" s="5"/>
-      <c r="N301" s="5"/>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A302" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C302" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="J302" t="s">
-        <v>85</v>
-      </c>
-      <c r="K302" s="18">
-        <v>100</v>
-      </c>
-      <c r="L302" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A303" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C303" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J303" t="s">
-        <v>85</v>
-      </c>
-      <c r="K303" s="18">
-        <v>100</v>
-      </c>
-      <c r="L303" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A304" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C304" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="J304" t="s">
-        <v>85</v>
-      </c>
-      <c r="K304" s="18">
-        <v>100</v>
-      </c>
-      <c r="L304" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="B304" s="4"/>
+      <c r="C304" s="4"/>
+      <c r="D304" s="4"/>
+      <c r="E304" s="4"/>
+      <c r="F304" s="4"/>
+      <c r="G304" s="4"/>
+      <c r="H304" s="4"/>
+      <c r="I304" s="4"/>
+      <c r="J304" s="5"/>
+      <c r="K304" s="5"/>
+      <c r="L304" s="5"/>
+      <c r="M304" s="5"/>
+      <c r="N304" s="5"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="J305" t="s">
         <v>85</v>
@@ -7512,10 +7500,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J306" t="s">
         <v>85</v>
@@ -7529,10 +7517,10 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J307" t="s">
         <v>85</v>
@@ -7546,18 +7534,11 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B308" s="8"/>
+        <v>138</v>
+      </c>
       <c r="C308" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D308" s="8"/>
-      <c r="E308" s="8"/>
-      <c r="F308" s="9"/>
-      <c r="G308" s="8"/>
-      <c r="H308" s="8"/>
-      <c r="I308" s="8"/>
+        <v>144</v>
+      </c>
       <c r="J308" t="s">
         <v>85</v>
       </c>
@@ -7567,22 +7548,14 @@
       <c r="L308" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M308" s="10"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B309" s="8"/>
+        <v>139</v>
+      </c>
       <c r="C309" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D309" s="8"/>
-      <c r="E309" s="8"/>
-      <c r="F309" s="9"/>
-      <c r="G309" s="8"/>
-      <c r="H309" s="8"/>
-      <c r="I309" s="8"/>
+        <v>145</v>
+      </c>
       <c r="J309" t="s">
         <v>85</v>
       </c>
@@ -7592,22 +7565,14 @@
       <c r="L309" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M309" s="10"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B310" s="8"/>
+        <v>140</v>
+      </c>
       <c r="C310" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D310" s="8"/>
-      <c r="E310" s="8"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="8"/>
-      <c r="H310" s="8"/>
-      <c r="I310" s="8"/>
+        <v>142</v>
+      </c>
       <c r="J310" t="s">
         <v>85</v>
       </c>
@@ -7617,89 +7582,103 @@
       <c r="L310" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M310" s="10"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B311" s="4"/>
-      <c r="C311" s="4"/>
-      <c r="D311" s="4"/>
-      <c r="E311" s="4"/>
-      <c r="F311" s="4"/>
-      <c r="G311" s="4"/>
-      <c r="H311" s="4"/>
-      <c r="I311" s="4"/>
-      <c r="J311" s="5"/>
-      <c r="K311" s="5"/>
-      <c r="L311" s="5"/>
-      <c r="M311" s="5"/>
-      <c r="N311" s="5"/>
+      <c r="A311" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B311" s="8"/>
+      <c r="C311" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D311" s="8"/>
+      <c r="E311" s="8"/>
+      <c r="F311" s="9"/>
+      <c r="G311" s="8"/>
+      <c r="H311" s="8"/>
+      <c r="I311" s="8"/>
+      <c r="J311" t="s">
+        <v>85</v>
+      </c>
+      <c r="K311" s="18">
+        <v>100</v>
+      </c>
+      <c r="L311" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M311" s="10"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="17" t="s">
-        <v>241</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B312" s="8"/>
       <c r="C312" s="9" t="s">
-        <v>238</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D312" s="8"/>
+      <c r="E312" s="8"/>
+      <c r="F312" s="9"/>
+      <c r="G312" s="8"/>
+      <c r="H312" s="8"/>
+      <c r="I312" s="8"/>
       <c r="J312" t="s">
         <v>85</v>
       </c>
-      <c r="K312" s="17">
+      <c r="K312" s="18">
         <v>100</v>
       </c>
       <c r="L312" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="M312" s="10"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="17" t="s">
-        <v>242</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B313" s="8"/>
       <c r="C313" s="9" t="s">
-        <v>238</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="D313" s="8"/>
+      <c r="E313" s="8"/>
+      <c r="F313" s="9"/>
+      <c r="G313" s="8"/>
+      <c r="H313" s="8"/>
+      <c r="I313" s="8"/>
       <c r="J313" t="s">
         <v>85</v>
       </c>
-      <c r="K313" s="17">
-        <v>65</v>
+      <c r="K313" s="18">
+        <v>100</v>
       </c>
       <c r="L313" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N313" t="s">
-        <v>92</v>
-      </c>
+      <c r="M313" s="10"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A314" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="C314" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F314" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="J314" t="s">
-        <v>86</v>
-      </c>
-      <c r="K314" s="17">
-        <v>35</v>
-      </c>
-      <c r="L314" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="N314" t="s">
-        <v>92</v>
-      </c>
+      <c r="A314" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B314" s="4"/>
+      <c r="C314" s="4"/>
+      <c r="D314" s="4"/>
+      <c r="E314" s="4"/>
+      <c r="F314" s="4"/>
+      <c r="G314" s="4"/>
+      <c r="H314" s="4"/>
+      <c r="I314" s="4"/>
+      <c r="J314" s="5"/>
+      <c r="K314" s="5"/>
+      <c r="L314" s="5"/>
+      <c r="M314" s="5"/>
+      <c r="N314" s="5"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C315" s="9" t="s">
         <v>238</v>
@@ -7708,30 +7687,24 @@
         <v>85</v>
       </c>
       <c r="K315" s="17">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="L315" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="N315" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C316" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F316" s="19" t="s">
-        <v>239</v>
-      </c>
       <c r="J316" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K316" s="17">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="L316" s="17" t="s">
         <v>38</v>
@@ -7742,61 +7715,76 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" s="17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
+      </c>
+      <c r="F317" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="J317" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K317" s="17">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L317" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="N317" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="17" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="J318" t="s">
         <v>85</v>
       </c>
       <c r="K318" s="17">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="L318" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="N318" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="17" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>260</v>
+        <v>238</v>
+      </c>
+      <c r="F319" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="J319" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K319" s="17">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L319" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="N319" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="17" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="J320" t="s">
         <v>85</v>
@@ -7810,10 +7798,10 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J321" t="s">
         <v>85</v>
@@ -7826,124 +7814,77 @@
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B322" s="4"/>
-      <c r="C322" s="4"/>
-      <c r="D322" s="4"/>
-      <c r="E322" s="4"/>
-      <c r="F322" s="4"/>
-      <c r="G322" s="4"/>
-      <c r="H322" s="4"/>
-      <c r="I322" s="4"/>
-      <c r="J322" s="5"/>
-      <c r="K322" s="5"/>
-      <c r="L322" s="5"/>
-      <c r="M322" s="5"/>
-      <c r="N322" s="5"/>
+      <c r="A322" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C322" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J322" t="s">
+        <v>85</v>
+      </c>
+      <c r="K322" s="17">
+        <v>100</v>
+      </c>
+      <c r="L322" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B323" s="10"/>
-      <c r="C323" s="10"/>
-      <c r="D323" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E323" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F323" s="10"/>
-      <c r="G323" s="10"/>
-      <c r="H323" s="10"/>
-      <c r="I323" s="10"/>
+      <c r="A323" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C323" s="9" t="s">
+        <v>262</v>
+      </c>
       <c r="J323" t="s">
         <v>85</v>
       </c>
-      <c r="K323" s="12">
-        <f>100-K324</f>
-        <v>90.75</v>
-      </c>
-      <c r="L323" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M323" t="s">
-        <v>71</v>
-      </c>
-      <c r="N323" s="8" t="s">
-        <v>93</v>
+      <c r="K323" s="17">
+        <v>100</v>
+      </c>
+      <c r="L323" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A324" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B324" s="10"/>
-      <c r="C324" s="10"/>
-      <c r="D324" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E324" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F324" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G324" s="10"/>
-      <c r="H324" s="10"/>
-      <c r="I324" s="10"/>
+      <c r="A324" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="C324" s="9" t="s">
+        <v>263</v>
+      </c>
       <c r="J324" t="s">
-        <v>86</v>
-      </c>
-      <c r="K324" s="12">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
-      </c>
-      <c r="L324" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N324" s="8" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="K324" s="17">
+        <v>100</v>
+      </c>
+      <c r="L324" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A325" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B325" s="10"/>
-      <c r="C325" s="10"/>
-      <c r="D325" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E325" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F325" s="10"/>
-      <c r="G325" s="10"/>
-      <c r="H325" s="10"/>
-      <c r="I325" s="10"/>
-      <c r="J325" t="s">
-        <v>85</v>
-      </c>
-      <c r="K325" s="12">
-        <f>100-K326</f>
-        <v>93.25</v>
-      </c>
-      <c r="L325" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M325" t="s">
-        <v>72</v>
-      </c>
-      <c r="N325" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="A325" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" s="4"/>
+      <c r="C325" s="4"/>
+      <c r="D325" s="4"/>
+      <c r="E325" s="4"/>
+      <c r="F325" s="4"/>
+      <c r="G325" s="4"/>
+      <c r="H325" s="4"/>
+      <c r="I325" s="4"/>
+      <c r="J325" s="5"/>
+      <c r="K325" s="5"/>
+      <c r="L325" s="5"/>
+      <c r="M325" s="5"/>
+      <c r="N325" s="5"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B326" s="10"/>
       <c r="C326" s="10"/>
@@ -7953,21 +7894,22 @@
       <c r="E326" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F326" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="F326" s="10"/>
       <c r="G326" s="10"/>
       <c r="H326" s="10"/>
       <c r="I326" s="10"/>
       <c r="J326" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K326" s="12">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>100-K327</f>
+        <v>90.75</v>
       </c>
       <c r="L326" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M326" t="s">
+        <v>71</v>
       </c>
       <c r="N326" s="8" t="s">
         <v>93</v>
@@ -7975,7 +7917,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B327" s="10"/>
       <c r="C327" s="10"/>
@@ -7985,22 +7927,21 @@
       <c r="E327" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F327" s="10"/>
+      <c r="F327" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="G327" s="10"/>
       <c r="H327" s="10"/>
       <c r="I327" s="10"/>
       <c r="J327" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K327" s="12">
-        <f>100-K328</f>
-        <v>97</v>
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="L327" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M327" t="s">
-        <v>73</v>
       </c>
       <c r="N327" s="8" t="s">
         <v>93</v>
@@ -8008,7 +7949,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B328" s="10"/>
       <c r="C328" s="10"/>
@@ -8018,21 +7959,22 @@
       <c r="E328" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F328" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="F328" s="10"/>
       <c r="G328" s="10"/>
       <c r="H328" s="10"/>
       <c r="I328" s="10"/>
       <c r="J328" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K328" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
+        <f>100-K329</f>
+        <v>93.25</v>
       </c>
       <c r="L328" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M328" t="s">
+        <v>72</v>
       </c>
       <c r="N328" s="8" t="s">
         <v>93</v>
@@ -8040,7 +7982,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B329" s="10"/>
       <c r="C329" s="10"/>
@@ -8050,22 +7992,21 @@
       <c r="E329" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F329" s="10"/>
+      <c r="F329" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="G329" s="10"/>
       <c r="H329" s="10"/>
       <c r="I329" s="10"/>
       <c r="J329" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K329" s="12">
-        <f>(100-K330)*0.1</f>
-        <v>9.7000000000000011</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="L329" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M329" t="s">
-        <v>80</v>
       </c>
       <c r="N329" s="8" t="s">
         <v>93</v>
@@ -8073,7 +8014,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B330" s="10"/>
       <c r="C330" s="10"/>
@@ -8083,21 +8024,22 @@
       <c r="E330" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F330" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="F330" s="10"/>
       <c r="G330" s="10"/>
       <c r="H330" s="10"/>
       <c r="I330" s="10"/>
       <c r="J330" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K330" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
+        <f>100-K331</f>
+        <v>97</v>
       </c>
       <c r="L330" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="M330" t="s">
+        <v>73</v>
       </c>
       <c r="N330" s="8" t="s">
         <v>93</v>
@@ -8105,7 +8047,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B331" s="10"/>
       <c r="C331" s="10"/>
@@ -8116,7 +8058,7 @@
         <v>59</v>
       </c>
       <c r="F331" s="10" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G331" s="10"/>
       <c r="H331" s="10"/>
@@ -8125,8 +8067,8 @@
         <v>86</v>
       </c>
       <c r="K331" s="12">
-        <f>(100-K330)*0.9</f>
-        <v>87.3</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="L331" s="10" t="s">
         <v>38</v>
@@ -8137,7 +8079,7 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B332" s="10"/>
       <c r="C332" s="10"/>
@@ -8145,7 +8087,7 @@
         <v>79</v>
       </c>
       <c r="E332" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F332" s="10"/>
       <c r="G332" s="10"/>
@@ -8154,23 +8096,23 @@
       <c r="J332" t="s">
         <v>85</v>
       </c>
-      <c r="K332" s="10">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+      <c r="K332" s="12">
+        <f>(100-K333)*0.1</f>
+        <v>9.7000000000000011</v>
       </c>
       <c r="L332" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M332" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N332" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" s="11" t="s">
-        <v>69</v>
+      <c r="A333" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="B333" s="10"/>
       <c r="C333" s="10"/>
@@ -8178,24 +8120,23 @@
         <v>79</v>
       </c>
       <c r="E333" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F333" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F333" s="10"/>
       <c r="G333" s="10"/>
       <c r="H333" s="10"/>
       <c r="I333" s="10"/>
       <c r="J333" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K333" s="12">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="L333" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M333" t="s">
-        <v>74</v>
       </c>
       <c r="N333" s="8" t="s">
         <v>93</v>
@@ -8203,7 +8144,7 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B334" s="10"/>
       <c r="C334" s="10"/>
@@ -8211,24 +8152,23 @@
         <v>79</v>
       </c>
       <c r="E334" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F334" s="10"/>
+        <v>59</v>
+      </c>
+      <c r="F334" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="G334" s="10"/>
       <c r="H334" s="10"/>
       <c r="I334" s="10"/>
       <c r="J334" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K334" s="12">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>(100-K333)*0.9</f>
+        <v>87.3</v>
       </c>
       <c r="L334" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="M334" t="s">
-        <v>75</v>
       </c>
       <c r="N334" s="8" t="s">
         <v>93</v>
@@ -8236,7 +8176,7 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B335" s="10"/>
       <c r="C335" s="10"/>
@@ -8254,22 +8194,22 @@
         <v>85</v>
       </c>
       <c r="K335" s="10">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
       </c>
       <c r="L335" s="10" t="s">
         <v>38</v>
       </c>
       <c r="M335" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N335" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A336" s="10" t="s">
-        <v>65</v>
+      <c r="A336" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="B336" s="10"/>
       <c r="C336" s="10"/>
@@ -8287,118 +8227,132 @@
         <v>85</v>
       </c>
       <c r="K336" s="12">
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
+      </c>
+      <c r="L336" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M336" t="s">
+        <v>74</v>
+      </c>
+      <c r="N336" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A337" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B337" s="10"/>
+      <c r="C337" s="10"/>
+      <c r="D337" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E337" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F337" s="10"/>
+      <c r="G337" s="10"/>
+      <c r="H337" s="10"/>
+      <c r="I337" s="10"/>
+      <c r="J337" t="s">
+        <v>85</v>
+      </c>
+      <c r="K337" s="12">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
+      </c>
+      <c r="L337" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M337" t="s">
+        <v>75</v>
+      </c>
+      <c r="N337" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A338" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B338" s="10"/>
+      <c r="C338" s="10"/>
+      <c r="D338" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E338" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F338" s="10"/>
+      <c r="G338" s="10"/>
+      <c r="H338" s="10"/>
+      <c r="I338" s="10"/>
+      <c r="J338" t="s">
+        <v>85</v>
+      </c>
+      <c r="K338" s="10">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
+      </c>
+      <c r="L338" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M338" t="s">
+        <v>76</v>
+      </c>
+      <c r="N338" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A339" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B339" s="10"/>
+      <c r="C339" s="10"/>
+      <c r="D339" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E339" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F339" s="10"/>
+      <c r="G339" s="10"/>
+      <c r="H339" s="10"/>
+      <c r="I339" s="10"/>
+      <c r="J339" t="s">
+        <v>85</v>
+      </c>
+      <c r="K339" s="12">
         <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
         <v>49.367088607594937</v>
       </c>
-      <c r="L336" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M336" t="s">
+      <c r="L339" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M339" t="s">
         <v>77</v>
       </c>
-      <c r="N336" s="8" t="s">
+      <c r="N339" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A337" s="10" t="s">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A340" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B337" s="8"/>
-      <c r="C337" s="8"/>
-      <c r="D337" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E337" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F337" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G337" s="8"/>
-      <c r="H337" s="8"/>
-      <c r="I337" s="8"/>
-      <c r="J337" t="s">
-        <v>86</v>
-      </c>
-      <c r="K337" s="14">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
-      </c>
-      <c r="L337" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M337" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N337" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B338" s="4"/>
-      <c r="C338" s="4"/>
-      <c r="D338" s="4"/>
-      <c r="E338" s="4"/>
-      <c r="F338" s="4"/>
-      <c r="G338" s="4"/>
-      <c r="H338" s="4"/>
-      <c r="I338" s="4"/>
-      <c r="J338" s="5"/>
-      <c r="K338" s="5"/>
-      <c r="L338" s="5"/>
-      <c r="M338" s="5"/>
-      <c r="N338" s="5"/>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A339" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B339" s="8"/>
-      <c r="C339" s="8"/>
-      <c r="D339" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E339" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F339" s="8"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
-      <c r="I339" s="8"/>
-      <c r="J339" t="s">
-        <v>85</v>
-      </c>
-      <c r="K339" s="11">
-        <v>73.5</v>
-      </c>
-      <c r="L339" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M339" s="46" t="s">
-        <v>368</v>
-      </c>
-      <c r="N339" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="B340" s="8"/>
       <c r="C340" s="8"/>
-      <c r="D340" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E340" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F340" s="8" t="s">
-        <v>117</v>
+      <c r="D340" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E340" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F340" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
@@ -8406,54 +8360,37 @@
       <c r="J340" t="s">
         <v>86</v>
       </c>
-      <c r="K340" s="16">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="L340" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M340" s="9" t="s">
-        <v>96</v>
+      <c r="K340" s="14">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="L340" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M340" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="N340" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A341" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B341" s="8"/>
-      <c r="C341" s="8"/>
-      <c r="D341" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E341" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F341" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G341" s="8"/>
-      <c r="H341" s="8"/>
-      <c r="I341" s="8"/>
-      <c r="J341" t="s">
-        <v>86</v>
-      </c>
-      <c r="K341" s="16">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
-      </c>
-      <c r="L341" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M341" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="N341" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="A341" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B341" s="4"/>
+      <c r="C341" s="4"/>
+      <c r="D341" s="4"/>
+      <c r="E341" s="4"/>
+      <c r="F341" s="4"/>
+      <c r="G341" s="4"/>
+      <c r="H341" s="4"/>
+      <c r="I341" s="4"/>
+      <c r="J341" s="5"/>
+      <c r="K341" s="5"/>
+      <c r="L341" s="5"/>
+      <c r="M341" s="5"/>
+      <c r="N341" s="5"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
@@ -8467,24 +8404,21 @@
       <c r="E342" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F342" s="8" t="s">
-        <v>119</v>
-      </c>
+      <c r="F342" s="8"/>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
       <c r="I342" s="8"/>
       <c r="J342" t="s">
-        <v>86</v>
-      </c>
-      <c r="K342" s="16">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
+        <v>85</v>
+      </c>
+      <c r="K342" s="11">
+        <v>73.5</v>
       </c>
       <c r="L342" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M342" s="9" t="s">
-        <v>96</v>
+      <c r="M342" s="46" t="s">
+        <v>368</v>
       </c>
       <c r="N342" s="8" t="s">
         <v>92</v>
@@ -8503,7 +8437,7 @@
         <v>55</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
@@ -8511,63 +8445,69 @@
       <c r="J343" t="s">
         <v>86</v>
       </c>
-      <c r="K343" s="9">
-        <v>18</v>
+      <c r="K343" s="16">
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="L343" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M343" s="8"/>
+      <c r="M343" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="N343" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>95</v>
+      <c r="A344" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
-      <c r="D344" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E344" s="9" t="s">
+      <c r="D344" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E344" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F344" s="8"/>
+      <c r="F344" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="G344" s="8"/>
       <c r="H344" s="8"/>
       <c r="I344" s="8"/>
       <c r="J344" t="s">
-        <v>85</v>
-      </c>
-      <c r="K344" s="11">
-        <v>77.7</v>
-      </c>
-      <c r="L344" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K344" s="16">
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
+      </c>
+      <c r="L344" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M344" s="9" t="s">
-        <v>369</v>
+        <v>96</v>
       </c>
       <c r="N344" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>95</v>
+      <c r="A345" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B345" s="8"/>
       <c r="C345" s="8"/>
-      <c r="D345" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E345" s="9" t="s">
+      <c r="D345" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E345" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F345" s="9" t="s">
-        <v>121</v>
+      <c r="F345" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="G345" s="8"/>
       <c r="H345" s="8"/>
@@ -8576,33 +8516,33 @@
         <v>86</v>
       </c>
       <c r="K345" s="16">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
-      </c>
-      <c r="L345" s="9" t="s">
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
+      </c>
+      <c r="L345" s="8" t="s">
         <v>38</v>
       </c>
       <c r="M345" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N345" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>95</v>
+      <c r="A346" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B346" s="8"/>
       <c r="C346" s="8"/>
-      <c r="D346" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E346" s="9" t="s">
+      <c r="D346" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E346" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F346" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G346" s="8"/>
       <c r="H346" s="8"/>
@@ -8610,16 +8550,13 @@
       <c r="J346" t="s">
         <v>86</v>
       </c>
-      <c r="K346" s="16">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
-      </c>
-      <c r="L346" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M346" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="K346" s="9">
+        <v>18</v>
+      </c>
+      <c r="L346" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M346" s="8"/>
       <c r="N346" s="8" t="s">
         <v>92</v>
       </c>
@@ -8636,24 +8573,21 @@
       <c r="E347" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F347" s="9" t="s">
-        <v>123</v>
-      </c>
+      <c r="F347" s="8"/>
       <c r="G347" s="8"/>
       <c r="H347" s="8"/>
       <c r="I347" s="8"/>
       <c r="J347" t="s">
-        <v>86</v>
-      </c>
-      <c r="K347" s="16">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
+        <v>85</v>
+      </c>
+      <c r="K347" s="11">
+        <v>77.7</v>
       </c>
       <c r="L347" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M347" s="9" t="s">
-        <v>97</v>
+        <v>369</v>
       </c>
       <c r="N347" s="8" t="s">
         <v>92</v>
@@ -8671,8 +8605,8 @@
       <c r="E348" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F348" s="8" t="s">
-        <v>124</v>
+      <c r="F348" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="G348" s="8"/>
       <c r="H348" s="8"/>
@@ -8680,98 +8614,104 @@
       <c r="J348" t="s">
         <v>86</v>
       </c>
-      <c r="K348" s="9">
-        <v>12</v>
+      <c r="K348" s="16">
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
       </c>
       <c r="L348" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M348" s="8"/>
+      <c r="M348" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="N348" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>346</v>
+        <v>95</v>
       </c>
       <c r="B349" s="8"/>
       <c r="C349" s="8"/>
       <c r="D349" s="9" t="s">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="E349" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F349" s="8"/>
+      <c r="F349" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G349" s="8"/>
       <c r="H349" s="8"/>
       <c r="I349" s="8"/>
       <c r="J349" t="s">
-        <v>85</v>
-      </c>
-      <c r="K349" s="11">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="K349" s="16">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
       </c>
       <c r="L349" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M349" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="N349" s="26" t="s">
-        <v>350</v>
+        <v>97</v>
+      </c>
+      <c r="N349" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>346</v>
+        <v>95</v>
       </c>
       <c r="B350" s="8"/>
       <c r="C350" s="8"/>
       <c r="D350" s="9" t="s">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="E350" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F350" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="G350" s="26"/>
-      <c r="H350" s="26"/>
-      <c r="I350" s="26"/>
+      <c r="F350" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G350" s="8"/>
+      <c r="H350" s="8"/>
+      <c r="I350" s="8"/>
       <c r="J350" t="s">
         <v>86</v>
       </c>
       <c r="K350" s="16">
-        <f>(1/0.5)*8</f>
-        <v>16</v>
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
       </c>
       <c r="L350" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M350" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="N350" s="26" t="s">
-        <v>350</v>
+        <v>97</v>
+      </c>
+      <c r="N350" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>346</v>
+        <v>95</v>
       </c>
       <c r="B351" s="8"/>
       <c r="C351" s="8"/>
       <c r="D351" s="9" t="s">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="E351" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F351" s="26" t="s">
-        <v>352</v>
+      <c r="F351" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="G351" s="8"/>
       <c r="H351" s="8"/>
@@ -8779,18 +8719,15 @@
       <c r="J351" t="s">
         <v>86</v>
       </c>
-      <c r="K351" s="16">
-        <f>(1/0.5)*3</f>
-        <v>6</v>
+      <c r="K351" s="9">
+        <v>12</v>
       </c>
       <c r="L351" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M351" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="N351" s="26" t="s">
-        <v>350</v>
+      <c r="M351" s="8"/>
+      <c r="N351" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
@@ -8805,24 +8742,21 @@
       <c r="E352" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F352" s="26" t="s">
-        <v>351</v>
-      </c>
+      <c r="F352" s="8"/>
       <c r="G352" s="8"/>
       <c r="H352" s="8"/>
       <c r="I352" s="8"/>
       <c r="J352" t="s">
-        <v>86</v>
-      </c>
-      <c r="K352" s="9">
-        <f>(1/0.5)*8</f>
-        <v>16</v>
+        <v>85</v>
+      </c>
+      <c r="K352" s="11">
+        <v>69</v>
       </c>
       <c r="L352" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M352" s="9" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="N352" s="26" t="s">
         <v>350</v>
@@ -8830,80 +8764,112 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="B353" s="8"/>
       <c r="C353" s="8"/>
       <c r="D353" s="9" t="s">
-        <v>268</v>
+        <v>349</v>
       </c>
       <c r="E353" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F353" s="8"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
-      <c r="I353" s="8"/>
+      <c r="F353" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="G353" s="26"/>
+      <c r="H353" s="26"/>
+      <c r="I353" s="26"/>
       <c r="J353" t="s">
-        <v>85</v>
-      </c>
-      <c r="K353" s="11">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="K353" s="16">
+        <f>(1/0.5)*8</f>
+        <v>16</v>
       </c>
       <c r="L353" s="9" t="s">
         <v>38</v>
       </c>
       <c r="M353" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="N353" s="47" t="s">
-        <v>370</v>
+        <v>354</v>
+      </c>
+      <c r="N353" s="26" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B354" s="10"/>
-      <c r="C354" s="10"/>
-      <c r="D354" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E354" s="11" t="s">
+      <c r="A354" t="s">
+        <v>346</v>
+      </c>
+      <c r="B354" s="8"/>
+      <c r="C354" s="8"/>
+      <c r="D354" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E354" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F354" s="11" t="s">
-        <v>269</v>
+      <c r="F354" s="26" t="s">
+        <v>352</v>
       </c>
       <c r="G354" s="8"/>
       <c r="H354" s="8"/>
       <c r="I354" s="8"/>
-      <c r="K354" s="9"/>
-      <c r="L354" s="9"/>
-      <c r="M354" s="8"/>
-      <c r="N354" s="8"/>
+      <c r="J354" t="s">
+        <v>86</v>
+      </c>
+      <c r="K354" s="16">
+        <f>(1/0.5)*3</f>
+        <v>6</v>
+      </c>
+      <c r="L354" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M354" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="N354" s="26" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A355" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B355" s="4"/>
-      <c r="C355" s="4"/>
-      <c r="D355" s="4"/>
-      <c r="E355" s="4"/>
-      <c r="F355" s="4"/>
-      <c r="G355" s="4"/>
-      <c r="H355" s="4"/>
-      <c r="I355" s="4"/>
-      <c r="J355" s="5"/>
-      <c r="K355" s="5"/>
-      <c r="L355" s="5"/>
-      <c r="M355" s="5"/>
-      <c r="N355" s="5"/>
+      <c r="A355" t="s">
+        <v>346</v>
+      </c>
+      <c r="B355" s="8"/>
+      <c r="C355" s="8"/>
+      <c r="D355" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E355" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F355" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="G355" s="8"/>
+      <c r="H355" s="8"/>
+      <c r="I355" s="8"/>
+      <c r="J355" t="s">
+        <v>86</v>
+      </c>
+      <c r="K355" s="9">
+        <f>(1/0.5)*8</f>
+        <v>16</v>
+      </c>
+      <c r="L355" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M355" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="N355" s="26" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="B356" s="8"/>
       <c r="C356" s="8"/>
@@ -8911,7 +8877,7 @@
         <v>268</v>
       </c>
       <c r="E356" s="9" t="s">
-        <v>325</v>
+        <v>55</v>
       </c>
       <c r="F356" s="8"/>
       <c r="G356" s="8"/>
@@ -8920,195 +8886,194 @@
       <c r="J356" t="s">
         <v>85</v>
       </c>
-      <c r="K356" s="9">
-        <v>100</v>
+      <c r="K356" s="11">
+        <v>90</v>
       </c>
       <c r="L356" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M356" s="8"/>
-      <c r="N356" s="8"/>
+      <c r="M356" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="N356" s="47" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A357" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B357" s="4"/>
-      <c r="C357" s="4"/>
-      <c r="D357" s="4"/>
-      <c r="E357" s="4"/>
-      <c r="F357" s="4"/>
-      <c r="G357" s="4"/>
-      <c r="H357" s="4"/>
-      <c r="I357" s="4"/>
-      <c r="J357" s="5"/>
-      <c r="K357" s="5"/>
-      <c r="L357" s="5"/>
-      <c r="M357" s="5"/>
-      <c r="N357" s="5"/>
+      <c r="A357" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B357" s="10"/>
+      <c r="C357" s="10"/>
+      <c r="D357" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E357" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F357" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G357" s="8"/>
+      <c r="H357" s="8"/>
+      <c r="I357" s="8"/>
+      <c r="K357" s="9"/>
+      <c r="L357" s="9"/>
+      <c r="M357" s="8"/>
+      <c r="N357" s="8"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>202</v>
-      </c>
-      <c r="C358" t="s">
-        <v>211</v>
-      </c>
-      <c r="J358" t="s">
-        <v>85</v>
-      </c>
-      <c r="K358">
-        <v>100</v>
-      </c>
-      <c r="L358" t="s">
-        <v>38</v>
-      </c>
+      <c r="A358" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B358" s="4"/>
+      <c r="C358" s="4"/>
+      <c r="D358" s="4"/>
+      <c r="E358" s="4"/>
+      <c r="F358" s="4"/>
+      <c r="G358" s="4"/>
+      <c r="H358" s="4"/>
+      <c r="I358" s="4"/>
+      <c r="J358" s="5"/>
+      <c r="K358" s="5"/>
+      <c r="L358" s="5"/>
+      <c r="M358" s="5"/>
+      <c r="N358" s="5"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A359" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C359" t="s">
-        <v>212</v>
-      </c>
+      <c r="A359" t="s">
+        <v>15</v>
+      </c>
+      <c r="B359" s="8"/>
+      <c r="C359" s="8"/>
+      <c r="D359" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E359" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F359" s="8"/>
+      <c r="G359" s="8"/>
+      <c r="H359" s="8"/>
+      <c r="I359" s="8"/>
       <c r="J359" t="s">
         <v>85</v>
       </c>
-      <c r="K359">
+      <c r="K359" s="9">
         <v>100</v>
       </c>
-      <c r="L359" t="s">
-        <v>38</v>
-      </c>
+      <c r="L359" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M359" s="8"/>
+      <c r="N359" s="8"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A360" s="26" t="s">
+      <c r="A360" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B360" s="4"/>
+      <c r="C360" s="4"/>
+      <c r="D360" s="4"/>
+      <c r="E360" s="4"/>
+      <c r="F360" s="4"/>
+      <c r="G360" s="4"/>
+      <c r="H360" s="4"/>
+      <c r="I360" s="4"/>
+      <c r="J360" s="5"/>
+      <c r="K360" s="5"/>
+      <c r="L360" s="5"/>
+      <c r="M360" s="5"/>
+      <c r="N360" s="5"/>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>202</v>
+      </c>
+      <c r="C361" t="s">
+        <v>211</v>
+      </c>
+      <c r="J361" t="s">
+        <v>85</v>
+      </c>
+      <c r="K361">
+        <v>100</v>
+      </c>
+      <c r="L361" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C362" t="s">
+        <v>212</v>
+      </c>
+      <c r="J362" t="s">
+        <v>85</v>
+      </c>
+      <c r="K362">
+        <v>100</v>
+      </c>
+      <c r="L362" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C360" t="s">
+      <c r="C363" t="s">
         <v>213</v>
       </c>
-      <c r="J360" t="s">
+      <c r="J363" t="s">
         <v>85</v>
       </c>
-      <c r="K360">
+      <c r="K363">
         <v>100</v>
       </c>
-      <c r="L360" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A361" s="6" t="s">
+      <c r="L363" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" s="6" t="s">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B362" s="8"/>
-      <c r="C362" s="8"/>
-      <c r="D362" s="9"/>
-      <c r="E362" s="9"/>
-      <c r="F362" s="8"/>
-      <c r="G362" s="8"/>
-      <c r="H362" s="8"/>
-      <c r="I362" s="8"/>
-      <c r="M362" s="8"/>
-      <c r="N362" s="8"/>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A363" s="4" t="s">
+      <c r="B365" s="8"/>
+      <c r="C365" s="8"/>
+      <c r="D365" s="9"/>
+      <c r="E365" s="9"/>
+      <c r="F365" s="8"/>
+      <c r="G365" s="8"/>
+      <c r="H365" s="8"/>
+      <c r="I365" s="8"/>
+      <c r="M365" s="8"/>
+      <c r="N365" s="8"/>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B363" s="4"/>
-      <c r="C363" s="4"/>
-      <c r="D363" s="4"/>
-      <c r="E363" s="4"/>
-      <c r="F363" s="4"/>
-      <c r="G363" s="4"/>
-      <c r="H363" s="4"/>
-      <c r="I363" s="4"/>
-      <c r="J363" s="5"/>
-      <c r="K363" s="5"/>
-      <c r="L363" s="5"/>
-      <c r="M363" s="5"/>
-      <c r="N363" s="5"/>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>126</v>
-      </c>
-      <c r="C364" t="s">
-        <v>128</v>
-      </c>
-      <c r="H364" t="s">
-        <v>45</v>
-      </c>
-      <c r="J364" t="s">
-        <v>85</v>
-      </c>
-      <c r="K364" s="21">
-        <v>38</v>
-      </c>
-      <c r="L364" t="s">
-        <v>38</v>
-      </c>
-      <c r="M364" s="11"/>
-      <c r="N364" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>126</v>
-      </c>
-      <c r="C365" t="s">
-        <v>128</v>
-      </c>
-      <c r="F365" t="s">
-        <v>129</v>
-      </c>
-      <c r="H365" t="s">
-        <v>45</v>
-      </c>
-      <c r="J365" t="s">
-        <v>86</v>
-      </c>
-      <c r="K365" s="21">
-        <v>60</v>
-      </c>
-      <c r="L365" t="s">
-        <v>38</v>
-      </c>
-      <c r="N365" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>126</v>
-      </c>
-      <c r="C366" t="s">
-        <v>128</v>
-      </c>
-      <c r="H366" t="s">
-        <v>43</v>
-      </c>
-      <c r="J366" t="s">
-        <v>85</v>
-      </c>
-      <c r="K366" s="21">
-        <v>32</v>
-      </c>
-      <c r="L366" t="s">
-        <v>38</v>
-      </c>
-      <c r="M366" t="s">
-        <v>131</v>
-      </c>
-      <c r="N366" s="8"/>
+      <c r="B366" s="4"/>
+      <c r="C366" s="4"/>
+      <c r="D366" s="4"/>
+      <c r="E366" s="4"/>
+      <c r="F366" s="4"/>
+      <c r="G366" s="4"/>
+      <c r="H366" s="4"/>
+      <c r="I366" s="4"/>
+      <c r="J366" s="5"/>
+      <c r="K366" s="5"/>
+      <c r="L366" s="5"/>
+      <c r="M366" s="5"/>
+      <c r="N366" s="5"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
@@ -9117,324 +9082,318 @@
       <c r="C367" t="s">
         <v>128</v>
       </c>
-      <c r="F367" t="s">
-        <v>130</v>
-      </c>
       <c r="H367" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J367" t="s">
+        <v>85</v>
+      </c>
+      <c r="K367" s="21">
+        <v>38</v>
+      </c>
+      <c r="L367" t="s">
+        <v>38</v>
+      </c>
+      <c r="M367" s="11"/>
+      <c r="N367" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>126</v>
+      </c>
+      <c r="C368" t="s">
+        <v>128</v>
+      </c>
+      <c r="F368" t="s">
+        <v>129</v>
+      </c>
+      <c r="H368" t="s">
+        <v>45</v>
+      </c>
+      <c r="J368" t="s">
         <v>86</v>
       </c>
-      <c r="K367" s="21">
-        <v>68</v>
-      </c>
-      <c r="L367" t="s">
-        <v>38</v>
-      </c>
-      <c r="N367" s="8"/>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A368" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B368" s="4"/>
-      <c r="C368" s="4"/>
-      <c r="D368" s="4"/>
-      <c r="E368" s="4"/>
-      <c r="F368" s="4"/>
-      <c r="G368" s="4"/>
-      <c r="H368" s="4"/>
-      <c r="I368" s="4"/>
-      <c r="J368" s="5"/>
-      <c r="K368" s="5"/>
-      <c r="L368" s="5"/>
-      <c r="M368" s="5"/>
-      <c r="N368" s="5"/>
+      <c r="K368" s="21">
+        <v>60</v>
+      </c>
+      <c r="L368" t="s">
+        <v>38</v>
+      </c>
+      <c r="N368" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="C369" t="s">
-        <v>224</v>
+        <v>128</v>
+      </c>
+      <c r="H369" t="s">
+        <v>43</v>
       </c>
       <c r="J369" t="s">
         <v>85</v>
       </c>
-      <c r="K369" s="22">
+      <c r="K369" s="21">
+        <v>32</v>
+      </c>
+      <c r="L369" t="s">
+        <v>38</v>
+      </c>
+      <c r="M369" t="s">
+        <v>131</v>
+      </c>
+      <c r="N369" s="8"/>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>126</v>
+      </c>
+      <c r="C370" t="s">
+        <v>128</v>
+      </c>
+      <c r="F370" t="s">
+        <v>130</v>
+      </c>
+      <c r="H370" t="s">
+        <v>43</v>
+      </c>
+      <c r="J370" t="s">
+        <v>86</v>
+      </c>
+      <c r="K370" s="21">
+        <v>68</v>
+      </c>
+      <c r="L370" t="s">
+        <v>38</v>
+      </c>
+      <c r="N370" s="8"/>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B371" s="4"/>
+      <c r="C371" s="4"/>
+      <c r="D371" s="4"/>
+      <c r="E371" s="4"/>
+      <c r="F371" s="4"/>
+      <c r="G371" s="4"/>
+      <c r="H371" s="4"/>
+      <c r="I371" s="4"/>
+      <c r="J371" s="5"/>
+      <c r="K371" s="5"/>
+      <c r="L371" s="5"/>
+      <c r="M371" s="5"/>
+      <c r="N371" s="5"/>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>217</v>
+      </c>
+      <c r="C372" t="s">
+        <v>224</v>
+      </c>
+      <c r="J372" t="s">
+        <v>85</v>
+      </c>
+      <c r="K372" s="22">
         <f>161/1000*100</f>
         <v>16.100000000000001</v>
       </c>
-      <c r="L369" t="s">
-        <v>38</v>
-      </c>
-      <c r="M369" t="s">
+      <c r="L372" t="s">
+        <v>38</v>
+      </c>
+      <c r="M372" t="s">
         <v>336</v>
       </c>
-      <c r="N369" s="17" t="s">
+      <c r="N372" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
         <v>217</v>
       </c>
-      <c r="C370" t="s">
+      <c r="C373" t="s">
         <v>224</v>
       </c>
-      <c r="F370" t="s">
+      <c r="F373" t="s">
         <v>225</v>
       </c>
-      <c r="J370" t="s">
+      <c r="J373" t="s">
         <v>86</v>
       </c>
-      <c r="K370" s="22">
+      <c r="K373" s="22">
         <f>(6.4+25.2)/1000/0.9*100</f>
         <v>3.5111111111111115</v>
       </c>
-      <c r="L370" t="s">
-        <v>38</v>
-      </c>
-      <c r="M370" t="s">
+      <c r="L373" t="s">
+        <v>38</v>
+      </c>
+      <c r="M373" t="s">
         <v>339</v>
       </c>
-      <c r="N370" s="17" t="s">
+      <c r="N373" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
         <v>217</v>
       </c>
-      <c r="C371" t="s">
+      <c r="C374" t="s">
         <v>224</v>
       </c>
-      <c r="F371" t="s">
+      <c r="F374" t="s">
         <v>226</v>
       </c>
-      <c r="J371" t="s">
+      <c r="J374" t="s">
         <v>86</v>
       </c>
-      <c r="K371" s="22">
+      <c r="K374" s="22">
         <f>19/1000/0.76*100</f>
         <v>2.5</v>
       </c>
-      <c r="L371" t="s">
-        <v>38</v>
-      </c>
-      <c r="M371" t="s">
+      <c r="L374" t="s">
+        <v>38</v>
+      </c>
+      <c r="M374" t="s">
         <v>340</v>
       </c>
-      <c r="N371" s="17" t="s">
+      <c r="N374" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
         <v>219</v>
       </c>
-      <c r="C372" t="s">
+      <c r="C375" t="s">
         <v>224</v>
       </c>
-      <c r="J372" t="s">
+      <c r="J375" t="s">
         <v>85</v>
       </c>
-      <c r="K372" s="43">
-        <f>K369/0.8</f>
+      <c r="K375" s="43">
+        <f>K372/0.8</f>
         <v>20.125</v>
       </c>
-      <c r="L372" t="s">
-        <v>38</v>
-      </c>
-      <c r="M372" s="17" t="s">
+      <c r="L375" t="s">
+        <v>38</v>
+      </c>
+      <c r="M375" s="17" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
         <v>219</v>
       </c>
-      <c r="C373" t="s">
+      <c r="C376" t="s">
         <v>224</v>
       </c>
-      <c r="F373" t="s">
+      <c r="F376" t="s">
         <v>225</v>
       </c>
-      <c r="J373" t="s">
+      <c r="J376" t="s">
         <v>86</v>
       </c>
-      <c r="K373" s="43">
-        <f>K370</f>
+      <c r="K376" s="43">
+        <f>K373</f>
         <v>3.5111111111111115</v>
       </c>
-      <c r="L373" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>219</v>
-      </c>
-      <c r="C374" t="s">
-        <v>224</v>
-      </c>
-      <c r="F374" t="s">
-        <v>226</v>
-      </c>
-      <c r="J374" t="s">
-        <v>86</v>
-      </c>
-      <c r="K374" s="43">
-        <f>K371</f>
-        <v>2.5</v>
-      </c>
-      <c r="L374" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B376" s="4"/>
-      <c r="C376" s="4"/>
-      <c r="D376" s="4"/>
-      <c r="E376" s="4"/>
-      <c r="F376" s="4"/>
-      <c r="G376" s="4"/>
-      <c r="H376" s="4"/>
-      <c r="I376" s="4"/>
-      <c r="J376" s="5"/>
-      <c r="K376" s="5"/>
-      <c r="L376" s="5"/>
-      <c r="M376" s="5"/>
-      <c r="N376" s="5"/>
+      <c r="L376" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>219</v>
+      </c>
+      <c r="C377" t="s">
+        <v>224</v>
+      </c>
+      <c r="F377" t="s">
+        <v>226</v>
+      </c>
+      <c r="J377" t="s">
+        <v>86</v>
+      </c>
+      <c r="K377" s="43">
+        <f>K374</f>
+        <v>2.5</v>
+      </c>
+      <c r="L377" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A378" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B379" s="4"/>
+      <c r="C379" s="4"/>
+      <c r="D379" s="4"/>
+      <c r="E379" s="4"/>
+      <c r="F379" s="4"/>
+      <c r="G379" s="4"/>
+      <c r="H379" s="4"/>
+      <c r="I379" s="4"/>
+      <c r="J379" s="5"/>
+      <c r="K379" s="5"/>
+      <c r="L379" s="5"/>
+      <c r="M379" s="5"/>
+      <c r="N379" s="5"/>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
         <v>227</v>
       </c>
-      <c r="B377" s="10"/>
-      <c r="C377" s="8" t="s">
+      <c r="B380" s="10"/>
+      <c r="C380" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D377" s="10"/>
-      <c r="E377" s="10"/>
-      <c r="F377" s="10"/>
-      <c r="G377" s="10"/>
-      <c r="H377" s="10"/>
-      <c r="I377" s="10"/>
-      <c r="J377" t="s">
-        <v>85</v>
-      </c>
-      <c r="K377" s="20">
-        <v>70</v>
-      </c>
-      <c r="L377" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M377" s="8"/>
-      <c r="N377" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
-        <v>230</v>
-      </c>
-      <c r="B378" s="10"/>
-      <c r="C378" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D378" s="10"/>
-      <c r="E378" s="10"/>
-      <c r="F378" s="10"/>
-      <c r="G378" s="10"/>
-      <c r="H378" s="10"/>
-      <c r="I378" s="10"/>
-      <c r="J378" t="s">
-        <v>85</v>
-      </c>
-      <c r="K378" s="20">
-        <f>655*0.7</f>
-        <v>458.49999999999994</v>
-      </c>
-      <c r="L378" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M378" s="8"/>
-      <c r="N378" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
-        <v>230</v>
-      </c>
-      <c r="B379" s="10"/>
-      <c r="C379" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D379" s="10"/>
-      <c r="E379" s="10"/>
-      <c r="F379" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="G379" s="10"/>
-      <c r="H379" s="10"/>
-      <c r="I379" s="10"/>
-      <c r="J379" t="s">
-        <v>86</v>
-      </c>
-      <c r="K379" s="20">
-        <f>1*(K378/100)*0.2*100</f>
-        <v>91.699999999999989</v>
-      </c>
-      <c r="L379" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M379" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="N379" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B380" s="10"/>
-      <c r="C380" s="8"/>
       <c r="D380" s="10"/>
       <c r="E380" s="10"/>
-      <c r="F380" s="10" t="s">
-        <v>176</v>
-      </c>
+      <c r="F380" s="10"/>
       <c r="G380" s="10"/>
       <c r="H380" s="10"/>
       <c r="I380" s="10"/>
-      <c r="K380" s="20"/>
-      <c r="L380" s="9"/>
-      <c r="M380" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="N380" s="8"/>
+      <c r="J380" t="s">
+        <v>85</v>
+      </c>
+      <c r="K380" s="20">
+        <v>70</v>
+      </c>
+      <c r="L380" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M380" s="8"/>
+      <c r="N380" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B381" s="10"/>
-      <c r="C381" s="9" t="s">
-        <v>238</v>
+      <c r="C381" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D381" s="10"/>
       <c r="E381" s="10"/>
-      <c r="F381" s="19"/>
+      <c r="F381" s="10"/>
       <c r="G381" s="10"/>
       <c r="H381" s="10"/>
       <c r="I381" s="10"/>
@@ -9442,7 +9401,8 @@
         <v>85</v>
       </c>
       <c r="K381" s="20">
-        <v>65</v>
+        <f>655*0.7</f>
+        <v>458.49999999999994</v>
       </c>
       <c r="L381" s="9" t="s">
         <v>38</v>
@@ -9454,16 +9414,16 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B382" s="10"/>
-      <c r="C382" s="9" t="s">
-        <v>238</v>
+      <c r="C382" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D382" s="10"/>
       <c r="E382" s="10"/>
       <c r="F382" s="19" t="s">
-        <v>239</v>
+        <v>125</v>
       </c>
       <c r="G382" s="10"/>
       <c r="H382" s="10"/>
@@ -9472,318 +9432,418 @@
         <v>86</v>
       </c>
       <c r="K382" s="20">
-        <v>35</v>
+        <f>1*(K381/100)*0.2*100</f>
+        <v>91.699999999999989</v>
       </c>
       <c r="L382" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M382" s="8"/>
+      <c r="M382" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="N382" s="8" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
-        <v>231</v>
-      </c>
       <c r="B383" s="10"/>
-      <c r="C383" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C383" s="8"/>
       <c r="D383" s="10"/>
       <c r="E383" s="10"/>
-      <c r="F383" s="19"/>
+      <c r="F383" s="10" t="s">
+        <v>176</v>
+      </c>
       <c r="G383" s="10"/>
       <c r="H383" s="10"/>
       <c r="I383" s="10"/>
-      <c r="J383" t="s">
-        <v>85</v>
-      </c>
-      <c r="K383" s="20">
-        <v>30</v>
-      </c>
-      <c r="L383" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M383" s="8"/>
-      <c r="N383" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="K383" s="20"/>
+      <c r="L383" s="9"/>
+      <c r="M383" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="N383" s="8"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B384" s="10"/>
       <c r="C384" s="9" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="D384" s="10"/>
       <c r="E384" s="10"/>
-      <c r="F384" s="10" t="s">
-        <v>240</v>
-      </c>
+      <c r="F384" s="19"/>
       <c r="G384" s="10"/>
       <c r="H384" s="10"/>
       <c r="I384" s="10"/>
-      <c r="J384" s="6" t="s">
+      <c r="J384" t="s">
+        <v>85</v>
+      </c>
+      <c r="K384" s="20">
+        <v>65</v>
+      </c>
+      <c r="L384" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M384" s="8"/>
+      <c r="N384" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>228</v>
+      </c>
+      <c r="B385" s="10"/>
+      <c r="C385" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D385" s="10"/>
+      <c r="E385" s="10"/>
+      <c r="F385" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="G385" s="10"/>
+      <c r="H385" s="10"/>
+      <c r="I385" s="10"/>
+      <c r="J385" t="s">
         <v>86</v>
       </c>
-      <c r="K384" s="12">
-        <v>11</v>
-      </c>
-      <c r="L384" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M384" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="N384" s="10" t="s">
+      <c r="K385" s="20">
+        <v>35</v>
+      </c>
+      <c r="L385" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M385" s="8"/>
+      <c r="N385" s="8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A385" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B385" s="4"/>
-      <c r="C385" s="4"/>
-      <c r="D385" s="4"/>
-      <c r="E385" s="4"/>
-      <c r="F385" s="4"/>
-      <c r="G385" s="4"/>
-      <c r="H385" s="4"/>
-      <c r="I385" s="4"/>
-      <c r="J385" s="5"/>
-      <c r="K385" s="5"/>
-      <c r="L385" s="5"/>
-      <c r="M385" s="5"/>
-      <c r="N385" s="5"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="B386" s="10"/>
-      <c r="C386" t="s">
-        <v>128</v>
-      </c>
+      <c r="C386" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D386" s="10"/>
+      <c r="E386" s="10"/>
+      <c r="F386" s="19"/>
+      <c r="G386" s="10"/>
+      <c r="H386" s="10"/>
+      <c r="I386" s="10"/>
       <c r="J386" t="s">
         <v>85</v>
       </c>
-      <c r="K386" s="21">
-        <v>38</v>
-      </c>
-      <c r="L386" t="s">
-        <v>38</v>
-      </c>
-      <c r="M386" s="11" t="s">
-        <v>201</v>
-      </c>
+      <c r="K386" s="20">
+        <v>30</v>
+      </c>
+      <c r="L386" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M386" s="8"/>
       <c r="N386" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>231</v>
+      </c>
+      <c r="B387" s="10"/>
+      <c r="C387" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D387" s="10"/>
+      <c r="E387" s="10"/>
+      <c r="F387" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G387" s="10"/>
+      <c r="H387" s="10"/>
+      <c r="I387" s="10"/>
+      <c r="J387" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K387" s="12">
+        <v>11</v>
+      </c>
+      <c r="L387" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M387" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="N387" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A388" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B388" s="4"/>
+      <c r="C388" s="4"/>
+      <c r="D388" s="4"/>
+      <c r="E388" s="4"/>
+      <c r="F388" s="4"/>
+      <c r="G388" s="4"/>
+      <c r="H388" s="4"/>
+      <c r="I388" s="4"/>
+      <c r="J388" s="5"/>
+      <c r="K388" s="5"/>
+      <c r="L388" s="5"/>
+      <c r="M388" s="5"/>
+      <c r="N388" s="5"/>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
         <v>195</v>
       </c>
-      <c r="B387" s="10"/>
-      <c r="C387" t="s">
+      <c r="B389" s="10"/>
+      <c r="C389" t="s">
         <v>128</v>
       </c>
-      <c r="F387" t="s">
+      <c r="J389" t="s">
+        <v>85</v>
+      </c>
+      <c r="K389" s="21">
+        <v>38</v>
+      </c>
+      <c r="L389" t="s">
+        <v>38</v>
+      </c>
+      <c r="M389" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="N389" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>195</v>
+      </c>
+      <c r="B390" s="10"/>
+      <c r="C390" t="s">
+        <v>128</v>
+      </c>
+      <c r="F390" t="s">
         <v>129</v>
       </c>
-      <c r="J387" t="s">
+      <c r="J390" t="s">
         <v>86</v>
       </c>
-      <c r="K387" s="21">
+      <c r="K390" s="21">
         <v>60</v>
       </c>
-      <c r="L387" t="s">
-        <v>38</v>
-      </c>
-      <c r="N387" s="8" t="s">
+      <c r="L390" t="s">
+        <v>38</v>
+      </c>
+      <c r="N390" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A388" s="17" t="s">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A391" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B388" s="10"/>
-      <c r="C388" t="s">
+      <c r="B391" s="10"/>
+      <c r="C391" t="s">
         <v>37</v>
       </c>
-      <c r="J388" t="s">
+      <c r="J391" t="s">
         <v>85</v>
       </c>
-      <c r="K388" s="15">
+      <c r="K391" s="15">
         <f>(1*0.766) / (2.1/0.86) * 100</f>
         <v>31.369523809523809</v>
       </c>
-      <c r="L388" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M388" s="17" t="s">
+      <c r="L391" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M391" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="N388" s="9" t="s">
+      <c r="N391" s="9" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A389" s="17" t="s">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B389" s="10"/>
-      <c r="C389" t="s">
+      <c r="B392" s="10"/>
+      <c r="C392" t="s">
         <v>37</v>
       </c>
-      <c r="F389" t="s">
+      <c r="F392" t="s">
         <v>311</v>
       </c>
-      <c r="J389" t="s">
+      <c r="J392" t="s">
         <v>86</v>
       </c>
-      <c r="K389" s="15">
+      <c r="K392" s="15">
         <f>(0.8/0.9) / (2.1/0.86) * 100</f>
         <v>36.402116402116405</v>
       </c>
-      <c r="L389" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="M389" s="42" t="s">
+      <c r="L392" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M392" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="N389" s="9" t="s">
+      <c r="N392" s="9" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A390" s="6"/>
-      <c r="B390" s="10"/>
-      <c r="F390" s="6" t="s">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" s="6"/>
+      <c r="B393" s="10"/>
+      <c r="F393" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="K390" s="23"/>
-      <c r="L390" s="6"/>
-      <c r="M390" s="6" t="s">
+      <c r="K393" s="23"/>
+      <c r="L393" s="6"/>
+      <c r="M393" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="N390" s="9"/>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A391" s="4" t="s">
+      <c r="N393" s="9"/>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B394" s="10"/>
+      <c r="C394" t="s">
+        <v>379</v>
+      </c>
+      <c r="F394" s="6"/>
+      <c r="J394" t="s">
+        <v>85</v>
+      </c>
+      <c r="K394" s="15">
+        <v>100</v>
+      </c>
+      <c r="L394" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M394" s="6"/>
+      <c r="N394" s="9"/>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B391" s="4"/>
-      <c r="C391" s="4"/>
-      <c r="D391" s="4"/>
-      <c r="E391" s="4"/>
-      <c r="F391" s="4"/>
-      <c r="G391" s="4"/>
-      <c r="H391" s="4"/>
-      <c r="I391" s="4"/>
-      <c r="J391" s="5"/>
-      <c r="K391" s="38" t="s">
+      <c r="B395" s="4"/>
+      <c r="C395" s="4"/>
+      <c r="D395" s="4"/>
+      <c r="E395" s="4"/>
+      <c r="F395" s="4"/>
+      <c r="G395" s="4"/>
+      <c r="H395" s="4"/>
+      <c r="I395" s="4"/>
+      <c r="J395" s="5"/>
+      <c r="K395" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="L391" s="5"/>
-      <c r="M391" s="5"/>
-      <c r="N391" s="5"/>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
+      <c r="L395" s="5"/>
+      <c r="M395" s="5"/>
+      <c r="N395" s="5"/>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
         <v>272</v>
       </c>
-      <c r="B392" s="10"/>
-      <c r="C392" s="10"/>
-      <c r="D392" s="19" t="s">
+      <c r="B396" s="10"/>
+      <c r="C396" s="10"/>
+      <c r="D396" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="E392" s="19" t="s">
+      <c r="E396" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F392" s="10"/>
-      <c r="G392" s="10"/>
-      <c r="H392" s="10"/>
-      <c r="I392" s="10"/>
-      <c r="J392" t="s">
+      <c r="F396" s="10"/>
+      <c r="G396" s="10"/>
+      <c r="H396" s="10"/>
+      <c r="I396" s="10"/>
+      <c r="J396" t="s">
         <v>85</v>
       </c>
-      <c r="K392" s="19">
+      <c r="K396" s="19">
         <v>100</v>
       </c>
-      <c r="L392" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M392" s="8"/>
-      <c r="N392" s="8"/>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
+      <c r="L396" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M396" s="8"/>
+      <c r="N396" s="8"/>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
         <v>347</v>
       </c>
-      <c r="B393" s="10"/>
-      <c r="C393" s="10"/>
-      <c r="D393" s="19" t="s">
+      <c r="B397" s="10"/>
+      <c r="C397" s="10"/>
+      <c r="D397" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="E393" s="19" t="s">
+      <c r="E397" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="F393" s="10"/>
-      <c r="G393" s="10"/>
-      <c r="H393" s="10"/>
-      <c r="I393" s="10"/>
-      <c r="J393" t="s">
+      <c r="F397" s="10"/>
+      <c r="G397" s="10"/>
+      <c r="H397" s="10"/>
+      <c r="I397" s="10"/>
+      <c r="J397" t="s">
         <v>85</v>
       </c>
-      <c r="K393" s="19">
+      <c r="K397" s="19">
         <v>100</v>
       </c>
-      <c r="L393" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M393" s="8"/>
-      <c r="N393" s="8"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B394" s="10"/>
-      <c r="C394" s="10"/>
-      <c r="D394" s="19"/>
-      <c r="E394" s="19"/>
-      <c r="F394" s="10"/>
-      <c r="G394" s="10"/>
-      <c r="H394" s="10"/>
-      <c r="I394" s="10"/>
-      <c r="K394" s="19"/>
-      <c r="L394" s="8"/>
-      <c r="M394" s="8"/>
-      <c r="N394" s="8"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A395" s="2" t="s">
+      <c r="L397" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M397" s="8"/>
+      <c r="N397" s="8"/>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B398" s="10"/>
+      <c r="C398" s="10"/>
+      <c r="D398" s="19"/>
+      <c r="E398" s="19"/>
+      <c r="F398" s="10"/>
+      <c r="G398" s="10"/>
+      <c r="H398" s="10"/>
+      <c r="I398" s="10"/>
+      <c r="K398" s="19"/>
+      <c r="L398" s="8"/>
+      <c r="M398" s="8"/>
+      <c r="N398" s="8"/>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A399" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B395" s="2"/>
-      <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
-      <c r="E395" s="2"/>
-      <c r="F395" s="2"/>
-      <c r="G395" s="2"/>
-      <c r="H395" s="2"/>
-      <c r="I395" s="2"/>
-      <c r="J395" s="2"/>
-      <c r="K395" s="2"/>
-      <c r="L395" s="2"/>
-      <c r="M395" s="2"/>
-      <c r="N395" s="2"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A396" s="6" t="s">
+      <c r="B399" s="2"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="2"/>
+      <c r="F399" s="2"/>
+      <c r="G399" s="2"/>
+      <c r="H399" s="2"/>
+      <c r="I399" s="2"/>
+      <c r="J399" s="2"/>
+      <c r="K399" s="2"/>
+      <c r="L399" s="2"/>
+      <c r="M399" s="2"/>
+      <c r="N399" s="2"/>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A400" s="6" t="s">
         <v>316</v>
       </c>
     </row>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="460">
   <si>
     <t>parameter</t>
   </si>
@@ -925,9 +925,6 @@
   </si>
   <si>
     <t>Oat grains</t>
-  </si>
-  <si>
-    <t>export</t>
   </si>
   <si>
     <t>export_demand</t>
@@ -1614,7 +1611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1667,14 +1664,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1689,6 +1680,7 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2095,13 +2087,13 @@
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>56</v>
@@ -2177,19 +2169,19 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
+        <v>373</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="N4" t="s">
         <v>374</v>
       </c>
-      <c r="M4" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>375</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>376</v>
-      </c>
-      <c r="P4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2250,10 +2242,10 @@
         <v>19</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2276,7 +2268,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -2292,15 +2284,15 @@
         <v>19</v>
       </c>
       <c r="O10" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="P10" t="s">
         <v>319</v>
-      </c>
-      <c r="P10" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -2335,7 +2327,7 @@
         <v>19</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2392,7 +2384,7 @@
         <v>19</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2432,7 +2424,7 @@
         <v>19</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2472,7 +2464,7 @@
         <v>19</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2495,21 +2487,31 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M21" s="52">
+      <c r="M21" s="29">
         <v>0.1</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="N21" s="17" t="s">
         <v>19</v>
       </c>
+      <c r="O21" s="17"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -2640,28 +2642,28 @@
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="A29" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7" t="s">
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="17">
         <v>3.6</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3181,28 +3183,28 @@
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B59" s="7" t="s">
+      <c r="A59" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B59" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7" t="s">
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M59" s="7">
+      <c r="M59" s="17">
         <v>0</v>
       </c>
-      <c r="N59" s="7" t="s">
+      <c r="N59" s="17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3262,7 +3264,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s">
         <v>55</v>
@@ -3277,7 +3279,7 @@
         <v>19</v>
       </c>
       <c r="O63" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3322,7 +3324,7 @@
         <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L66" t="s">
         <v>18</v>
@@ -3335,36 +3337,36 @@
         <v>19</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M67" s="17">
+        <v>0</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O67" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M67" s="7">
-        <v>0</v>
-      </c>
-      <c r="N67" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -3476,55 +3478,55 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M74" s="17">
+        <v>0</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O74" s="7"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B75" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7" t="s">
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M74" s="7">
+      <c r="M75" s="17">
         <v>0</v>
       </c>
-      <c r="N74" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O74" s="7"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M75" s="7">
-        <v>0</v>
-      </c>
-      <c r="N75" s="7" t="s">
+      <c r="N75" s="17" t="s">
         <v>19</v>
       </c>
       <c r="O75" s="7"/>
@@ -3567,102 +3569,108 @@
       <c r="P77" s="5"/>
     </row>
     <row r="78" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48" t="s">
+      <c r="A78" s="58" t="s">
+        <v>388</v>
+      </c>
+      <c r="B78" s="58" t="s">
         <v>389</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="C78" s="58"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
+      <c r="J78" s="59"/>
+      <c r="K78" s="59"/>
+      <c r="L78" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M78" s="58">
+        <v>0.2</v>
+      </c>
+      <c r="N78" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="O78" s="58"/>
+      <c r="P78" s="58"/>
+    </row>
+    <row r="79" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="58" t="s">
         <v>390</v>
       </c>
-      <c r="C78" s="48"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
-      <c r="L78" s="7" t="s">
+      <c r="B79" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="C79" s="58"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
+      <c r="J79" s="59"/>
+      <c r="K79" s="59"/>
+      <c r="L79" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M78" s="48">
-        <v>0.2</v>
-      </c>
-      <c r="N78" s="48" t="s">
+      <c r="M79" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="N79" s="58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="48" t="s">
+      <c r="O79" s="58"/>
+      <c r="P79" s="58"/>
+    </row>
+    <row r="80" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="53" t="s">
         <v>391</v>
       </c>
-      <c r="B79" s="48" t="s">
-        <v>390</v>
-      </c>
-      <c r="C79" s="48"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
-      <c r="L79" s="7" t="s">
+      <c r="B80" s="55"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="53"/>
+      <c r="K80" s="53"/>
+      <c r="L80" s="55"/>
+      <c r="M80" s="55"/>
+      <c r="N80" s="55"/>
+      <c r="O80" s="55"/>
+      <c r="P80" s="55"/>
+    </row>
+    <row r="81" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="58" t="s">
+        <v>392</v>
+      </c>
+      <c r="B81" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="C81" s="58"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="59"/>
+      <c r="L81" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M79" s="48">
-        <v>0.1</v>
-      </c>
-      <c r="N79" s="48" t="s">
+      <c r="M81" s="58">
+        <v>0</v>
+      </c>
+      <c r="N81" s="58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="50" t="s">
-        <v>392</v>
-      </c>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
-      <c r="J80" s="50"/>
-      <c r="K80" s="50"/>
-      <c r="L80" s="51"/>
-      <c r="M80" s="51"/>
-      <c r="N80" s="51"/>
-      <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
-    </row>
-    <row r="81" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="48" t="s">
-        <v>393</v>
-      </c>
-      <c r="B81" s="48" t="s">
-        <v>394</v>
-      </c>
-      <c r="C81" s="48"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="49"/>
-      <c r="J81" s="49"/>
-      <c r="K81" s="49"/>
-      <c r="L81" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M81" s="48">
-        <v>0</v>
-      </c>
-      <c r="N81" s="48" t="s">
-        <v>19</v>
-      </c>
+      <c r="O81" s="58"/>
+      <c r="P81" s="58"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
@@ -3706,23 +3714,32 @@
       </c>
     </row>
     <row r="84" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" s="29">
+        <v>0</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O84" s="17" t="s">
         <v>395</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="L84" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M84" s="52">
-        <v>0</v>
-      </c>
-      <c r="N84" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O84" s="7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -4016,356 +4033,366 @@
       <c r="P99" s="5"/>
     </row>
     <row r="100" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="48" t="s">
+      <c r="A100" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B100" s="58" t="s">
         <v>397</v>
       </c>
-      <c r="B100" s="48" t="s">
+      <c r="C100" s="58"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="59"/>
+      <c r="H100" s="59"/>
+      <c r="I100" s="59"/>
+      <c r="J100" s="59"/>
+      <c r="K100" s="59"/>
+      <c r="L100" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="M100" s="58">
+        <v>0</v>
+      </c>
+      <c r="N100" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="O100" s="58"/>
+    </row>
+    <row r="101" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="58" t="s">
         <v>398</v>
       </c>
-      <c r="C100" s="48"/>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
-      <c r="F100" s="49"/>
-      <c r="G100" s="49"/>
-      <c r="H100" s="49"/>
-      <c r="I100" s="49"/>
-      <c r="J100" s="49"/>
-      <c r="K100" s="49"/>
-      <c r="L100" s="48" t="s">
+      <c r="B101" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C101" s="58"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="59"/>
+      <c r="F101" s="59"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="59"/>
+      <c r="I101" s="59"/>
+      <c r="J101" s="59"/>
+      <c r="K101" s="59"/>
+      <c r="L101" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M100" s="48">
+      <c r="M101" s="58">
         <v>0</v>
       </c>
-      <c r="N100" s="48" t="s">
+      <c r="N101" s="58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="48" t="s">
+      <c r="O101" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="B101" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C101" s="48"/>
-      <c r="D101" s="49"/>
-      <c r="E101" s="49"/>
-      <c r="F101" s="49"/>
-      <c r="G101" s="49"/>
-      <c r="H101" s="49"/>
-      <c r="I101" s="49"/>
-      <c r="J101" s="49"/>
-      <c r="K101" s="49"/>
-      <c r="L101" s="48" t="s">
+    </row>
+    <row r="102" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B102" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="58"/>
+      <c r="I102" s="58"/>
+      <c r="J102" s="58"/>
+      <c r="K102" s="58"/>
+      <c r="L102" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M101" s="48">
+      <c r="M102" s="58">
         <v>0</v>
       </c>
-      <c r="N101" s="48" t="s">
+      <c r="N102" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O101" s="48" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="48" t="s">
+      <c r="O102" s="58"/>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="58" t="s">
         <v>401</v>
       </c>
-      <c r="B102" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C102" s="48"/>
-      <c r="D102" s="48"/>
-      <c r="E102" s="48"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
-      <c r="J102" s="48"/>
-      <c r="K102" s="48"/>
-      <c r="L102" s="48" t="s">
+      <c r="B103" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="58"/>
+      <c r="G103" s="58"/>
+      <c r="H103" s="58"/>
+      <c r="I103" s="58"/>
+      <c r="J103" s="58"/>
+      <c r="K103" s="58"/>
+      <c r="L103" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M102" s="48">
+      <c r="M103" s="58">
         <v>0</v>
       </c>
-      <c r="N102" s="48" t="s">
+      <c r="N103" s="58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="48" t="s">
+      <c r="O103" s="17"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B104" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C104" s="58"/>
+      <c r="D104" s="59"/>
+      <c r="E104" s="59"/>
+      <c r="F104" s="59"/>
+      <c r="G104" s="59"/>
+      <c r="H104" s="59"/>
+      <c r="I104" s="59"/>
+      <c r="J104" s="59"/>
+      <c r="K104" s="59"/>
+      <c r="L104" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="M104" s="58">
+        <v>0</v>
+      </c>
+      <c r="N104" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="O104" s="17"/>
+      <c r="P104" s="49"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B105" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="B103" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C103" s="48"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="48"/>
-      <c r="L103" s="48" t="s">
+      <c r="C105" s="58"/>
+      <c r="D105" s="59"/>
+      <c r="E105" s="59"/>
+      <c r="F105" s="59"/>
+      <c r="G105" s="59"/>
+      <c r="H105" s="59"/>
+      <c r="I105" s="59"/>
+      <c r="J105" s="59"/>
+      <c r="K105" s="59"/>
+      <c r="L105" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M103" s="48">
+      <c r="M105" s="58">
         <v>0</v>
       </c>
-      <c r="N103" s="48" t="s">
+      <c r="N105" s="58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="B104" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C104" s="48"/>
-      <c r="D104" s="53"/>
-      <c r="E104" s="49"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="53"/>
-      <c r="I104" s="53"/>
-      <c r="J104" s="53"/>
-      <c r="K104" s="53"/>
-      <c r="L104" s="48" t="s">
+      <c r="O105" s="17"/>
+      <c r="P105" s="49"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B106" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C106" s="58"/>
+      <c r="D106" s="58"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="58"/>
+      <c r="G106" s="58"/>
+      <c r="H106" s="58"/>
+      <c r="I106" s="58"/>
+      <c r="J106" s="58"/>
+      <c r="K106" s="58"/>
+      <c r="L106" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M104" s="48">
+      <c r="M106" s="58">
         <v>0</v>
       </c>
-      <c r="N104" s="48" t="s">
+      <c r="N106" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O104" s="54"/>
-      <c r="P104" s="54"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="B105" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C105" s="48"/>
-      <c r="D105" s="53"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="53"/>
-      <c r="I105" s="53"/>
-      <c r="J105" s="53"/>
-      <c r="K105" s="53"/>
-      <c r="L105" s="48" t="s">
+      <c r="O106" s="17"/>
+      <c r="P106" s="49"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B107" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C107" s="58"/>
+      <c r="D107" s="59"/>
+      <c r="E107" s="59"/>
+      <c r="F107" s="59"/>
+      <c r="G107" s="59"/>
+      <c r="H107" s="59"/>
+      <c r="I107" s="59"/>
+      <c r="J107" s="59"/>
+      <c r="K107" s="59"/>
+      <c r="L107" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M105" s="48">
+      <c r="M107" s="58">
         <v>0</v>
       </c>
-      <c r="N105" s="48" t="s">
+      <c r="N107" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O105" s="54"/>
-      <c r="P105" s="54"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="48" t="s">
-        <v>406</v>
-      </c>
-      <c r="B106" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C106" s="48"/>
-      <c r="D106" s="48"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="48"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="48"/>
-      <c r="J106" s="48"/>
-      <c r="K106" s="48"/>
-      <c r="L106" s="48" t="s">
+      <c r="O107" s="17"/>
+      <c r="P107" s="49"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="B108" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C108" s="58"/>
+      <c r="D108" s="59"/>
+      <c r="E108" s="59"/>
+      <c r="F108" s="59"/>
+      <c r="G108" s="59"/>
+      <c r="H108" s="59"/>
+      <c r="I108" s="59"/>
+      <c r="J108" s="59"/>
+      <c r="K108" s="59"/>
+      <c r="L108" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M106" s="48">
+      <c r="M108" s="58">
         <v>0</v>
       </c>
-      <c r="N106" s="48" t="s">
+      <c r="N108" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O106" s="54"/>
-      <c r="P106" s="54"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="B107" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C107" s="48"/>
-      <c r="D107" s="53"/>
-      <c r="E107" s="49"/>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
-      <c r="H107" s="53"/>
-      <c r="I107" s="53"/>
-      <c r="J107" s="53"/>
-      <c r="K107" s="53"/>
-      <c r="L107" s="48" t="s">
+      <c r="O108" s="17"/>
+      <c r="P108" s="49"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B109" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C109" s="58"/>
+      <c r="D109" s="59"/>
+      <c r="E109" s="59"/>
+      <c r="F109" s="59"/>
+      <c r="G109" s="59"/>
+      <c r="H109" s="59"/>
+      <c r="I109" s="59"/>
+      <c r="J109" s="59"/>
+      <c r="K109" s="59"/>
+      <c r="L109" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M107" s="48">
+      <c r="M109" s="58">
         <v>0</v>
       </c>
-      <c r="N107" s="48" t="s">
+      <c r="N109" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O107" s="54"/>
-      <c r="P107" s="54"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="48" t="s">
-        <v>408</v>
-      </c>
-      <c r="B108" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C108" s="48"/>
-      <c r="D108" s="53"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="53"/>
-      <c r="G108" s="53"/>
-      <c r="H108" s="53"/>
-      <c r="I108" s="53"/>
-      <c r="J108" s="53"/>
-      <c r="K108" s="53"/>
-      <c r="L108" s="48" t="s">
+      <c r="O109" s="17"/>
+      <c r="P109" s="49"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="B110" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C110" s="58"/>
+      <c r="D110" s="59"/>
+      <c r="E110" s="59"/>
+      <c r="F110" s="59"/>
+      <c r="G110" s="59"/>
+      <c r="H110" s="59"/>
+      <c r="I110" s="59"/>
+      <c r="J110" s="59"/>
+      <c r="K110" s="59"/>
+      <c r="L110" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M108" s="48">
+      <c r="M110" s="58">
         <v>0</v>
       </c>
-      <c r="N108" s="48" t="s">
+      <c r="N110" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O108" s="54"/>
-      <c r="P108" s="54"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="48" t="s">
-        <v>409</v>
-      </c>
-      <c r="B109" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C109" s="48"/>
-      <c r="D109" s="53"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
-      <c r="H109" s="53"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="48" t="s">
+      <c r="O110" s="17"/>
+      <c r="P110" s="49"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B111" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C111" s="58"/>
+      <c r="D111" s="59"/>
+      <c r="E111" s="59"/>
+      <c r="F111" s="59"/>
+      <c r="G111" s="59"/>
+      <c r="H111" s="59"/>
+      <c r="I111" s="59"/>
+      <c r="J111" s="59"/>
+      <c r="K111" s="59"/>
+      <c r="L111" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M109" s="48">
+      <c r="M111" s="58">
         <v>0</v>
       </c>
-      <c r="N109" s="48" t="s">
+      <c r="N111" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O109" s="54"/>
-      <c r="P109" s="54"/>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="48" t="s">
-        <v>410</v>
-      </c>
-      <c r="B110" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C110" s="48"/>
-      <c r="D110" s="53"/>
-      <c r="E110" s="49"/>
-      <c r="F110" s="53"/>
-      <c r="G110" s="53"/>
-      <c r="H110" s="53"/>
-      <c r="I110" s="53"/>
-      <c r="J110" s="53"/>
-      <c r="K110" s="53"/>
-      <c r="L110" s="48" t="s">
+      <c r="O111" s="17"/>
+      <c r="P111" s="49"/>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B112" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C112" s="58"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="17"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="17"/>
+      <c r="I112" s="17"/>
+      <c r="J112" s="17"/>
+      <c r="K112" s="17"/>
+      <c r="L112" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M110" s="48">
+      <c r="M112" s="58">
         <v>0</v>
       </c>
-      <c r="N110" s="48" t="s">
+      <c r="N112" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O110" s="54"/>
-      <c r="P110" s="54"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="48" t="s">
-        <v>411</v>
-      </c>
-      <c r="B111" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="53"/>
-      <c r="E111" s="49"/>
-      <c r="F111" s="53"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="53"/>
-      <c r="I111" s="53"/>
-      <c r="J111" s="53"/>
-      <c r="K111" s="53"/>
-      <c r="L111" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="M111" s="48">
-        <v>0</v>
-      </c>
-      <c r="N111" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="O111" s="54"/>
-      <c r="P111" s="54"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="48" t="s">
-        <v>412</v>
-      </c>
-      <c r="B112" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C112" s="48"/>
-      <c r="E112" s="7"/>
-      <c r="L112" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="M112" s="48">
-        <v>0</v>
-      </c>
-      <c r="N112" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="O112" s="54"/>
-      <c r="P112" s="54"/>
+      <c r="O112" s="17"/>
+      <c r="P112" s="49"/>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
@@ -4408,7 +4435,7 @@
         <v>190</v>
       </c>
       <c r="O115" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P115" s="21"/>
     </row>
@@ -4436,34 +4463,34 @@
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="17"/>
+      <c r="G117" s="17"/>
+      <c r="H117" s="17"/>
+      <c r="I117" s="17"/>
+      <c r="J117" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K117" s="17"/>
+      <c r="L117" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="M117" s="64">
+        <v>0</v>
+      </c>
+      <c r="N117" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O117" s="17" t="s">
         <v>413</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="M117" s="55">
-        <v>0</v>
-      </c>
-      <c r="N117" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O117" s="7" t="s">
-        <v>414</v>
       </c>
       <c r="P117" s="7"/>
     </row>
@@ -4490,10 +4517,10 @@
         <v>190</v>
       </c>
       <c r="O119" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
@@ -4524,13 +4551,13 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M122" s="37"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B123" t="s">
         <v>200</v>
@@ -4547,12 +4574,12 @@
         <v>273</v>
       </c>
       <c r="O123" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B124" t="s">
         <v>200</v>
@@ -4579,7 +4606,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B127" t="s">
         <v>200</v>
@@ -4594,7 +4621,7 @@
         <v>1000</v>
       </c>
       <c r="N127" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O127" s="6"/>
       <c r="P127" s="9"/>
@@ -4627,13 +4654,13 @@
         <v>289</v>
       </c>
       <c r="B130" t="s">
-        <v>293</v>
+        <v>26</v>
       </c>
       <c r="J130" t="s">
         <v>45</v>
       </c>
       <c r="L130" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M130" s="33">
         <v>558249.80000000005</v>
@@ -4642,10 +4669,10 @@
         <v>190</v>
       </c>
       <c r="O130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.25">
@@ -4653,13 +4680,13 @@
         <v>290</v>
       </c>
       <c r="B131" t="s">
-        <v>293</v>
+        <v>26</v>
       </c>
       <c r="J131" t="s">
         <v>45</v>
       </c>
       <c r="L131" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M131" s="33">
         <f>304650.4+303000</f>
@@ -4669,13 +4696,13 @@
         <v>190</v>
       </c>
       <c r="O131" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P131" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T131" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.25">
@@ -4683,13 +4710,13 @@
         <v>291</v>
       </c>
       <c r="B132" t="s">
-        <v>293</v>
+        <v>26</v>
       </c>
       <c r="J132" t="s">
         <v>45</v>
       </c>
       <c r="L132" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M132" s="33">
         <v>32965.800000000003</v>
@@ -4698,10 +4725,10 @@
         <v>190</v>
       </c>
       <c r="O132" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.25">
@@ -4709,13 +4736,13 @@
         <v>292</v>
       </c>
       <c r="B133" t="s">
-        <v>293</v>
+        <v>26</v>
       </c>
       <c r="J133" t="s">
         <v>45</v>
       </c>
       <c r="L133" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M133" s="33">
         <f>177249.6+246000</f>
@@ -4725,13 +4752,13 @@
         <v>190</v>
       </c>
       <c r="O133" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P133" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T133" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.25">
@@ -4739,13 +4766,13 @@
         <v>202</v>
       </c>
       <c r="B134" t="s">
-        <v>293</v>
+        <v>207</v>
       </c>
       <c r="J134" t="s">
         <v>45</v>
       </c>
       <c r="L134" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M134" s="33">
         <v>22062.799999999999</v>
@@ -4754,10 +4781,10 @@
         <v>190</v>
       </c>
       <c r="O134" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.25">
@@ -4765,13 +4792,13 @@
         <v>101</v>
       </c>
       <c r="B135" t="s">
-        <v>293</v>
+        <v>103</v>
       </c>
       <c r="J135" t="s">
         <v>45</v>
       </c>
       <c r="L135" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M135" s="33">
         <v>25000</v>
@@ -4780,689 +4807,689 @@
         <v>190</v>
       </c>
       <c r="O135" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P135" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" s="17"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="17"/>
+      <c r="G136" s="17"/>
+      <c r="H136" s="17"/>
+      <c r="I136" s="17"/>
+      <c r="J136" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K136" s="17"/>
+      <c r="L136" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="7" t="s">
+      <c r="M136" s="64">
+        <v>0</v>
+      </c>
+      <c r="N136" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O136" s="17"/>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A137" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C137" s="17"/>
+      <c r="D137" s="17"/>
+      <c r="E137" s="17"/>
+      <c r="F137" s="17"/>
+      <c r="G137" s="17"/>
+      <c r="H137" s="17"/>
+      <c r="I137" s="17"/>
+      <c r="J137" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K137" s="17"/>
+      <c r="L137" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M137" s="64">
+        <v>0</v>
+      </c>
+      <c r="N137" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O137" s="17"/>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A138" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C138" s="17"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="17"/>
+      <c r="G138" s="17"/>
+      <c r="H138" s="17"/>
+      <c r="I138" s="17"/>
+      <c r="J138" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M136" s="55">
+      <c r="K138" s="17"/>
+      <c r="L138" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M138" s="64">
         <v>0</v>
       </c>
-      <c r="N136" s="7" t="s">
+      <c r="N138" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O136" s="7"/>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M137" s="55">
-        <v>0</v>
-      </c>
-      <c r="N137" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O137" s="7"/>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M138" s="55">
-        <v>0</v>
-      </c>
-      <c r="N138" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O138" s="7" t="s">
-        <v>415</v>
+      <c r="O138" s="17" t="s">
+        <v>414</v>
       </c>
       <c r="P138">
         <v>20000</v>
       </c>
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C139" s="17"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="17"/>
+      <c r="F139" s="17"/>
+      <c r="G139" s="17"/>
+      <c r="H139" s="17"/>
+      <c r="I139" s="17"/>
+      <c r="J139" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K139" s="17"/>
+      <c r="L139" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-      <c r="I139" s="7"/>
-      <c r="J139" s="7" t="s">
+      <c r="M139" s="64">
+        <v>0</v>
+      </c>
+      <c r="N139" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O139" s="17"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A140" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C140" s="17"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="17"/>
+      <c r="G140" s="17"/>
+      <c r="H140" s="17"/>
+      <c r="I140" s="17"/>
+      <c r="J140" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K140" s="17"/>
+      <c r="L140" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M140" s="64">
+        <v>0</v>
+      </c>
+      <c r="N140" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O140" s="17"/>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A141" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="17"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="17"/>
+      <c r="G141" s="17"/>
+      <c r="H141" s="17"/>
+      <c r="I141" s="17"/>
+      <c r="J141" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M139" s="55">
+      <c r="K141" s="17"/>
+      <c r="L141" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M141" s="64">
         <v>0</v>
       </c>
-      <c r="N139" s="7" t="s">
+      <c r="N141" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O139" s="7"/>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B140" s="7" t="s">
+      <c r="O141" s="17"/>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A142" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C142" s="17"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="17"/>
+      <c r="G142" s="17"/>
+      <c r="H142" s="17"/>
+      <c r="I142" s="17"/>
+      <c r="J142" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K142" s="17"/>
+      <c r="L142" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7" t="s">
+      <c r="M142" s="64">
+        <v>0</v>
+      </c>
+      <c r="N142" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O142" s="17"/>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A143" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143" s="17"/>
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="17"/>
+      <c r="G143" s="17"/>
+      <c r="H143" s="17"/>
+      <c r="I143" s="17"/>
+      <c r="J143" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K143" s="17"/>
+      <c r="L143" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M143" s="64">
+        <v>0</v>
+      </c>
+      <c r="N143" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O143" s="17"/>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A144" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C144" s="17"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="17"/>
+      <c r="G144" s="17"/>
+      <c r="H144" s="17"/>
+      <c r="I144" s="17"/>
+      <c r="J144" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M140" s="55">
+      <c r="K144" s="17"/>
+      <c r="L144" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M144" s="64">
         <v>0</v>
       </c>
-      <c r="N140" s="7" t="s">
+      <c r="N144" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O140" s="7"/>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B141" s="7" t="s">
+      <c r="O144" s="17"/>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A145" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C145" s="17"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="17"/>
+      <c r="G145" s="17"/>
+      <c r="H145" s="17"/>
+      <c r="I145" s="17"/>
+      <c r="J145" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K145" s="17"/>
+      <c r="L145" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="7"/>
-      <c r="I141" s="7"/>
-      <c r="J141" s="7" t="s">
+      <c r="M145" s="64">
+        <v>0</v>
+      </c>
+      <c r="N145" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O145" s="17"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A146" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C146" s="17"/>
+      <c r="D146" s="17"/>
+      <c r="E146" s="17"/>
+      <c r="F146" s="17"/>
+      <c r="G146" s="17"/>
+      <c r="H146" s="17"/>
+      <c r="I146" s="17"/>
+      <c r="J146" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K146" s="17"/>
+      <c r="L146" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M146" s="64">
+        <v>20000</v>
+      </c>
+      <c r="N146" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O146" s="17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C147" s="17"/>
+      <c r="D147" s="17"/>
+      <c r="E147" s="17"/>
+      <c r="F147" s="17"/>
+      <c r="G147" s="17"/>
+      <c r="H147" s="17"/>
+      <c r="I147" s="17"/>
+      <c r="J147" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="K141" s="7"/>
-      <c r="L141" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M141" s="55">
+      <c r="K147" s="17"/>
+      <c r="L147" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M147" s="64">
         <v>0</v>
       </c>
-      <c r="N141" s="7" t="s">
+      <c r="N147" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O141" s="7"/>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B142" s="7" t="s">
+      <c r="O147" s="17"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A148" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B148" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C148" s="17"/>
+      <c r="D148" s="17"/>
+      <c r="E148" s="17"/>
+      <c r="F148" s="17"/>
+      <c r="G148" s="17"/>
+      <c r="H148" s="17"/>
+      <c r="I148" s="17"/>
+      <c r="J148" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K148" s="17"/>
+      <c r="L148" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7" t="s">
+      <c r="M148" s="64">
+        <v>0</v>
+      </c>
+      <c r="N148" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O148" s="17"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A149" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B149" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C149" s="17"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="17"/>
+      <c r="G149" s="17"/>
+      <c r="H149" s="17"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M142" s="55">
+      <c r="K149" s="17"/>
+      <c r="L149" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M149" s="64">
         <v>0</v>
       </c>
-      <c r="N142" s="7" t="s">
+      <c r="N149" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O142" s="7"/>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A143" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B143" s="7" t="s">
+      <c r="O149" s="17"/>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A150" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B150" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="17"/>
+      <c r="H150" s="17"/>
+      <c r="I150" s="17"/>
+      <c r="J150" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K150" s="17"/>
+      <c r="L150" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
-      <c r="I143" s="7"/>
-      <c r="J143" s="7" t="s">
+      <c r="M150" s="64">
+        <v>0</v>
+      </c>
+      <c r="N150" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O150" s="17"/>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A151" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B151" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C151" s="17"/>
+      <c r="D151" s="17"/>
+      <c r="E151" s="17"/>
+      <c r="F151" s="17"/>
+      <c r="G151" s="17"/>
+      <c r="H151" s="17"/>
+      <c r="I151" s="17"/>
+      <c r="J151" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K151" s="17"/>
+      <c r="L151" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M151" s="64">
+        <v>0</v>
+      </c>
+      <c r="N151" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O151" s="17"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A152" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B152" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C152" s="17"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="17"/>
+      <c r="F152" s="17"/>
+      <c r="G152" s="17"/>
+      <c r="H152" s="17"/>
+      <c r="I152" s="17"/>
+      <c r="J152" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="K143" s="7"/>
-      <c r="L143" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M143" s="55">
+      <c r="K152" s="17"/>
+      <c r="L152" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M152" s="64">
         <v>0</v>
       </c>
-      <c r="N143" s="7" t="s">
+      <c r="N152" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O143" s="7"/>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A144" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B144" s="7" t="s">
+      <c r="O152" s="17"/>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A153" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B153" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C153" s="17"/>
+      <c r="D153" s="17"/>
+      <c r="E153" s="17"/>
+      <c r="F153" s="17"/>
+      <c r="G153" s="17"/>
+      <c r="H153" s="17"/>
+      <c r="I153" s="17"/>
+      <c r="J153" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K153" s="17"/>
+      <c r="L153" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7" t="s">
+      <c r="M153" s="64">
+        <v>0</v>
+      </c>
+      <c r="N153" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O153" s="17"/>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A154" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B154" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C154" s="17"/>
+      <c r="D154" s="17"/>
+      <c r="E154" s="17"/>
+      <c r="F154" s="17"/>
+      <c r="G154" s="17"/>
+      <c r="H154" s="17"/>
+      <c r="I154" s="17"/>
+      <c r="J154" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K154" s="17"/>
+      <c r="L154" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M154" s="64">
+        <v>0</v>
+      </c>
+      <c r="N154" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O154" s="17"/>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A155" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B155" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="17"/>
+      <c r="F155" s="17"/>
+      <c r="G155" s="17"/>
+      <c r="H155" s="17"/>
+      <c r="I155" s="17"/>
+      <c r="J155" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K144" s="7"/>
-      <c r="L144" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M144" s="55">
+      <c r="K155" s="17"/>
+      <c r="L155" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M155" s="64">
         <v>0</v>
       </c>
-      <c r="N144" s="7" t="s">
+      <c r="N155" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O144" s="7"/>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A145" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B145" s="7" t="s">
+      <c r="O155" s="17"/>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A156" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B156" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C156" s="17"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="17"/>
+      <c r="F156" s="17"/>
+      <c r="G156" s="17"/>
+      <c r="H156" s="17"/>
+      <c r="I156" s="17"/>
+      <c r="J156" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="17"/>
+      <c r="L156" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
-      <c r="I145" s="7"/>
-      <c r="J145" s="7" t="s">
+      <c r="M156" s="64">
+        <v>0</v>
+      </c>
+      <c r="N156" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O156" s="17"/>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A157" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B157" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="17"/>
+      <c r="F157" s="17"/>
+      <c r="G157" s="17"/>
+      <c r="H157" s="17"/>
+      <c r="I157" s="17"/>
+      <c r="J157" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K157" s="17"/>
+      <c r="L157" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M157" s="64">
+        <v>0</v>
+      </c>
+      <c r="N157" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="O157" s="17"/>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A158" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B158" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="17"/>
+      <c r="G158" s="17"/>
+      <c r="H158" s="17"/>
+      <c r="I158" s="17"/>
+      <c r="J158" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M145" s="55">
+      <c r="K158" s="17"/>
+      <c r="L158" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="M158" s="64">
         <v>0</v>
       </c>
-      <c r="N145" s="7" t="s">
+      <c r="N158" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="O145" s="7"/>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A146" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="7"/>
-      <c r="J146" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M146" s="55">
-        <v>20000</v>
-      </c>
-      <c r="N146" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O146" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M147" s="55">
-        <v>0</v>
-      </c>
-      <c r="N147" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O147" s="7"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A148" s="48" t="s">
-        <v>397</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-      <c r="I148" s="7"/>
-      <c r="J148" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M148" s="55">
-        <v>0</v>
-      </c>
-      <c r="N148" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O148" s="7"/>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A149" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-      <c r="I149" s="7"/>
-      <c r="J149" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K149" s="7"/>
-      <c r="L149" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M149" s="55">
-        <v>0</v>
-      </c>
-      <c r="N149" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O149" s="7"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A150" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K150" s="7"/>
-      <c r="L150" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M150" s="55">
-        <v>0</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O150" s="7"/>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A151" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K151" s="7"/>
-      <c r="L151" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M151" s="55">
-        <v>0</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O151" s="7"/>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A152" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K152" s="7"/>
-      <c r="L152" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M152" s="55">
-        <v>0</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O152" s="7"/>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A153" s="48" t="s">
-        <v>409</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-      <c r="I153" s="7"/>
-      <c r="J153" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K153" s="7"/>
-      <c r="L153" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M153" s="55">
-        <v>0</v>
-      </c>
-      <c r="N153" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O153" s="7"/>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A154" s="48" t="s">
-        <v>409</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
-      <c r="G154" s="7"/>
-      <c r="H154" s="7"/>
-      <c r="I154" s="7"/>
-      <c r="J154" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K154" s="7"/>
-      <c r="L154" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M154" s="55">
-        <v>0</v>
-      </c>
-      <c r="N154" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O154" s="7"/>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K155" s="7"/>
-      <c r="L155" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M155" s="55">
-        <v>0</v>
-      </c>
-      <c r="N155" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O155" s="7"/>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
-      <c r="I156" s="7"/>
-      <c r="J156" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="7"/>
-      <c r="L156" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M156" s="55">
-        <v>0</v>
-      </c>
-      <c r="N156" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O156" s="7"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
-      <c r="I157" s="7"/>
-      <c r="J157" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K157" s="7"/>
-      <c r="L157" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M157" s="55">
-        <v>0</v>
-      </c>
-      <c r="N157" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O157" s="7"/>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K158" s="7"/>
-      <c r="L158" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="M158" s="55">
-        <v>0</v>
-      </c>
-      <c r="N158" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="O158" s="7"/>
+      <c r="O158" s="17"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A160" s="68" t="s">
-        <v>452</v>
+      <c r="A160" s="62" t="s">
+        <v>451</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5481,34 +5508,34 @@
       <c r="P160" s="3"/>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A161" s="69" t="s">
+      <c r="A161" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A162" s="63" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A162" s="69" t="s">
-        <v>457</v>
-      </c>
-    </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A163" s="69" t="s">
+      <c r="A163" s="63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A164" s="63" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A164" s="69" t="s">
-        <v>460</v>
-      </c>
-    </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A165" s="64" t="s">
-        <v>453</v>
+      <c r="A165" s="58" t="s">
+        <v>452</v>
       </c>
       <c r="C165" t="s">
         <v>202</v>
       </c>
       <c r="L165" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M165">
         <v>50</v>
@@ -5517,18 +5544,18 @@
         <v>38</v>
       </c>
       <c r="O165" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A166" s="64" t="s">
-        <v>453</v>
+      <c r="A166" s="58" t="s">
+        <v>452</v>
       </c>
       <c r="C166" t="s">
         <v>126</v>
       </c>
       <c r="L166" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M166">
         <v>50</v>
@@ -5884,7 +5911,7 @@
     </row>
     <row r="187" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K187" t="s">
         <v>50</v>
@@ -5901,7 +5928,7 @@
     </row>
     <row r="188" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K188" t="s">
         <v>51</v>
@@ -5918,7 +5945,7 @@
     </row>
     <row r="189" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K189" t="s">
         <v>52</v>
@@ -6154,318 +6181,318 @@
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="7"/>
-      <c r="B202" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="C202" s="7"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="7"/>
-      <c r="H202" s="7"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
-      <c r="K202" s="7" t="s">
+      <c r="B202" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="C202" s="17"/>
+      <c r="D202" s="17"/>
+      <c r="E202" s="17"/>
+      <c r="F202" s="17"/>
+      <c r="G202" s="17"/>
+      <c r="H202" s="17"/>
+      <c r="I202" s="17"/>
+      <c r="J202" s="17"/>
+      <c r="K202" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="L202" s="7" t="s">
+      <c r="L202" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M202" s="7">
+      <c r="M202" s="17">
         <v>11</v>
       </c>
-      <c r="N202" s="7" t="s">
+      <c r="N202" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O202" s="7"/>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="7"/>
-      <c r="B203" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="7"/>
-      <c r="I203" s="7"/>
-      <c r="J203" s="7"/>
-      <c r="K203" s="7" t="s">
+      <c r="B203" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="C203" s="17"/>
+      <c r="D203" s="17"/>
+      <c r="E203" s="17"/>
+      <c r="F203" s="17"/>
+      <c r="G203" s="17"/>
+      <c r="H203" s="17"/>
+      <c r="I203" s="17"/>
+      <c r="J203" s="17"/>
+      <c r="K203" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="L203" s="7" t="s">
+      <c r="L203" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M203" s="7">
+      <c r="M203" s="17">
         <v>4</v>
       </c>
-      <c r="N203" s="7" t="s">
+      <c r="N203" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O203" s="7"/>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="7"/>
-      <c r="B204" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="C204" s="7"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
-      <c r="G204" s="7"/>
-      <c r="H204" s="7"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
-      <c r="K204" s="7" t="s">
+      <c r="B204" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="C204" s="17"/>
+      <c r="D204" s="17"/>
+      <c r="E204" s="17"/>
+      <c r="F204" s="17"/>
+      <c r="G204" s="17"/>
+      <c r="H204" s="17"/>
+      <c r="I204" s="17"/>
+      <c r="J204" s="17"/>
+      <c r="K204" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="L204" s="7" t="s">
+      <c r="L204" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M204" s="7">
+      <c r="M204" s="17">
         <v>5</v>
       </c>
-      <c r="N204" s="7" t="s">
+      <c r="N204" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O204" s="7"/>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
-      <c r="B205" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C205" s="48"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
-      <c r="F205" s="7"/>
-      <c r="G205" s="7"/>
-      <c r="H205" s="7"/>
-      <c r="I205" s="7"/>
-      <c r="J205" s="7"/>
-      <c r="K205" s="7" t="s">
+      <c r="B205" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C205" s="58"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
+      <c r="F205" s="17"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="17"/>
+      <c r="I205" s="17"/>
+      <c r="J205" s="17"/>
+      <c r="K205" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="L205" s="7" t="s">
+      <c r="L205" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M205" s="7">
+      <c r="M205" s="17">
         <v>11</v>
       </c>
-      <c r="N205" s="7" t="s">
+      <c r="N205" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O205" s="7"/>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
-      <c r="B206" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C206" s="48"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
-      <c r="G206" s="7"/>
-      <c r="H206" s="7"/>
-      <c r="I206" s="7"/>
-      <c r="J206" s="7"/>
-      <c r="K206" s="7" t="s">
+      <c r="B206" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C206" s="58"/>
+      <c r="D206" s="17"/>
+      <c r="E206" s="17"/>
+      <c r="F206" s="17"/>
+      <c r="G206" s="17"/>
+      <c r="H206" s="17"/>
+      <c r="I206" s="17"/>
+      <c r="J206" s="17"/>
+      <c r="K206" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="L206" s="7" t="s">
+      <c r="L206" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M206" s="7">
+      <c r="M206" s="17">
         <f>0.5</f>
         <v>0.5</v>
       </c>
-      <c r="N206" s="7" t="s">
+      <c r="N206" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O206" s="7"/>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B207" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C207" s="48"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
-      <c r="G207" s="7"/>
-      <c r="H207" s="7"/>
-      <c r="I207" s="7"/>
-      <c r="J207" s="7"/>
-      <c r="K207" s="7" t="s">
+      <c r="B207" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C207" s="58"/>
+      <c r="D207" s="17"/>
+      <c r="E207" s="17"/>
+      <c r="F207" s="17"/>
+      <c r="G207" s="17"/>
+      <c r="H207" s="17"/>
+      <c r="I207" s="17"/>
+      <c r="J207" s="17"/>
+      <c r="K207" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="L207" s="7" t="s">
+      <c r="L207" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M207" s="7">
+      <c r="M207" s="17">
         <v>1</v>
       </c>
-      <c r="N207" s="7" t="s">
+      <c r="N207" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O207" s="6"/>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B208" s="48" t="s">
-        <v>390</v>
-      </c>
-      <c r="C208" s="48"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
-      <c r="G208" s="7"/>
-      <c r="H208" s="7"/>
-      <c r="I208" s="7"/>
-      <c r="J208" s="7"/>
-      <c r="K208" s="7" t="s">
+      <c r="B208" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="C208" s="58"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="17"/>
+      <c r="G208" s="17"/>
+      <c r="H208" s="17"/>
+      <c r="I208" s="17"/>
+      <c r="J208" s="17"/>
+      <c r="K208" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="L208" s="7" t="s">
+      <c r="L208" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M208" s="7">
+      <c r="M208" s="17">
         <v>4</v>
       </c>
-      <c r="N208" s="7" t="s">
+      <c r="N208" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O208" s="6"/>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B209" s="48" t="s">
-        <v>390</v>
-      </c>
-      <c r="C209" s="48"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
-      <c r="G209" s="7"/>
-      <c r="H209" s="7"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7"/>
-      <c r="K209" s="7" t="s">
+      <c r="B209" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="C209" s="58"/>
+      <c r="D209" s="17"/>
+      <c r="E209" s="17"/>
+      <c r="F209" s="17"/>
+      <c r="G209" s="17"/>
+      <c r="H209" s="17"/>
+      <c r="I209" s="17"/>
+      <c r="J209" s="17"/>
+      <c r="K209" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="L209" s="7" t="s">
+      <c r="L209" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M209" s="7">
+      <c r="M209" s="17">
         <v>1</v>
       </c>
-      <c r="N209" s="7" t="s">
+      <c r="N209" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O209" s="6"/>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B210" s="48" t="s">
-        <v>390</v>
-      </c>
-      <c r="C210" s="48"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="7"/>
-      <c r="H210" s="7"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
-      <c r="K210" s="7" t="s">
+      <c r="B210" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="C210" s="58"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="17"/>
+      <c r="G210" s="17"/>
+      <c r="H210" s="17"/>
+      <c r="I210" s="17"/>
+      <c r="J210" s="17"/>
+      <c r="K210" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="L210" s="7" t="s">
+      <c r="L210" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M210" s="7">
+      <c r="M210" s="17">
         <v>5</v>
       </c>
-      <c r="N210" s="7" t="s">
+      <c r="N210" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O210" s="6"/>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B211" s="48" t="s">
-        <v>394</v>
-      </c>
-      <c r="C211" s="48"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
-      <c r="H211" s="7"/>
-      <c r="I211" s="7"/>
-      <c r="J211" s="7"/>
-      <c r="K211" s="7" t="s">
+      <c r="B211" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="C211" s="58"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="17"/>
+      <c r="F211" s="17"/>
+      <c r="G211" s="17"/>
+      <c r="H211" s="17"/>
+      <c r="I211" s="17"/>
+      <c r="J211" s="17"/>
+      <c r="K211" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="L211" s="7" t="s">
+      <c r="L211" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M211" s="7">
+      <c r="M211" s="17">
         <v>4</v>
       </c>
-      <c r="N211" s="7" t="s">
+      <c r="N211" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O211" s="6"/>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B212" s="48" t="s">
-        <v>394</v>
-      </c>
-      <c r="C212" s="48"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
-      <c r="G212" s="7"/>
-      <c r="H212" s="7"/>
-      <c r="I212" s="7"/>
-      <c r="J212" s="7"/>
-      <c r="K212" s="7" t="s">
+      <c r="B212" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="C212" s="58"/>
+      <c r="D212" s="17"/>
+      <c r="E212" s="17"/>
+      <c r="F212" s="17"/>
+      <c r="G212" s="17"/>
+      <c r="H212" s="17"/>
+      <c r="I212" s="17"/>
+      <c r="J212" s="17"/>
+      <c r="K212" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="L212" s="7" t="s">
+      <c r="L212" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M212" s="7">
+      <c r="M212" s="17">
         <v>1</v>
       </c>
-      <c r="N212" s="7" t="s">
+      <c r="N212" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O212" s="6"/>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B213" s="48" t="s">
-        <v>394</v>
-      </c>
-      <c r="C213" s="48"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
-      <c r="G213" s="7"/>
-      <c r="H213" s="7"/>
-      <c r="I213" s="7"/>
-      <c r="J213" s="7"/>
-      <c r="K213" s="7" t="s">
+      <c r="B213" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="C213" s="58"/>
+      <c r="D213" s="17"/>
+      <c r="E213" s="17"/>
+      <c r="F213" s="17"/>
+      <c r="G213" s="17"/>
+      <c r="H213" s="17"/>
+      <c r="I213" s="17"/>
+      <c r="J213" s="17"/>
+      <c r="K213" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="L213" s="7" t="s">
+      <c r="L213" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M213" s="7">
+      <c r="M213" s="17">
         <v>5</v>
       </c>
-      <c r="N213" s="7" t="s">
+      <c r="N213" s="17" t="s">
         <v>38</v>
       </c>
       <c r="O213" s="6"/>
@@ -6562,7 +6589,7 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L220" t="s">
         <v>40</v>
@@ -6576,7 +6603,7 @@
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L221" t="s">
         <v>40</v>
@@ -6739,7 +6766,7 @@
     </row>
     <row r="231" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L231" s="17" t="s">
         <v>40</v>
@@ -7006,7 +7033,7 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
@@ -7028,7 +7055,7 @@
         <v>38</v>
       </c>
       <c r="O248" s="17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
@@ -7181,7 +7208,7 @@
       <c r="L258" s="5"/>
       <c r="M258" s="5"/>
       <c r="N258" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O258" s="41">
         <v>0.81799999999999995</v>
@@ -7325,7 +7352,7 @@
     </row>
     <row r="268" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L268" s="17" t="s">
         <v>40</v>
@@ -7337,7 +7364,7 @@
         <v>38</v>
       </c>
       <c r="O268" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.25">
@@ -7392,7 +7419,7 @@
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L272" t="s">
         <v>40</v>
@@ -7455,15 +7482,15 @@
         <v>38</v>
       </c>
       <c r="O275" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P275" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
@@ -7593,7 +7620,7 @@
     </row>
     <row r="283" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B283" s="19"/>
       <c r="C283" s="19"/>
@@ -7615,13 +7642,13 @@
         <v>38</v>
       </c>
       <c r="O283" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P283" s="19"/>
     </row>
     <row r="284" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B284" s="19"/>
       <c r="C284" s="19"/>
@@ -7643,7 +7670,7 @@
         <v>38</v>
       </c>
       <c r="O284" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P284" s="19"/>
     </row>
@@ -7654,7 +7681,7 @@
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
-      <c r="E285" s="50"/>
+      <c r="E285" s="48"/>
       <c r="F285" s="4"/>
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
@@ -7669,7 +7696,7 @@
     </row>
     <row r="286" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B286" s="19"/>
       <c r="C286" s="19"/>
@@ -7684,20 +7711,20 @@
       <c r="L286" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="M286" s="58">
+      <c r="M286" s="52">
         <v>100</v>
       </c>
       <c r="N286" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O286" s="56" t="s">
-        <v>420</v>
-      </c>
-      <c r="P286" s="56"/>
+      <c r="O286" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="P286" s="50"/>
     </row>
     <row r="287" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B287" s="19"/>
       <c r="C287" s="19"/>
@@ -7712,40 +7739,40 @@
       <c r="L287" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="M287" s="58">
+      <c r="M287" s="52">
         <v>100</v>
       </c>
       <c r="N287" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O287" s="56" t="s">
-        <v>420</v>
-      </c>
-      <c r="P287" s="56"/>
+      <c r="O287" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="P287" s="50"/>
     </row>
     <row r="288" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="B288" s="60"/>
-      <c r="C288" s="60"/>
-      <c r="D288" s="60"/>
-      <c r="E288" s="60"/>
-      <c r="F288" s="60"/>
-      <c r="G288" s="60"/>
-      <c r="H288" s="60"/>
-      <c r="I288" s="60"/>
-      <c r="J288" s="60"/>
-      <c r="K288" s="60"/>
-      <c r="L288" s="61"/>
-      <c r="M288" s="62"/>
-      <c r="N288" s="61"/>
-      <c r="O288" s="57"/>
-      <c r="P288" s="57"/>
+      <c r="A288" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="B288" s="54"/>
+      <c r="C288" s="54"/>
+      <c r="D288" s="54"/>
+      <c r="E288" s="54"/>
+      <c r="F288" s="54"/>
+      <c r="G288" s="54"/>
+      <c r="H288" s="54"/>
+      <c r="I288" s="54"/>
+      <c r="J288" s="54"/>
+      <c r="K288" s="54"/>
+      <c r="L288" s="55"/>
+      <c r="M288" s="56"/>
+      <c r="N288" s="55"/>
+      <c r="O288" s="51"/>
+      <c r="P288" s="51"/>
     </row>
     <row r="289" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B289" s="19"/>
       <c r="C289" s="19"/>
@@ -7760,16 +7787,16 @@
       <c r="L289" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="M289" s="58">
+      <c r="M289" s="52">
         <v>100</v>
       </c>
       <c r="N289" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O289" s="56" t="s">
-        <v>420</v>
-      </c>
-      <c r="P289" s="56"/>
+      <c r="O289" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="P289" s="50"/>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
@@ -7808,7 +7835,7 @@
     </row>
     <row r="292" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L292" s="17" t="s">
         <v>40</v>
@@ -7819,8 +7846,8 @@
       <c r="N292" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O292" s="63" t="s">
-        <v>421</v>
+      <c r="O292" s="57" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="293" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -7836,7 +7863,7 @@
       <c r="N293" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O293" s="63"/>
+      <c r="O293" s="57"/>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
@@ -7993,119 +8020,119 @@
       </c>
     </row>
     <row r="303" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="59" t="s">
+      <c r="A303" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B303" s="59"/>
-      <c r="C303" s="59"/>
-      <c r="D303" s="59"/>
-      <c r="E303" s="59"/>
-      <c r="F303" s="59"/>
-      <c r="G303" s="59"/>
-      <c r="H303" s="59"/>
-      <c r="I303" s="59"/>
-      <c r="J303" s="59"/>
-      <c r="K303" s="59"/>
-      <c r="L303" s="61"/>
-      <c r="M303" s="61"/>
-      <c r="N303" s="61"/>
-      <c r="O303" s="61"/>
-      <c r="P303" s="61"/>
+      <c r="B303" s="53"/>
+      <c r="C303" s="53"/>
+      <c r="D303" s="53"/>
+      <c r="E303" s="53"/>
+      <c r="F303" s="53"/>
+      <c r="G303" s="53"/>
+      <c r="H303" s="53"/>
+      <c r="I303" s="53"/>
+      <c r="J303" s="53"/>
+      <c r="K303" s="53"/>
+      <c r="L303" s="55"/>
+      <c r="M303" s="55"/>
+      <c r="N303" s="55"/>
+      <c r="O303" s="55"/>
+      <c r="P303" s="55"/>
     </row>
     <row r="304" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="64" t="s">
+      <c r="A304" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B304" s="58" t="s">
         <v>397</v>
       </c>
-      <c r="B304" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C304" s="64"/>
-      <c r="D304" s="65"/>
-      <c r="E304" s="65"/>
-      <c r="F304" s="65"/>
-      <c r="G304" s="65"/>
-      <c r="H304" s="65"/>
-      <c r="I304" s="65"/>
-      <c r="J304" s="65"/>
-      <c r="K304" s="65"/>
-      <c r="L304" s="64" t="s">
+      <c r="C304" s="58"/>
+      <c r="D304" s="59"/>
+      <c r="E304" s="59"/>
+      <c r="F304" s="59"/>
+      <c r="G304" s="59"/>
+      <c r="H304" s="59"/>
+      <c r="I304" s="59"/>
+      <c r="J304" s="59"/>
+      <c r="K304" s="59"/>
+      <c r="L304" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M304" s="17">
         <v>5</v>
       </c>
-      <c r="N304" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O304" s="64" t="s">
+      <c r="N304" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O304" s="58" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="58" t="s">
+        <v>398</v>
+      </c>
+      <c r="B305" s="58" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="305" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="B305" s="64" t="s">
-        <v>423</v>
-      </c>
-      <c r="C305" s="64"/>
-      <c r="D305" s="65"/>
-      <c r="E305" s="65"/>
-      <c r="F305" s="65"/>
-      <c r="G305" s="65"/>
-      <c r="H305" s="65"/>
-      <c r="I305" s="65"/>
-      <c r="J305" s="65"/>
-      <c r="K305" s="65"/>
-      <c r="L305" s="64" t="s">
+      <c r="C305" s="58"/>
+      <c r="D305" s="59"/>
+      <c r="E305" s="59"/>
+      <c r="F305" s="59"/>
+      <c r="G305" s="59"/>
+      <c r="H305" s="59"/>
+      <c r="I305" s="59"/>
+      <c r="J305" s="59"/>
+      <c r="K305" s="59"/>
+      <c r="L305" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M305" s="17">
         <v>100</v>
       </c>
-      <c r="N305" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O305" s="64" t="s">
-        <v>424</v>
+      <c r="N305" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O305" s="58" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="306" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B306" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C306" s="64"/>
-      <c r="D306" s="64"/>
-      <c r="E306" s="64"/>
-      <c r="F306" s="64"/>
-      <c r="G306" s="64"/>
-      <c r="H306" s="64"/>
-      <c r="I306" s="64"/>
-      <c r="J306" s="64"/>
-      <c r="K306" s="64"/>
-      <c r="L306" s="64" t="s">
+      <c r="A306" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B306" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C306" s="58"/>
+      <c r="D306" s="58"/>
+      <c r="E306" s="58"/>
+      <c r="F306" s="58"/>
+      <c r="G306" s="58"/>
+      <c r="H306" s="58"/>
+      <c r="I306" s="58"/>
+      <c r="J306" s="58"/>
+      <c r="K306" s="58"/>
+      <c r="L306" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M306" s="17">
         <v>22</v>
       </c>
-      <c r="N306" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O306" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="P306" s="64"/>
+      <c r="N306" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O306" s="58" t="s">
+        <v>424</v>
+      </c>
+      <c r="P306" s="58"/>
     </row>
     <row r="307" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B307" s="17" t="s">
         <v>402</v>
-      </c>
-      <c r="B307" s="17" t="s">
-        <v>403</v>
       </c>
       <c r="L307" s="17" t="s">
         <v>40</v>
@@ -8116,27 +8143,27 @@
       <c r="N307" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O307" s="64" t="s">
-        <v>426</v>
+      <c r="O307" s="58" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="308" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="B308" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C308" s="64"/>
-      <c r="D308" s="65"/>
-      <c r="E308" s="65"/>
-      <c r="F308" s="65"/>
-      <c r="G308" s="65"/>
-      <c r="H308" s="65"/>
-      <c r="I308" s="65"/>
-      <c r="J308" s="65"/>
-      <c r="K308" s="65"/>
-      <c r="L308" s="64" t="s">
+      <c r="A308" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B308" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C308" s="58"/>
+      <c r="D308" s="59"/>
+      <c r="E308" s="59"/>
+      <c r="F308" s="59"/>
+      <c r="G308" s="59"/>
+      <c r="H308" s="59"/>
+      <c r="I308" s="59"/>
+      <c r="J308" s="59"/>
+      <c r="K308" s="59"/>
+      <c r="L308" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M308" s="17">
@@ -8145,27 +8172,27 @@
       <c r="N308" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O308" s="64" t="s">
-        <v>427</v>
+      <c r="O308" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="309" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="B309" s="64" t="s">
-        <v>403</v>
-      </c>
-      <c r="C309" s="64"/>
-      <c r="D309" s="65"/>
-      <c r="E309" s="65"/>
-      <c r="F309" s="65"/>
-      <c r="G309" s="65"/>
-      <c r="H309" s="65"/>
-      <c r="I309" s="65"/>
-      <c r="J309" s="65"/>
-      <c r="K309" s="65"/>
-      <c r="L309" s="64" t="s">
+      <c r="A309" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B309" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C309" s="58"/>
+      <c r="D309" s="59"/>
+      <c r="E309" s="59"/>
+      <c r="F309" s="59"/>
+      <c r="G309" s="59"/>
+      <c r="H309" s="59"/>
+      <c r="I309" s="59"/>
+      <c r="J309" s="59"/>
+      <c r="K309" s="59"/>
+      <c r="L309" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M309" s="17">
@@ -8174,27 +8201,27 @@
       <c r="N309" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O309" s="64" t="s">
-        <v>427</v>
+      <c r="O309" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="310" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="64" t="s">
-        <v>406</v>
-      </c>
-      <c r="B310" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C310" s="64"/>
-      <c r="D310" s="65"/>
-      <c r="E310" s="65"/>
-      <c r="F310" s="65"/>
-      <c r="G310" s="65"/>
-      <c r="H310" s="65"/>
-      <c r="I310" s="65"/>
-      <c r="J310" s="65"/>
-      <c r="K310" s="65"/>
-      <c r="L310" s="64" t="s">
+      <c r="A310" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B310" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C310" s="58"/>
+      <c r="D310" s="59"/>
+      <c r="E310" s="59"/>
+      <c r="F310" s="59"/>
+      <c r="G310" s="59"/>
+      <c r="H310" s="59"/>
+      <c r="I310" s="59"/>
+      <c r="J310" s="59"/>
+      <c r="K310" s="59"/>
+      <c r="L310" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M310" s="17">
@@ -8203,174 +8230,174 @@
       <c r="N310" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O310" s="64" t="s">
-        <v>427</v>
+      <c r="O310" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="311" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="64" t="s">
-        <v>407</v>
-      </c>
-      <c r="B311" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C311" s="64"/>
-      <c r="D311" s="65"/>
-      <c r="E311" s="65"/>
-      <c r="F311" s="65"/>
-      <c r="G311" s="65"/>
-      <c r="H311" s="65"/>
-      <c r="I311" s="65"/>
-      <c r="J311" s="65"/>
-      <c r="K311" s="65"/>
-      <c r="L311" s="64" t="s">
+      <c r="A311" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B311" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C311" s="58"/>
+      <c r="D311" s="59"/>
+      <c r="E311" s="59"/>
+      <c r="F311" s="59"/>
+      <c r="G311" s="59"/>
+      <c r="H311" s="59"/>
+      <c r="I311" s="59"/>
+      <c r="J311" s="59"/>
+      <c r="K311" s="59"/>
+      <c r="L311" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M311" s="17">
         <v>0.4</v>
       </c>
-      <c r="N311" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O311" s="64" t="s">
-        <v>428</v>
+      <c r="N311" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O311" s="58" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="312" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="64" t="s">
-        <v>408</v>
-      </c>
-      <c r="B312" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C312" s="64"/>
-      <c r="D312" s="65"/>
-      <c r="E312" s="65"/>
-      <c r="F312" s="65"/>
-      <c r="G312" s="65"/>
-      <c r="H312" s="65"/>
-      <c r="I312" s="65"/>
-      <c r="J312" s="65"/>
-      <c r="K312" s="65"/>
-      <c r="L312" s="64" t="s">
+      <c r="A312" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="B312" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C312" s="58"/>
+      <c r="D312" s="59"/>
+      <c r="E312" s="59"/>
+      <c r="F312" s="59"/>
+      <c r="G312" s="59"/>
+      <c r="H312" s="59"/>
+      <c r="I312" s="59"/>
+      <c r="J312" s="59"/>
+      <c r="K312" s="59"/>
+      <c r="L312" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M312" s="17">
         <v>0.4</v>
       </c>
-      <c r="N312" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O312" s="64" t="s">
-        <v>428</v>
+      <c r="N312" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O312" s="58" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="313" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="B313" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C313" s="64"/>
-      <c r="D313" s="65"/>
-      <c r="E313" s="65"/>
-      <c r="F313" s="65"/>
-      <c r="G313" s="65"/>
-      <c r="H313" s="65"/>
-      <c r="I313" s="65"/>
-      <c r="J313" s="65"/>
-      <c r="K313" s="65"/>
-      <c r="L313" s="64" t="s">
+      <c r="A313" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B313" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C313" s="58"/>
+      <c r="D313" s="59"/>
+      <c r="E313" s="59"/>
+      <c r="F313" s="59"/>
+      <c r="G313" s="59"/>
+      <c r="H313" s="59"/>
+      <c r="I313" s="59"/>
+      <c r="J313" s="59"/>
+      <c r="K313" s="59"/>
+      <c r="L313" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M313" s="17">
         <v>24</v>
       </c>
-      <c r="N313" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O313" s="64" t="s">
-        <v>427</v>
+      <c r="N313" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O313" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="314" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="64" t="s">
+      <c r="A314" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="B314" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C314" s="58"/>
+      <c r="D314" s="59"/>
+      <c r="E314" s="59"/>
+      <c r="F314" s="59"/>
+      <c r="G314" s="59"/>
+      <c r="H314" s="59"/>
+      <c r="I314" s="59"/>
+      <c r="J314" s="59"/>
+      <c r="K314" s="59"/>
+      <c r="L314" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="M314" s="58">
+        <v>0</v>
+      </c>
+      <c r="N314" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O314" s="58" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="58" t="s">
         <v>410</v>
       </c>
-      <c r="B314" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C314" s="64"/>
-      <c r="D314" s="65"/>
-      <c r="E314" s="65"/>
-      <c r="F314" s="65"/>
-      <c r="G314" s="65"/>
-      <c r="H314" s="65"/>
-      <c r="I314" s="65"/>
-      <c r="J314" s="65"/>
-      <c r="K314" s="65"/>
-      <c r="L314" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="M314" s="64">
-        <v>0</v>
-      </c>
-      <c r="N314" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O314" s="64" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="315" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="B315" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C315" s="64"/>
-      <c r="D315" s="65"/>
-      <c r="E315" s="65"/>
-      <c r="F315" s="65"/>
-      <c r="G315" s="65"/>
-      <c r="H315" s="65"/>
-      <c r="I315" s="65"/>
-      <c r="J315" s="65"/>
-      <c r="K315" s="65"/>
-      <c r="L315" s="64" t="s">
+      <c r="B315" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C315" s="58"/>
+      <c r="D315" s="59"/>
+      <c r="E315" s="59"/>
+      <c r="F315" s="59"/>
+      <c r="G315" s="59"/>
+      <c r="H315" s="59"/>
+      <c r="I315" s="59"/>
+      <c r="J315" s="59"/>
+      <c r="K315" s="59"/>
+      <c r="L315" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M315" s="17">
         <v>24</v>
       </c>
-      <c r="N315" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O315" s="64" t="s">
-        <v>427</v>
+      <c r="N315" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O315" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="316" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="B316" s="64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C316" s="64"/>
-      <c r="L316" s="64" t="s">
+      <c r="A316" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B316" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C316" s="58"/>
+      <c r="L316" s="58" t="s">
         <v>40</v>
       </c>
       <c r="M316" s="17">
         <v>24</v>
       </c>
-      <c r="N316" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O316" s="64" t="s">
-        <v>427</v>
+      <c r="N316" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O316" s="58" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.25">
@@ -8683,7 +8710,7 @@
     </row>
     <row r="332" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I332" s="17" t="s">
         <v>87</v>
@@ -8701,7 +8728,7 @@
         <v>38</v>
       </c>
       <c r="O332" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.25">
@@ -8858,7 +8885,7 @@
     </row>
     <row r="340" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I340" s="17" t="s">
         <v>87</v>
@@ -8876,7 +8903,7 @@
         <v>38</v>
       </c>
       <c r="O340" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P340" s="17" t="s">
         <v>167</v>
@@ -9208,7 +9235,7 @@
         <v>38</v>
       </c>
       <c r="O354" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.25">
@@ -9231,12 +9258,12 @@
         <v>38</v>
       </c>
       <c r="O355" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I356" t="s">
         <v>87</v>
@@ -9254,7 +9281,7 @@
         <v>38</v>
       </c>
       <c r="O356" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="357" spans="1:16" x14ac:dyDescent="0.25">
@@ -9277,7 +9304,7 @@
         <v>38</v>
       </c>
       <c r="O357" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.25">
@@ -9320,7 +9347,7 @@
         <v>38</v>
       </c>
       <c r="O359" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P359" s="26" t="s">
         <v>215</v>
@@ -9328,7 +9355,7 @@
     </row>
     <row r="360" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I360" s="17" t="s">
         <v>87</v>
@@ -9390,28 +9417,28 @@
       </c>
     </row>
     <row r="363" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="59" t="s">
+      <c r="A363" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="B363" s="59"/>
-      <c r="C363" s="59"/>
-      <c r="D363" s="59"/>
-      <c r="E363" s="59"/>
-      <c r="F363" s="59"/>
-      <c r="G363" s="59"/>
-      <c r="H363" s="59"/>
-      <c r="I363" s="59"/>
-      <c r="J363" s="59"/>
-      <c r="K363" s="59"/>
-      <c r="L363" s="61"/>
-      <c r="M363" s="61"/>
-      <c r="N363" s="61"/>
-      <c r="O363" s="61"/>
-      <c r="P363" s="61"/>
+      <c r="B363" s="53"/>
+      <c r="C363" s="53"/>
+      <c r="D363" s="53"/>
+      <c r="E363" s="53"/>
+      <c r="F363" s="53"/>
+      <c r="G363" s="53"/>
+      <c r="H363" s="53"/>
+      <c r="I363" s="53"/>
+      <c r="J363" s="53"/>
+      <c r="K363" s="53"/>
+      <c r="L363" s="55"/>
+      <c r="M363" s="55"/>
+      <c r="N363" s="55"/>
+      <c r="O363" s="55"/>
+      <c r="P363" s="55"/>
     </row>
     <row r="364" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I364" s="17" t="s">
         <v>87</v>
@@ -9429,12 +9456,12 @@
         <v>38</v>
       </c>
       <c r="O364" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="365" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I365" s="17" t="s">
         <v>87</v>
@@ -9452,32 +9479,32 @@
         <v>38</v>
       </c>
       <c r="O365" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="366" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="B366" s="61"/>
-      <c r="C366" s="61"/>
-      <c r="D366" s="61"/>
-      <c r="E366" s="61"/>
-      <c r="F366" s="61"/>
-      <c r="G366" s="61"/>
-      <c r="H366" s="61"/>
-      <c r="I366" s="61"/>
-      <c r="J366" s="61"/>
-      <c r="K366" s="61"/>
-      <c r="L366" s="61"/>
-      <c r="M366" s="61"/>
-      <c r="N366" s="61"/>
-      <c r="O366" s="61"/>
-      <c r="P366" s="61"/>
+      <c r="A366" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="B366" s="55"/>
+      <c r="C366" s="55"/>
+      <c r="D366" s="55"/>
+      <c r="E366" s="55"/>
+      <c r="F366" s="55"/>
+      <c r="G366" s="55"/>
+      <c r="H366" s="55"/>
+      <c r="I366" s="55"/>
+      <c r="J366" s="55"/>
+      <c r="K366" s="55"/>
+      <c r="L366" s="55"/>
+      <c r="M366" s="55"/>
+      <c r="N366" s="55"/>
+      <c r="O366" s="55"/>
+      <c r="P366" s="55"/>
     </row>
     <row r="367" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I367" s="17" t="s">
         <v>87</v>
@@ -9495,7 +9522,7 @@
         <v>38</v>
       </c>
       <c r="O367" s="17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="368" spans="1:16" x14ac:dyDescent="0.25">
@@ -9539,30 +9566,30 @@
       </c>
     </row>
     <row r="370" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="64" t="s">
-        <v>395</v>
-      </c>
-      <c r="B370" s="64"/>
-      <c r="C370" s="64"/>
-      <c r="D370" s="64"/>
-      <c r="E370" s="64"/>
-      <c r="F370" s="64"/>
-      <c r="G370" s="64"/>
-      <c r="H370" s="64"/>
-      <c r="I370" s="64" t="s">
+      <c r="A370" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="B370" s="58"/>
+      <c r="C370" s="58"/>
+      <c r="D370" s="58"/>
+      <c r="E370" s="58"/>
+      <c r="F370" s="58"/>
+      <c r="G370" s="58"/>
+      <c r="H370" s="58"/>
+      <c r="I370" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="J370" s="64" t="s">
+      <c r="J370" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="K370" s="64"/>
-      <c r="L370" s="64" t="s">
+      <c r="K370" s="58"/>
+      <c r="L370" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="M370" s="66">
+      <c r="M370" s="60">
         <v>1</v>
       </c>
-      <c r="N370" s="64" t="s">
+      <c r="N370" s="58" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9685,7 +9712,7 @@
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
-      <c r="E376" s="50"/>
+      <c r="E376" s="48"/>
       <c r="F376" s="4"/>
       <c r="G376" s="4"/>
       <c r="H376" s="4"/>
@@ -9699,50 +9726,50 @@
       <c r="P376" s="5"/>
     </row>
     <row r="377" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="B377" s="64"/>
-      <c r="C377" s="64"/>
-      <c r="D377" s="65"/>
-      <c r="E377" s="65"/>
-      <c r="F377" s="65"/>
-      <c r="G377" s="65"/>
-      <c r="H377" s="65"/>
-      <c r="I377" s="65"/>
-      <c r="J377" s="64" t="s">
+      <c r="A377" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B377" s="58"/>
+      <c r="C377" s="58"/>
+      <c r="D377" s="59"/>
+      <c r="E377" s="59"/>
+      <c r="F377" s="59"/>
+      <c r="G377" s="59"/>
+      <c r="H377" s="59"/>
+      <c r="I377" s="59"/>
+      <c r="J377" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="K377" s="65"/>
+      <c r="K377" s="59"/>
       <c r="L377" s="17" t="s">
         <v>41</v>
       </c>
       <c r="M377" s="17">
         <v>34.200000000000003</v>
       </c>
-      <c r="N377" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O377" s="64" t="s">
-        <v>422</v>
+      <c r="N377" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O377" s="58" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="378" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B378" s="64"/>
-      <c r="C378" s="64"/>
-      <c r="D378" s="64"/>
-      <c r="E378" s="64"/>
-      <c r="F378" s="64"/>
-      <c r="G378" s="64"/>
-      <c r="H378" s="64"/>
-      <c r="I378" s="64"/>
-      <c r="J378" s="64" t="s">
+      <c r="A378" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B378" s="58"/>
+      <c r="C378" s="58"/>
+      <c r="D378" s="58"/>
+      <c r="E378" s="58"/>
+      <c r="F378" s="58"/>
+      <c r="G378" s="58"/>
+      <c r="H378" s="58"/>
+      <c r="I378" s="58"/>
+      <c r="J378" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="K378" s="64"/>
+      <c r="K378" s="58"/>
       <c r="L378" s="17" t="s">
         <v>41</v>
       </c>
@@ -9752,13 +9779,13 @@
       <c r="N378" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O378" s="64" t="s">
-        <v>425</v>
+      <c r="O378" s="58" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="379" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J379" s="17" t="s">
         <v>43</v>
@@ -9772,8 +9799,8 @@
       <c r="N379" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O379" s="64" t="s">
-        <v>426</v>
+      <c r="O379" s="58" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.25">
@@ -9872,7 +9899,7 @@
         <v>37</v>
       </c>
       <c r="H387" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L387" t="s">
         <v>86</v>
@@ -9885,7 +9912,7 @@
         <v>38</v>
       </c>
       <c r="O387" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P387" t="s">
         <v>92</v>
@@ -9908,7 +9935,7 @@
         <v>38</v>
       </c>
       <c r="P388" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.25">
@@ -9919,7 +9946,7 @@
         <v>37</v>
       </c>
       <c r="H389" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L389" t="s">
         <v>86</v>
@@ -9931,10 +9958,10 @@
         <v>38</v>
       </c>
       <c r="O389" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P389" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.25">
@@ -9980,7 +10007,7 @@
       <c r="F391" s="8"/>
       <c r="G391" s="8"/>
       <c r="H391" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I391" s="8"/>
       <c r="J391" s="8"/>
@@ -9995,7 +10022,7 @@
         <v>38</v>
       </c>
       <c r="O391" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P391" t="s">
         <v>92</v>
@@ -10044,7 +10071,7 @@
       <c r="F393" s="8"/>
       <c r="G393" s="8"/>
       <c r="H393" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I393" s="8"/>
       <c r="J393" s="8"/>
@@ -10059,7 +10086,7 @@
         <v>38</v>
       </c>
       <c r="O393" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P393" t="s">
         <v>92</v>
@@ -10108,7 +10135,7 @@
       <c r="F395" s="8"/>
       <c r="G395" s="8"/>
       <c r="H395" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I395" s="8"/>
       <c r="J395" s="8"/>
@@ -10123,7 +10150,7 @@
         <v>38</v>
       </c>
       <c r="O395" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P395" t="s">
         <v>92</v>
@@ -10202,7 +10229,7 @@
       <c r="F398" s="8"/>
       <c r="G398" s="8"/>
       <c r="H398" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I398" s="8"/>
       <c r="J398" s="8"/>
@@ -10218,7 +10245,7 @@
         <v>38</v>
       </c>
       <c r="O398" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P398" t="s">
         <v>92</v>
@@ -10267,7 +10294,7 @@
       <c r="F400" s="8"/>
       <c r="G400" s="8"/>
       <c r="H400" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I400" s="8"/>
       <c r="J400" s="8"/>
@@ -10282,7 +10309,7 @@
         <v>38</v>
       </c>
       <c r="O400" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P400" t="s">
         <v>92</v>
@@ -10314,7 +10341,7 @@
         <v>38</v>
       </c>
       <c r="O401" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P401" s="8"/>
     </row>
@@ -10344,7 +10371,7 @@
         <v>38</v>
       </c>
       <c r="O402" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P402" s="8"/>
     </row>
@@ -10374,7 +10401,7 @@
         <v>38</v>
       </c>
       <c r="O403" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P403" s="8"/>
     </row>
@@ -10404,7 +10431,7 @@
         <v>38</v>
       </c>
       <c r="O404" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P404" s="8"/>
     </row>
@@ -10644,10 +10671,10 @@
     </row>
     <row r="414" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D414" s="18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E414" s="18"/>
       <c r="L414" s="17" t="s">
@@ -11593,7 +11620,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B450" s="8"/>
       <c r="C450" s="8"/>
@@ -11658,7 +11685,7 @@
         <v>38</v>
       </c>
       <c r="O452" s="46" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P452" s="8" t="s">
         <v>92</v>
@@ -11837,7 +11864,7 @@
         <v>38</v>
       </c>
       <c r="O457" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P457" s="8" t="s">
         <v>92</v>
@@ -11990,14 +12017,14 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B462" s="8"/>
       <c r="C462" s="8"/>
       <c r="D462" s="8"/>
       <c r="E462" s="8"/>
       <c r="F462" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G462" s="9" t="s">
         <v>55</v>
@@ -12016,28 +12043,28 @@
         <v>38</v>
       </c>
       <c r="O462" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P462" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B463" s="8"/>
       <c r="C463" s="8"/>
       <c r="D463" s="8"/>
       <c r="E463" s="8"/>
       <c r="F463" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G463" s="9" t="s">
         <v>55</v>
       </c>
       <c r="H463" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I463" s="26"/>
       <c r="J463" s="26"/>
@@ -12053,28 +12080,28 @@
         <v>38</v>
       </c>
       <c r="O463" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P463" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B464" s="8"/>
       <c r="C464" s="8"/>
       <c r="D464" s="8"/>
       <c r="E464" s="8"/>
       <c r="F464" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G464" s="9" t="s">
         <v>55</v>
       </c>
       <c r="H464" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I464" s="8"/>
       <c r="J464" s="8"/>
@@ -12090,28 +12117,28 @@
         <v>38</v>
       </c>
       <c r="O464" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P464" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B465" s="8"/>
       <c r="C465" s="8"/>
       <c r="D465" s="8"/>
       <c r="E465" s="8"/>
       <c r="F465" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G465" s="9" t="s">
         <v>55</v>
       </c>
       <c r="H465" s="26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I465" s="8"/>
       <c r="J465" s="8"/>
@@ -12127,10 +12154,10 @@
         <v>38</v>
       </c>
       <c r="O465" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P465" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.25">
@@ -12161,10 +12188,10 @@
         <v>38</v>
       </c>
       <c r="O466" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P466" s="47" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.25">
@@ -12224,7 +12251,7 @@
         <v>268</v>
       </c>
       <c r="G469" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H469" s="8"/>
       <c r="I469" s="8"/>
@@ -12244,7 +12271,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A470" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B470" s="10"/>
       <c r="C470" s="10"/>
@@ -12254,7 +12281,7 @@
         <v>268</v>
       </c>
       <c r="G470" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H470" s="10"/>
       <c r="I470" s="10"/>
@@ -12355,7 +12382,7 @@
       <c r="B476" s="19"/>
       <c r="C476" s="19"/>
       <c r="D476" s="19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E476" s="19"/>
       <c r="F476" s="18"/>
@@ -12378,12 +12405,12 @@
     </row>
     <row r="477" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B477" s="19"/>
       <c r="C477" s="19"/>
       <c r="D477" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E477" s="19"/>
       <c r="F477" s="18"/>
@@ -12406,12 +12433,12 @@
     </row>
     <row r="478" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B478" s="19"/>
       <c r="C478" s="19"/>
       <c r="D478" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E478" s="19"/>
       <c r="F478" s="18"/>
@@ -12552,7 +12579,7 @@
     </row>
     <row r="484" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D484" s="17" t="s">
         <v>128</v>
@@ -12573,7 +12600,7 @@
     </row>
     <row r="485" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D485" s="17" t="s">
         <v>128</v>
@@ -12597,7 +12624,7 @@
     </row>
     <row r="486" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D486" s="17" t="s">
         <v>128</v>
@@ -12618,7 +12645,7 @@
     </row>
     <row r="487" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D487" s="17" t="s">
         <v>128</v>
@@ -12645,7 +12672,7 @@
         <v>133</v>
       </c>
       <c r="D488" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L488" s="17" t="s">
         <v>85</v>
@@ -12657,7 +12684,7 @@
         <v>38</v>
       </c>
       <c r="O488" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P488" s="19"/>
     </row>
@@ -12666,10 +12693,10 @@
         <v>133</v>
       </c>
       <c r="D489" s="17" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H489" s="17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L489" s="17" t="s">
         <v>86</v>
@@ -12720,10 +12747,10 @@
         <v>38</v>
       </c>
       <c r="O491" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P491" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.25">
@@ -12747,10 +12774,10 @@
         <v>38</v>
       </c>
       <c r="O492" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P492" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.25">
@@ -12774,10 +12801,10 @@
         <v>38</v>
       </c>
       <c r="O493" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P493" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.25">
@@ -12798,7 +12825,7 @@
         <v>38</v>
       </c>
       <c r="O494" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.25">
@@ -13104,7 +13131,7 @@
         <v>38</v>
       </c>
       <c r="O506" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P506" s="10" t="s">
         <v>92</v>
@@ -13117,7 +13144,7 @@
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
       <c r="D507" s="4"/>
-      <c r="E507" s="50"/>
+      <c r="E507" s="48"/>
       <c r="F507" s="4"/>
       <c r="G507" s="4"/>
       <c r="H507" s="4"/>
@@ -13131,51 +13158,51 @@
       <c r="P507" s="5"/>
     </row>
     <row r="508" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="B508" s="64"/>
-      <c r="C508" s="64"/>
-      <c r="D508" s="64" t="s">
+      <c r="A508" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B508" s="58"/>
+      <c r="C508" s="58"/>
+      <c r="D508" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="E508" s="64"/>
-      <c r="F508" s="65"/>
-      <c r="G508" s="65"/>
-      <c r="H508" s="65"/>
-      <c r="I508" s="65"/>
-      <c r="J508" s="64"/>
-      <c r="K508" s="65"/>
+      <c r="E508" s="58"/>
+      <c r="F508" s="59"/>
+      <c r="G508" s="59"/>
+      <c r="H508" s="59"/>
+      <c r="I508" s="59"/>
+      <c r="J508" s="58"/>
+      <c r="K508" s="59"/>
       <c r="L508" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M508" s="58">
+      <c r="M508" s="52">
         <v>94</v>
       </c>
-      <c r="N508" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O508" s="64"/>
+      <c r="N508" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O508" s="58"/>
       <c r="P508" s="19"/>
     </row>
     <row r="509" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="64" t="s">
-        <v>397</v>
-      </c>
-      <c r="B509" s="64"/>
-      <c r="C509" s="64"/>
-      <c r="D509" s="64" t="s">
+      <c r="A509" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B509" s="58"/>
+      <c r="C509" s="58"/>
+      <c r="D509" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="E509" s="64"/>
-      <c r="F509" s="65"/>
-      <c r="G509" s="65"/>
-      <c r="H509" s="64" t="s">
-        <v>441</v>
-      </c>
-      <c r="I509" s="65"/>
-      <c r="J509" s="64"/>
-      <c r="K509" s="65"/>
+      <c r="E509" s="58"/>
+      <c r="F509" s="59"/>
+      <c r="G509" s="59"/>
+      <c r="H509" s="58" t="s">
+        <v>440</v>
+      </c>
+      <c r="I509" s="59"/>
+      <c r="J509" s="58"/>
+      <c r="K509" s="59"/>
       <c r="L509" s="17" t="s">
         <v>86</v>
       </c>
@@ -13183,62 +13210,62 @@
         <f>11*0.94</f>
         <v>10.34</v>
       </c>
-      <c r="N509" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O509" s="64" t="s">
-        <v>442</v>
+      <c r="N509" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O509" s="58" t="s">
+        <v>441</v>
       </c>
       <c r="P509" s="19"/>
     </row>
     <row r="510" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B510" s="64"/>
-      <c r="C510" s="64"/>
-      <c r="D510" s="64" t="s">
+      <c r="A510" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B510" s="58"/>
+      <c r="C510" s="58"/>
+      <c r="D510" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="E510" s="64"/>
-      <c r="F510" s="64"/>
-      <c r="G510" s="64"/>
-      <c r="H510" s="64"/>
-      <c r="I510" s="64"/>
-      <c r="J510" s="64"/>
-      <c r="K510" s="64"/>
+      <c r="E510" s="58"/>
+      <c r="F510" s="58"/>
+      <c r="G510" s="58"/>
+      <c r="H510" s="58"/>
+      <c r="I510" s="58"/>
+      <c r="J510" s="58"/>
+      <c r="K510" s="58"/>
       <c r="L510" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M510" s="17">
         <v>31</v>
       </c>
-      <c r="N510" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O510" s="64" t="s">
-        <v>425</v>
+      <c r="N510" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O510" s="58" t="s">
+        <v>424</v>
       </c>
       <c r="P510" s="19"/>
     </row>
     <row r="511" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B511" s="64"/>
-      <c r="C511" s="64"/>
-      <c r="D511" s="64" t="s">
+      <c r="A511" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B511" s="58"/>
+      <c r="C511" s="58"/>
+      <c r="D511" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="E511" s="64"/>
-      <c r="F511" s="64"/>
-      <c r="G511" s="64"/>
-      <c r="H511" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="I511" s="64"/>
-      <c r="J511" s="64"/>
-      <c r="K511" s="64"/>
+      <c r="E511" s="58"/>
+      <c r="F511" s="58"/>
+      <c r="G511" s="58"/>
+      <c r="H511" s="58" t="s">
+        <v>442</v>
+      </c>
+      <c r="I511" s="58"/>
+      <c r="J511" s="58"/>
+      <c r="K511" s="58"/>
       <c r="L511" s="17" t="s">
         <v>86</v>
       </c>
@@ -13246,30 +13273,30 @@
         <f>69*0.31</f>
         <v>21.39</v>
       </c>
-      <c r="N511" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O511" s="64"/>
+      <c r="N511" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O511" s="58"/>
       <c r="P511" s="19"/>
     </row>
     <row r="512" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B512" s="64"/>
-      <c r="C512" s="64"/>
-      <c r="D512" s="64" t="s">
+      <c r="A512" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B512" s="58"/>
+      <c r="C512" s="58"/>
+      <c r="D512" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="E512" s="64"/>
-      <c r="F512" s="64"/>
-      <c r="G512" s="64"/>
-      <c r="H512" s="64" t="s">
-        <v>444</v>
-      </c>
-      <c r="I512" s="64"/>
-      <c r="J512" s="64"/>
-      <c r="K512" s="64"/>
+      <c r="E512" s="58"/>
+      <c r="F512" s="58"/>
+      <c r="G512" s="58"/>
+      <c r="H512" s="58" t="s">
+        <v>443</v>
+      </c>
+      <c r="I512" s="58"/>
+      <c r="J512" s="58"/>
+      <c r="K512" s="58"/>
       <c r="L512" s="17" t="s">
         <v>86</v>
       </c>
@@ -13277,58 +13304,58 @@
         <f>1.9*0.31</f>
         <v>0.58899999999999997</v>
       </c>
-      <c r="N512" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O512" s="64"/>
+      <c r="N512" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O512" s="58"/>
       <c r="P512" s="19"/>
     </row>
     <row r="513" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A513" s="64" t="s">
-        <v>402</v>
-      </c>
-      <c r="B513" s="64"/>
-      <c r="C513" s="64"/>
-      <c r="D513" s="64" t="s">
+      <c r="A513" s="58" t="s">
+        <v>401</v>
+      </c>
+      <c r="B513" s="58"/>
+      <c r="C513" s="58"/>
+      <c r="D513" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="E513" s="64"/>
-      <c r="F513" s="64"/>
-      <c r="G513" s="64"/>
-      <c r="H513" s="64"/>
-      <c r="I513" s="64"/>
-      <c r="J513" s="64"/>
-      <c r="K513" s="64"/>
+      <c r="E513" s="58"/>
+      <c r="F513" s="58"/>
+      <c r="G513" s="58"/>
+      <c r="H513" s="58"/>
+      <c r="I513" s="58"/>
+      <c r="J513" s="58"/>
+      <c r="K513" s="58"/>
       <c r="L513" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M513" s="17">
         <v>769</v>
       </c>
-      <c r="N513" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O513" s="64"/>
+      <c r="N513" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O513" s="58"/>
       <c r="P513" s="19"/>
     </row>
     <row r="514" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A514" s="64" t="s">
-        <v>402</v>
-      </c>
-      <c r="B514" s="64"/>
-      <c r="C514" s="64"/>
-      <c r="D514" s="64" t="s">
+      <c r="A514" s="58" t="s">
+        <v>401</v>
+      </c>
+      <c r="B514" s="58"/>
+      <c r="C514" s="58"/>
+      <c r="D514" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="E514" s="64"/>
-      <c r="F514" s="64"/>
-      <c r="G514" s="64"/>
-      <c r="H514" s="64" t="s">
-        <v>445</v>
-      </c>
-      <c r="I514" s="64"/>
-      <c r="J514" s="64"/>
-      <c r="K514" s="64"/>
+      <c r="E514" s="58"/>
+      <c r="F514" s="58"/>
+      <c r="G514" s="58"/>
+      <c r="H514" s="58" t="s">
+        <v>444</v>
+      </c>
+      <c r="I514" s="58"/>
+      <c r="J514" s="58"/>
+      <c r="K514" s="58"/>
       <c r="L514" s="17" t="s">
         <v>86</v>
       </c>
@@ -13336,28 +13363,28 @@
         <f>1.5*7.69</f>
         <v>11.535</v>
       </c>
-      <c r="N514" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O514" s="64"/>
+      <c r="N514" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O514" s="58"/>
       <c r="P514" s="19"/>
     </row>
     <row r="515" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A515" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="B515" s="64"/>
-      <c r="C515" s="64"/>
-      <c r="D515" s="64" t="s">
+      <c r="A515" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B515" s="58"/>
+      <c r="C515" s="58"/>
+      <c r="D515" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E515" s="64"/>
-      <c r="F515" s="65"/>
-      <c r="G515" s="65"/>
-      <c r="H515" s="65"/>
-      <c r="I515" s="65"/>
-      <c r="J515" s="64"/>
-      <c r="K515" s="65"/>
+      <c r="E515" s="58"/>
+      <c r="F515" s="59"/>
+      <c r="G515" s="59"/>
+      <c r="H515" s="59"/>
+      <c r="I515" s="59"/>
+      <c r="J515" s="58"/>
+      <c r="K515" s="59"/>
       <c r="L515" s="17" t="s">
         <v>85</v>
       </c>
@@ -13365,30 +13392,30 @@
         <f>M491*0.55</f>
         <v>8.8550000000000022</v>
       </c>
-      <c r="N515" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O515" s="64"/>
+      <c r="N515" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O515" s="58"/>
       <c r="P515" s="19"/>
     </row>
     <row r="516" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A516" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="B516" s="64"/>
-      <c r="C516" s="64"/>
-      <c r="D516" s="64" t="s">
+      <c r="A516" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B516" s="58"/>
+      <c r="C516" s="58"/>
+      <c r="D516" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E516" s="64"/>
-      <c r="F516" s="65"/>
-      <c r="G516" s="65"/>
+      <c r="E516" s="58"/>
+      <c r="F516" s="59"/>
+      <c r="G516" s="59"/>
       <c r="H516" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="I516" s="65"/>
-      <c r="J516" s="64"/>
-      <c r="K516" s="65"/>
+      <c r="I516" s="59"/>
+      <c r="J516" s="58"/>
+      <c r="K516" s="59"/>
       <c r="L516" s="17" t="s">
         <v>86</v>
       </c>
@@ -13396,30 +13423,30 @@
         <f>M492*0.55</f>
         <v>1.9311111111111114</v>
       </c>
-      <c r="N516" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O516" s="64"/>
+      <c r="N516" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O516" s="58"/>
       <c r="P516" s="19"/>
     </row>
     <row r="517" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A517" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="B517" s="64"/>
-      <c r="C517" s="64"/>
-      <c r="D517" s="64" t="s">
+      <c r="A517" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B517" s="58"/>
+      <c r="C517" s="58"/>
+      <c r="D517" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E517" s="64"/>
-      <c r="F517" s="65"/>
-      <c r="G517" s="65"/>
+      <c r="E517" s="58"/>
+      <c r="F517" s="59"/>
+      <c r="G517" s="59"/>
       <c r="H517" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I517" s="65"/>
-      <c r="J517" s="64"/>
-      <c r="K517" s="65"/>
+      <c r="I517" s="59"/>
+      <c r="J517" s="58"/>
+      <c r="K517" s="59"/>
       <c r="L517" s="17" t="s">
         <v>86</v>
       </c>
@@ -13427,28 +13454,28 @@
         <f>M493*0.55</f>
         <v>1.375</v>
       </c>
-      <c r="N517" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O517" s="64"/>
+      <c r="N517" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O517" s="58"/>
       <c r="P517" s="19"/>
     </row>
     <row r="518" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A518" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="B518" s="64"/>
-      <c r="C518" s="64"/>
-      <c r="D518" s="64" t="s">
+      <c r="A518" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B518" s="58"/>
+      <c r="C518" s="58"/>
+      <c r="D518" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E518" s="64"/>
-      <c r="F518" s="65"/>
-      <c r="G518" s="65"/>
-      <c r="H518" s="65"/>
-      <c r="I518" s="65"/>
-      <c r="J518" s="64"/>
-      <c r="K518" s="65"/>
+      <c r="E518" s="58"/>
+      <c r="F518" s="59"/>
+      <c r="G518" s="59"/>
+      <c r="H518" s="59"/>
+      <c r="I518" s="59"/>
+      <c r="J518" s="58"/>
+      <c r="K518" s="59"/>
       <c r="L518" s="17" t="s">
         <v>85</v>
       </c>
@@ -13456,30 +13483,30 @@
         <f>M491*1.09</f>
         <v>17.549000000000003</v>
       </c>
-      <c r="N518" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O518" s="64"/>
+      <c r="N518" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O518" s="58"/>
       <c r="P518" s="19"/>
     </row>
     <row r="519" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A519" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="B519" s="64"/>
-      <c r="C519" s="64"/>
-      <c r="D519" s="64" t="s">
+      <c r="A519" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B519" s="58"/>
+      <c r="C519" s="58"/>
+      <c r="D519" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E519" s="64"/>
-      <c r="F519" s="65"/>
-      <c r="G519" s="65"/>
+      <c r="E519" s="58"/>
+      <c r="F519" s="59"/>
+      <c r="G519" s="59"/>
       <c r="H519" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="I519" s="65"/>
-      <c r="J519" s="64"/>
-      <c r="K519" s="65"/>
+      <c r="I519" s="59"/>
+      <c r="J519" s="58"/>
+      <c r="K519" s="59"/>
       <c r="L519" s="17" t="s">
         <v>86</v>
       </c>
@@ -13487,30 +13514,30 @@
         <f t="shared" ref="M519:M520" si="0">M492*1.09</f>
         <v>3.8271111111111118</v>
       </c>
-      <c r="N519" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O519" s="64"/>
+      <c r="N519" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O519" s="58"/>
       <c r="P519" s="19"/>
     </row>
     <row r="520" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A520" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="B520" s="64"/>
-      <c r="C520" s="64"/>
-      <c r="D520" s="64" t="s">
+      <c r="A520" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B520" s="58"/>
+      <c r="C520" s="58"/>
+      <c r="D520" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E520" s="64"/>
-      <c r="F520" s="65"/>
-      <c r="G520" s="65"/>
+      <c r="E520" s="58"/>
+      <c r="F520" s="59"/>
+      <c r="G520" s="59"/>
       <c r="H520" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I520" s="65"/>
-      <c r="J520" s="64"/>
-      <c r="K520" s="65"/>
+      <c r="I520" s="59"/>
+      <c r="J520" s="58"/>
+      <c r="K520" s="59"/>
       <c r="L520" s="17" t="s">
         <v>86</v>
       </c>
@@ -13518,28 +13545,28 @@
         <f t="shared" si="0"/>
         <v>2.7250000000000001</v>
       </c>
-      <c r="N520" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O520" s="64"/>
+      <c r="N520" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O520" s="58"/>
       <c r="P520" s="19"/>
     </row>
     <row r="521" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A521" s="64" t="s">
-        <v>406</v>
-      </c>
-      <c r="B521" s="64"/>
-      <c r="C521" s="64"/>
-      <c r="D521" s="64" t="s">
+      <c r="A521" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B521" s="58"/>
+      <c r="C521" s="58"/>
+      <c r="D521" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E521" s="64"/>
-      <c r="F521" s="65"/>
-      <c r="G521" s="65"/>
-      <c r="H521" s="65"/>
-      <c r="I521" s="65"/>
-      <c r="J521" s="64"/>
-      <c r="K521" s="65"/>
+      <c r="E521" s="58"/>
+      <c r="F521" s="59"/>
+      <c r="G521" s="59"/>
+      <c r="H521" s="59"/>
+      <c r="I521" s="59"/>
+      <c r="J521" s="58"/>
+      <c r="K521" s="59"/>
       <c r="L521" s="17" t="s">
         <v>85</v>
       </c>
@@ -13547,30 +13574,30 @@
         <f>M491*0.67</f>
         <v>10.787000000000001</v>
       </c>
-      <c r="N521" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O521" s="64"/>
+      <c r="N521" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O521" s="58"/>
       <c r="P521" s="19"/>
     </row>
     <row r="522" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A522" s="64" t="s">
-        <v>406</v>
-      </c>
-      <c r="B522" s="64"/>
-      <c r="C522" s="64"/>
-      <c r="D522" s="64" t="s">
+      <c r="A522" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B522" s="58"/>
+      <c r="C522" s="58"/>
+      <c r="D522" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E522" s="64"/>
-      <c r="F522" s="65"/>
-      <c r="G522" s="65"/>
+      <c r="E522" s="58"/>
+      <c r="F522" s="59"/>
+      <c r="G522" s="59"/>
       <c r="H522" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="I522" s="65"/>
-      <c r="J522" s="64"/>
-      <c r="K522" s="65"/>
+      <c r="I522" s="59"/>
+      <c r="J522" s="58"/>
+      <c r="K522" s="59"/>
       <c r="L522" s="17" t="s">
         <v>86</v>
       </c>
@@ -13578,30 +13605,30 @@
         <f t="shared" ref="M522:M523" si="1">M492*0.67</f>
         <v>2.352444444444445</v>
       </c>
-      <c r="N522" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O522" s="64"/>
+      <c r="N522" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O522" s="58"/>
       <c r="P522" s="19"/>
     </row>
     <row r="523" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A523" s="64" t="s">
-        <v>406</v>
-      </c>
-      <c r="B523" s="64"/>
-      <c r="C523" s="64"/>
-      <c r="D523" s="64" t="s">
+      <c r="A523" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B523" s="58"/>
+      <c r="C523" s="58"/>
+      <c r="D523" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E523" s="64"/>
-      <c r="F523" s="65"/>
-      <c r="G523" s="65"/>
+      <c r="E523" s="58"/>
+      <c r="F523" s="59"/>
+      <c r="G523" s="59"/>
       <c r="H523" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I523" s="65"/>
-      <c r="J523" s="64"/>
-      <c r="K523" s="65"/>
+      <c r="I523" s="59"/>
+      <c r="J523" s="58"/>
+      <c r="K523" s="59"/>
       <c r="L523" s="17" t="s">
         <v>86</v>
       </c>
@@ -13609,325 +13636,325 @@
         <f t="shared" si="1"/>
         <v>1.675</v>
       </c>
-      <c r="N523" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O523" s="64"/>
+      <c r="N523" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O523" s="58"/>
       <c r="P523" s="19"/>
     </row>
     <row r="524" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A524" s="64" t="s">
-        <v>407</v>
-      </c>
-      <c r="B524" s="64"/>
-      <c r="C524" s="64"/>
-      <c r="D524" s="64" t="s">
+      <c r="A524" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B524" s="58"/>
+      <c r="C524" s="58"/>
+      <c r="D524" s="58" t="s">
         <v>212</v>
       </c>
-      <c r="E524" s="64"/>
-      <c r="F524" s="65"/>
-      <c r="G524" s="65"/>
-      <c r="H524" s="65"/>
-      <c r="I524" s="65"/>
-      <c r="J524" s="64"/>
-      <c r="K524" s="65"/>
+      <c r="E524" s="58"/>
+      <c r="F524" s="59"/>
+      <c r="G524" s="59"/>
+      <c r="H524" s="59"/>
+      <c r="I524" s="59"/>
+      <c r="J524" s="58"/>
+      <c r="K524" s="59"/>
       <c r="L524" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M524" s="17">
         <v>150</v>
       </c>
-      <c r="N524" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O524" s="64"/>
+      <c r="N524" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O524" s="58"/>
       <c r="P524" s="19"/>
     </row>
     <row r="525" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A525" s="64" t="s">
-        <v>408</v>
-      </c>
-      <c r="B525" s="64"/>
-      <c r="C525" s="64"/>
-      <c r="D525" s="64" t="s">
+      <c r="A525" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="B525" s="58"/>
+      <c r="C525" s="58"/>
+      <c r="D525" s="58" t="s">
         <v>212</v>
       </c>
-      <c r="E525" s="64"/>
-      <c r="F525" s="65"/>
-      <c r="G525" s="65"/>
-      <c r="H525" s="65"/>
-      <c r="I525" s="65"/>
-      <c r="J525" s="64"/>
-      <c r="K525" s="65"/>
+      <c r="E525" s="58"/>
+      <c r="F525" s="59"/>
+      <c r="G525" s="59"/>
+      <c r="H525" s="59"/>
+      <c r="I525" s="59"/>
+      <c r="J525" s="58"/>
+      <c r="K525" s="59"/>
       <c r="L525" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M525" s="17">
         <v>100</v>
       </c>
-      <c r="N525" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O525" s="64"/>
+      <c r="N525" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O525" s="58"/>
       <c r="P525" s="19"/>
     </row>
     <row r="526" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A526" s="64" t="s">
-        <v>408</v>
-      </c>
-      <c r="B526" s="64"/>
-      <c r="C526" s="64"/>
-      <c r="D526" s="64" t="s">
+      <c r="A526" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="B526" s="58"/>
+      <c r="C526" s="58"/>
+      <c r="D526" s="58" t="s">
         <v>212</v>
       </c>
-      <c r="E526" s="64"/>
-      <c r="F526" s="65"/>
-      <c r="G526" s="65"/>
-      <c r="H526" s="64" t="s">
-        <v>446</v>
-      </c>
-      <c r="I526" s="65"/>
-      <c r="J526" s="64"/>
-      <c r="K526" s="65"/>
+      <c r="E526" s="58"/>
+      <c r="F526" s="59"/>
+      <c r="G526" s="59"/>
+      <c r="H526" s="58" t="s">
+        <v>445</v>
+      </c>
+      <c r="I526" s="59"/>
+      <c r="J526" s="58"/>
+      <c r="K526" s="59"/>
       <c r="L526" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M526" s="17">
         <v>22</v>
       </c>
-      <c r="N526" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O526" s="64"/>
+      <c r="N526" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O526" s="58"/>
       <c r="P526" s="19"/>
     </row>
     <row r="527" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A527" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="B527" s="64"/>
-      <c r="C527" s="64"/>
-      <c r="D527" s="64" t="s">
+      <c r="A527" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B527" s="58"/>
+      <c r="C527" s="58"/>
+      <c r="D527" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E527" s="64"/>
-      <c r="F527" s="65"/>
-      <c r="G527" s="65"/>
-      <c r="H527" s="65"/>
-      <c r="I527" s="65"/>
-      <c r="J527" s="64"/>
-      <c r="K527" s="65"/>
+      <c r="E527" s="58"/>
+      <c r="F527" s="59"/>
+      <c r="G527" s="59"/>
+      <c r="H527" s="59"/>
+      <c r="I527" s="59"/>
+      <c r="J527" s="58"/>
+      <c r="K527" s="59"/>
       <c r="L527" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M527" s="29">
         <v>8.9</v>
       </c>
-      <c r="N527" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O527" s="64"/>
+      <c r="N527" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O527" s="58"/>
       <c r="P527" s="19"/>
     </row>
     <row r="528" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A528" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="B528" s="64"/>
-      <c r="C528" s="64"/>
-      <c r="D528" s="64" t="s">
+      <c r="A528" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B528" s="58"/>
+      <c r="C528" s="58"/>
+      <c r="D528" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E528" s="64"/>
-      <c r="F528" s="65"/>
-      <c r="G528" s="65"/>
+      <c r="E528" s="58"/>
+      <c r="F528" s="59"/>
+      <c r="G528" s="59"/>
       <c r="H528" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="I528" s="65"/>
-      <c r="J528" s="64"/>
-      <c r="K528" s="65"/>
+      <c r="I528" s="59"/>
+      <c r="J528" s="58"/>
+      <c r="K528" s="59"/>
       <c r="L528" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M528" s="29">
         <v>1.9</v>
       </c>
-      <c r="N528" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O528" s="64"/>
+      <c r="N528" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O528" s="58"/>
       <c r="P528" s="19"/>
     </row>
     <row r="529" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A529" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="B529" s="64"/>
-      <c r="C529" s="64"/>
-      <c r="D529" s="64" t="s">
+      <c r="A529" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B529" s="58"/>
+      <c r="C529" s="58"/>
+      <c r="D529" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E529" s="64"/>
-      <c r="F529" s="65"/>
-      <c r="G529" s="65"/>
+      <c r="E529" s="58"/>
+      <c r="F529" s="59"/>
+      <c r="G529" s="59"/>
       <c r="H529" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I529" s="65"/>
-      <c r="J529" s="64"/>
-      <c r="K529" s="65"/>
+      <c r="I529" s="59"/>
+      <c r="J529" s="58"/>
+      <c r="K529" s="59"/>
       <c r="L529" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M529" s="29">
         <v>1.4</v>
       </c>
-      <c r="N529" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O529" s="64"/>
+      <c r="N529" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O529" s="58"/>
       <c r="P529" s="19"/>
     </row>
     <row r="530" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A530" s="64" t="s">
+      <c r="A530" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="B530" s="58"/>
+      <c r="C530" s="58"/>
+      <c r="D530" s="59"/>
+      <c r="E530" s="59"/>
+      <c r="F530" s="59"/>
+      <c r="G530" s="59"/>
+      <c r="H530" s="59"/>
+      <c r="I530" s="59"/>
+      <c r="J530" s="58"/>
+      <c r="K530" s="59"/>
+      <c r="M530" s="58"/>
+      <c r="N530" s="58"/>
+      <c r="O530" s="58"/>
+      <c r="P530" s="19"/>
+    </row>
+    <row r="531" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="58" t="s">
         <v>410</v>
       </c>
-      <c r="B530" s="64"/>
-      <c r="C530" s="64"/>
-      <c r="D530" s="65"/>
-      <c r="E530" s="65"/>
-      <c r="F530" s="65"/>
-      <c r="G530" s="65"/>
-      <c r="H530" s="65"/>
-      <c r="I530" s="65"/>
-      <c r="J530" s="64"/>
-      <c r="K530" s="65"/>
-      <c r="M530" s="64"/>
-      <c r="N530" s="64"/>
-      <c r="O530" s="64"/>
-      <c r="P530" s="19"/>
-    </row>
-    <row r="531" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A531" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="B531" s="64"/>
-      <c r="C531" s="64"/>
-      <c r="D531" s="64" t="s">
+      <c r="B531" s="58"/>
+      <c r="C531" s="58"/>
+      <c r="D531" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E531" s="64"/>
-      <c r="F531" s="65"/>
-      <c r="G531" s="65"/>
-      <c r="H531" s="65"/>
-      <c r="I531" s="65"/>
-      <c r="J531" s="64"/>
-      <c r="K531" s="65"/>
+      <c r="E531" s="58"/>
+      <c r="F531" s="59"/>
+      <c r="G531" s="59"/>
+      <c r="H531" s="59"/>
+      <c r="I531" s="59"/>
+      <c r="J531" s="58"/>
+      <c r="K531" s="59"/>
       <c r="L531" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M531" s="29">
         <v>4.83</v>
       </c>
-      <c r="N531" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O531" s="64"/>
+      <c r="N531" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O531" s="58"/>
       <c r="P531" s="19"/>
     </row>
     <row r="532" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A532" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="B532" s="64"/>
-      <c r="C532" s="64"/>
-      <c r="D532" s="64" t="s">
+      <c r="A532" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B532" s="58"/>
+      <c r="C532" s="58"/>
+      <c r="D532" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E532" s="64"/>
-      <c r="F532" s="65"/>
-      <c r="G532" s="65"/>
+      <c r="E532" s="58"/>
+      <c r="F532" s="59"/>
+      <c r="G532" s="59"/>
       <c r="H532" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="I532" s="65"/>
-      <c r="J532" s="64"/>
-      <c r="K532" s="65"/>
+      <c r="I532" s="59"/>
+      <c r="J532" s="58"/>
+      <c r="K532" s="59"/>
       <c r="L532" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M532" s="67">
+      <c r="M532" s="61">
         <v>1.0533300000000001</v>
       </c>
-      <c r="N532" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O532" s="64"/>
+      <c r="N532" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O532" s="58"/>
       <c r="P532" s="19"/>
     </row>
     <row r="533" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A533" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="B533" s="64"/>
-      <c r="C533" s="64"/>
-      <c r="D533" s="64" t="s">
+      <c r="A533" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B533" s="58"/>
+      <c r="C533" s="58"/>
+      <c r="D533" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E533" s="64"/>
-      <c r="F533" s="65"/>
-      <c r="G533" s="65"/>
+      <c r="E533" s="58"/>
+      <c r="F533" s="59"/>
+      <c r="G533" s="59"/>
       <c r="H533" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I533" s="65"/>
-      <c r="J533" s="64"/>
-      <c r="K533" s="65"/>
+      <c r="I533" s="59"/>
+      <c r="J533" s="58"/>
+      <c r="K533" s="59"/>
       <c r="L533" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M533" s="17">
         <v>0.75</v>
       </c>
-      <c r="N533" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O533" s="64"/>
+      <c r="N533" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O533" s="58"/>
       <c r="P533" s="19"/>
     </row>
     <row r="534" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A534" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="B534" s="64"/>
-      <c r="C534" s="64"/>
-      <c r="D534" s="64" t="s">
+      <c r="A534" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B534" s="58"/>
+      <c r="C534" s="58"/>
+      <c r="D534" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E534" s="64"/>
+      <c r="E534" s="58"/>
       <c r="L534" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M534" s="29">
         <v>6.9</v>
       </c>
-      <c r="N534" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O534" s="64"/>
+      <c r="N534" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O534" s="58"/>
       <c r="P534" s="19"/>
     </row>
     <row r="535" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A535" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="B535" s="64"/>
-      <c r="C535" s="64"/>
-      <c r="D535" s="64" t="s">
+      <c r="A535" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B535" s="58"/>
+      <c r="C535" s="58"/>
+      <c r="D535" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E535" s="64"/>
+      <c r="E535" s="58"/>
       <c r="H535" s="17" t="s">
         <v>225</v>
       </c>
@@ -13937,22 +13964,22 @@
       <c r="M535" s="29">
         <v>1.5</v>
       </c>
-      <c r="N535" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O535" s="64"/>
+      <c r="N535" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O535" s="58"/>
       <c r="P535" s="19"/>
     </row>
     <row r="536" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A536" s="64" t="s">
-        <v>412</v>
-      </c>
-      <c r="B536" s="64"/>
-      <c r="C536" s="64"/>
-      <c r="D536" s="64" t="s">
+      <c r="A536" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B536" s="58"/>
+      <c r="C536" s="58"/>
+      <c r="D536" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="E536" s="64"/>
+      <c r="E536" s="58"/>
       <c r="H536" s="17" t="s">
         <v>226</v>
       </c>
@@ -13962,10 +13989,10 @@
       <c r="M536" s="29">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N536" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O536" s="64"/>
+      <c r="N536" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O536" s="58"/>
       <c r="P536" s="19"/>
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.25">
@@ -14058,10 +14085,10 @@
         <v>38</v>
       </c>
       <c r="O540" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P540" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.25">
@@ -14074,7 +14101,7 @@
         <v>37</v>
       </c>
       <c r="H541" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L541" t="s">
         <v>86</v>
@@ -14087,10 +14114,10 @@
         <v>38</v>
       </c>
       <c r="O541" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P541" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.25">
@@ -14098,23 +14125,23 @@
       <c r="B542" s="10"/>
       <c r="C542" s="10"/>
       <c r="H542" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M542" s="23"/>
       <c r="N542" s="6"/>
       <c r="O542" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P542" s="9"/>
     </row>
     <row r="543" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B543" s="19"/>
       <c r="C543" s="19"/>
       <c r="E543" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L543" s="17" t="s">
         <v>85</v>
@@ -14127,24 +14154,24 @@
         <v>38</v>
       </c>
       <c r="O543" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P543" s="18"/>
     </row>
     <row r="544" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B544" s="10"/>
       <c r="C544" s="10"/>
       <c r="D544" s="6"/>
       <c r="E544" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F544" s="6"/>
       <c r="G544" s="6"/>
       <c r="H544" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I544" s="6"/>
       <c r="J544" s="6"/>
@@ -14160,18 +14187,18 @@
         <v>38</v>
       </c>
       <c r="O544" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P544" s="18"/>
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B545" s="10"/>
       <c r="C545" s="10"/>
       <c r="D545" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H545" s="6"/>
       <c r="L545" t="s">
@@ -14188,7 +14215,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -14202,7 +14229,7 @@
       <c r="K546" s="4"/>
       <c r="L546" s="5"/>
       <c r="M546" s="38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N546" s="5"/>
       <c r="O546" s="5"/>
@@ -14240,14 +14267,14 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B548" s="10"/>
       <c r="C548" s="10"/>
       <c r="D548" s="10"/>
       <c r="E548" s="10"/>
       <c r="F548" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G548" s="19" t="s">
         <v>271</v>
@@ -14286,7 +14313,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -14306,7 +14333,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A551" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -14431,7 +14458,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C5" s="25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -14573,7 +14600,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
         <v>281</v>
@@ -14643,7 +14670,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s">
         <v>283</v>
@@ -14713,7 +14740,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B11" t="s">
         <v>284</v>
@@ -14783,7 +14810,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B12" t="s">
         <v>285</v>
@@ -14853,7 +14880,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C14" s="25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -14925,7 +14952,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B17" t="s">
         <v>202</v>
@@ -15009,12 +15036,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="470">
   <si>
     <t>parameter</t>
   </si>
@@ -1470,6 +1470,12 @@
   </si>
   <si>
     <t>Use net exports as no feed imports assumed</t>
+  </si>
+  <si>
+    <t>Adjusted to match prod. 90% in Hanna's sheet</t>
+  </si>
+  <si>
+    <t>Adjusted to match prod. 46% in Hanna's sheet</t>
   </si>
 </sst>
 </file>
@@ -7368,10 +7374,13 @@
         <v>40</v>
       </c>
       <c r="M259" s="17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N259" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="O259" s="6" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
@@ -7382,10 +7391,13 @@
         <v>40</v>
       </c>
       <c r="M260" s="17">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N260" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="O260" s="6" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.25">

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="475">
   <si>
     <t>parameter</t>
   </si>
@@ -1476,6 +1476,21 @@
   </si>
   <si>
     <t>Adjusted to match prod. 46% in Hanna's sheet</t>
+  </si>
+  <si>
+    <t>quinoa</t>
+  </si>
+  <si>
+    <t>hazelnuts</t>
+  </si>
+  <si>
+    <t>walnuts</t>
+  </si>
+  <si>
+    <t>hazelnut shells</t>
+  </si>
+  <si>
+    <t>walnut shells</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1714,6 +1729,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2098,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T567"/>
+  <dimension ref="A1:T575"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -4498,7 +4516,7 @@
         <v>188</v>
       </c>
       <c r="M117" s="33">
-        <f>600000*(M557/100)</f>
+        <f>600000*(M565/100)</f>
         <v>188217.14285714284</v>
       </c>
       <c r="N117" t="s">
@@ -10755,57 +10773,56 @@
       <c r="P413" s="8"/>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A414" s="4" t="s">
+      <c r="A414" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="B414" s="68"/>
+      <c r="C414" s="68"/>
+      <c r="D414" s="69" t="s">
+        <v>470</v>
+      </c>
+      <c r="E414" s="69"/>
+      <c r="F414" s="68"/>
+      <c r="G414" s="68"/>
+      <c r="H414" s="68"/>
+      <c r="I414" s="68"/>
+      <c r="J414" s="68"/>
+      <c r="K414" s="68"/>
+      <c r="L414" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="M414" s="70">
+        <v>100</v>
+      </c>
+      <c r="N414" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="O414" s="8"/>
+      <c r="P414" s="8"/>
+    </row>
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A415" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B414" s="4"/>
-      <c r="C414" s="4"/>
-      <c r="D414" s="4"/>
-      <c r="E414" s="4"/>
-      <c r="F414" s="4"/>
-      <c r="G414" s="4"/>
-      <c r="H414" s="4"/>
-      <c r="I414" s="4"/>
-      <c r="J414" s="4"/>
-      <c r="K414" s="4"/>
-      <c r="L414" s="5"/>
-      <c r="M414" s="5"/>
-      <c r="N414" s="5"/>
-      <c r="O414" s="5"/>
-      <c r="P414" s="5"/>
-    </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A415" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B415" s="8"/>
-      <c r="C415" s="8"/>
-      <c r="D415" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E415" s="9"/>
-      <c r="F415" s="8"/>
-      <c r="G415" s="8"/>
-      <c r="H415" s="9"/>
-      <c r="I415" s="8"/>
-      <c r="J415" s="8"/>
-      <c r="K415" s="8"/>
-      <c r="L415" t="s">
-        <v>85</v>
-      </c>
-      <c r="M415" s="11">
-        <v>100</v>
-      </c>
-      <c r="N415" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O415" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="B415" s="4"/>
+      <c r="C415" s="4"/>
+      <c r="D415" s="4"/>
+      <c r="E415" s="4"/>
+      <c r="F415" s="4"/>
+      <c r="G415" s="4"/>
+      <c r="H415" s="4"/>
+      <c r="I415" s="4"/>
+      <c r="J415" s="4"/>
+      <c r="K415" s="4"/>
+      <c r="L415" s="5"/>
+      <c r="M415" s="5"/>
+      <c r="N415" s="5"/>
+      <c r="O415" s="5"/>
+      <c r="P415" s="5"/>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B416" s="8"/>
       <c r="C416" s="8"/>
@@ -10822,13 +10839,15 @@
       <c r="L416" t="s">
         <v>85</v>
       </c>
-      <c r="M416" s="9">
-        <v>50</v>
+      <c r="M416" s="11">
+        <v>100</v>
       </c>
       <c r="N416" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O416" s="8"/>
+      <c r="O416" s="10" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" s="17" t="s">
@@ -10842,14 +10861,12 @@
       <c r="E417" s="9"/>
       <c r="F417" s="8"/>
       <c r="G417" s="8"/>
-      <c r="H417" s="9" t="s">
-        <v>115</v>
-      </c>
+      <c r="H417" s="9"/>
       <c r="I417" s="8"/>
       <c r="J417" s="8"/>
       <c r="K417" s="8"/>
       <c r="L417" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M417" s="9">
         <v>50</v>
@@ -10861,43 +10878,43 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" s="17" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="B418" s="8"/>
       <c r="C418" s="8"/>
-      <c r="D418" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E418" s="11"/>
+      <c r="D418" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E418" s="9"/>
       <c r="F418" s="8"/>
       <c r="G418" s="8"/>
-      <c r="H418" s="9"/>
+      <c r="H418" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="I418" s="8"/>
       <c r="J418" s="8"/>
       <c r="K418" s="8"/>
       <c r="L418" t="s">
-        <v>85</v>
-      </c>
-      <c r="M418" s="18">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="M418" s="9">
+        <v>50</v>
       </c>
       <c r="N418" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O418" s="10" t="s">
-        <v>201</v>
-      </c>
+      <c r="O418" s="8"/>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" s="17" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="B419" s="8"/>
       <c r="C419" s="8"/>
-      <c r="D419" s="9" t="s">
+      <c r="D419" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E419" s="9"/>
+      <c r="E419" s="11"/>
       <c r="F419" s="8"/>
       <c r="G419" s="8"/>
       <c r="H419" s="9"/>
@@ -10908,12 +10925,14 @@
         <v>85</v>
       </c>
       <c r="M419" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N419" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O419" s="19"/>
+      <c r="O419" s="10" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" s="17" t="s">
@@ -10927,76 +10946,85 @@
       <c r="E420" s="9"/>
       <c r="F420" s="8"/>
       <c r="G420" s="8"/>
-      <c r="H420" t="s">
-        <v>182</v>
-      </c>
+      <c r="H420" s="9"/>
       <c r="I420" s="8"/>
       <c r="J420" s="8"/>
       <c r="K420" s="8"/>
       <c r="L420" t="s">
+        <v>85</v>
+      </c>
+      <c r="M420" s="18">
+        <v>19</v>
+      </c>
+      <c r="N420" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O420" s="19"/>
+    </row>
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A421" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B421" s="8"/>
+      <c r="C421" s="8"/>
+      <c r="D421" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E421" s="9"/>
+      <c r="F421" s="8"/>
+      <c r="G421" s="8"/>
+      <c r="H421" t="s">
+        <v>182</v>
+      </c>
+      <c r="I421" s="8"/>
+      <c r="J421" s="8"/>
+      <c r="K421" s="8"/>
+      <c r="L421" t="s">
         <v>86</v>
       </c>
-      <c r="M420" s="28">
+      <c r="M421" s="28">
         <f>0.02*0.5*100/(844/1000)/0.9</f>
         <v>1.3164823591363877</v>
       </c>
-      <c r="N420" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O420" s="19" t="s">
+      <c r="N421" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O421" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="P420" s="9" t="s">
+      <c r="P421" s="9" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A421" s="4" t="s">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A422" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B421" s="4"/>
-      <c r="C421" s="4"/>
-      <c r="D421" s="4"/>
-      <c r="E421" s="4"/>
-      <c r="F421" s="4"/>
-      <c r="G421" s="4"/>
-      <c r="H421" s="4"/>
-      <c r="I421" s="4"/>
-      <c r="J421" s="4"/>
-      <c r="K421" s="4"/>
-      <c r="L421" s="5"/>
-      <c r="M421" s="5"/>
-      <c r="N421" s="5"/>
-      <c r="O421" s="5"/>
-      <c r="P421" s="5"/>
-    </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A422" s="17" t="s">
+      <c r="B422" s="4"/>
+      <c r="C422" s="4"/>
+      <c r="D422" s="4"/>
+      <c r="E422" s="4"/>
+      <c r="F422" s="4"/>
+      <c r="G422" s="4"/>
+      <c r="H422" s="4"/>
+      <c r="I422" s="4"/>
+      <c r="J422" s="4"/>
+      <c r="K422" s="4"/>
+      <c r="L422" s="5"/>
+      <c r="M422" s="5"/>
+      <c r="N422" s="5"/>
+      <c r="O422" s="5"/>
+      <c r="P422" s="5"/>
+    </row>
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A423" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D422" s="9" t="s">
+      <c r="D423" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E422" s="9"/>
-      <c r="L422" t="s">
-        <v>85</v>
-      </c>
-      <c r="M422" s="18">
-        <v>100</v>
-      </c>
-      <c r="N422" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="423" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A423" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="D423" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="E423" s="18"/>
-      <c r="L423" s="17" t="s">
+      <c r="E423" s="9"/>
+      <c r="L423" t="s">
         <v>85</v>
       </c>
       <c r="M423" s="18">
@@ -11006,15 +11034,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D424" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E424" s="9"/>
-      <c r="L424" t="s">
+        <v>358</v>
+      </c>
+      <c r="D424" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="E424" s="18"/>
+      <c r="L424" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M424" s="18">
@@ -11026,10 +11054,10 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" s="17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D425" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E425" s="9"/>
       <c r="L425" t="s">
@@ -11044,10 +11072,10 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D426" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E426" s="9"/>
       <c r="L426" t="s">
@@ -11062,10 +11090,10 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D427" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E427" s="9"/>
       <c r="L427" t="s">
@@ -11080,10 +11108,10 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D428" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E428" s="9"/>
       <c r="L428" t="s">
@@ -11098,20 +11126,12 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B429" s="8"/>
-      <c r="C429" s="8"/>
+        <v>131</v>
+      </c>
       <c r="D429" s="9" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E429" s="9"/>
-      <c r="F429" s="8"/>
-      <c r="G429" s="8"/>
-      <c r="H429" s="9"/>
-      <c r="I429" s="8"/>
-      <c r="J429" s="8"/>
-      <c r="K429" s="8"/>
       <c r="L429" t="s">
         <v>85</v>
       </c>
@@ -11121,16 +11141,15 @@
       <c r="N429" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O429" s="10"/>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B430" s="8"/>
       <c r="C430" s="8"/>
       <c r="D430" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E430" s="9"/>
       <c r="F430" s="8"/>
@@ -11152,12 +11171,12 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" s="17" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
       <c r="D431" s="9" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="E431" s="9"/>
       <c r="F431" s="8"/>
@@ -11178,46 +11197,55 @@
       <c r="O431" s="10"/>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A432" s="4" t="s">
+      <c r="A432" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B432" s="8"/>
+      <c r="C432" s="8"/>
+      <c r="D432" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E432" s="9"/>
+      <c r="F432" s="8"/>
+      <c r="G432" s="8"/>
+      <c r="H432" s="9"/>
+      <c r="I432" s="8"/>
+      <c r="J432" s="8"/>
+      <c r="K432" s="8"/>
+      <c r="L432" t="s">
+        <v>85</v>
+      </c>
+      <c r="M432" s="18">
+        <v>100</v>
+      </c>
+      <c r="N432" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O432" s="10"/>
+    </row>
+    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A433" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B432" s="4"/>
-      <c r="C432" s="4"/>
-      <c r="D432" s="4"/>
-      <c r="E432" s="4"/>
-      <c r="F432" s="4"/>
-      <c r="G432" s="4"/>
-      <c r="H432" s="4"/>
-      <c r="I432" s="4"/>
-      <c r="J432" s="4"/>
-      <c r="K432" s="4"/>
-      <c r="L432" s="5"/>
-      <c r="M432" s="5"/>
-      <c r="N432" s="5"/>
-      <c r="O432" s="5"/>
-      <c r="P432" s="5"/>
-    </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A433" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D433" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E433" s="9"/>
-      <c r="L433" t="s">
-        <v>85</v>
-      </c>
-      <c r="M433" s="17">
-        <v>100</v>
-      </c>
-      <c r="N433" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="B433" s="4"/>
+      <c r="C433" s="4"/>
+      <c r="D433" s="4"/>
+      <c r="E433" s="4"/>
+      <c r="F433" s="4"/>
+      <c r="G433" s="4"/>
+      <c r="H433" s="4"/>
+      <c r="I433" s="4"/>
+      <c r="J433" s="4"/>
+      <c r="K433" s="4"/>
+      <c r="L433" s="5"/>
+      <c r="M433" s="5"/>
+      <c r="N433" s="5"/>
+      <c r="O433" s="5"/>
+      <c r="P433" s="5"/>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A434" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D434" s="9" t="s">
         <v>229</v>
@@ -11227,13 +11255,10 @@
         <v>85</v>
       </c>
       <c r="M434" s="17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="N434" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="P434" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.25">
@@ -11244,14 +11269,11 @@
         <v>229</v>
       </c>
       <c r="E435" s="9"/>
-      <c r="H435" s="19" t="s">
-        <v>230</v>
-      </c>
       <c r="L435" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M435" s="17">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="N435" s="17" t="s">
         <v>38</v>
@@ -11262,17 +11284,20 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A436" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D436" s="9" t="s">
         <v>229</v>
       </c>
       <c r="E436" s="9"/>
+      <c r="H436" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="L436" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M436" s="17">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="N436" s="17" t="s">
         <v>38</v>
@@ -11289,14 +11314,11 @@
         <v>229</v>
       </c>
       <c r="E437" s="9"/>
-      <c r="H437" s="19" t="s">
-        <v>230</v>
-      </c>
       <c r="L437" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M437" s="17">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="N437" s="17" t="s">
         <v>38</v>
@@ -11307,28 +11329,34 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A438" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D438" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E438" s="9"/>
+      <c r="H438" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="L438" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M438" s="17">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="N438" s="17" t="s">
         <v>38</v>
+      </c>
+      <c r="P438" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" s="17" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D439" s="9" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E439" s="9"/>
       <c r="L439" t="s">
@@ -11343,10 +11371,10 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D440" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E440" s="9"/>
       <c r="L440" t="s">
@@ -11361,10 +11389,10 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D441" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E441" s="9"/>
       <c r="L441" t="s">
@@ -11379,10 +11407,10 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" s="17" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D442" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E442" s="9"/>
       <c r="L442" t="s">
@@ -11396,59 +11424,42 @@
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D443" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E443" s="9"/>
+      <c r="L443" t="s">
+        <v>85</v>
+      </c>
+      <c r="M443" s="17">
+        <v>100</v>
+      </c>
+      <c r="N443" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A444" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B443" s="4"/>
-      <c r="C443" s="4"/>
-      <c r="D443" s="4"/>
-      <c r="E443" s="4"/>
-      <c r="F443" s="4"/>
-      <c r="G443" s="4"/>
-      <c r="H443" s="4"/>
-      <c r="I443" s="4"/>
-      <c r="J443" s="4"/>
-      <c r="K443" s="4"/>
-      <c r="L443" s="5"/>
-      <c r="M443" s="5"/>
-      <c r="N443" s="5"/>
-      <c r="O443" s="5"/>
-      <c r="P443" s="5"/>
-    </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A444" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B444" s="10"/>
-      <c r="C444" s="10"/>
-      <c r="D444" s="10"/>
-      <c r="E444" s="10"/>
-      <c r="F444" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G444" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H444" s="10"/>
-      <c r="I444" s="10"/>
-      <c r="J444" s="10"/>
-      <c r="K444" s="10"/>
-      <c r="L444" t="s">
-        <v>85</v>
-      </c>
-      <c r="M444" s="12">
-        <f>100-M445</f>
-        <v>90.75</v>
-      </c>
-      <c r="N444" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="O444" t="s">
-        <v>71</v>
-      </c>
-      <c r="P444" s="8" t="s">
-        <v>92</v>
-      </c>
+      <c r="B444" s="4"/>
+      <c r="C444" s="4"/>
+      <c r="D444" s="4"/>
+      <c r="E444" s="4"/>
+      <c r="F444" s="4"/>
+      <c r="G444" s="4"/>
+      <c r="H444" s="4"/>
+      <c r="I444" s="4"/>
+      <c r="J444" s="4"/>
+      <c r="K444" s="4"/>
+      <c r="L444" s="5"/>
+      <c r="M444" s="5"/>
+      <c r="N444" s="5"/>
+      <c r="O444" s="5"/>
+      <c r="P444" s="5"/>
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
@@ -11464,21 +11475,22 @@
       <c r="G445" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H445" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="H445" s="10"/>
       <c r="I445" s="10"/>
       <c r="J445" s="10"/>
       <c r="K445" s="10"/>
       <c r="L445" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M445" s="12">
-        <f>(0.042-0.005)/0.4*100</f>
-        <v>9.2500000000000018</v>
+        <f>100-M446</f>
+        <v>90.75</v>
       </c>
       <c r="N445" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="O445" t="s">
+        <v>71</v>
       </c>
       <c r="P445" s="8" t="s">
         <v>92</v>
@@ -11486,7 +11498,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B446" s="10"/>
       <c r="C446" s="10"/>
@@ -11498,22 +11510,21 @@
       <c r="G446" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H446" s="10"/>
+      <c r="H446" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="I446" s="10"/>
       <c r="J446" s="10"/>
       <c r="K446" s="10"/>
       <c r="L446" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M446" s="12">
-        <f>100-M447</f>
-        <v>93.25</v>
+        <f>(0.042-0.005)/0.4*100</f>
+        <v>9.2500000000000018</v>
       </c>
       <c r="N446" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="O446" t="s">
-        <v>72</v>
       </c>
       <c r="P446" s="8" t="s">
         <v>92</v>
@@ -11533,21 +11544,22 @@
       <c r="G447" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H447" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="H447" s="10"/>
       <c r="I447" s="10"/>
       <c r="J447" s="10"/>
       <c r="K447" s="10"/>
       <c r="L447" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M447" s="12">
-        <f>(0.042-0.015)/0.4*100</f>
-        <v>6.75</v>
+        <f>100-M448</f>
+        <v>93.25</v>
       </c>
       <c r="N447" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="O447" t="s">
+        <v>72</v>
       </c>
       <c r="P447" s="8" t="s">
         <v>92</v>
@@ -11555,7 +11567,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B448" s="10"/>
       <c r="C448" s="10"/>
@@ -11567,22 +11579,21 @@
       <c r="G448" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H448" s="10"/>
+      <c r="H448" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="I448" s="10"/>
       <c r="J448" s="10"/>
       <c r="K448" s="10"/>
       <c r="L448" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M448" s="12">
-        <f>100-M449</f>
-        <v>97</v>
+        <f>(0.042-0.015)/0.4*100</f>
+        <v>6.75</v>
       </c>
       <c r="N448" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="O448" t="s">
-        <v>73</v>
       </c>
       <c r="P448" s="8" t="s">
         <v>92</v>
@@ -11602,21 +11613,22 @@
       <c r="G449" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H449" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="H449" s="10"/>
       <c r="I449" s="10"/>
       <c r="J449" s="10"/>
       <c r="K449" s="10"/>
       <c r="L449" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M449" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
+        <f>100-M450</f>
+        <v>97</v>
       </c>
       <c r="N449" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="O449" t="s">
+        <v>73</v>
       </c>
       <c r="P449" s="8" t="s">
         <v>92</v>
@@ -11624,7 +11636,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B450" s="10"/>
       <c r="C450" s="10"/>
@@ -11636,22 +11648,21 @@
       <c r="G450" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H450" s="10"/>
+      <c r="H450" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="I450" s="10"/>
       <c r="J450" s="10"/>
       <c r="K450" s="10"/>
       <c r="L450" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M450" s="12">
-        <f>(100-M451)*0.1</f>
-        <v>9.7000000000000011</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="N450" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="O450" t="s">
-        <v>80</v>
       </c>
       <c r="P450" s="8" t="s">
         <v>92</v>
@@ -11671,21 +11682,22 @@
       <c r="G451" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H451" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="H451" s="10"/>
       <c r="I451" s="10"/>
       <c r="J451" s="10"/>
       <c r="K451" s="10"/>
       <c r="L451" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M451" s="12">
-        <f>(0.042-0.03)/0.4*100</f>
-        <v>3.0000000000000009</v>
+        <f>(100-M452)*0.1</f>
+        <v>9.7000000000000011</v>
       </c>
       <c r="N451" s="10" t="s">
         <v>38</v>
+      </c>
+      <c r="O451" t="s">
+        <v>80</v>
       </c>
       <c r="P451" s="8" t="s">
         <v>92</v>
@@ -11706,7 +11718,7 @@
         <v>59</v>
       </c>
       <c r="H452" s="10" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I452" s="10"/>
       <c r="J452" s="10"/>
@@ -11715,8 +11727,8 @@
         <v>86</v>
       </c>
       <c r="M452" s="12">
-        <f>(100-M451)*0.9</f>
-        <v>87.3</v>
+        <f>(0.042-0.03)/0.4*100</f>
+        <v>3.0000000000000009</v>
       </c>
       <c r="N452" s="10" t="s">
         <v>38</v>
@@ -11727,7 +11739,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B453" s="10"/>
       <c r="C453" s="10"/>
@@ -11737,32 +11749,31 @@
         <v>79</v>
       </c>
       <c r="G453" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H453" s="10"/>
+        <v>59</v>
+      </c>
+      <c r="H453" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="I453" s="10"/>
       <c r="J453" s="10"/>
       <c r="K453" s="10"/>
       <c r="L453" t="s">
-        <v>85</v>
-      </c>
-      <c r="M453" s="10">
-        <f>1/(0.1/0.4)*100</f>
-        <v>400</v>
+        <v>86</v>
+      </c>
+      <c r="M453" s="12">
+        <f>(100-M452)*0.9</f>
+        <v>87.3</v>
       </c>
       <c r="N453" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="O453" t="s">
-        <v>78</v>
       </c>
       <c r="P453" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A454" s="11" t="s">
-        <v>69</v>
+      <c r="A454" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="B454" s="10"/>
       <c r="C454" s="10"/>
@@ -11781,23 +11792,23 @@
       <c r="L454" t="s">
         <v>85</v>
       </c>
-      <c r="M454" s="12">
-        <f>1/(0.12/0.4)*100</f>
-        <v>333.33333333333337</v>
+      <c r="M454" s="10">
+        <f>1/(0.1/0.4)*100</f>
+        <v>400</v>
       </c>
       <c r="N454" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O454" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P454" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A455" s="10" t="s">
-        <v>66</v>
+      <c r="A455" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -11817,14 +11828,14 @@
         <v>85</v>
       </c>
       <c r="M455" s="12">
-        <f>1/(0.13/0.4)*100</f>
-        <v>307.69230769230768</v>
+        <f>1/(0.12/0.4)*100</f>
+        <v>333.33333333333337</v>
       </c>
       <c r="N455" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O455" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P455" s="8" t="s">
         <v>92</v>
@@ -11832,7 +11843,7 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B456" s="10"/>
       <c r="C456" s="10"/>
@@ -11851,15 +11862,15 @@
       <c r="L456" t="s">
         <v>85</v>
       </c>
-      <c r="M456" s="10">
-        <f>1/(0.4/0.4)*100</f>
-        <v>100</v>
+      <c r="M456" s="12">
+        <f>1/(0.13/0.4)*100</f>
+        <v>307.69230769230768</v>
       </c>
       <c r="N456" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O456" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P456" s="8" t="s">
         <v>92</v>
@@ -11867,7 +11878,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B457" s="10"/>
       <c r="C457" s="10"/>
@@ -11886,15 +11897,15 @@
       <c r="L457" t="s">
         <v>85</v>
       </c>
-      <c r="M457" s="12">
-        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
-        <v>49.367088607594937</v>
+      <c r="M457" s="10">
+        <f>1/(0.4/0.4)*100</f>
+        <v>100</v>
       </c>
       <c r="N457" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O457" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P457" s="8" t="s">
         <v>92</v>
@@ -11904,34 +11915,32 @@
       <c r="A458" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B458" s="8"/>
-      <c r="C458" s="8"/>
-      <c r="D458" s="8"/>
-      <c r="E458" s="8"/>
+      <c r="B458" s="10"/>
+      <c r="C458" s="10"/>
+      <c r="D458" s="10"/>
+      <c r="E458" s="10"/>
       <c r="F458" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G458" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H458" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I458" s="8"/>
-      <c r="J458" s="8"/>
-      <c r="K458" s="8"/>
+      <c r="H458" s="10"/>
+      <c r="I458" s="10"/>
+      <c r="J458" s="10"/>
+      <c r="K458" s="10"/>
       <c r="L458" t="s">
-        <v>86</v>
-      </c>
-      <c r="M458" s="14">
-        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
-        <v>50.632911392405056</v>
+        <v>85</v>
+      </c>
+      <c r="M458" s="12">
+        <f>1/((0.4-0.8)/(0.01-0.4)+1)*100</f>
+        <v>49.367088607594937</v>
       </c>
       <c r="N458" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O458" s="8" t="s">
-        <v>83</v>
+      <c r="O458" t="s">
+        <v>77</v>
       </c>
       <c r="P458" s="8" t="s">
         <v>92</v>
@@ -11939,76 +11948,79 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>410</v>
+        <v>65</v>
       </c>
       <c r="B459" s="8"/>
       <c r="C459" s="8"/>
       <c r="D459" s="8"/>
       <c r="E459" s="8"/>
-      <c r="F459" s="10"/>
-      <c r="G459" s="10"/>
-      <c r="H459" s="10"/>
+      <c r="F459" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G459" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H459" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="I459" s="8"/>
       <c r="J459" s="8"/>
       <c r="K459" s="8"/>
-      <c r="M459" s="14"/>
-      <c r="N459" s="10"/>
-      <c r="O459" s="8"/>
-      <c r="P459" s="8"/>
+      <c r="L459" t="s">
+        <v>86</v>
+      </c>
+      <c r="M459" s="14">
+        <f>1/((0.01-0.4)/(0.4-0.8)+1)*100</f>
+        <v>50.632911392405056</v>
+      </c>
+      <c r="N459" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O459" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="P459" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A460" s="4" t="s">
+      <c r="A460" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B460" s="8"/>
+      <c r="C460" s="8"/>
+      <c r="D460" s="8"/>
+      <c r="E460" s="8"/>
+      <c r="F460" s="10"/>
+      <c r="G460" s="10"/>
+      <c r="H460" s="10"/>
+      <c r="I460" s="8"/>
+      <c r="J460" s="8"/>
+      <c r="K460" s="8"/>
+      <c r="M460" s="14"/>
+      <c r="N460" s="10"/>
+      <c r="O460" s="8"/>
+      <c r="P460" s="8"/>
+    </row>
+    <row r="461" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A461" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B460" s="4"/>
-      <c r="C460" s="4"/>
-      <c r="D460" s="4"/>
-      <c r="E460" s="4"/>
-      <c r="F460" s="4"/>
-      <c r="G460" s="4"/>
-      <c r="H460" s="4"/>
-      <c r="I460" s="4"/>
-      <c r="J460" s="4"/>
-      <c r="K460" s="4"/>
-      <c r="L460" s="5"/>
-      <c r="M460" s="5"/>
-      <c r="N460" s="5"/>
-      <c r="O460" s="5"/>
-      <c r="P460" s="5"/>
-    </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A461" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B461" s="8"/>
-      <c r="C461" s="8"/>
-      <c r="D461" s="8"/>
-      <c r="E461" s="8"/>
-      <c r="F461" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G461" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H461" s="8"/>
-      <c r="I461" s="8"/>
-      <c r="J461" s="8"/>
-      <c r="K461" s="8"/>
-      <c r="L461" t="s">
-        <v>85</v>
-      </c>
-      <c r="M461" s="11">
-        <v>71</v>
-      </c>
-      <c r="N461" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O461" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="P461" s="8" t="s">
-        <v>91</v>
-      </c>
+      <c r="B461" s="4"/>
+      <c r="C461" s="4"/>
+      <c r="D461" s="4"/>
+      <c r="E461" s="4"/>
+      <c r="F461" s="4"/>
+      <c r="G461" s="4"/>
+      <c r="H461" s="4"/>
+      <c r="I461" s="4"/>
+      <c r="J461" s="4"/>
+      <c r="K461" s="4"/>
+      <c r="L461" s="5"/>
+      <c r="M461" s="5"/>
+      <c r="N461" s="5"/>
+      <c r="O461" s="5"/>
+      <c r="P461" s="5"/>
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
@@ -12024,24 +12036,21 @@
       <c r="G462" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H462" s="8" t="s">
-        <v>443</v>
-      </c>
+      <c r="H462" s="8"/>
       <c r="I462" s="8"/>
       <c r="J462" s="8"/>
       <c r="K462" s="8"/>
       <c r="L462" t="s">
-        <v>86</v>
-      </c>
-      <c r="M462" s="65">
-        <f>(1/0.76)*4</f>
-        <v>5.2631578947368425</v>
+        <v>85</v>
+      </c>
+      <c r="M462" s="11">
+        <v>71</v>
       </c>
       <c r="N462" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="O462" s="9" t="s">
-        <v>95</v>
+      <c r="O462" s="46" t="s">
+        <v>347</v>
       </c>
       <c r="P462" s="8" t="s">
         <v>91</v>
@@ -12062,7 +12071,7 @@
         <v>55</v>
       </c>
       <c r="H463" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="I463" s="8"/>
       <c r="J463" s="8"/>
@@ -12071,8 +12080,8 @@
         <v>86</v>
       </c>
       <c r="M463" s="65">
-        <f>(1/0.76)*6</f>
-        <v>7.8947368421052637</v>
+        <f>(1/0.76)*4</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="N463" s="8" t="s">
         <v>38</v>
@@ -12099,7 +12108,7 @@
         <v>55</v>
       </c>
       <c r="H464" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I464" s="8"/>
       <c r="J464" s="8"/>
@@ -12108,8 +12117,8 @@
         <v>86</v>
       </c>
       <c r="M464" s="65">
-        <f>(1/0.76)*5</f>
-        <v>6.5789473684210531</v>
+        <f>(1/0.76)*6</f>
+        <v>7.8947368421052637</v>
       </c>
       <c r="N464" s="8" t="s">
         <v>38</v>
@@ -12135,8 +12144,8 @@
       <c r="G465" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H465" s="9" t="s">
-        <v>454</v>
+      <c r="H465" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="I465" s="8"/>
       <c r="J465" s="8"/>
@@ -12145,17 +12154,17 @@
         <v>86</v>
       </c>
       <c r="M465" s="65">
-        <f>(1/0.76)*3.5</f>
-        <v>4.6052631578947372</v>
+        <f>(1/0.76)*5</f>
+        <v>6.5789473684210531</v>
       </c>
       <c r="N465" s="8" t="s">
         <v>38</v>
       </c>
       <c r="O465" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="P465" s="64" t="s">
-        <v>451</v>
+        <v>95</v>
+      </c>
+      <c r="P465" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.25">
@@ -12172,8 +12181,8 @@
       <c r="G466" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H466" s="8" t="s">
-        <v>450</v>
+      <c r="H466" s="9" t="s">
+        <v>454</v>
       </c>
       <c r="I466" s="8"/>
       <c r="J466" s="8"/>
@@ -12181,47 +12190,50 @@
       <c r="L466" t="s">
         <v>86</v>
       </c>
-      <c r="M466" s="9">
-        <v>18</v>
+      <c r="M466" s="65">
+        <f>(1/0.76)*3.5</f>
+        <v>4.6052631578947372</v>
       </c>
       <c r="N466" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="O466" s="8"/>
-      <c r="P466" s="8" t="s">
-        <v>91</v>
+      <c r="O466" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="P466" s="64" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
-        <v>94</v>
+      <c r="A467" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B467" s="8"/>
       <c r="C467" s="8"/>
       <c r="D467" s="8"/>
       <c r="E467" s="8"/>
-      <c r="F467" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G467" s="9" t="s">
+      <c r="F467" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G467" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H467" s="8"/>
+      <c r="H467" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="I467" s="8"/>
       <c r="J467" s="8"/>
       <c r="K467" s="8"/>
       <c r="L467" t="s">
-        <v>85</v>
-      </c>
-      <c r="M467" s="11">
-        <v>75</v>
-      </c>
-      <c r="N467" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O467" s="9" t="s">
-        <v>348</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="M467" s="9">
+        <v>18</v>
+      </c>
+      <c r="N467" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O467" s="8"/>
       <c r="P467" s="8" t="s">
         <v>91</v>
       </c>
@@ -12240,24 +12252,21 @@
       <c r="G468" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H468" s="9" t="s">
-        <v>443</v>
-      </c>
+      <c r="H468" s="8"/>
       <c r="I468" s="8"/>
       <c r="J468" s="8"/>
       <c r="K468" s="8"/>
       <c r="L468" t="s">
-        <v>86</v>
-      </c>
-      <c r="M468" s="16">
-        <f>(1/0.52)*7</f>
-        <v>13.46153846153846</v>
+        <v>85</v>
+      </c>
+      <c r="M468" s="11">
+        <v>75</v>
       </c>
       <c r="N468" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O468" s="9" t="s">
-        <v>96</v>
+        <v>348</v>
       </c>
       <c r="P468" s="8" t="s">
         <v>91</v>
@@ -12277,8 +12286,8 @@
       <c r="G469" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H469" s="8" t="s">
-        <v>448</v>
+      <c r="H469" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="I469" s="8"/>
       <c r="J469" s="8"/>
@@ -12286,9 +12295,9 @@
       <c r="L469" t="s">
         <v>86</v>
       </c>
-      <c r="M469" s="65">
-        <f>(1/0.52)*3</f>
-        <v>5.7692307692307683</v>
+      <c r="M469" s="16">
+        <f>(1/0.52)*7</f>
+        <v>13.46153846153846</v>
       </c>
       <c r="N469" s="9" t="s">
         <v>38</v>
@@ -12314,8 +12323,8 @@
       <c r="G470" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H470" s="9" t="s">
-        <v>449</v>
+      <c r="H470" s="8" t="s">
+        <v>448</v>
       </c>
       <c r="I470" s="8"/>
       <c r="J470" s="8"/>
@@ -12323,9 +12332,9 @@
       <c r="L470" t="s">
         <v>86</v>
       </c>
-      <c r="M470" s="16">
-        <f>(1/0.52)*6</f>
-        <v>11.538461538461537</v>
+      <c r="M470" s="65">
+        <f>(1/0.52)*3</f>
+        <v>5.7692307692307683</v>
       </c>
       <c r="N470" s="9" t="s">
         <v>38</v>
@@ -12352,7 +12361,7 @@
         <v>55</v>
       </c>
       <c r="H471" s="9" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="I471" s="8"/>
       <c r="J471" s="8"/>
@@ -12360,18 +12369,18 @@
       <c r="L471" t="s">
         <v>86</v>
       </c>
-      <c r="M471" s="65">
-        <f>(1/0.52)*4.5</f>
-        <v>8.6538461538461533</v>
+      <c r="M471" s="16">
+        <f>(1/0.52)*6</f>
+        <v>11.538461538461537</v>
       </c>
       <c r="N471" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O471" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="P471" s="64" t="s">
-        <v>451</v>
+        <v>96</v>
+      </c>
+      <c r="P471" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.25">
@@ -12388,8 +12397,8 @@
       <c r="G472" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H472" s="8" t="s">
-        <v>450</v>
+      <c r="H472" s="9" t="s">
+        <v>454</v>
       </c>
       <c r="I472" s="8"/>
       <c r="J472" s="8"/>
@@ -12397,49 +12406,52 @@
       <c r="L472" t="s">
         <v>86</v>
       </c>
-      <c r="M472" s="9">
-        <v>12</v>
+      <c r="M472" s="65">
+        <f>(1/0.52)*4.5</f>
+        <v>8.6538461538461533</v>
       </c>
       <c r="N472" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O472" s="8"/>
-      <c r="P472" s="8" t="s">
-        <v>91</v>
+      <c r="O472" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="P472" s="64" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>329</v>
+        <v>94</v>
       </c>
       <c r="B473" s="8"/>
       <c r="C473" s="8"/>
       <c r="D473" s="8"/>
       <c r="E473" s="8"/>
       <c r="F473" s="9" t="s">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="G473" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H473" s="8"/>
+      <c r="H473" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="I473" s="8"/>
       <c r="J473" s="8"/>
       <c r="K473" s="8"/>
       <c r="L473" t="s">
-        <v>85</v>
-      </c>
-      <c r="M473" s="11">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="M473" s="9">
+        <v>12</v>
       </c>
       <c r="N473" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O473" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="P473" s="26" t="s">
-        <v>333</v>
+      <c r="O473" s="8"/>
+      <c r="P473" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.25">
@@ -12456,24 +12468,21 @@
       <c r="G474" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H474" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="I474" s="26"/>
-      <c r="J474" s="26"/>
-      <c r="K474" s="26"/>
+      <c r="H474" s="8"/>
+      <c r="I474" s="8"/>
+      <c r="J474" s="8"/>
+      <c r="K474" s="8"/>
       <c r="L474" t="s">
-        <v>86</v>
-      </c>
-      <c r="M474" s="16">
-        <f>(1/0.5)*8</f>
-        <v>16</v>
+        <v>85</v>
+      </c>
+      <c r="M474" s="11">
+        <v>69</v>
       </c>
       <c r="N474" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O474" s="9" t="s">
-        <v>334</v>
+        <v>462</v>
       </c>
       <c r="P474" s="26" t="s">
         <v>333</v>
@@ -12493,18 +12502,18 @@
       <c r="G475" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H475" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="I475" s="8"/>
-      <c r="J475" s="8"/>
-      <c r="K475" s="8"/>
+      <c r="H475" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I475" s="26"/>
+      <c r="J475" s="26"/>
+      <c r="K475" s="26"/>
       <c r="L475" t="s">
         <v>86</v>
       </c>
-      <c r="M475" s="65">
-        <f>(1/0.5)*3</f>
-        <v>6</v>
+      <c r="M475" s="16">
+        <f>(1/0.5)*8</f>
+        <v>16</v>
       </c>
       <c r="N475" s="9" t="s">
         <v>38</v>
@@ -12530,8 +12539,8 @@
       <c r="G476" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H476" s="9" t="s">
-        <v>455</v>
+      <c r="H476" s="26" t="s">
+        <v>448</v>
       </c>
       <c r="I476" s="8"/>
       <c r="J476" s="8"/>
@@ -12540,16 +12549,18 @@
         <v>86</v>
       </c>
       <c r="M476" s="65">
-        <f>(1/0.5)*4.5</f>
-        <v>9</v>
+        <f>(1/0.5)*3</f>
+        <v>6</v>
       </c>
       <c r="N476" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O476" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="P476" s="26"/>
+        <v>334</v>
+      </c>
+      <c r="P476" s="26" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
@@ -12565,8 +12576,8 @@
       <c r="G477" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H477" s="26" t="s">
-        <v>449</v>
+      <c r="H477" s="9" t="s">
+        <v>455</v>
       </c>
       <c r="I477" s="8"/>
       <c r="J477" s="8"/>
@@ -12574,89 +12585,87 @@
       <c r="L477" t="s">
         <v>86</v>
       </c>
-      <c r="M477" s="9">
-        <f>(1/0.5)*8</f>
-        <v>16</v>
+      <c r="M477" s="65">
+        <f>(1/0.5)*4.5</f>
+        <v>9</v>
       </c>
       <c r="N477" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O477" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="P477" s="26" t="s">
-        <v>333</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="P477" s="26"/>
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="B478" s="8"/>
       <c r="C478" s="8"/>
       <c r="D478" s="8"/>
       <c r="E478" s="8"/>
       <c r="F478" s="9" t="s">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="G478" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H478" s="8"/>
+      <c r="H478" s="26" t="s">
+        <v>449</v>
+      </c>
       <c r="I478" s="8"/>
       <c r="J478" s="8"/>
       <c r="K478" s="8"/>
       <c r="L478" t="s">
-        <v>85</v>
-      </c>
-      <c r="M478" s="11">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="M478" s="9">
+        <f>(1/0.5)*8</f>
+        <v>16</v>
       </c>
       <c r="N478" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O478" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="P478" s="8" t="s">
-        <v>91</v>
+        <v>334</v>
+      </c>
+      <c r="P478" s="26" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A479" s="17" t="s">
+      <c r="A479" t="s">
         <v>257</v>
       </c>
-      <c r="B479" s="19"/>
-      <c r="C479" s="19"/>
-      <c r="D479" s="19"/>
-      <c r="E479" s="19"/>
-      <c r="F479" s="18" t="s">
+      <c r="B479" s="8"/>
+      <c r="C479" s="8"/>
+      <c r="D479" s="8"/>
+      <c r="E479" s="8"/>
+      <c r="F479" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="G479" s="18" t="s">
+      <c r="G479" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H479" s="26" t="s">
-        <v>458</v>
-      </c>
+      <c r="H479" s="8"/>
       <c r="I479" s="8"/>
       <c r="J479" s="8"/>
       <c r="K479" s="8"/>
       <c r="L479" t="s">
-        <v>86</v>
-      </c>
-      <c r="M479" s="21">
-        <f>(1/0.78)*21.32</f>
-        <v>27.333333333333332</v>
+        <v>85</v>
+      </c>
+      <c r="M479" s="11">
+        <v>87</v>
       </c>
       <c r="N479" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O479" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P479" s="8" t="s">
-        <v>461</v>
+        <v>91</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.25">
@@ -12673,20 +12682,25 @@
       <c r="G480" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="H480" t="s">
-        <v>457</v>
-      </c>
+      <c r="H480" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="I480" s="8"/>
+      <c r="J480" s="8"/>
+      <c r="K480" s="8"/>
       <c r="L480" t="s">
         <v>86</v>
       </c>
       <c r="M480" s="21">
-        <f>(1/0.78)*(4.1+3+8.06+3.01+3.64+0.57+1.99)</f>
-        <v>31.243589743589741</v>
+        <f>(1/0.78)*21.32</f>
+        <v>27.333333333333332</v>
       </c>
       <c r="N480" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O480" s="9"/>
+      <c r="O480" s="9" t="s">
+        <v>459</v>
+      </c>
       <c r="P480" s="8" t="s">
         <v>461</v>
       </c>
@@ -12705,18 +12719,15 @@
       <c r="G481" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="H481" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="I481" s="8"/>
-      <c r="J481" s="8"/>
-      <c r="K481" s="8"/>
+      <c r="H481" t="s">
+        <v>457</v>
+      </c>
       <c r="L481" t="s">
         <v>86</v>
       </c>
-      <c r="M481" s="65">
-        <f>(1/0.78)*3.12</f>
-        <v>4</v>
+      <c r="M481" s="21">
+        <f>(1/0.78)*(4.1+3+8.06+3.01+3.64+0.57+1.99)</f>
+        <v>31.243589743589741</v>
       </c>
       <c r="N481" s="9" t="s">
         <v>38</v>
@@ -12727,44 +12738,62 @@
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A482" s="6"/>
-      <c r="B482" s="10"/>
-      <c r="C482" s="10"/>
-      <c r="D482" s="10"/>
-      <c r="E482" s="10"/>
-      <c r="F482" s="11"/>
-      <c r="G482" s="11"/>
-      <c r="H482" s="11"/>
+      <c r="A482" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="B482" s="19"/>
+      <c r="C482" s="19"/>
+      <c r="D482" s="19"/>
+      <c r="E482" s="19"/>
+      <c r="F482" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="G482" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H482" s="9" t="s">
+        <v>455</v>
+      </c>
       <c r="I482" s="8"/>
       <c r="J482" s="8"/>
       <c r="K482" s="8"/>
-      <c r="M482" s="9"/>
-      <c r="N482" s="9"/>
-      <c r="P482" s="9"/>
+      <c r="L482" t="s">
+        <v>86</v>
+      </c>
+      <c r="M482" s="65">
+        <f>(1/0.78)*3.12</f>
+        <v>4</v>
+      </c>
+      <c r="N482" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O482" s="9"/>
+      <c r="P482" s="8" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
-        <v>435</v>
-      </c>
-      <c r="H483" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="L483" t="s">
-        <v>85</v>
-      </c>
-      <c r="M483">
-        <v>100</v>
-      </c>
-      <c r="N483" t="s">
-        <v>38</v>
-      </c>
+      <c r="A483" s="6"/>
+      <c r="B483" s="10"/>
+      <c r="C483" s="10"/>
+      <c r="D483" s="10"/>
+      <c r="E483" s="10"/>
+      <c r="F483" s="11"/>
+      <c r="G483" s="11"/>
+      <c r="H483" s="11"/>
+      <c r="I483" s="8"/>
+      <c r="J483" s="8"/>
+      <c r="K483" s="8"/>
+      <c r="M483" s="9"/>
+      <c r="N483" s="9"/>
+      <c r="P483" s="9"/>
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>436</v>
-      </c>
-      <c r="H484" s="9" t="s">
-        <v>454</v>
+        <v>435</v>
+      </c>
+      <c r="H484" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="L484" t="s">
         <v>85</v>
@@ -12777,128 +12806,128 @@
       </c>
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A485" s="4" t="s">
+      <c r="A485" t="s">
+        <v>436</v>
+      </c>
+      <c r="H485" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="L485" t="s">
+        <v>85</v>
+      </c>
+      <c r="M485">
+        <v>100</v>
+      </c>
+      <c r="N485" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="486" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A486" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B485" s="4"/>
-      <c r="C485" s="4"/>
-      <c r="D485" s="4"/>
-      <c r="E485" s="4"/>
-      <c r="F485" s="4"/>
-      <c r="G485" s="4"/>
-      <c r="H485" s="4"/>
-      <c r="I485" s="4"/>
-      <c r="J485" s="4"/>
-      <c r="K485" s="4"/>
-      <c r="L485" s="5"/>
-      <c r="M485" s="5"/>
-      <c r="N485" s="5"/>
-      <c r="O485" s="5"/>
-      <c r="P485" s="5"/>
-    </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
+      <c r="B486" s="4"/>
+      <c r="C486" s="4"/>
+      <c r="D486" s="4"/>
+      <c r="E486" s="4"/>
+      <c r="F486" s="4"/>
+      <c r="G486" s="4"/>
+      <c r="H486" s="4"/>
+      <c r="I486" s="4"/>
+      <c r="J486" s="4"/>
+      <c r="K486" s="4"/>
+      <c r="L486" s="5"/>
+      <c r="M486" s="5"/>
+      <c r="N486" s="5"/>
+      <c r="O486" s="5"/>
+      <c r="P486" s="5"/>
+    </row>
+    <row r="487" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
         <v>15</v>
       </c>
-      <c r="B486" s="8"/>
-      <c r="C486" s="8"/>
-      <c r="D486" s="8"/>
-      <c r="E486" s="8"/>
-      <c r="F486" s="9" t="s">
+      <c r="B487" s="8"/>
+      <c r="C487" s="8"/>
+      <c r="D487" s="8"/>
+      <c r="E487" s="8"/>
+      <c r="F487" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="G486" s="9" t="s">
+      <c r="G487" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="H486" s="8"/>
-      <c r="I486" s="8"/>
-      <c r="J486" s="8"/>
-      <c r="K486" s="8"/>
-      <c r="L486" t="s">
+      <c r="H487" s="8"/>
+      <c r="I487" s="8"/>
+      <c r="J487" s="8"/>
+      <c r="K487" s="8"/>
+      <c r="L487" t="s">
         <v>85</v>
       </c>
-      <c r="M486" s="9">
+      <c r="M487" s="9">
         <v>100</v>
       </c>
-      <c r="N486" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O486" s="8"/>
-      <c r="P486" s="8"/>
-    </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A487" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B487" s="10"/>
-      <c r="C487" s="10"/>
-      <c r="D487" s="10"/>
-      <c r="E487" s="10"/>
-      <c r="F487" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="G487" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="H487" s="10"/>
-      <c r="I487" s="10"/>
-      <c r="J487" s="10"/>
-      <c r="K487" s="10"/>
-      <c r="L487" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M487" s="11">
-        <v>100</v>
-      </c>
-      <c r="N487" s="11" t="s">
+      <c r="N487" s="9" t="s">
         <v>38</v>
       </c>
       <c r="O487" s="8"/>
       <c r="P487" s="8"/>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A488" s="4" t="s">
+      <c r="A488" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B488" s="10"/>
+      <c r="C488" s="10"/>
+      <c r="D488" s="10"/>
+      <c r="E488" s="10"/>
+      <c r="F488" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="G488" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="H488" s="10"/>
+      <c r="I488" s="10"/>
+      <c r="J488" s="10"/>
+      <c r="K488" s="10"/>
+      <c r="L488" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M488" s="11">
+        <v>100</v>
+      </c>
+      <c r="N488" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O488" s="8"/>
+      <c r="P488" s="8"/>
+    </row>
+    <row r="489" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A489" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B488" s="4"/>
-      <c r="C488" s="4"/>
-      <c r="D488" s="4"/>
-      <c r="E488" s="4"/>
-      <c r="F488" s="4"/>
-      <c r="G488" s="4"/>
-      <c r="H488" s="4"/>
-      <c r="I488" s="4"/>
-      <c r="J488" s="4"/>
-      <c r="K488" s="4"/>
-      <c r="L488" s="5"/>
-      <c r="M488" s="5"/>
-      <c r="N488" s="5"/>
-      <c r="O488" s="5"/>
-      <c r="P488" s="5"/>
-    </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
+      <c r="B489" s="4"/>
+      <c r="C489" s="4"/>
+      <c r="D489" s="4"/>
+      <c r="E489" s="4"/>
+      <c r="F489" s="4"/>
+      <c r="G489" s="4"/>
+      <c r="H489" s="4"/>
+      <c r="I489" s="4"/>
+      <c r="J489" s="4"/>
+      <c r="K489" s="4"/>
+      <c r="L489" s="5"/>
+      <c r="M489" s="5"/>
+      <c r="N489" s="5"/>
+      <c r="O489" s="5"/>
+      <c r="P489" s="5"/>
+    </row>
+    <row r="490" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
         <v>193</v>
       </c>
-      <c r="D489" t="s">
+      <c r="D490" t="s">
         <v>202</v>
-      </c>
-      <c r="L489" t="s">
-        <v>85</v>
-      </c>
-      <c r="M489">
-        <v>100</v>
-      </c>
-      <c r="N489" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A490" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="D490" t="s">
-        <v>203</v>
       </c>
       <c r="L490" t="s">
         <v>85</v>
@@ -12912,10 +12941,10 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D491" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L491" t="s">
         <v>85</v>
@@ -12928,46 +12957,35 @@
       </c>
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A492" s="6" t="s">
+      <c r="A492" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D492" t="s">
+        <v>204</v>
+      </c>
+      <c r="L492" t="s">
+        <v>85</v>
+      </c>
+      <c r="M492">
+        <v>100</v>
+      </c>
+      <c r="N492" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="493" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A493" s="6" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="493" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A493" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B493" s="19"/>
-      <c r="C493" s="19"/>
-      <c r="D493" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="E493" s="19"/>
-      <c r="F493" s="18"/>
-      <c r="G493" s="18"/>
-      <c r="H493" s="19"/>
-      <c r="I493" s="19"/>
-      <c r="J493" s="19"/>
-      <c r="K493" s="19"/>
-      <c r="L493" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M493" s="17">
-        <v>100</v>
-      </c>
-      <c r="N493" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O493" s="19"/>
-      <c r="P493" s="19"/>
     </row>
     <row r="494" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="17" t="s">
-        <v>363</v>
+        <v>197</v>
       </c>
       <c r="B494" s="19"/>
       <c r="C494" s="19"/>
       <c r="D494" s="19" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E494" s="19"/>
       <c r="F494" s="18"/>
@@ -12990,12 +13008,12 @@
     </row>
     <row r="495" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B495" s="19"/>
       <c r="C495" s="19"/>
       <c r="D495" s="19" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E495" s="19"/>
       <c r="F495" s="18"/>
@@ -13016,425 +13034,471 @@
       <c r="O495" s="19"/>
       <c r="P495" s="19"/>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A496" s="4" t="s">
+    <row r="496" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="B496" s="19"/>
+      <c r="C496" s="19"/>
+      <c r="D496" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E496" s="19"/>
+      <c r="F496" s="18"/>
+      <c r="G496" s="18"/>
+      <c r="H496" s="19"/>
+      <c r="I496" s="19"/>
+      <c r="J496" s="19"/>
+      <c r="K496" s="19"/>
+      <c r="L496" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M496" s="17">
+        <v>100</v>
+      </c>
+      <c r="N496" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O496" s="19"/>
+      <c r="P496" s="19"/>
+    </row>
+    <row r="497" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="B497" s="53"/>
+      <c r="C497" s="53"/>
+      <c r="D497" s="53"/>
+      <c r="E497" s="53"/>
+      <c r="F497" s="53"/>
+      <c r="G497" s="53"/>
+      <c r="H497" s="53"/>
+      <c r="I497" s="53"/>
+      <c r="J497" s="53"/>
+      <c r="K497" s="53"/>
+      <c r="L497" s="54"/>
+      <c r="M497" s="54"/>
+      <c r="N497" s="54"/>
+      <c r="O497" s="53"/>
+      <c r="P497" s="53"/>
+    </row>
+    <row r="498" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="B498" s="68"/>
+      <c r="C498" s="68"/>
+      <c r="D498" s="68" t="s">
+        <v>471</v>
+      </c>
+      <c r="E498" s="68"/>
+      <c r="F498" s="69"/>
+      <c r="G498" s="69"/>
+      <c r="H498" s="68"/>
+      <c r="I498" s="68"/>
+      <c r="J498" s="68"/>
+      <c r="K498" s="68"/>
+      <c r="L498" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="M498" s="48">
+        <v>50</v>
+      </c>
+      <c r="N498" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O498" s="19"/>
+      <c r="P498" s="19"/>
+    </row>
+    <row r="499" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="B499" s="68"/>
+      <c r="C499" s="68"/>
+      <c r="D499" s="68" t="s">
+        <v>471</v>
+      </c>
+      <c r="E499" s="68"/>
+      <c r="F499" s="69"/>
+      <c r="G499" s="69"/>
+      <c r="H499" s="68" t="s">
+        <v>473</v>
+      </c>
+      <c r="I499" s="68"/>
+      <c r="J499" s="68"/>
+      <c r="K499" s="68"/>
+      <c r="L499" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="M499" s="48">
+        <v>50</v>
+      </c>
+      <c r="N499" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O499" s="19"/>
+      <c r="P499" s="19"/>
+    </row>
+    <row r="500" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="48" t="s">
+        <v>367</v>
+      </c>
+      <c r="B500" s="68"/>
+      <c r="C500" s="68"/>
+      <c r="D500" s="68" t="s">
+        <v>472</v>
+      </c>
+      <c r="E500" s="68"/>
+      <c r="F500" s="69"/>
+      <c r="G500" s="69"/>
+      <c r="H500" s="68"/>
+      <c r="I500" s="68"/>
+      <c r="J500" s="68"/>
+      <c r="K500" s="68"/>
+      <c r="L500" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="M500" s="48">
+        <v>53</v>
+      </c>
+      <c r="N500" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O500" s="19"/>
+      <c r="P500" s="19"/>
+    </row>
+    <row r="501" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="48" t="s">
+        <v>367</v>
+      </c>
+      <c r="B501" s="68"/>
+      <c r="C501" s="68"/>
+      <c r="D501" s="68" t="s">
+        <v>472</v>
+      </c>
+      <c r="E501" s="68"/>
+      <c r="F501" s="69"/>
+      <c r="G501" s="69"/>
+      <c r="H501" s="68" t="s">
+        <v>474</v>
+      </c>
+      <c r="I501" s="68"/>
+      <c r="J501" s="68"/>
+      <c r="K501" s="68"/>
+      <c r="L501" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="M501" s="48">
+        <v>47</v>
+      </c>
+      <c r="N501" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O501" s="19"/>
+      <c r="P501" s="19"/>
+    </row>
+    <row r="502" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="B502" s="53"/>
+      <c r="C502" s="53"/>
+      <c r="D502" s="53"/>
+      <c r="E502" s="53"/>
+      <c r="F502" s="53"/>
+      <c r="G502" s="53"/>
+      <c r="H502" s="53"/>
+      <c r="I502" s="53"/>
+      <c r="J502" s="53"/>
+      <c r="K502" s="53"/>
+      <c r="L502" s="54"/>
+      <c r="M502" s="54"/>
+      <c r="N502" s="54"/>
+      <c r="O502" s="53"/>
+      <c r="P502" s="53"/>
+    </row>
+    <row r="503" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="B503" s="68"/>
+      <c r="C503" s="68"/>
+      <c r="D503" s="68" t="s">
+        <v>414</v>
+      </c>
+      <c r="E503" s="68"/>
+      <c r="F503" s="69"/>
+      <c r="G503" s="69"/>
+      <c r="H503" s="68"/>
+      <c r="I503" s="68"/>
+      <c r="J503" s="68"/>
+      <c r="K503" s="68"/>
+      <c r="L503" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="M503" s="48">
+        <v>100</v>
+      </c>
+      <c r="N503" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O503" s="19"/>
+      <c r="P503" s="19"/>
+    </row>
+    <row r="504" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A504" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B496" s="4"/>
-      <c r="C496" s="4"/>
-      <c r="D496" s="4"/>
-      <c r="E496" s="4"/>
-      <c r="F496" s="4"/>
-      <c r="G496" s="4"/>
-      <c r="H496" s="4"/>
-      <c r="I496" s="4"/>
-      <c r="J496" s="4"/>
-      <c r="K496" s="4"/>
-      <c r="L496" s="5"/>
-      <c r="M496" s="5"/>
-      <c r="N496" s="5"/>
-      <c r="O496" s="5"/>
-      <c r="P496" s="5"/>
-    </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+      <c r="B504" s="4"/>
+      <c r="C504" s="4"/>
+      <c r="D504" s="4"/>
+      <c r="E504" s="4"/>
+      <c r="F504" s="4"/>
+      <c r="G504" s="4"/>
+      <c r="H504" s="4"/>
+      <c r="I504" s="4"/>
+      <c r="J504" s="4"/>
+      <c r="K504" s="4"/>
+      <c r="L504" s="5"/>
+      <c r="M504" s="5"/>
+      <c r="N504" s="5"/>
+      <c r="O504" s="5"/>
+      <c r="P504" s="5"/>
+    </row>
+    <row r="505" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>117</v>
       </c>
-      <c r="D497" t="s">
+      <c r="D505" t="s">
         <v>119</v>
       </c>
-      <c r="J497" t="s">
+      <c r="J505" t="s">
         <v>45</v>
       </c>
-      <c r="L497" t="s">
+      <c r="L505" t="s">
         <v>85</v>
       </c>
-      <c r="M497" s="21">
-        <v>38</v>
-      </c>
-      <c r="N497" t="s">
-        <v>38</v>
-      </c>
-      <c r="O497" s="11"/>
-      <c r="P497" s="8" t="s">
+      <c r="M505" s="21">
+        <v>38</v>
+      </c>
+      <c r="N505" t="s">
+        <v>38</v>
+      </c>
+      <c r="O505" s="11"/>
+      <c r="P505" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
         <v>117</v>
       </c>
-      <c r="D498" t="s">
+      <c r="D506" t="s">
         <v>119</v>
       </c>
-      <c r="H498" t="s">
+      <c r="H506" t="s">
         <v>120</v>
       </c>
-      <c r="J498" t="s">
+      <c r="J506" t="s">
         <v>45</v>
       </c>
-      <c r="L498" t="s">
+      <c r="L506" t="s">
         <v>86</v>
       </c>
-      <c r="M498" s="21">
+      <c r="M506" s="21">
         <v>60</v>
       </c>
-      <c r="N498" t="s">
-        <v>38</v>
-      </c>
-      <c r="P498" s="8" t="s">
+      <c r="N506" t="s">
+        <v>38</v>
+      </c>
+      <c r="P506" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
         <v>117</v>
       </c>
-      <c r="D499" t="s">
+      <c r="D507" t="s">
         <v>119</v>
       </c>
-      <c r="J499" t="s">
+      <c r="J507" t="s">
         <v>43</v>
       </c>
-      <c r="L499" t="s">
+      <c r="L507" t="s">
         <v>85</v>
       </c>
-      <c r="M499" s="21">
+      <c r="M507" s="21">
         <v>32</v>
       </c>
-      <c r="N499" t="s">
-        <v>38</v>
-      </c>
-      <c r="O499" t="s">
+      <c r="N507" t="s">
+        <v>38</v>
+      </c>
+      <c r="O507" t="s">
         <v>122</v>
       </c>
-      <c r="P499" s="8"/>
-    </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>117</v>
-      </c>
-      <c r="D500" t="s">
-        <v>119</v>
-      </c>
-      <c r="H500" t="s">
-        <v>121</v>
-      </c>
-      <c r="J500" t="s">
-        <v>43</v>
-      </c>
-      <c r="L500" t="s">
-        <v>86</v>
-      </c>
-      <c r="M500" s="21">
-        <v>68</v>
-      </c>
-      <c r="N500" t="s">
-        <v>38</v>
-      </c>
-      <c r="P500" s="8"/>
-    </row>
-    <row r="501" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A501" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D501" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="J501" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L501" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M501" s="15">
-        <v>38</v>
-      </c>
-      <c r="N501" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P501" s="19"/>
-    </row>
-    <row r="502" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A502" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D502" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H502" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="J502" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L502" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M502" s="15">
-        <v>60</v>
-      </c>
-      <c r="N502" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P502" s="19"/>
-    </row>
-    <row r="503" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A503" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D503" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="J503" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="L503" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M503" s="15">
-        <v>32</v>
-      </c>
-      <c r="N503" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P503" s="19"/>
-    </row>
-    <row r="504" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A504" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D504" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="H504" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="J504" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="L504" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M504" s="15">
-        <v>68</v>
-      </c>
-      <c r="N504" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P504" s="19"/>
-    </row>
-    <row r="505" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A505" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D505" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="L505" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M505" s="15">
-        <v>43</v>
-      </c>
-      <c r="N505" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O505" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="P505" s="19"/>
-    </row>
-    <row r="506" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D506" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="H506" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="L506" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M506" s="15">
-        <v>47</v>
-      </c>
-      <c r="N506" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P506" s="19"/>
-    </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A507" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B507" s="4"/>
-      <c r="C507" s="4"/>
-      <c r="D507" s="4"/>
-      <c r="E507" s="4"/>
-      <c r="F507" s="4"/>
-      <c r="G507" s="4"/>
-      <c r="H507" s="4"/>
-      <c r="I507" s="4"/>
-      <c r="J507" s="4"/>
-      <c r="K507" s="4"/>
-      <c r="L507" s="5"/>
-      <c r="M507" s="5"/>
-      <c r="N507" s="5"/>
-      <c r="O507" s="5"/>
-      <c r="P507" s="5"/>
+      <c r="P507" s="8"/>
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="D508" t="s">
-        <v>215</v>
+        <v>119</v>
+      </c>
+      <c r="H508" t="s">
+        <v>121</v>
+      </c>
+      <c r="J508" t="s">
+        <v>43</v>
       </c>
       <c r="L508" t="s">
+        <v>86</v>
+      </c>
+      <c r="M508" s="21">
+        <v>68</v>
+      </c>
+      <c r="N508" t="s">
+        <v>38</v>
+      </c>
+      <c r="P508" s="8"/>
+    </row>
+    <row r="509" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D509" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="J509" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L509" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M508" s="22">
-        <f>161/1000*100</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="N508" t="s">
-        <v>38</v>
-      </c>
-      <c r="O508" t="s">
-        <v>319</v>
-      </c>
-      <c r="P508" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A509" t="s">
-        <v>208</v>
-      </c>
-      <c r="D509" t="s">
-        <v>215</v>
-      </c>
-      <c r="H509" t="s">
-        <v>216</v>
-      </c>
-      <c r="L509" t="s">
+      <c r="M509" s="15">
+        <v>38</v>
+      </c>
+      <c r="N509" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P509" s="19"/>
+    </row>
+    <row r="510" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D510" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H510" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J510" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L510" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M509" s="22">
-        <f>(6.4+25.2)/1000/0.9*100</f>
-        <v>3.5111111111111115</v>
-      </c>
-      <c r="N509" t="s">
-        <v>38</v>
-      </c>
-      <c r="O509" t="s">
-        <v>322</v>
-      </c>
-      <c r="P509" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A510" t="s">
-        <v>208</v>
-      </c>
-      <c r="D510" t="s">
-        <v>215</v>
-      </c>
-      <c r="H510" t="s">
-        <v>217</v>
-      </c>
-      <c r="L510" t="s">
+      <c r="M510" s="15">
+        <v>60</v>
+      </c>
+      <c r="N510" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P510" s="19"/>
+    </row>
+    <row r="511" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D511" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="J511" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L511" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M511" s="15">
+        <v>32</v>
+      </c>
+      <c r="N511" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P511" s="19"/>
+    </row>
+    <row r="512" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D512" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H512" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="J512" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L512" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M510" s="22">
-        <f>19/1000/0.76*100</f>
-        <v>2.5</v>
-      </c>
-      <c r="N510" t="s">
-        <v>38</v>
-      </c>
-      <c r="O510" t="s">
-        <v>323</v>
-      </c>
-      <c r="P510" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
-        <v>210</v>
-      </c>
-      <c r="D511" t="s">
-        <v>215</v>
-      </c>
-      <c r="L511" t="s">
+      <c r="M512" s="15">
+        <v>68</v>
+      </c>
+      <c r="N512" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P512" s="19"/>
+    </row>
+    <row r="513" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D513" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="L513" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M511" s="43">
-        <f>M508/0.8</f>
-        <v>20.125</v>
-      </c>
-      <c r="N511" t="s">
-        <v>38</v>
-      </c>
-      <c r="O511" s="17" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
-        <v>210</v>
-      </c>
-      <c r="D512" t="s">
-        <v>215</v>
-      </c>
-      <c r="H512" t="s">
-        <v>216</v>
-      </c>
-      <c r="L512" t="s">
+      <c r="M513" s="15">
+        <v>43</v>
+      </c>
+      <c r="N513" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O513" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="P513" s="19"/>
+    </row>
+    <row r="514" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D514" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="H514" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="L514" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M512" s="43">
-        <f>M509</f>
-        <v>3.5111111111111115</v>
-      </c>
-      <c r="N512" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
-        <v>210</v>
-      </c>
-      <c r="D513" t="s">
-        <v>215</v>
-      </c>
-      <c r="H513" t="s">
-        <v>217</v>
-      </c>
-      <c r="L513" t="s">
-        <v>86</v>
-      </c>
-      <c r="M513" s="43">
-        <f>M510</f>
-        <v>2.5</v>
-      </c>
-      <c r="N513" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A514" s="6" t="s">
-        <v>209</v>
-      </c>
+      <c r="M514" s="15">
+        <v>47</v>
+      </c>
+      <c r="N514" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P514" s="19"/>
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -13454,530 +13518,452 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>218</v>
-      </c>
-      <c r="B516" s="10"/>
-      <c r="C516" s="10"/>
-      <c r="D516" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E516" s="8"/>
-      <c r="F516" s="10"/>
-      <c r="G516" s="10"/>
-      <c r="H516" s="10"/>
-      <c r="I516" s="10"/>
-      <c r="J516" s="10"/>
-      <c r="K516" s="10"/>
+        <v>208</v>
+      </c>
+      <c r="D516" t="s">
+        <v>215</v>
+      </c>
       <c r="L516" t="s">
         <v>85</v>
       </c>
-      <c r="M516" s="20">
-        <v>70</v>
-      </c>
-      <c r="N516" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O516" s="8"/>
-      <c r="P516" s="8" t="s">
-        <v>91</v>
+      <c r="M516" s="22">
+        <f>161/1000*100</f>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="N516" t="s">
+        <v>38</v>
+      </c>
+      <c r="O516" t="s">
+        <v>319</v>
+      </c>
+      <c r="P516" s="17" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
+        <v>208</v>
+      </c>
+      <c r="D517" t="s">
+        <v>215</v>
+      </c>
+      <c r="H517" t="s">
+        <v>216</v>
+      </c>
+      <c r="L517" t="s">
+        <v>86</v>
+      </c>
+      <c r="M517" s="22">
+        <f>(6.4+25.2)/1000/0.9*100</f>
+        <v>3.5111111111111115</v>
+      </c>
+      <c r="N517" t="s">
+        <v>38</v>
+      </c>
+      <c r="O517" t="s">
+        <v>322</v>
+      </c>
+      <c r="P517" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="518" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>208</v>
+      </c>
+      <c r="D518" t="s">
+        <v>215</v>
+      </c>
+      <c r="H518" t="s">
+        <v>217</v>
+      </c>
+      <c r="L518" t="s">
+        <v>86</v>
+      </c>
+      <c r="M518" s="22">
+        <f>19/1000/0.76*100</f>
+        <v>2.5</v>
+      </c>
+      <c r="N518" t="s">
+        <v>38</v>
+      </c>
+      <c r="O518" t="s">
+        <v>323</v>
+      </c>
+      <c r="P518" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="519" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>210</v>
+      </c>
+      <c r="D519" t="s">
+        <v>215</v>
+      </c>
+      <c r="L519" t="s">
+        <v>85</v>
+      </c>
+      <c r="M519" s="43">
+        <f>M516/0.8</f>
+        <v>20.125</v>
+      </c>
+      <c r="N519" t="s">
+        <v>38</v>
+      </c>
+      <c r="O519" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="520" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>210</v>
+      </c>
+      <c r="D520" t="s">
+        <v>215</v>
+      </c>
+      <c r="H520" t="s">
+        <v>216</v>
+      </c>
+      <c r="L520" t="s">
+        <v>86</v>
+      </c>
+      <c r="M520" s="43">
+        <f>M517</f>
+        <v>3.5111111111111115</v>
+      </c>
+      <c r="N520" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="521" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>210</v>
+      </c>
+      <c r="D521" t="s">
+        <v>215</v>
+      </c>
+      <c r="H521" t="s">
+        <v>217</v>
+      </c>
+      <c r="L521" t="s">
+        <v>86</v>
+      </c>
+      <c r="M521" s="43">
+        <f>M518</f>
+        <v>2.5</v>
+      </c>
+      <c r="N521" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="522" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A522" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="523" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A523" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B523" s="4"/>
+      <c r="C523" s="4"/>
+      <c r="D523" s="4"/>
+      <c r="E523" s="4"/>
+      <c r="F523" s="4"/>
+      <c r="G523" s="4"/>
+      <c r="H523" s="4"/>
+      <c r="I523" s="4"/>
+      <c r="J523" s="4"/>
+      <c r="K523" s="4"/>
+      <c r="L523" s="5"/>
+      <c r="M523" s="5"/>
+      <c r="N523" s="5"/>
+      <c r="O523" s="5"/>
+      <c r="P523" s="5"/>
+    </row>
+    <row r="524" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>218</v>
+      </c>
+      <c r="B524" s="10"/>
+      <c r="C524" s="10"/>
+      <c r="D524" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E524" s="8"/>
+      <c r="F524" s="10"/>
+      <c r="G524" s="10"/>
+      <c r="H524" s="10"/>
+      <c r="I524" s="10"/>
+      <c r="J524" s="10"/>
+      <c r="K524" s="10"/>
+      <c r="L524" t="s">
+        <v>85</v>
+      </c>
+      <c r="M524" s="20">
+        <v>70</v>
+      </c>
+      <c r="N524" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O524" s="8"/>
+      <c r="P524" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="525" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
         <v>221</v>
       </c>
-      <c r="B517" s="10"/>
-      <c r="C517" s="10"/>
-      <c r="D517" s="8" t="s">
+      <c r="B525" s="10"/>
+      <c r="C525" s="10"/>
+      <c r="D525" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E517" s="8"/>
-      <c r="F517" s="10"/>
-      <c r="G517" s="10"/>
-      <c r="H517" s="10"/>
-      <c r="I517" s="10"/>
-      <c r="J517" s="10"/>
-      <c r="K517" s="10"/>
-      <c r="L517" t="s">
+      <c r="E525" s="8"/>
+      <c r="F525" s="10"/>
+      <c r="G525" s="10"/>
+      <c r="H525" s="10"/>
+      <c r="I525" s="10"/>
+      <c r="J525" s="10"/>
+      <c r="K525" s="10"/>
+      <c r="L525" t="s">
         <v>85</v>
       </c>
-      <c r="M517" s="20">
+      <c r="M525" s="20">
         <f>655*0.7</f>
         <v>458.49999999999994</v>
       </c>
-      <c r="N517" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O517" s="8"/>
-      <c r="P517" s="8" t="s">
+      <c r="N525" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O525" s="8"/>
+      <c r="P525" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
         <v>221</v>
       </c>
-      <c r="B518" s="10"/>
-      <c r="C518" s="10"/>
-      <c r="D518" s="8" t="s">
+      <c r="B526" s="10"/>
+      <c r="C526" s="10"/>
+      <c r="D526" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E518" s="8"/>
-      <c r="F518" s="10"/>
-      <c r="G518" s="10"/>
-      <c r="H518" s="19" t="s">
+      <c r="E526" s="8"/>
+      <c r="F526" s="10"/>
+      <c r="G526" s="10"/>
+      <c r="H526" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="I518" s="10"/>
-      <c r="J518" s="10"/>
-      <c r="K518" s="10"/>
-      <c r="L518" t="s">
+      <c r="I526" s="10"/>
+      <c r="J526" s="10"/>
+      <c r="K526" s="10"/>
+      <c r="L526" t="s">
         <v>86</v>
       </c>
-      <c r="M518" s="20">
-        <f>1*(M517/100)*0.2*100</f>
+      <c r="M526" s="20">
+        <f>1*(M525/100)*0.2*100</f>
         <v>91.699999999999989</v>
       </c>
-      <c r="N518" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O518" s="8" t="s">
+      <c r="N526" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O526" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="P518" s="8" t="s">
+      <c r="P526" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B519" s="10"/>
-      <c r="C519" s="10"/>
-      <c r="D519" s="8"/>
-      <c r="E519" s="8"/>
-      <c r="F519" s="10"/>
-      <c r="G519" s="10"/>
-      <c r="H519" s="10" t="s">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B527" s="10"/>
+      <c r="C527" s="10"/>
+      <c r="D527" s="8"/>
+      <c r="E527" s="8"/>
+      <c r="F527" s="10"/>
+      <c r="G527" s="10"/>
+      <c r="H527" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="I519" s="10"/>
-      <c r="J519" s="10"/>
-      <c r="K519" s="10"/>
-      <c r="M519" s="20"/>
-      <c r="N519" s="9"/>
-      <c r="O519" s="10" t="s">
+      <c r="I527" s="10"/>
+      <c r="J527" s="10"/>
+      <c r="K527" s="10"/>
+      <c r="M527" s="20"/>
+      <c r="N527" s="9"/>
+      <c r="O527" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="P519" s="8"/>
-    </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A520" t="s">
+      <c r="P527" s="8"/>
+    </row>
+    <row r="528" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
         <v>219</v>
       </c>
-      <c r="B520" s="10"/>
-      <c r="C520" s="10"/>
-      <c r="D520" s="9" t="s">
+      <c r="B528" s="10"/>
+      <c r="C528" s="10"/>
+      <c r="D528" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E520" s="9"/>
-      <c r="F520" s="10"/>
-      <c r="G520" s="10"/>
-      <c r="H520" s="19"/>
-      <c r="I520" s="10"/>
-      <c r="J520" s="10"/>
-      <c r="K520" s="10"/>
-      <c r="L520" t="s">
+      <c r="E528" s="9"/>
+      <c r="F528" s="10"/>
+      <c r="G528" s="10"/>
+      <c r="H528" s="19"/>
+      <c r="I528" s="10"/>
+      <c r="J528" s="10"/>
+      <c r="K528" s="10"/>
+      <c r="L528" t="s">
         <v>85</v>
       </c>
-      <c r="M520" s="20">
+      <c r="M528" s="20">
         <v>65</v>
       </c>
-      <c r="N520" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O520" s="8"/>
-      <c r="P520" s="8" t="s">
+      <c r="N528" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O528" s="8"/>
+      <c r="P528" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A521" t="s">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
         <v>219</v>
       </c>
-      <c r="B521" s="10"/>
-      <c r="C521" s="10"/>
-      <c r="D521" s="9" t="s">
+      <c r="B529" s="10"/>
+      <c r="C529" s="10"/>
+      <c r="D529" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E521" s="9"/>
-      <c r="F521" s="10"/>
-      <c r="G521" s="10"/>
-      <c r="H521" s="19" t="s">
+      <c r="E529" s="9"/>
+      <c r="F529" s="10"/>
+      <c r="G529" s="10"/>
+      <c r="H529" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I521" s="10"/>
-      <c r="J521" s="10"/>
-      <c r="K521" s="10"/>
-      <c r="L521" t="s">
+      <c r="I529" s="10"/>
+      <c r="J529" s="10"/>
+      <c r="K529" s="10"/>
+      <c r="L529" t="s">
         <v>86</v>
       </c>
-      <c r="M521" s="20">
+      <c r="M529" s="20">
         <v>35</v>
       </c>
-      <c r="N521" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O521" s="8"/>
-      <c r="P521" s="8" t="s">
+      <c r="N529" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O529" s="8"/>
+      <c r="P529" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A522" t="s">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
         <v>222</v>
       </c>
-      <c r="B522" s="10"/>
-      <c r="C522" s="10"/>
-      <c r="D522" s="9" t="s">
+      <c r="B530" s="10"/>
+      <c r="C530" s="10"/>
+      <c r="D530" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E522" s="9"/>
-      <c r="F522" s="10"/>
-      <c r="G522" s="10"/>
-      <c r="H522" s="19"/>
-      <c r="I522" s="10"/>
-      <c r="J522" s="10"/>
-      <c r="K522" s="10"/>
-      <c r="L522" t="s">
+      <c r="E530" s="9"/>
+      <c r="F530" s="10"/>
+      <c r="G530" s="10"/>
+      <c r="H530" s="19"/>
+      <c r="I530" s="10"/>
+      <c r="J530" s="10"/>
+      <c r="K530" s="10"/>
+      <c r="L530" t="s">
         <v>85</v>
       </c>
-      <c r="M522" s="20">
+      <c r="M530" s="20">
         <v>68</v>
       </c>
-      <c r="N522" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O522" s="8"/>
-      <c r="P522" s="8" t="s">
+      <c r="N530" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O530" s="8"/>
+      <c r="P530" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
         <v>222</v>
       </c>
-      <c r="B523" s="10"/>
-      <c r="C523" s="10"/>
-      <c r="D523" s="9" t="s">
+      <c r="B531" s="10"/>
+      <c r="C531" s="10"/>
+      <c r="D531" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E523" s="9"/>
-      <c r="F523" s="10"/>
-      <c r="G523" s="10"/>
-      <c r="H523" t="s">
+      <c r="E531" s="9"/>
+      <c r="F531" s="10"/>
+      <c r="G531" s="10"/>
+      <c r="H531" t="s">
         <v>296</v>
       </c>
-      <c r="I523" s="10"/>
-      <c r="J523" s="10"/>
-      <c r="K523" s="10"/>
-      <c r="L523" t="s">
+      <c r="I531" s="10"/>
+      <c r="J531" s="10"/>
+      <c r="K531" s="10"/>
+      <c r="L531" t="s">
         <v>86</v>
       </c>
-      <c r="M523" s="66">
-        <f>M558</f>
+      <c r="M531" s="66">
+        <f>M566</f>
         <v>36.402116402116405</v>
       </c>
-      <c r="N523" s="67" t="s">
-        <v>38</v>
-      </c>
-      <c r="O523" s="19" t="s">
+      <c r="N531" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="O531" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="P523" s="10"/>
-    </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A524" s="4" t="s">
+      <c r="P531" s="10"/>
+    </row>
+    <row r="532" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A532" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B524" s="4"/>
-      <c r="C524" s="4"/>
-      <c r="D524" s="4"/>
-      <c r="E524" s="47"/>
-      <c r="F524" s="4"/>
-      <c r="G524" s="4"/>
-      <c r="H524" s="4"/>
-      <c r="I524" s="4"/>
-      <c r="J524" s="4"/>
-      <c r="K524" s="4"/>
-      <c r="L524" s="5"/>
-      <c r="M524" s="5"/>
-      <c r="N524" s="5"/>
-      <c r="O524" s="5"/>
-      <c r="P524" s="5"/>
-    </row>
-    <row r="525" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A525" s="57" t="s">
-        <v>373</v>
-      </c>
-      <c r="B525" s="57"/>
-      <c r="C525" s="57"/>
-      <c r="D525" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="E525" s="57"/>
-      <c r="F525" s="58"/>
-      <c r="G525" s="58"/>
-      <c r="H525" s="58"/>
-      <c r="I525" s="58"/>
-      <c r="J525" s="57"/>
-      <c r="K525" s="58"/>
-      <c r="L525" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M525" s="51">
-        <v>94</v>
-      </c>
-      <c r="N525" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O525" s="57"/>
-      <c r="P525" s="19"/>
-    </row>
-    <row r="526" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A526" s="57" t="s">
-        <v>373</v>
-      </c>
-      <c r="B526" s="57"/>
-      <c r="C526" s="57"/>
-      <c r="D526" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="E526" s="57"/>
-      <c r="F526" s="58"/>
-      <c r="G526" s="58"/>
-      <c r="H526" s="57" t="s">
-        <v>416</v>
-      </c>
-      <c r="I526" s="58"/>
-      <c r="J526" s="57"/>
-      <c r="K526" s="58"/>
-      <c r="L526" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M526" s="29">
-        <f>11*0.94</f>
-        <v>10.34</v>
-      </c>
-      <c r="N526" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O526" s="57" t="s">
-        <v>417</v>
-      </c>
-      <c r="P526" s="19"/>
-    </row>
-    <row r="527" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A527" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="B527" s="57"/>
-      <c r="C527" s="57"/>
-      <c r="D527" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E527" s="57"/>
-      <c r="F527" s="57"/>
-      <c r="G527" s="57"/>
-      <c r="H527" s="57"/>
-      <c r="I527" s="57"/>
-      <c r="J527" s="57"/>
-      <c r="K527" s="57"/>
-      <c r="L527" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M527" s="17">
-        <v>31</v>
-      </c>
-      <c r="N527" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O527" s="57" t="s">
-        <v>401</v>
-      </c>
-      <c r="P527" s="19"/>
-    </row>
-    <row r="528" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A528" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="B528" s="57"/>
-      <c r="C528" s="57"/>
-      <c r="D528" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E528" s="57"/>
-      <c r="F528" s="57"/>
-      <c r="G528" s="57"/>
-      <c r="H528" s="57" t="s">
-        <v>418</v>
-      </c>
-      <c r="I528" s="57"/>
-      <c r="J528" s="57"/>
-      <c r="K528" s="57"/>
-      <c r="L528" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M528" s="29">
-        <f>69*0.31</f>
-        <v>21.39</v>
-      </c>
-      <c r="N528" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O528" s="57"/>
-      <c r="P528" s="19"/>
-    </row>
-    <row r="529" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A529" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="B529" s="57"/>
-      <c r="C529" s="57"/>
-      <c r="D529" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E529" s="57"/>
-      <c r="F529" s="57"/>
-      <c r="G529" s="57"/>
-      <c r="H529" s="57" t="s">
-        <v>419</v>
-      </c>
-      <c r="I529" s="57"/>
-      <c r="J529" s="57"/>
-      <c r="K529" s="57"/>
-      <c r="L529" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M529" s="29">
-        <f>1.9*0.31</f>
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="N529" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O529" s="57"/>
-      <c r="P529" s="19"/>
-    </row>
-    <row r="530" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A530" s="57" t="s">
-        <v>378</v>
-      </c>
-      <c r="B530" s="57"/>
-      <c r="C530" s="57"/>
-      <c r="D530" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E530" s="57"/>
-      <c r="F530" s="57"/>
-      <c r="G530" s="57"/>
-      <c r="H530" s="57"/>
-      <c r="I530" s="57"/>
-      <c r="J530" s="57"/>
-      <c r="K530" s="57"/>
-      <c r="L530" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M530" s="17">
-        <v>769</v>
-      </c>
-      <c r="N530" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O530" s="57"/>
-      <c r="P530" s="19"/>
-    </row>
-    <row r="531" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A531" s="57" t="s">
-        <v>378</v>
-      </c>
-      <c r="B531" s="57"/>
-      <c r="C531" s="57"/>
-      <c r="D531" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E531" s="57"/>
-      <c r="F531" s="57"/>
-      <c r="G531" s="57"/>
-      <c r="H531" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="I531" s="57"/>
-      <c r="J531" s="57"/>
-      <c r="K531" s="57"/>
-      <c r="L531" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M531" s="29">
-        <f>1.5*7.69</f>
-        <v>11.535</v>
-      </c>
-      <c r="N531" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O531" s="57"/>
-      <c r="P531" s="19"/>
-    </row>
-    <row r="532" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A532" s="57" t="s">
-        <v>380</v>
-      </c>
-      <c r="B532" s="57"/>
-      <c r="C532" s="57"/>
-      <c r="D532" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="E532" s="57"/>
-      <c r="F532" s="58"/>
-      <c r="G532" s="58"/>
-      <c r="H532" s="58"/>
-      <c r="I532" s="58"/>
-      <c r="J532" s="57"/>
-      <c r="K532" s="58"/>
-      <c r="L532" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M532" s="29">
-        <f>M508*0.55</f>
-        <v>8.8550000000000022</v>
-      </c>
-      <c r="N532" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O532" s="57"/>
-      <c r="P532" s="19"/>
+      <c r="B532" s="4"/>
+      <c r="C532" s="4"/>
+      <c r="D532" s="4"/>
+      <c r="E532" s="47"/>
+      <c r="F532" s="4"/>
+      <c r="G532" s="4"/>
+      <c r="H532" s="4"/>
+      <c r="I532" s="4"/>
+      <c r="J532" s="4"/>
+      <c r="K532" s="4"/>
+      <c r="L532" s="5"/>
+      <c r="M532" s="5"/>
+      <c r="N532" s="5"/>
+      <c r="O532" s="5"/>
+      <c r="P532" s="5"/>
     </row>
     <row r="533" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="57" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B533" s="57"/>
       <c r="C533" s="57"/>
       <c r="D533" s="57" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E533" s="57"/>
       <c r="F533" s="58"/>
       <c r="G533" s="58"/>
-      <c r="H533" s="17" t="s">
-        <v>216</v>
-      </c>
+      <c r="H533" s="58"/>
       <c r="I533" s="58"/>
       <c r="J533" s="57"/>
       <c r="K533" s="58"/>
       <c r="L533" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M533" s="29">
-        <f>M509*0.55</f>
-        <v>1.9311111111111114</v>
+        <v>85</v>
+      </c>
+      <c r="M533" s="51">
+        <v>94</v>
       </c>
       <c r="N533" s="57" t="s">
         <v>38</v>
@@ -13987,18 +13973,18 @@
     </row>
     <row r="534" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="57" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B534" s="57"/>
       <c r="C534" s="57"/>
       <c r="D534" s="57" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="E534" s="57"/>
       <c r="F534" s="58"/>
       <c r="G534" s="58"/>
-      <c r="H534" s="17" t="s">
-        <v>217</v>
+      <c r="H534" s="57" t="s">
+        <v>416</v>
       </c>
       <c r="I534" s="58"/>
       <c r="J534" s="57"/>
@@ -14007,68 +13993,71 @@
         <v>86</v>
       </c>
       <c r="M534" s="29">
-        <f>M510*0.55</f>
-        <v>1.375</v>
+        <f>11*0.94</f>
+        <v>10.34</v>
       </c>
       <c r="N534" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="O534" s="57"/>
+      <c r="O534" s="57" t="s">
+        <v>417</v>
+      </c>
       <c r="P534" s="19"/>
     </row>
     <row r="535" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="57" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B535" s="57"/>
       <c r="C535" s="57"/>
       <c r="D535" s="57" t="s">
-        <v>215</v>
+        <v>37</v>
       </c>
       <c r="E535" s="57"/>
-      <c r="F535" s="58"/>
-      <c r="G535" s="58"/>
-      <c r="H535" s="58"/>
-      <c r="I535" s="58"/>
+      <c r="F535" s="57"/>
+      <c r="G535" s="57"/>
+      <c r="H535" s="57"/>
+      <c r="I535" s="57"/>
       <c r="J535" s="57"/>
-      <c r="K535" s="58"/>
+      <c r="K535" s="57"/>
       <c r="L535" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M535" s="29">
-        <f>M508*1.09</f>
-        <v>17.549000000000003</v>
+      <c r="M535" s="17">
+        <v>31</v>
       </c>
       <c r="N535" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="O535" s="57"/>
+      <c r="O535" s="57" t="s">
+        <v>401</v>
+      </c>
       <c r="P535" s="19"/>
     </row>
     <row r="536" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="57" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B536" s="57"/>
       <c r="C536" s="57"/>
       <c r="D536" s="57" t="s">
-        <v>215</v>
+        <v>37</v>
       </c>
       <c r="E536" s="57"/>
-      <c r="F536" s="58"/>
-      <c r="G536" s="58"/>
-      <c r="H536" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="I536" s="58"/>
+      <c r="F536" s="57"/>
+      <c r="G536" s="57"/>
+      <c r="H536" s="57" t="s">
+        <v>418</v>
+      </c>
+      <c r="I536" s="57"/>
       <c r="J536" s="57"/>
-      <c r="K536" s="58"/>
+      <c r="K536" s="57"/>
       <c r="L536" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M536" s="29">
-        <f t="shared" ref="M536:M537" si="3">M509*1.09</f>
-        <v>3.8271111111111118</v>
+        <f>69*0.31</f>
+        <v>21.39</v>
       </c>
       <c r="N536" s="57" t="s">
         <v>38</v>
@@ -14078,28 +14067,28 @@
     </row>
     <row r="537" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="57" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B537" s="57"/>
       <c r="C537" s="57"/>
       <c r="D537" s="57" t="s">
-        <v>215</v>
+        <v>37</v>
       </c>
       <c r="E537" s="57"/>
-      <c r="F537" s="58"/>
-      <c r="G537" s="58"/>
-      <c r="H537" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="I537" s="58"/>
+      <c r="F537" s="57"/>
+      <c r="G537" s="57"/>
+      <c r="H537" s="57" t="s">
+        <v>419</v>
+      </c>
+      <c r="I537" s="57"/>
       <c r="J537" s="57"/>
-      <c r="K537" s="58"/>
+      <c r="K537" s="57"/>
       <c r="L537" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M537" s="29">
-        <f t="shared" si="3"/>
-        <v>2.7250000000000001</v>
+        <f>1.9*0.31</f>
+        <v>0.58899999999999997</v>
       </c>
       <c r="N537" s="57" t="s">
         <v>38</v>
@@ -14109,26 +14098,25 @@
     </row>
     <row r="538" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="57" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B538" s="57"/>
       <c r="C538" s="57"/>
       <c r="D538" s="57" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="E538" s="57"/>
-      <c r="F538" s="58"/>
-      <c r="G538" s="58"/>
-      <c r="H538" s="58"/>
-      <c r="I538" s="58"/>
+      <c r="F538" s="57"/>
+      <c r="G538" s="57"/>
+      <c r="H538" s="57"/>
+      <c r="I538" s="57"/>
       <c r="J538" s="57"/>
-      <c r="K538" s="58"/>
+      <c r="K538" s="57"/>
       <c r="L538" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M538" s="29">
-        <f>M508*0.67</f>
-        <v>10.787000000000001</v>
+      <c r="M538" s="17">
+        <v>769</v>
       </c>
       <c r="N538" s="57" t="s">
         <v>38</v>
@@ -14138,28 +14126,28 @@
     </row>
     <row r="539" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="57" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B539" s="57"/>
       <c r="C539" s="57"/>
       <c r="D539" s="57" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="E539" s="57"/>
-      <c r="F539" s="58"/>
-      <c r="G539" s="58"/>
-      <c r="H539" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="I539" s="58"/>
+      <c r="F539" s="57"/>
+      <c r="G539" s="57"/>
+      <c r="H539" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="I539" s="57"/>
       <c r="J539" s="57"/>
-      <c r="K539" s="58"/>
+      <c r="K539" s="57"/>
       <c r="L539" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M539" s="29">
-        <f t="shared" ref="M539:M540" si="4">M509*0.67</f>
-        <v>2.352444444444445</v>
+        <f>1.5*7.69</f>
+        <v>11.535</v>
       </c>
       <c r="N539" s="57" t="s">
         <v>38</v>
@@ -14169,7 +14157,7 @@
     </row>
     <row r="540" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B540" s="57"/>
       <c r="C540" s="57"/>
@@ -14179,18 +14167,16 @@
       <c r="E540" s="57"/>
       <c r="F540" s="58"/>
       <c r="G540" s="58"/>
-      <c r="H540" s="17" t="s">
-        <v>217</v>
-      </c>
+      <c r="H540" s="58"/>
       <c r="I540" s="58"/>
       <c r="J540" s="57"/>
       <c r="K540" s="58"/>
       <c r="L540" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M540" s="29">
-        <f t="shared" si="4"/>
-        <v>1.675</v>
+        <f>M516*0.55</f>
+        <v>8.8550000000000022</v>
       </c>
       <c r="N540" s="57" t="s">
         <v>38</v>
@@ -14200,25 +14186,28 @@
     </row>
     <row r="541" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="57" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B541" s="57"/>
       <c r="C541" s="57"/>
       <c r="D541" s="57" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E541" s="57"/>
       <c r="F541" s="58"/>
       <c r="G541" s="58"/>
-      <c r="H541" s="58"/>
+      <c r="H541" s="17" t="s">
+        <v>216</v>
+      </c>
       <c r="I541" s="58"/>
       <c r="J541" s="57"/>
       <c r="K541" s="58"/>
       <c r="L541" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M541" s="17">
-        <v>150</v>
+        <v>86</v>
+      </c>
+      <c r="M541" s="29">
+        <f>M517*0.55</f>
+        <v>1.9311111111111114</v>
       </c>
       <c r="N541" s="57" t="s">
         <v>38</v>
@@ -14228,25 +14217,28 @@
     </row>
     <row r="542" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="57" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B542" s="57"/>
       <c r="C542" s="57"/>
       <c r="D542" s="57" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E542" s="57"/>
       <c r="F542" s="58"/>
       <c r="G542" s="58"/>
-      <c r="H542" s="58"/>
+      <c r="H542" s="17" t="s">
+        <v>217</v>
+      </c>
       <c r="I542" s="58"/>
       <c r="J542" s="57"/>
       <c r="K542" s="58"/>
       <c r="L542" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M542" s="17">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="M542" s="29">
+        <f>M518*0.55</f>
+        <v>1.375</v>
       </c>
       <c r="N542" s="57" t="s">
         <v>38</v>
@@ -14256,27 +14248,26 @@
     </row>
     <row r="543" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="57" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B543" s="57"/>
       <c r="C543" s="57"/>
       <c r="D543" s="57" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E543" s="57"/>
       <c r="F543" s="58"/>
       <c r="G543" s="58"/>
-      <c r="H543" s="57" t="s">
-        <v>421</v>
-      </c>
+      <c r="H543" s="58"/>
       <c r="I543" s="58"/>
       <c r="J543" s="57"/>
       <c r="K543" s="58"/>
       <c r="L543" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M543" s="17">
-        <v>22</v>
+        <v>85</v>
+      </c>
+      <c r="M543" s="29">
+        <f>M516*1.09</f>
+        <v>17.549000000000003</v>
       </c>
       <c r="N543" s="57" t="s">
         <v>38</v>
@@ -14286,7 +14277,7 @@
     </row>
     <row r="544" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="57" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B544" s="57"/>
       <c r="C544" s="57"/>
@@ -14296,15 +14287,18 @@
       <c r="E544" s="57"/>
       <c r="F544" s="58"/>
       <c r="G544" s="58"/>
-      <c r="H544" s="58"/>
+      <c r="H544" s="17" t="s">
+        <v>216</v>
+      </c>
       <c r="I544" s="58"/>
       <c r="J544" s="57"/>
       <c r="K544" s="58"/>
       <c r="L544" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M544" s="29">
-        <v>8.9</v>
+        <f t="shared" ref="M544:M545" si="3">M517*1.09</f>
+        <v>3.8271111111111118</v>
       </c>
       <c r="N544" s="57" t="s">
         <v>38</v>
@@ -14314,7 +14308,7 @@
     </row>
     <row r="545" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="57" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B545" s="57"/>
       <c r="C545" s="57"/>
@@ -14325,7 +14319,7 @@
       <c r="F545" s="58"/>
       <c r="G545" s="58"/>
       <c r="H545" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I545" s="58"/>
       <c r="J545" s="57"/>
@@ -14334,7 +14328,8 @@
         <v>86</v>
       </c>
       <c r="M545" s="29">
-        <v>1.9</v>
+        <f t="shared" si="3"/>
+        <v>2.7250000000000001</v>
       </c>
       <c r="N545" s="57" t="s">
         <v>38</v>
@@ -14344,7 +14339,7 @@
     </row>
     <row r="546" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="57" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B546" s="57"/>
       <c r="C546" s="57"/>
@@ -14354,17 +14349,16 @@
       <c r="E546" s="57"/>
       <c r="F546" s="58"/>
       <c r="G546" s="58"/>
-      <c r="H546" s="17" t="s">
-        <v>217</v>
-      </c>
+      <c r="H546" s="58"/>
       <c r="I546" s="58"/>
       <c r="J546" s="57"/>
       <c r="K546" s="58"/>
       <c r="L546" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M546" s="29">
-        <v>1.4</v>
+        <f>M516*0.67</f>
+        <v>10.787000000000001</v>
       </c>
       <c r="N546" s="57" t="s">
         <v>38</v>
@@ -14374,26 +14368,38 @@
     </row>
     <row r="547" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="57" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B547" s="57"/>
       <c r="C547" s="57"/>
-      <c r="D547" s="58"/>
-      <c r="E547" s="58"/>
+      <c r="D547" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E547" s="57"/>
       <c r="F547" s="58"/>
       <c r="G547" s="58"/>
-      <c r="H547" s="58"/>
+      <c r="H547" s="17" t="s">
+        <v>216</v>
+      </c>
       <c r="I547" s="58"/>
       <c r="J547" s="57"/>
       <c r="K547" s="58"/>
-      <c r="M547" s="57"/>
-      <c r="N547" s="57"/>
+      <c r="L547" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="M547" s="29">
+        <f t="shared" ref="M547:M548" si="4">M517*0.67</f>
+        <v>2.352444444444445</v>
+      </c>
+      <c r="N547" s="57" t="s">
+        <v>38</v>
+      </c>
       <c r="O547" s="57"/>
       <c r="P547" s="19"/>
     </row>
     <row r="548" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="57" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B548" s="57"/>
       <c r="C548" s="57"/>
@@ -14403,15 +14409,18 @@
       <c r="E548" s="57"/>
       <c r="F548" s="58"/>
       <c r="G548" s="58"/>
-      <c r="H548" s="58"/>
+      <c r="H548" s="17" t="s">
+        <v>217</v>
+      </c>
       <c r="I548" s="58"/>
       <c r="J548" s="57"/>
       <c r="K548" s="58"/>
       <c r="L548" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M548" s="29">
-        <v>4.83</v>
+        <f t="shared" si="4"/>
+        <v>1.675</v>
       </c>
       <c r="N548" s="57" t="s">
         <v>38</v>
@@ -14421,27 +14430,25 @@
     </row>
     <row r="549" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="57" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B549" s="57"/>
       <c r="C549" s="57"/>
       <c r="D549" s="57" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E549" s="57"/>
       <c r="F549" s="58"/>
       <c r="G549" s="58"/>
-      <c r="H549" s="17" t="s">
-        <v>216</v>
-      </c>
+      <c r="H549" s="58"/>
       <c r="I549" s="58"/>
       <c r="J549" s="57"/>
       <c r="K549" s="58"/>
       <c r="L549" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M549" s="60">
-        <v>1.0533300000000001</v>
+        <v>85</v>
+      </c>
+      <c r="M549" s="17">
+        <v>150</v>
       </c>
       <c r="N549" s="57" t="s">
         <v>38</v>
@@ -14451,27 +14458,25 @@
     </row>
     <row r="550" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="57" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B550" s="57"/>
       <c r="C550" s="57"/>
       <c r="D550" s="57" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E550" s="57"/>
       <c r="F550" s="58"/>
       <c r="G550" s="58"/>
-      <c r="H550" s="17" t="s">
-        <v>217</v>
-      </c>
+      <c r="H550" s="58"/>
       <c r="I550" s="58"/>
       <c r="J550" s="57"/>
       <c r="K550" s="58"/>
       <c r="L550" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M550" s="17">
-        <v>0.75</v>
+        <v>100</v>
       </c>
       <c r="N550" s="57" t="s">
         <v>38</v>
@@ -14481,19 +14486,27 @@
     </row>
     <row r="551" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="57" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B551" s="57"/>
       <c r="C551" s="57"/>
       <c r="D551" s="57" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E551" s="57"/>
+      <c r="F551" s="58"/>
+      <c r="G551" s="58"/>
+      <c r="H551" s="57" t="s">
+        <v>421</v>
+      </c>
+      <c r="I551" s="58"/>
+      <c r="J551" s="57"/>
+      <c r="K551" s="58"/>
       <c r="L551" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M551" s="29">
-        <v>6.9</v>
+        <v>86</v>
+      </c>
+      <c r="M551" s="17">
+        <v>22</v>
       </c>
       <c r="N551" s="57" t="s">
         <v>38</v>
@@ -14503,7 +14516,7 @@
     </row>
     <row r="552" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="57" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B552" s="57"/>
       <c r="C552" s="57"/>
@@ -14511,14 +14524,17 @@
         <v>215</v>
       </c>
       <c r="E552" s="57"/>
-      <c r="H552" s="17" t="s">
-        <v>216</v>
-      </c>
+      <c r="F552" s="58"/>
+      <c r="G552" s="58"/>
+      <c r="H552" s="58"/>
+      <c r="I552" s="58"/>
+      <c r="J552" s="57"/>
+      <c r="K552" s="58"/>
       <c r="L552" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M552" s="29">
-        <v>1.5</v>
+        <v>8.9</v>
       </c>
       <c r="N552" s="57" t="s">
         <v>38</v>
@@ -14528,7 +14544,7 @@
     </row>
     <row r="553" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="57" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B553" s="57"/>
       <c r="C553" s="57"/>
@@ -14536,14 +14552,19 @@
         <v>215</v>
       </c>
       <c r="E553" s="57"/>
+      <c r="F553" s="58"/>
+      <c r="G553" s="58"/>
       <c r="H553" s="17" t="s">
-        <v>217</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="I553" s="58"/>
+      <c r="J553" s="57"/>
+      <c r="K553" s="58"/>
       <c r="L553" s="17" t="s">
         <v>86</v>
       </c>
       <c r="M553" s="29">
-        <v>1.1000000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="N553" s="57" t="s">
         <v>38</v>
@@ -14551,211 +14572,218 @@
       <c r="O553" s="57"/>
       <c r="P553" s="19"/>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A554" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B554" s="4"/>
-      <c r="C554" s="4"/>
-      <c r="D554" s="4"/>
-      <c r="E554" s="4"/>
-      <c r="F554" s="4"/>
-      <c r="G554" s="4"/>
-      <c r="H554" s="4"/>
-      <c r="I554" s="4"/>
-      <c r="J554" s="4"/>
-      <c r="K554" s="4"/>
-      <c r="L554" s="5"/>
-      <c r="M554" s="5"/>
-      <c r="N554" s="5"/>
-      <c r="O554" s="5"/>
-      <c r="P554" s="5"/>
-    </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A555" t="s">
-        <v>186</v>
-      </c>
-      <c r="B555" s="10"/>
-      <c r="C555" s="10"/>
-      <c r="D555" t="s">
-        <v>119</v>
-      </c>
-      <c r="L555" t="s">
+    <row r="554" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A554" s="57" t="s">
+        <v>385</v>
+      </c>
+      <c r="B554" s="57"/>
+      <c r="C554" s="57"/>
+      <c r="D554" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E554" s="57"/>
+      <c r="F554" s="58"/>
+      <c r="G554" s="58"/>
+      <c r="H554" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="I554" s="58"/>
+      <c r="J554" s="57"/>
+      <c r="K554" s="58"/>
+      <c r="L554" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="M554" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="N554" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O554" s="57"/>
+      <c r="P554" s="19"/>
+    </row>
+    <row r="555" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A555" s="57" t="s">
+        <v>386</v>
+      </c>
+      <c r="B555" s="57"/>
+      <c r="C555" s="57"/>
+      <c r="D555" s="58"/>
+      <c r="E555" s="58"/>
+      <c r="F555" s="58"/>
+      <c r="G555" s="58"/>
+      <c r="H555" s="58"/>
+      <c r="I555" s="58"/>
+      <c r="J555" s="57"/>
+      <c r="K555" s="58"/>
+      <c r="M555" s="57"/>
+      <c r="N555" s="57"/>
+      <c r="O555" s="57"/>
+      <c r="P555" s="19"/>
+    </row>
+    <row r="556" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A556" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="B556" s="57"/>
+      <c r="C556" s="57"/>
+      <c r="D556" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E556" s="57"/>
+      <c r="F556" s="58"/>
+      <c r="G556" s="58"/>
+      <c r="H556" s="58"/>
+      <c r="I556" s="58"/>
+      <c r="J556" s="57"/>
+      <c r="K556" s="58"/>
+      <c r="L556" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M555" s="21">
-        <v>38</v>
-      </c>
-      <c r="N555" t="s">
-        <v>38</v>
-      </c>
-      <c r="O555" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="P555" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
-        <v>186</v>
-      </c>
-      <c r="B556" s="10"/>
-      <c r="C556" s="10"/>
-      <c r="D556" t="s">
-        <v>119</v>
-      </c>
-      <c r="H556" t="s">
-        <v>120</v>
-      </c>
-      <c r="L556" t="s">
+      <c r="M556" s="29">
+        <v>4.83</v>
+      </c>
+      <c r="N556" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O556" s="57"/>
+      <c r="P556" s="19"/>
+    </row>
+    <row r="557" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="B557" s="57"/>
+      <c r="C557" s="57"/>
+      <c r="D557" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E557" s="57"/>
+      <c r="F557" s="58"/>
+      <c r="G557" s="58"/>
+      <c r="H557" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="I557" s="58"/>
+      <c r="J557" s="57"/>
+      <c r="K557" s="58"/>
+      <c r="L557" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M556" s="21">
-        <v>60</v>
-      </c>
-      <c r="N556" t="s">
-        <v>38</v>
-      </c>
-      <c r="P556" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A557" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B557" s="10"/>
-      <c r="C557" s="10"/>
-      <c r="D557" t="s">
-        <v>37</v>
-      </c>
-      <c r="L557" t="s">
-        <v>85</v>
-      </c>
-      <c r="M557" s="15">
-        <f>(1*0.766) / (2.1/0.86) * 100</f>
-        <v>31.369523809523809</v>
-      </c>
-      <c r="N557" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O557" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="P557" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A558" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B558" s="10"/>
-      <c r="C558" s="10"/>
-      <c r="D558" t="s">
-        <v>37</v>
-      </c>
-      <c r="H558" t="s">
-        <v>296</v>
-      </c>
-      <c r="L558" t="s">
+      <c r="M557" s="60">
+        <v>1.0533300000000001</v>
+      </c>
+      <c r="N557" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O557" s="57"/>
+      <c r="P557" s="19"/>
+    </row>
+    <row r="558" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="57" t="s">
+        <v>387</v>
+      </c>
+      <c r="B558" s="57"/>
+      <c r="C558" s="57"/>
+      <c r="D558" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E558" s="57"/>
+      <c r="F558" s="58"/>
+      <c r="G558" s="58"/>
+      <c r="H558" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="I558" s="58"/>
+      <c r="J558" s="57"/>
+      <c r="K558" s="58"/>
+      <c r="L558" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M558" s="15">
-        <f>(0.8/0.9) / (2.1/0.86) * 100</f>
-        <v>36.402116402116405</v>
-      </c>
-      <c r="N558" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O558" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="P558" s="9" t="s">
-        <v>316</v>
-      </c>
+      <c r="M558" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="N558" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O558" s="57"/>
+      <c r="P558" s="19"/>
     </row>
     <row r="559" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="B559" s="19"/>
-      <c r="C559" s="19"/>
-      <c r="E559" s="17" t="s">
-        <v>422</v>
-      </c>
+      <c r="A559" s="57" t="s">
+        <v>388</v>
+      </c>
+      <c r="B559" s="57"/>
+      <c r="C559" s="57"/>
+      <c r="D559" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E559" s="57"/>
       <c r="L559" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M559" s="15">
-        <f>((7.8762418/27)/(1/0.86))*100</f>
-        <v>25.087288696296294</v>
-      </c>
-      <c r="N559" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O559" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="P559" s="18"/>
+      <c r="M559" s="29">
+        <v>6.9</v>
+      </c>
+      <c r="N559" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O559" s="57"/>
+      <c r="P559" s="19"/>
     </row>
     <row r="560" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="B560" s="10"/>
-      <c r="C560" s="10"/>
-      <c r="D560" s="6"/>
-      <c r="E560" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="F560" s="6"/>
-      <c r="G560" s="6"/>
-      <c r="H560" s="6"/>
-      <c r="I560" s="6"/>
-      <c r="J560" s="6"/>
-      <c r="K560" s="6"/>
-      <c r="L560" s="6" t="s">
+      <c r="A560" s="57" t="s">
+        <v>388</v>
+      </c>
+      <c r="B560" s="57"/>
+      <c r="C560" s="57"/>
+      <c r="D560" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E560" s="57"/>
+      <c r="H560" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L560" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M560" s="13">
-        <f>((0.4565/55)/(1/0.86))*100</f>
-        <v>0.71379999999999999</v>
-      </c>
-      <c r="N560" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="O560" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="P560" s="18"/>
-    </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A561" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="B561" s="10"/>
-      <c r="C561" s="10"/>
-      <c r="D561" t="s">
-        <v>355</v>
-      </c>
-      <c r="H561" s="6"/>
-      <c r="L561" t="s">
-        <v>85</v>
-      </c>
-      <c r="M561" s="15">
-        <v>100</v>
-      </c>
-      <c r="N561" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O561" s="6"/>
-      <c r="P561" s="9"/>
+      <c r="M560" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="N560" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O560" s="57"/>
+      <c r="P560" s="19"/>
+    </row>
+    <row r="561" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="57" t="s">
+        <v>388</v>
+      </c>
+      <c r="B561" s="57"/>
+      <c r="C561" s="57"/>
+      <c r="D561" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E561" s="57"/>
+      <c r="H561" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="L561" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="M561" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N561" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O561" s="57"/>
+      <c r="P561" s="19"/>
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
-        <v>287</v>
+        <v>190</v>
       </c>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -14768,118 +14796,320 @@
       <c r="J562" s="4"/>
       <c r="K562" s="4"/>
       <c r="L562" s="5"/>
-      <c r="M562" s="38" t="s">
-        <v>297</v>
-      </c>
+      <c r="M562" s="5"/>
       <c r="N562" s="5"/>
       <c r="O562" s="5"/>
       <c r="P562" s="5"/>
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="B563" s="10"/>
       <c r="C563" s="10"/>
-      <c r="D563" s="10"/>
-      <c r="E563" s="10"/>
-      <c r="F563" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G563" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="H563" s="10"/>
-      <c r="I563" s="10"/>
-      <c r="J563" s="10"/>
-      <c r="K563" s="10"/>
+      <c r="D563" t="s">
+        <v>119</v>
+      </c>
       <c r="L563" t="s">
         <v>85</v>
       </c>
-      <c r="M563" s="19">
-        <v>100</v>
-      </c>
-      <c r="N563" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O563" s="8"/>
-      <c r="P563" s="8"/>
+      <c r="M563" s="21">
+        <v>38</v>
+      </c>
+      <c r="N563" t="s">
+        <v>38</v>
+      </c>
+      <c r="O563" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="P563" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="B564" s="10"/>
       <c r="C564" s="10"/>
-      <c r="D564" s="10"/>
-      <c r="E564" s="10"/>
-      <c r="F564" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="G564" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="H564" s="10"/>
-      <c r="I564" s="10"/>
-      <c r="J564" s="10"/>
-      <c r="K564" s="10"/>
+      <c r="D564" t="s">
+        <v>119</v>
+      </c>
+      <c r="H564" t="s">
+        <v>120</v>
+      </c>
       <c r="L564" t="s">
-        <v>85</v>
-      </c>
-      <c r="M564" s="19">
-        <v>100</v>
-      </c>
-      <c r="N564" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O564" s="8"/>
-      <c r="P564" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="M564" s="21">
+        <v>60</v>
+      </c>
+      <c r="N564" t="s">
+        <v>38</v>
+      </c>
+      <c r="P564" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A565" s="17" t="s">
+        <v>185</v>
+      </c>
       <c r="B565" s="10"/>
       <c r="C565" s="10"/>
-      <c r="D565" s="10"/>
-      <c r="E565" s="10"/>
-      <c r="F565" s="19"/>
-      <c r="G565" s="19"/>
-      <c r="H565" s="10"/>
-      <c r="I565" s="10"/>
-      <c r="J565" s="10"/>
-      <c r="K565" s="10"/>
-      <c r="M565" s="19"/>
-      <c r="N565" s="8"/>
-      <c r="O565" s="8"/>
-      <c r="P565" s="8"/>
+      <c r="D565" t="s">
+        <v>37</v>
+      </c>
+      <c r="L565" t="s">
+        <v>85</v>
+      </c>
+      <c r="M565" s="15">
+        <f>(1*0.766) / (2.1/0.86) * 100</f>
+        <v>31.369523809523809</v>
+      </c>
+      <c r="N565" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O565" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="P565" s="9" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A566" s="2" t="s">
+      <c r="A566" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B566" s="10"/>
+      <c r="C566" s="10"/>
+      <c r="D566" t="s">
+        <v>37</v>
+      </c>
+      <c r="H566" t="s">
+        <v>296</v>
+      </c>
+      <c r="L566" t="s">
+        <v>86</v>
+      </c>
+      <c r="M566" s="15">
+        <f>(0.8/0.9) / (2.1/0.86) * 100</f>
+        <v>36.402116402116405</v>
+      </c>
+      <c r="N566" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O566" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="P566" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="567" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B567" s="19"/>
+      <c r="C567" s="19"/>
+      <c r="E567" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="L567" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M567" s="15">
+        <f>((7.8762418/27)/(1/0.86))*100</f>
+        <v>25.087288696296294</v>
+      </c>
+      <c r="N567" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O567" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="P567" s="18"/>
+    </row>
+    <row r="568" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B568" s="10"/>
+      <c r="C568" s="10"/>
+      <c r="D568" s="6"/>
+      <c r="E568" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F568" s="6"/>
+      <c r="G568" s="6"/>
+      <c r="H568" s="6"/>
+      <c r="I568" s="6"/>
+      <c r="J568" s="6"/>
+      <c r="K568" s="6"/>
+      <c r="L568" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M568" s="13">
+        <f>((0.4565/55)/(1/0.86))*100</f>
+        <v>0.71379999999999999</v>
+      </c>
+      <c r="N568" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O568" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="P568" s="18"/>
+    </row>
+    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A569" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B569" s="10"/>
+      <c r="C569" s="10"/>
+      <c r="D569" t="s">
+        <v>355</v>
+      </c>
+      <c r="H569" s="6"/>
+      <c r="L569" t="s">
+        <v>85</v>
+      </c>
+      <c r="M569" s="15">
+        <v>100</v>
+      </c>
+      <c r="N569" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O569" s="6"/>
+      <c r="P569" s="9"/>
+    </row>
+    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A570" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B570" s="4"/>
+      <c r="C570" s="4"/>
+      <c r="D570" s="4"/>
+      <c r="E570" s="4"/>
+      <c r="F570" s="4"/>
+      <c r="G570" s="4"/>
+      <c r="H570" s="4"/>
+      <c r="I570" s="4"/>
+      <c r="J570" s="4"/>
+      <c r="K570" s="4"/>
+      <c r="L570" s="5"/>
+      <c r="M570" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="N570" s="5"/>
+      <c r="O570" s="5"/>
+      <c r="P570" s="5"/>
+    </row>
+    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>261</v>
+      </c>
+      <c r="B571" s="10"/>
+      <c r="C571" s="10"/>
+      <c r="D571" s="10"/>
+      <c r="E571" s="10"/>
+      <c r="F571" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G571" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H571" s="10"/>
+      <c r="I571" s="10"/>
+      <c r="J571" s="10"/>
+      <c r="K571" s="10"/>
+      <c r="L571" t="s">
+        <v>85</v>
+      </c>
+      <c r="M571" s="19">
+        <v>100</v>
+      </c>
+      <c r="N571" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O571" s="8"/>
+      <c r="P571" s="8"/>
+    </row>
+    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>330</v>
+      </c>
+      <c r="B572" s="10"/>
+      <c r="C572" s="10"/>
+      <c r="D572" s="10"/>
+      <c r="E572" s="10"/>
+      <c r="F572" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="G572" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H572" s="10"/>
+      <c r="I572" s="10"/>
+      <c r="J572" s="10"/>
+      <c r="K572" s="10"/>
+      <c r="L572" t="s">
+        <v>85</v>
+      </c>
+      <c r="M572" s="19">
+        <v>100</v>
+      </c>
+      <c r="N572" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O572" s="8"/>
+      <c r="P572" s="8"/>
+    </row>
+    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B573" s="10"/>
+      <c r="C573" s="10"/>
+      <c r="D573" s="10"/>
+      <c r="E573" s="10"/>
+      <c r="F573" s="19"/>
+      <c r="G573" s="19"/>
+      <c r="H573" s="10"/>
+      <c r="I573" s="10"/>
+      <c r="J573" s="10"/>
+      <c r="K573" s="10"/>
+      <c r="M573" s="19"/>
+      <c r="N573" s="8"/>
+      <c r="O573" s="8"/>
+      <c r="P573" s="8"/>
+    </row>
+    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A574" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B566" s="2"/>
-      <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
-      <c r="E566" s="2"/>
-      <c r="F566" s="2"/>
-      <c r="G566" s="2"/>
-      <c r="H566" s="2"/>
-      <c r="I566" s="2"/>
-      <c r="J566" s="2"/>
-      <c r="K566" s="2"/>
-      <c r="L566" s="2"/>
-      <c r="M566" s="2"/>
-      <c r="N566" s="2"/>
-      <c r="O566" s="2"/>
-      <c r="P566" s="2"/>
-    </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A567" s="6" t="s">
+      <c r="B574" s="2"/>
+      <c r="C574" s="2"/>
+      <c r="D574" s="2"/>
+      <c r="E574" s="2"/>
+      <c r="F574" s="2"/>
+      <c r="G574" s="2"/>
+      <c r="H574" s="2"/>
+      <c r="I574" s="2"/>
+      <c r="J574" s="2"/>
+      <c r="K574" s="2"/>
+      <c r="L574" s="2"/>
+      <c r="M574" s="2"/>
+      <c r="N574" s="2"/>
+      <c r="O574" s="2"/>
+      <c r="P574" s="2"/>
+    </row>
+    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A575" s="6" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="P465" r:id="rId1"/>
-    <hyperlink ref="P471" r:id="rId2"/>
+    <hyperlink ref="P466" r:id="rId1"/>
+    <hyperlink ref="P472" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="480">
   <si>
     <t>parameter</t>
   </si>
@@ -1097,12 +1097,6 @@
     <t>Unprocessed commodity</t>
   </si>
   <si>
-    <t>adjusted from 73% to match slaughter statistics</t>
-  </si>
-  <si>
-    <t>adjusted from 71% to match slaughter statistics</t>
-  </si>
-  <si>
     <t>population_region</t>
   </si>
   <si>
@@ -1433,15 +1427,9 @@
     <t>Incl. absorbed water. (1/0.78)=carcass weight--&gt;live weight</t>
   </si>
   <si>
-    <t>adjusted to match slaughter statistics. &lt;92% in ref.</t>
-  </si>
-  <si>
     <t xml:space="preserve">FAO 1992 / https://doi.org/10.3382/ps.0592243 </t>
   </si>
   <si>
-    <t>chanaged from 66% to match slaughter statistics</t>
-  </si>
-  <si>
     <t>assumed same as for bioethanol</t>
   </si>
   <si>
@@ -1511,7 +1499,13 @@
     <t>Avg. 2016-2020. (imp-exp)/consumption</t>
   </si>
   <si>
-    <t>Avg.2016-2020. Based on "totalkonsumtion" adjusted for assumed CW to retail weight factor and losses</t>
+    <t>JBV. Konsumtion animalieprodukter. Priser och marknads­information för livsmedel. https://jordbruksverket.se/mat-och-drycker/handel-och-marknad/priser-och-marknadsinformation-for-livsmedel</t>
+  </si>
+  <si>
+    <t>Retail weight</t>
+  </si>
+  <si>
+    <t>Avg.2016-2020. Based on "totalkonsumtion" adjusted with JBV factors for CW --&gt; retail weight</t>
   </si>
 </sst>
 </file>
@@ -2235,13 +2229,13 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>55</v>
@@ -2308,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="P3" t="s">
         <v>7</v>
@@ -2316,19 +2310,19 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
+        <v>343</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="N4" t="s">
+        <v>344</v>
+      </c>
+      <c r="O4" t="s">
         <v>345</v>
       </c>
-      <c r="M4" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>346</v>
-      </c>
-      <c r="O4" t="s">
-        <v>347</v>
-      </c>
-      <c r="P4" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2635,7 +2629,7 @@
     </row>
     <row r="21" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>25</v>
@@ -2790,7 +2784,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>105</v>
@@ -3331,7 +3325,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B59" s="17" t="s">
         <v>79</v>
@@ -3386,17 +3380,17 @@
         <v>17</v>
       </c>
       <c r="M61" s="22">
-        <f>31.8*1000/365.25 * 0.73 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
-        <v>53.759619942505125</v>
+        <f>31.8*1000/365.25 * 0.78 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
+        <v>57.44178569199179</v>
       </c>
       <c r="N61" t="s">
         <v>18</v>
       </c>
       <c r="O61" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P61" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
@@ -3410,17 +3404,17 @@
         <v>17</v>
       </c>
       <c r="M62" s="22">
-        <f>24.5*1000/365.25 * 0.71 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
-        <v>40.283819630390141</v>
+        <f>24.5*1000/365.25 * 0.7 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
+        <v>39.716441889117036</v>
       </c>
       <c r="N62" t="s">
         <v>18</v>
       </c>
       <c r="O62" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P62" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -3434,17 +3428,17 @@
         <v>17</v>
       </c>
       <c r="M63" s="29">
-        <f>1.8*1000/365.25 * 0.66 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
-        <v>2.7512030882956875</v>
+        <f>1.8*1000/365.25 * 0.88 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
+        <v>3.6682707843942506</v>
       </c>
       <c r="N63" t="s">
         <v>18</v>
       </c>
       <c r="O63" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P63" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -3458,25 +3452,25 @@
         <v>17</v>
       </c>
       <c r="M64" s="22">
-        <f>22.7*1000/365.25 * 0.87 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
-        <v>45.735277601642707</v>
+        <f>22.7*1000/365.25 * 0.88 * (1-M188/100) * (1-M187/100) * (1-M186/100)</f>
+        <v>46.260970447638599</v>
       </c>
       <c r="N64" t="s">
         <v>18</v>
       </c>
       <c r="O64" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P64" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>428</v>
+      </c>
+      <c r="B65" t="s">
         <v>430</v>
-      </c>
-      <c r="B65" t="s">
-        <v>432</v>
       </c>
       <c r="L65" t="s">
         <v>17</v>
@@ -3488,15 +3482,15 @@
         <v>18</v>
       </c>
       <c r="O65" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L66" t="s">
         <v>17</v>
@@ -3551,7 +3545,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B69" s="17" t="s">
         <v>307</v>
@@ -3575,7 +3569,7 @@
         <v>18</v>
       </c>
       <c r="O69" s="17" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -3688,7 +3682,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>196</v>
@@ -3715,7 +3709,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>196</v>
@@ -3779,10 +3773,10 @@
     </row>
     <row r="80" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="57" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B80" s="57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C80" s="57"/>
       <c r="D80" s="58"/>
@@ -3807,10 +3801,10 @@
     </row>
     <row r="81" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="57" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B81" s="57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C81" s="57"/>
       <c r="D81" s="58"/>
@@ -3835,7 +3829,7 @@
     </row>
     <row r="82" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="52" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B82" s="54"/>
       <c r="C82" s="54"/>
@@ -3855,10 +3849,10 @@
     </row>
     <row r="83" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B83" s="57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C83" s="57"/>
       <c r="D83" s="58"/>
@@ -3924,7 +3918,7 @@
     </row>
     <row r="86" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>116</v>
@@ -3948,7 +3942,7 @@
         <v>18</v>
       </c>
       <c r="O86" s="17" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
@@ -4243,10 +4237,10 @@
     </row>
     <row r="102" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B102" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C102" s="57"/>
       <c r="D102" s="58"/>
@@ -4270,10 +4264,10 @@
     </row>
     <row r="103" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="57" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B103" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C103" s="57"/>
       <c r="D103" s="58"/>
@@ -4294,15 +4288,15 @@
         <v>18</v>
       </c>
       <c r="O103" s="57" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B104" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C104" s="57"/>
       <c r="D104" s="57"/>
@@ -4326,10 +4320,10 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="57" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B105" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C105" s="57"/>
       <c r="D105" s="57"/>
@@ -4353,10 +4347,10 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B106" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C106" s="57"/>
       <c r="D106" s="58"/>
@@ -4381,10 +4375,10 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B107" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C107" s="57"/>
       <c r="D107" s="58"/>
@@ -4409,10 +4403,10 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B108" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C108" s="57"/>
       <c r="D108" s="57"/>
@@ -4437,10 +4431,10 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="57" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B109" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C109" s="57"/>
       <c r="D109" s="58"/>
@@ -4465,10 +4459,10 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="57" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B110" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C110" s="57"/>
       <c r="D110" s="58"/>
@@ -4493,10 +4487,10 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B111" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C111" s="57"/>
       <c r="D111" s="58"/>
@@ -4521,10 +4515,10 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="57" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B112" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C112" s="57"/>
       <c r="D112" s="58"/>
@@ -4549,10 +4543,10 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B113" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C113" s="57"/>
       <c r="D113" s="58"/>
@@ -4577,10 +4571,10 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B114" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C114" s="57"/>
       <c r="D114" s="17"/>
@@ -4673,7 +4667,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B119" s="17" t="s">
         <v>189</v>
@@ -4699,7 +4693,7 @@
         <v>179</v>
       </c>
       <c r="O119" s="17" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P119" s="7"/>
     </row>
@@ -4815,7 +4809,7 @@
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B129" t="s">
         <v>189</v>
@@ -4830,7 +4824,7 @@
         <v>1000</v>
       </c>
       <c r="N129" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="O129" s="6"/>
       <c r="P129" s="9"/>
@@ -4878,7 +4872,7 @@
         <v>179</v>
       </c>
       <c r="O132" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P132" t="s">
         <v>281</v>
@@ -4905,7 +4899,7 @@
         <v>179</v>
       </c>
       <c r="O133" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="P133" t="s">
         <v>281</v>
@@ -4934,7 +4928,7 @@
         <v>179</v>
       </c>
       <c r="O134" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="P134" t="s">
         <v>281</v>
@@ -4960,7 +4954,7 @@
         <v>179</v>
       </c>
       <c r="O135" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="P135" t="s">
         <v>281</v>
@@ -4989,7 +4983,7 @@
         <v>179</v>
       </c>
       <c r="O136" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P136" t="s">
         <v>281</v>
@@ -5107,7 +5101,7 @@
         <v>179</v>
       </c>
       <c r="O140" s="17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P140">
         <v>20000</v>
@@ -5260,7 +5254,7 @@
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B146" s="17" t="s">
         <v>79</v>
@@ -5289,7 +5283,7 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B147" s="17" t="s">
         <v>79</v>
@@ -5344,7 +5338,7 @@
         <v>179</v>
       </c>
       <c r="O148" s="17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
@@ -5378,10 +5372,10 @@
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B150" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
@@ -5407,10 +5401,10 @@
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B151" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
@@ -5436,10 +5430,10 @@
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B152" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
@@ -5465,10 +5459,10 @@
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B153" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
@@ -5494,10 +5488,10 @@
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B154" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
@@ -5523,10 +5517,10 @@
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B155" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
@@ -5552,10 +5546,10 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B156" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
@@ -5581,10 +5575,10 @@
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B157" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
@@ -5610,10 +5604,10 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="17" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B158" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
@@ -5639,10 +5633,10 @@
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B159" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
@@ -5668,10 +5662,10 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B160" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
@@ -5697,7 +5691,7 @@
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="61" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5717,33 +5711,33 @@
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="62" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="62" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="62" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="62" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="57" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C167" t="s">
         <v>191</v>
       </c>
       <c r="L167" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M167">
         <v>50</v>
@@ -5752,18 +5746,18 @@
         <v>37</v>
       </c>
       <c r="O167" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="57" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C168" t="s">
         <v>115</v>
       </c>
       <c r="L168" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M168">
         <v>50</v>
@@ -5809,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="P171" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.25">
@@ -5829,7 +5823,7 @@
         <v>37</v>
       </c>
       <c r="P172" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
@@ -5850,7 +5844,7 @@
       </c>
       <c r="O173" s="6"/>
       <c r="P173" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.25">
@@ -5870,7 +5864,7 @@
         <v>37</v>
       </c>
       <c r="P174" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.25">
@@ -5890,7 +5884,7 @@
         <v>37</v>
       </c>
       <c r="P175" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.25">
@@ -5911,7 +5905,7 @@
       </c>
       <c r="O176" s="6"/>
       <c r="P176" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="2:16" x14ac:dyDescent="0.25">
@@ -5931,7 +5925,7 @@
         <v>37</v>
       </c>
       <c r="P177" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="2:16" x14ac:dyDescent="0.25">
@@ -5951,7 +5945,7 @@
         <v>37</v>
       </c>
       <c r="P178" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="2:16" x14ac:dyDescent="0.25">
@@ -5972,7 +5966,7 @@
       </c>
       <c r="O179" s="6"/>
       <c r="P179" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="180" spans="2:16" x14ac:dyDescent="0.25">
@@ -5992,7 +5986,7 @@
         <v>37</v>
       </c>
       <c r="P180" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="181" spans="2:16" x14ac:dyDescent="0.25">
@@ -6012,7 +6006,7 @@
         <v>37</v>
       </c>
       <c r="P181" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="182" spans="2:16" x14ac:dyDescent="0.25">
@@ -6033,7 +6027,7 @@
       </c>
       <c r="O182" s="6"/>
       <c r="P182" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="183" spans="2:16" x14ac:dyDescent="0.25">
@@ -6053,7 +6047,7 @@
         <v>37</v>
       </c>
       <c r="P183" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="184" spans="2:16" x14ac:dyDescent="0.25">
@@ -6074,7 +6068,7 @@
         <v>37</v>
       </c>
       <c r="P184" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="185" spans="2:16" x14ac:dyDescent="0.25">
@@ -6095,7 +6089,7 @@
       </c>
       <c r="O185" s="6"/>
       <c r="P185" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="2:16" x14ac:dyDescent="0.25">
@@ -6115,7 +6109,7 @@
         <v>37</v>
       </c>
       <c r="P186" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="187" spans="2:16" x14ac:dyDescent="0.25">
@@ -6135,7 +6129,7 @@
         <v>37</v>
       </c>
       <c r="P187" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="2:16" x14ac:dyDescent="0.25">
@@ -6155,15 +6149,15 @@
         <v>37</v>
       </c>
       <c r="O188" s="17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P188" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K189" t="s">
         <v>49</v>
@@ -6179,12 +6173,12 @@
         <v>37</v>
       </c>
       <c r="O189" s="17" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K190" t="s">
         <v>50</v>
@@ -6203,7 +6197,7 @@
     </row>
     <row r="191" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K191" t="s">
         <v>51</v>
@@ -6237,7 +6231,7 @@
         <v>37</v>
       </c>
       <c r="P192" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.25">
@@ -6257,7 +6251,7 @@
         <v>37</v>
       </c>
       <c r="P193" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
@@ -6278,7 +6272,7 @@
       </c>
       <c r="O194" s="6"/>
       <c r="P194" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.25">
@@ -6298,7 +6292,7 @@
         <v>37</v>
       </c>
       <c r="P195" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
@@ -6318,7 +6312,7 @@
         <v>37</v>
       </c>
       <c r="P196" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
@@ -6339,7 +6333,7 @@
       </c>
       <c r="O197" s="6"/>
       <c r="P197" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
@@ -6359,7 +6353,7 @@
         <v>37</v>
       </c>
       <c r="P198" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
@@ -6379,7 +6373,7 @@
         <v>37</v>
       </c>
       <c r="P199" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
@@ -6400,7 +6394,7 @@
       </c>
       <c r="O200" s="6"/>
       <c r="P200" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.25">
@@ -6420,7 +6414,7 @@
         <v>37</v>
       </c>
       <c r="P201" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
@@ -6440,7 +6434,7 @@
         <v>37</v>
       </c>
       <c r="P202" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
@@ -6461,7 +6455,7 @@
       </c>
       <c r="O203" s="6"/>
       <c r="P203" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
@@ -6481,7 +6475,7 @@
         <v>37</v>
       </c>
       <c r="P204" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.25">
@@ -6501,7 +6495,7 @@
         <v>37</v>
       </c>
       <c r="P205" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
@@ -6522,13 +6516,13 @@
       </c>
       <c r="O206" s="6"/>
       <c r="P206" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
       <c r="B207" s="17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C207" s="17"/>
       <c r="D207" s="17"/>
@@ -6552,13 +6546,13 @@
         <v>37</v>
       </c>
       <c r="O207" s="17" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="7"/>
       <c r="B208" s="17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C208" s="17"/>
       <c r="D208" s="17"/>
@@ -6586,7 +6580,7 @@
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="7"/>
       <c r="B209" s="17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C209" s="17"/>
       <c r="D209" s="17"/>
@@ -6614,7 +6608,7 @@
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="7"/>
       <c r="B210" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C210" s="57"/>
       <c r="D210" s="17"/>
@@ -6638,13 +6632,13 @@
         <v>37</v>
       </c>
       <c r="O210" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="7"/>
       <c r="B211" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C211" s="57"/>
       <c r="D211" s="17"/>
@@ -6671,7 +6665,7 @@
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B212" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C212" s="57"/>
       <c r="D212" s="17"/>
@@ -6698,7 +6692,7 @@
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B213" s="57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C213" s="57"/>
       <c r="D213" s="17"/>
@@ -6722,12 +6716,12 @@
       </c>
       <c r="O213" s="6"/>
       <c r="P213" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B214" s="57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C214" s="57"/>
       <c r="D214" s="17"/>
@@ -6751,12 +6745,12 @@
       </c>
       <c r="O214" s="6"/>
       <c r="P214" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B215" s="57" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C215" s="57"/>
       <c r="D215" s="17"/>
@@ -6780,12 +6774,12 @@
       </c>
       <c r="O215" s="6"/>
       <c r="P215" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B216" s="57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C216" s="57"/>
       <c r="D216" s="17"/>
@@ -6809,12 +6803,12 @@
       </c>
       <c r="O216" s="6"/>
       <c r="P216" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B217" s="57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C217" s="57"/>
       <c r="D217" s="17"/>
@@ -6838,12 +6832,12 @@
       </c>
       <c r="O217" s="6"/>
       <c r="P217" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B218" s="57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C218" s="57"/>
       <c r="D218" s="17"/>
@@ -6867,7 +6861,7 @@
       </c>
       <c r="O218" s="6"/>
       <c r="P218" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
@@ -7139,7 +7133,7 @@
     </row>
     <row r="236" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L236" s="17" t="s">
         <v>39</v>
@@ -7406,7 +7400,7 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
@@ -7428,7 +7422,7 @@
         <v>37</v>
       </c>
       <c r="O253" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
@@ -7519,7 +7513,7 @@
         <v>37</v>
       </c>
       <c r="O259" s="6" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.25">
@@ -7536,7 +7530,7 @@
         <v>37</v>
       </c>
       <c r="O260" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.25">
@@ -7731,7 +7725,7 @@
     </row>
     <row r="273" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L273" s="17" t="s">
         <v>39</v>
@@ -7743,7 +7737,7 @@
         <v>37</v>
       </c>
       <c r="O273" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.25">
@@ -7780,10 +7774,10 @@
         <v>37</v>
       </c>
       <c r="O275" s="17" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P275" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.25">
@@ -7800,10 +7794,10 @@
         <v>37</v>
       </c>
       <c r="O276" s="17" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P276" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.25">
@@ -7820,10 +7814,10 @@
         <v>37</v>
       </c>
       <c r="O277" s="17" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P277" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.25">
@@ -7840,15 +7834,15 @@
         <v>37</v>
       </c>
       <c r="O278" s="17" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P278" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L279" t="s">
         <v>39</v>
@@ -7860,12 +7854,12 @@
         <v>37</v>
       </c>
       <c r="O279" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L280" t="s">
         <v>39</v>
@@ -7914,7 +7908,7 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
@@ -8044,7 +8038,7 @@
     </row>
     <row r="290" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B290" s="19"/>
       <c r="C290" s="19"/>
@@ -8066,13 +8060,13 @@
         <v>37</v>
       </c>
       <c r="O290" s="19" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P290" s="19"/>
     </row>
     <row r="291" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B291" s="19"/>
       <c r="C291" s="19"/>
@@ -8094,7 +8088,7 @@
         <v>37</v>
       </c>
       <c r="O291" s="19" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P291" s="19"/>
     </row>
@@ -8120,7 +8114,7 @@
     </row>
     <row r="293" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B293" s="19"/>
       <c r="C293" s="19"/>
@@ -8142,13 +8136,13 @@
         <v>37</v>
       </c>
       <c r="O293" s="49" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P293" s="49"/>
     </row>
     <row r="294" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="17" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B294" s="19"/>
       <c r="C294" s="19"/>
@@ -8170,13 +8164,13 @@
         <v>37</v>
       </c>
       <c r="O294" s="49" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P294" s="49"/>
     </row>
     <row r="295" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="52" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B295" s="53"/>
       <c r="C295" s="53"/>
@@ -8196,7 +8190,7 @@
     </row>
     <row r="296" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B296" s="19"/>
       <c r="C296" s="19"/>
@@ -8218,7 +8212,7 @@
         <v>37</v>
       </c>
       <c r="O296" s="49" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P296" s="49"/>
     </row>
@@ -8259,7 +8253,7 @@
     </row>
     <row r="299" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L299" s="17" t="s">
         <v>39</v>
@@ -8271,7 +8265,7 @@
         <v>37</v>
       </c>
       <c r="O299" s="56" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="300" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -8465,10 +8459,10 @@
     </row>
     <row r="311" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B311" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C311" s="57"/>
       <c r="D311" s="58"/>
@@ -8489,15 +8483,15 @@
         <v>37</v>
       </c>
       <c r="O311" s="57" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="312" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="57" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B312" s="57" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C312" s="57"/>
       <c r="D312" s="58"/>
@@ -8518,15 +8512,15 @@
         <v>37</v>
       </c>
       <c r="O312" s="57" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="313" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B313" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C313" s="57"/>
       <c r="D313" s="57"/>
@@ -8547,16 +8541,16 @@
         <v>37</v>
       </c>
       <c r="O313" s="57" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P313" s="57"/>
     </row>
     <row r="314" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="17" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B314" s="17" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L314" s="17" t="s">
         <v>39</v>
@@ -8568,15 +8562,15 @@
         <v>37</v>
       </c>
       <c r="O314" s="57" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="315" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B315" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C315" s="57"/>
       <c r="D315" s="58"/>
@@ -8597,15 +8591,15 @@
         <v>37</v>
       </c>
       <c r="O315" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="316" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B316" s="57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C316" s="57"/>
       <c r="D316" s="58"/>
@@ -8626,15 +8620,15 @@
         <v>37</v>
       </c>
       <c r="O316" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="317" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B317" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C317" s="57"/>
       <c r="D317" s="58"/>
@@ -8655,15 +8649,15 @@
         <v>37</v>
       </c>
       <c r="O317" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="318" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="57" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B318" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C318" s="57"/>
       <c r="D318" s="58"/>
@@ -8684,15 +8678,15 @@
         <v>37</v>
       </c>
       <c r="O318" s="57" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="319" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="57" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B319" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C319" s="57"/>
       <c r="D319" s="58"/>
@@ -8713,15 +8707,15 @@
         <v>37</v>
       </c>
       <c r="O319" s="57" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="320" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B320" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C320" s="57"/>
       <c r="D320" s="58"/>
@@ -8742,15 +8736,15 @@
         <v>37</v>
       </c>
       <c r="O320" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="321" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="57" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B321" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C321" s="57"/>
       <c r="D321" s="58"/>
@@ -8771,15 +8765,15 @@
         <v>37</v>
       </c>
       <c r="O321" s="57" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="322" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B322" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C322" s="57"/>
       <c r="D322" s="58"/>
@@ -8800,15 +8794,15 @@
         <v>37</v>
       </c>
       <c r="O322" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="323" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B323" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C323" s="57"/>
       <c r="L323" s="57" t="s">
@@ -8821,7 +8815,7 @@
         <v>37</v>
       </c>
       <c r="O323" s="57" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.25">
@@ -9134,7 +9128,7 @@
     </row>
     <row r="339" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I339" s="17" t="s">
         <v>85</v>
@@ -9152,7 +9146,7 @@
         <v>37</v>
       </c>
       <c r="O339" s="17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.25">
@@ -9309,7 +9303,7 @@
     </row>
     <row r="347" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I347" s="17" t="s">
         <v>85</v>
@@ -9327,7 +9321,7 @@
         <v>37</v>
       </c>
       <c r="O347" s="17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P347" s="17" t="s">
         <v>156</v>
@@ -9733,7 +9727,7 @@
     </row>
     <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I365" t="s">
         <v>85</v>
@@ -9752,12 +9746,12 @@
         <v>37</v>
       </c>
       <c r="O365" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I366" t="s">
         <v>85</v>
@@ -9776,7 +9770,7 @@
         <v>37</v>
       </c>
       <c r="O366" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.25">
@@ -9827,7 +9821,7 @@
     </row>
     <row r="369" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I369" s="17" t="s">
         <v>85</v>
@@ -9910,7 +9904,7 @@
     </row>
     <row r="373" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="17" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I373" s="17" t="s">
         <v>85</v>
@@ -9928,12 +9922,12 @@
         <v>37</v>
       </c>
       <c r="O373" s="17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="374" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="17" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I374" s="17" t="s">
         <v>85</v>
@@ -9951,12 +9945,12 @@
         <v>37</v>
       </c>
       <c r="O374" s="17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="375" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="52" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B375" s="54"/>
       <c r="C375" s="54"/>
@@ -9976,7 +9970,7 @@
     </row>
     <row r="376" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I376" s="17" t="s">
         <v>85</v>
@@ -9994,7 +9988,7 @@
         <v>37</v>
       </c>
       <c r="O376" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.25">
@@ -10039,7 +10033,7 @@
     </row>
     <row r="379" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="57" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B379" s="57"/>
       <c r="C379" s="57"/>
@@ -10199,7 +10193,7 @@
     </row>
     <row r="386" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B386" s="57"/>
       <c r="C386" s="57"/>
@@ -10223,12 +10217,12 @@
         <v>37</v>
       </c>
       <c r="O386" s="57" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="387" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B387" s="57"/>
       <c r="C387" s="57"/>
@@ -10252,12 +10246,12 @@
         <v>37</v>
       </c>
       <c r="O387" s="57" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="17" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J388" s="17" t="s">
         <v>42</v>
@@ -10272,7 +10266,7 @@
         <v>37</v>
       </c>
       <c r="O388" s="57" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.25">
@@ -10909,12 +10903,12 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="48" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B414" s="68"/>
       <c r="C414" s="68"/>
       <c r="D414" s="69" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E414" s="69"/>
       <c r="F414" s="68"/>
@@ -11171,10 +11165,10 @@
     </row>
     <row r="424" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D424" s="18" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E424" s="18"/>
       <c r="L424" s="17" t="s">
@@ -11577,7 +11571,7 @@
       </c>
       <c r="R443" s="76"/>
       <c r="S443" s="77" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="444" spans="1:19" x14ac:dyDescent="0.25">
@@ -11600,7 +11594,7 @@
       <c r="O444" s="5"/>
       <c r="P444" s="5"/>
       <c r="R444" s="72" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="S444" s="79">
         <v>4.2000000000000003E-2</v>
@@ -11608,7 +11602,7 @@
     </row>
     <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" s="83" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B445" s="83"/>
       <c r="C445" s="83"/>
@@ -11978,7 +11972,7 @@
     </row>
     <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" s="83" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -12223,7 +12217,7 @@
     </row>
     <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" s="83" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B462" s="10"/>
       <c r="C462" s="10"/>
@@ -12348,7 +12342,7 @@
     </row>
     <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B466" s="8"/>
       <c r="C466" s="8"/>
@@ -12408,17 +12402,17 @@
       <c r="L468" t="s">
         <v>83</v>
       </c>
-      <c r="M468" s="11">
-        <v>73</v>
+      <c r="M468" s="18">
+        <v>78</v>
       </c>
       <c r="N468" s="8" t="s">
         <v>37</v>
       </c>
       <c r="O468" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="P468" s="8" t="s">
-        <v>89</v>
+        <v>478</v>
+      </c>
+      <c r="P468" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="469" spans="1:19" x14ac:dyDescent="0.25">
@@ -12436,7 +12430,7 @@
         <v>54</v>
       </c>
       <c r="H469" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I469" s="8"/>
       <c r="J469" s="8"/>
@@ -12473,7 +12467,7 @@
         <v>54</v>
       </c>
       <c r="H470" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I470" s="8"/>
       <c r="J470" s="8"/>
@@ -12510,7 +12504,7 @@
         <v>54</v>
       </c>
       <c r="H471" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I471" s="8"/>
       <c r="J471" s="8"/>
@@ -12547,7 +12541,7 @@
         <v>54</v>
       </c>
       <c r="H472" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I472" s="8"/>
       <c r="J472" s="8"/>
@@ -12563,10 +12557,10 @@
         <v>37</v>
       </c>
       <c r="O472" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P472" s="64" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="473" spans="1:19" x14ac:dyDescent="0.25">
@@ -12584,7 +12578,7 @@
         <v>54</v>
       </c>
       <c r="H473" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I473" s="8"/>
       <c r="J473" s="8"/>
@@ -12624,17 +12618,17 @@
       <c r="L474" t="s">
         <v>83</v>
       </c>
-      <c r="M474" s="11">
-        <v>71</v>
+      <c r="M474" s="18">
+        <v>70</v>
       </c>
       <c r="N474" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O474" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="P474" s="8" t="s">
-        <v>89</v>
+      <c r="O474" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="P474" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="475" spans="1:19" x14ac:dyDescent="0.25">
@@ -12652,7 +12646,7 @@
         <v>54</v>
       </c>
       <c r="H475" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I475" s="8"/>
       <c r="J475" s="8"/>
@@ -12689,7 +12683,7 @@
         <v>54</v>
       </c>
       <c r="H476" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I476" s="8"/>
       <c r="J476" s="8"/>
@@ -12726,7 +12720,7 @@
         <v>54</v>
       </c>
       <c r="H477" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I477" s="8"/>
       <c r="J477" s="8"/>
@@ -12763,7 +12757,7 @@
         <v>54</v>
       </c>
       <c r="H478" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I478" s="8"/>
       <c r="J478" s="8"/>
@@ -12779,10 +12773,10 @@
         <v>37</v>
       </c>
       <c r="O478" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P478" s="64" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="479" spans="1:19" x14ac:dyDescent="0.25">
@@ -12800,7 +12794,7 @@
         <v>54</v>
       </c>
       <c r="H479" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I479" s="8"/>
       <c r="J479" s="8"/>
@@ -12840,17 +12834,17 @@
       <c r="L480" t="s">
         <v>83</v>
       </c>
-      <c r="M480" s="11">
-        <v>66</v>
+      <c r="M480" s="18">
+        <v>88</v>
       </c>
       <c r="N480" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O480" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="P480" s="26" t="s">
-        <v>329</v>
+      <c r="O480" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="P480" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.25">
@@ -12868,7 +12862,7 @@
         <v>54</v>
       </c>
       <c r="H481" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I481" s="26"/>
       <c r="J481" s="26"/>
@@ -12905,7 +12899,7 @@
         <v>54</v>
       </c>
       <c r="H482" s="26" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I482" s="8"/>
       <c r="J482" s="8"/>
@@ -12942,7 +12936,7 @@
         <v>54</v>
       </c>
       <c r="H483" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I483" s="8"/>
       <c r="J483" s="8"/>
@@ -12958,7 +12952,7 @@
         <v>37</v>
       </c>
       <c r="O483" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P483" s="26"/>
     </row>
@@ -12977,7 +12971,7 @@
         <v>54</v>
       </c>
       <c r="H484" s="26" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I484" s="8"/>
       <c r="J484" s="8"/>
@@ -13020,17 +13014,17 @@
       <c r="L485" t="s">
         <v>83</v>
       </c>
-      <c r="M485" s="11">
-        <v>87</v>
+      <c r="M485" s="18">
+        <v>88</v>
       </c>
       <c r="N485" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O485" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="P485" s="8" t="s">
-        <v>89</v>
+      <c r="O485" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="P485" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.25">
@@ -13048,7 +13042,7 @@
         <v>54</v>
       </c>
       <c r="H486" s="26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I486" s="8"/>
       <c r="J486" s="8"/>
@@ -13064,10 +13058,10 @@
         <v>37</v>
       </c>
       <c r="O486" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P486" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.25">
@@ -13085,7 +13079,7 @@
         <v>54</v>
       </c>
       <c r="H487" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L487" t="s">
         <v>84</v>
@@ -13099,7 +13093,7 @@
       </c>
       <c r="O487" s="9"/>
       <c r="P487" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.25">
@@ -13117,7 +13111,7 @@
         <v>54</v>
       </c>
       <c r="H488" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I488" s="8"/>
       <c r="J488" s="8"/>
@@ -13134,7 +13128,7 @@
       </c>
       <c r="O488" s="9"/>
       <c r="P488" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.25">
@@ -13155,10 +13149,10 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H490" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L490" t="s">
         <v>83</v>
@@ -13172,10 +13166,10 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H491" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L491" t="s">
         <v>83</v>
@@ -13239,7 +13233,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A494" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B494" s="10"/>
       <c r="C494" s="10"/>
@@ -13350,7 +13344,7 @@
       <c r="B500" s="19"/>
       <c r="C500" s="19"/>
       <c r="D500" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E500" s="19"/>
       <c r="F500" s="18"/>
@@ -13373,12 +13367,12 @@
     </row>
     <row r="501" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B501" s="19"/>
       <c r="C501" s="19"/>
       <c r="D501" s="19" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E501" s="19"/>
       <c r="F501" s="18"/>
@@ -13401,12 +13395,12 @@
     </row>
     <row r="502" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B502" s="19"/>
       <c r="C502" s="19"/>
       <c r="D502" s="19" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E502" s="19"/>
       <c r="F502" s="18"/>
@@ -13449,12 +13443,12 @@
     </row>
     <row r="504" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="48" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B504" s="68"/>
       <c r="C504" s="68"/>
       <c r="D504" s="68" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E504" s="68"/>
       <c r="F504" s="69"/>
@@ -13477,18 +13471,18 @@
     </row>
     <row r="505" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="48" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B505" s="68"/>
       <c r="C505" s="68"/>
       <c r="D505" s="68" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E505" s="68"/>
       <c r="F505" s="69"/>
       <c r="G505" s="69"/>
       <c r="H505" s="68" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I505" s="68"/>
       <c r="J505" s="68"/>
@@ -13507,12 +13501,12 @@
     </row>
     <row r="506" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="48" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B506" s="68"/>
       <c r="C506" s="68"/>
       <c r="D506" s="68" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E506" s="68"/>
       <c r="F506" s="69"/>
@@ -13535,18 +13529,18 @@
     </row>
     <row r="507" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="48" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B507" s="68"/>
       <c r="C507" s="68"/>
       <c r="D507" s="68" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E507" s="68"/>
       <c r="F507" s="69"/>
       <c r="G507" s="69"/>
       <c r="H507" s="68" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I507" s="68"/>
       <c r="J507" s="68"/>
@@ -13565,7 +13559,7 @@
     </row>
     <row r="508" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="52" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B508" s="53"/>
       <c r="C508" s="53"/>
@@ -13585,12 +13579,12 @@
     </row>
     <row r="509" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B509" s="68"/>
       <c r="C509" s="68"/>
       <c r="D509" s="68" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E509" s="68"/>
       <c r="F509" s="69"/>
@@ -13731,7 +13725,7 @@
     </row>
     <row r="515" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D515" s="17" t="s">
         <v>117</v>
@@ -13752,7 +13746,7 @@
     </row>
     <row r="516" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D516" s="17" t="s">
         <v>117</v>
@@ -13776,7 +13770,7 @@
     </row>
     <row r="517" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D517" s="17" t="s">
         <v>117</v>
@@ -13797,7 +13791,7 @@
     </row>
     <row r="518" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D518" s="17" t="s">
         <v>117</v>
@@ -13824,7 +13818,7 @@
         <v>122</v>
       </c>
       <c r="D519" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L519" s="17" t="s">
         <v>83</v>
@@ -13836,7 +13830,7 @@
         <v>37</v>
       </c>
       <c r="O519" s="17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P519" s="19"/>
     </row>
@@ -13845,10 +13839,10 @@
         <v>122</v>
       </c>
       <c r="D520" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H520" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L520" s="17" t="s">
         <v>84</v>
@@ -14284,7 +14278,7 @@
         <v>37</v>
       </c>
       <c r="O537" s="19" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="P537" s="10"/>
     </row>
@@ -14310,7 +14304,7 @@
     </row>
     <row r="539" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B539" s="57"/>
       <c r="C539" s="57"/>
@@ -14338,7 +14332,7 @@
     </row>
     <row r="540" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B540" s="57"/>
       <c r="C540" s="57"/>
@@ -14349,7 +14343,7 @@
       <c r="F540" s="58"/>
       <c r="G540" s="58"/>
       <c r="H540" s="57" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I540" s="58"/>
       <c r="J540" s="57"/>
@@ -14365,13 +14359,13 @@
         <v>37</v>
       </c>
       <c r="O540" s="57" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P540" s="19"/>
     </row>
     <row r="541" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B541" s="57"/>
       <c r="C541" s="57"/>
@@ -14395,13 +14389,13 @@
         <v>37</v>
       </c>
       <c r="O541" s="57" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P541" s="19"/>
     </row>
     <row r="542" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B542" s="57"/>
       <c r="C542" s="57"/>
@@ -14412,7 +14406,7 @@
       <c r="F542" s="57"/>
       <c r="G542" s="57"/>
       <c r="H542" s="57" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I542" s="57"/>
       <c r="J542" s="57"/>
@@ -14432,7 +14426,7 @@
     </row>
     <row r="543" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="57" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B543" s="57"/>
       <c r="C543" s="57"/>
@@ -14443,7 +14437,7 @@
       <c r="F543" s="57"/>
       <c r="G543" s="57"/>
       <c r="H543" s="57" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I543" s="57"/>
       <c r="J543" s="57"/>
@@ -14463,7 +14457,7 @@
     </row>
     <row r="544" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="57" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B544" s="57"/>
       <c r="C544" s="57"/>
@@ -14491,7 +14485,7 @@
     </row>
     <row r="545" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="57" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B545" s="57"/>
       <c r="C545" s="57"/>
@@ -14502,7 +14496,7 @@
       <c r="F545" s="57"/>
       <c r="G545" s="57"/>
       <c r="H545" s="57" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I545" s="57"/>
       <c r="J545" s="57"/>
@@ -14522,7 +14516,7 @@
     </row>
     <row r="546" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B546" s="57"/>
       <c r="C546" s="57"/>
@@ -14551,7 +14545,7 @@
     </row>
     <row r="547" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B547" s="57"/>
       <c r="C547" s="57"/>
@@ -14582,7 +14576,7 @@
     </row>
     <row r="548" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B548" s="57"/>
       <c r="C548" s="57"/>
@@ -14613,7 +14607,7 @@
     </row>
     <row r="549" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B549" s="57"/>
       <c r="C549" s="57"/>
@@ -14642,7 +14636,7 @@
     </row>
     <row r="550" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B550" s="57"/>
       <c r="C550" s="57"/>
@@ -14673,7 +14667,7 @@
     </row>
     <row r="551" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="57" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B551" s="57"/>
       <c r="C551" s="57"/>
@@ -14704,7 +14698,7 @@
     </row>
     <row r="552" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B552" s="57"/>
       <c r="C552" s="57"/>
@@ -14733,7 +14727,7 @@
     </row>
     <row r="553" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B553" s="57"/>
       <c r="C553" s="57"/>
@@ -14764,7 +14758,7 @@
     </row>
     <row r="554" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B554" s="57"/>
       <c r="C554" s="57"/>
@@ -14795,7 +14789,7 @@
     </row>
     <row r="555" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="57" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B555" s="57"/>
       <c r="C555" s="57"/>
@@ -14823,7 +14817,7 @@
     </row>
     <row r="556" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="57" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B556" s="57"/>
       <c r="C556" s="57"/>
@@ -14851,7 +14845,7 @@
     </row>
     <row r="557" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="57" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B557" s="57"/>
       <c r="C557" s="57"/>
@@ -14862,7 +14856,7 @@
       <c r="F557" s="58"/>
       <c r="G557" s="58"/>
       <c r="H557" s="57" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I557" s="58"/>
       <c r="J557" s="57"/>
@@ -14881,7 +14875,7 @@
     </row>
     <row r="558" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B558" s="57"/>
       <c r="C558" s="57"/>
@@ -14909,7 +14903,7 @@
     </row>
     <row r="559" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B559" s="57"/>
       <c r="C559" s="57"/>
@@ -14939,7 +14933,7 @@
     </row>
     <row r="560" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="57" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B560" s="57"/>
       <c r="C560" s="57"/>
@@ -14969,7 +14963,7 @@
     </row>
     <row r="561" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="57" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B561" s="57"/>
       <c r="C561" s="57"/>
@@ -14988,7 +14982,7 @@
     </row>
     <row r="562" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B562" s="57"/>
       <c r="C562" s="57"/>
@@ -15016,7 +15010,7 @@
     </row>
     <row r="563" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B563" s="57"/>
       <c r="C563" s="57"/>
@@ -15046,7 +15040,7 @@
     </row>
     <row r="564" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B564" s="57"/>
       <c r="C564" s="57"/>
@@ -15076,7 +15070,7 @@
     </row>
     <row r="565" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B565" s="57"/>
       <c r="C565" s="57"/>
@@ -15098,7 +15092,7 @@
     </row>
     <row r="566" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B566" s="57"/>
       <c r="C566" s="57"/>
@@ -15123,7 +15117,7 @@
     </row>
     <row r="567" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B567" s="57"/>
       <c r="C567" s="57"/>
@@ -15273,12 +15267,12 @@
     </row>
     <row r="573" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B573" s="19"/>
       <c r="C573" s="19"/>
       <c r="E573" s="17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L573" s="17" t="s">
         <v>83</v>
@@ -15291,19 +15285,19 @@
         <v>37</v>
       </c>
       <c r="O573" s="17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P573" s="18"/>
     </row>
     <row r="574" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B574" s="10"/>
       <c r="C574" s="10"/>
       <c r="D574" s="6"/>
       <c r="E574" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F574" s="6"/>
       <c r="G574" s="6"/>
@@ -15322,18 +15316,18 @@
         <v>37</v>
       </c>
       <c r="O574" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P574" s="18"/>
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B575" s="10"/>
       <c r="C575" s="10"/>
       <c r="D575" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H575" s="6"/>
       <c r="L575" t="s">
@@ -16048,7 +16042,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C14" s="33"/>
       <c r="D14" s="33"/>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2736" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="528">
   <si>
     <t>parameter</t>
   </si>
@@ -1644,6 +1644,12 @@
   </si>
   <si>
     <t>&lt;-- Adjusted to align w. stat. on net exports of milk powder after solving "cream balance"</t>
+  </si>
+  <si>
+    <t>25,000 tonnes oat okara per year 0.2L okara per L oat drink</t>
+  </si>
+  <si>
+    <t>https://www.axfoundation.se/en/projects/over-n-oat-residues</t>
   </si>
 </sst>
 </file>
@@ -1880,7 +1886,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1973,6 +1979,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5271,13 +5278,19 @@
       <c r="L132" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="M132" s="55">
-        <v>0</v>
+      <c r="M132" s="88">
+        <f>25000/0.2 / (M3*1000) / 365.25 * 1000</f>
+        <v>33.691964177904516</v>
       </c>
       <c r="N132" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="O132" s="15"/>
+      <c r="O132" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="P132" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="55" t="s">

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0E270E-EC8B-4682-9925-EC6098E27F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E2CB8A-91DA-41FD-AF4D-C3EEFFC3B09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="2910" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -10444,7 +10444,7 @@
         <v>40</v>
       </c>
       <c r="M397" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N397" t="s">
         <v>37</v>
@@ -10487,7 +10487,7 @@
         <v>42</v>
       </c>
       <c r="L399" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M399" s="12">
         <f>M395*0.6+M396*0.4</f>
@@ -10511,7 +10511,7 @@
         <v>42</v>
       </c>
       <c r="L400" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M400" s="12">
         <f>M395*0.6+M396*0.4</f>

--- a/data/default/DemandAndConversions.xlsx
+++ b/data/default/DemandAndConversions.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A9F66D-371D-4C04-AC8C-CA496D4DD28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941DAB52-6E3A-4640-A4B3-3BC4738CA820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27300" yWindow="795" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -1250,12 +1250,6 @@
     <t>f_food_ingr</t>
   </si>
   <si>
-    <t>recipie</t>
-  </si>
-  <si>
-    <t>Here recipies for foods made up of several other foods can be specified (i.e. compound foods). In the model these foods are converted to their constituent foods.</t>
-  </si>
-  <si>
     <t>Import shares are applied both for the compound food and the constituent foods, so that e.g. a compound food can be specified as 100% domestic while some</t>
   </si>
   <si>
@@ -1265,9 +1259,6 @@
     <t>of its ingredients are 100% imported. For production system shares the share of the compound food are used also for its ingredients. NOTE! Conversion factors</t>
   </si>
   <si>
-    <t>are not applicable for compound foods (i.e. all fods with the 'recipie' parameter specified).</t>
-  </si>
-  <si>
     <t>Offals</t>
   </si>
   <si>
@@ -1611,6 +1602,15 @@
   </si>
   <si>
     <t xml:space="preserve"> Artichokes + Asparagus + Chillies and peppers, green (capsicum spp. and pimenta spp.) + Sweet corn frozen + Sweet corn prepared or preserved</t>
+  </si>
+  <si>
+    <t>Here recipes for foods made up of several other foods can be specified (i.e. compound foods). In the model these foods are converted to their constituent foods.</t>
+  </si>
+  <si>
+    <t>recipe</t>
+  </si>
+  <si>
+    <t>are not applicable for compound foods (i.e. all fods with the 'recipe' parameter specified).</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2272,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="P3" t="s">
         <v>7</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="27" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>98</v>
@@ -2960,12 +2960,12 @@
         <v>18</v>
       </c>
       <c r="O39" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B40" t="s">
         <v>103</v>
@@ -2981,7 +2981,7 @@
         <v>18</v>
       </c>
       <c r="O40" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3153,7 +3153,7 @@
     </row>
     <row r="50" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>217</v>
@@ -3177,7 +3177,7 @@
         <v>18</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="S50"/>
     </row>
@@ -3219,7 +3219,7 @@
         <v>18</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -3261,7 +3261,7 @@
         <v>18</v>
       </c>
       <c r="O54" s="11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -3430,10 +3430,10 @@
         <v>18</v>
       </c>
       <c r="O63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P63" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -3454,10 +3454,10 @@
         <v>18</v>
       </c>
       <c r="O64" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P64" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -3478,10 +3478,10 @@
         <v>18</v>
       </c>
       <c r="O65" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P65" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
@@ -3502,18 +3502,18 @@
         <v>18</v>
       </c>
       <c r="O66" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P66" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="L67" t="s">
         <v>17</v>
@@ -3525,15 +3525,15 @@
         <v>18</v>
       </c>
       <c r="O67" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B68" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="L68" t="s">
         <v>17</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B75" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B76" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B77" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B78" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -3819,10 +3819,10 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B83" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B84" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B85" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="97" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>336</v>
@@ -4234,13 +4234,13 @@
         <v>18</v>
       </c>
       <c r="O97" s="11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="S97"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B98" s="36"/>
       <c r="C98" s="36"/>
@@ -4288,7 +4288,7 @@
     </row>
     <row r="100" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>340</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="101" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>340</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="102" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>340</v>
@@ -4364,13 +4364,13 @@
         <v>18</v>
       </c>
       <c r="O102" s="11" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="S102"/>
     </row>
     <row r="103" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>340</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="104" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>340</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="110" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>114</v>
@@ -4550,7 +4550,7 @@
         <v>18</v>
       </c>
       <c r="O110" s="11" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="S110"/>
     </row>
@@ -4591,7 +4591,7 @@
         <v>18</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="121" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>25</v>
@@ -4762,7 +4762,7 @@
       <c r="J121" s="38"/>
       <c r="K121" s="38"/>
       <c r="L121" s="11" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="M121" s="11">
         <v>31.9</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B124" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B125" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B126" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B127" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B128" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -5072,10 +5072,10 @@
         <v>18</v>
       </c>
       <c r="O133" s="11" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="P133" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
@@ -5161,7 +5161,7 @@
     </row>
     <row r="137" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>344</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>344</v>
@@ -5544,7 +5544,7 @@
         <v>327</v>
       </c>
       <c r="O155" s="11" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.25">
@@ -5590,10 +5590,10 @@
         <v>164</v>
       </c>
       <c r="O158" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="P158" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.25">
@@ -5617,10 +5617,10 @@
         <v>164</v>
       </c>
       <c r="O159" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="P159" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="T159" s="6"/>
     </row>
@@ -5644,10 +5644,10 @@
         <v>164</v>
       </c>
       <c r="O160" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="P160" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.25">
@@ -5670,10 +5670,10 @@
         <v>164</v>
       </c>
       <c r="O161" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="P161" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="T161" s="6"/>
     </row>
@@ -5697,10 +5697,10 @@
         <v>164</v>
       </c>
       <c r="O162" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="P162" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.25">
@@ -5751,7 +5751,7 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B165" t="s">
         <v>98</v>
@@ -5771,7 +5771,7 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B166" t="s">
         <v>114</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="40" t="s">
-        <v>398</v>
+        <v>515</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="40" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="40" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="40" t="s">
-        <v>402</v>
+        <v>517</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
@@ -6535,7 +6535,7 @@
         <v>176</v>
       </c>
       <c r="L197" t="s">
-        <v>397</v>
+        <v>516</v>
       </c>
       <c r="M197">
         <v>50</v>
@@ -6544,7 +6544,7 @@
         <v>37</v>
       </c>
       <c r="O197" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
@@ -6555,7 +6555,7 @@
         <v>113</v>
       </c>
       <c r="L198" t="s">
-        <v>397</v>
+        <v>516</v>
       </c>
       <c r="M198">
         <v>50</v>
@@ -6569,7 +6569,7 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="39" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6589,10 +6589,10 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L202" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M202" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
@@ -6632,7 +6632,7 @@
         <v>37</v>
       </c>
       <c r="P205" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
@@ -6652,7 +6652,7 @@
         <v>37</v>
       </c>
       <c r="P206" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="O207" s="6"/>
       <c r="P207" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
@@ -6693,7 +6693,7 @@
         <v>37</v>
       </c>
       <c r="P208" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="209" spans="2:16" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
         <v>37</v>
       </c>
       <c r="P209" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="210" spans="2:16" x14ac:dyDescent="0.25">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O210" s="6"/>
       <c r="P210" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="211" spans="2:16" x14ac:dyDescent="0.25">
@@ -6754,7 +6754,7 @@
         <v>37</v>
       </c>
       <c r="P211" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="212" spans="2:16" x14ac:dyDescent="0.25">
@@ -6774,7 +6774,7 @@
         <v>37</v>
       </c>
       <c r="P212" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="213" spans="2:16" x14ac:dyDescent="0.25">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="O213" s="6"/>
       <c r="P213" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="214" spans="2:16" x14ac:dyDescent="0.25">
@@ -6815,7 +6815,7 @@
         <v>37</v>
       </c>
       <c r="P214" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="215" spans="2:16" x14ac:dyDescent="0.25">
@@ -6835,7 +6835,7 @@
         <v>37</v>
       </c>
       <c r="P215" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="216" spans="2:16" x14ac:dyDescent="0.25">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="O216" s="6"/>
       <c r="P216" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="217" spans="2:16" x14ac:dyDescent="0.25">
@@ -6876,10 +6876,10 @@
         <v>37</v>
       </c>
       <c r="O217" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="P217" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="218" spans="2:16" x14ac:dyDescent="0.25">
@@ -6900,7 +6900,7 @@
         <v>37</v>
       </c>
       <c r="P218" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="219" spans="2:16" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="O219" s="6"/>
       <c r="P219" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="220" spans="2:16" x14ac:dyDescent="0.25">
@@ -6941,7 +6941,7 @@
         <v>37</v>
       </c>
       <c r="P220" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="221" spans="2:16" x14ac:dyDescent="0.25">
@@ -6961,7 +6961,7 @@
         <v>37</v>
       </c>
       <c r="P221" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="222" spans="2:16" x14ac:dyDescent="0.25">
@@ -6981,15 +6981,15 @@
         <v>37</v>
       </c>
       <c r="O222" s="11" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P222" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="223" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="K223" t="s">
         <v>49</v>
@@ -7005,12 +7005,12 @@
         <v>37</v>
       </c>
       <c r="O223" s="11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="224" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="K224" t="s">
         <v>50</v>
@@ -7029,7 +7029,7 @@
     </row>
     <row r="225" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="K225" t="s">
         <v>51</v>
@@ -7063,7 +7063,7 @@
         <v>37</v>
       </c>
       <c r="P226" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="227" spans="2:16" x14ac:dyDescent="0.25">
@@ -7083,7 +7083,7 @@
         <v>37</v>
       </c>
       <c r="P227" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="228" spans="2:16" x14ac:dyDescent="0.25">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="O228" s="6"/>
       <c r="P228" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="229" spans="2:16" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>37</v>
       </c>
       <c r="P229" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="230" spans="2:16" x14ac:dyDescent="0.25">
@@ -7144,7 +7144,7 @@
         <v>37</v>
       </c>
       <c r="P230" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="231" spans="2:16" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="O231" s="6"/>
       <c r="P231" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="232" spans="2:16" x14ac:dyDescent="0.25">
@@ -7185,7 +7185,7 @@
         <v>37</v>
       </c>
       <c r="P232" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="233" spans="2:16" x14ac:dyDescent="0.25">
@@ -7205,7 +7205,7 @@
         <v>37</v>
       </c>
       <c r="P233" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="234" spans="2:16" x14ac:dyDescent="0.25">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="O234" s="6"/>
       <c r="P234" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="235" spans="2:16" x14ac:dyDescent="0.25">
@@ -7246,7 +7246,7 @@
         <v>37</v>
       </c>
       <c r="P235" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="236" spans="2:16" x14ac:dyDescent="0.25">
@@ -7266,7 +7266,7 @@
         <v>37</v>
       </c>
       <c r="P236" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="237" spans="2:16" x14ac:dyDescent="0.25">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="O237" s="6"/>
       <c r="P237" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="238" spans="2:16" x14ac:dyDescent="0.25">
@@ -7307,7 +7307,7 @@
         <v>37</v>
       </c>
       <c r="P238" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="239" spans="2:16" x14ac:dyDescent="0.25">
@@ -7327,7 +7327,7 @@
         <v>37</v>
       </c>
       <c r="P239" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="240" spans="2:16" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="O240" s="6"/>
       <c r="P240" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
@@ -7378,7 +7378,7 @@
         <v>37</v>
       </c>
       <c r="O241" s="11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
@@ -7464,7 +7464,7 @@
         <v>37</v>
       </c>
       <c r="O244" s="11" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="O247" s="6"/>
       <c r="P247" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="O248" s="6"/>
       <c r="P248" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="O249" s="6"/>
       <c r="P249" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="O250" s="6"/>
       <c r="P250" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="O251" s="6"/>
       <c r="P251" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="O252" s="6"/>
       <c r="P252" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B253" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C253" s="11"/>
       <c r="D253" s="11"/>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B254" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C254" s="11"/>
       <c r="D254" s="11"/>
@@ -7750,7 +7750,7 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B255" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C255" s="11"/>
       <c r="D255" s="11"/>
@@ -7776,7 +7776,7 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B256" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C256" s="11"/>
       <c r="D256" s="11"/>
@@ -7802,7 +7802,7 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B257" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C257" s="11"/>
       <c r="D257" s="11"/>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B258" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C258" s="11"/>
       <c r="D258" s="11"/>
@@ -8499,7 +8499,7 @@
         <v>37</v>
       </c>
       <c r="O299" s="6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
@@ -8516,7 +8516,7 @@
         <v>37</v>
       </c>
       <c r="O300" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.25">
@@ -8552,7 +8552,7 @@
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L303" t="s">
         <v>39</v>
@@ -8775,10 +8775,10 @@
         <v>37</v>
       </c>
       <c r="O316" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P316" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.25">
@@ -8795,10 +8795,10 @@
         <v>37</v>
       </c>
       <c r="O317" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P317" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.25">
@@ -8815,10 +8815,10 @@
         <v>37</v>
       </c>
       <c r="O318" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P318" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.25">
@@ -8835,15 +8835,15 @@
         <v>37</v>
       </c>
       <c r="O319" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P319" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L320" t="s">
         <v>39</v>
@@ -8855,12 +8855,12 @@
         <v>37</v>
       </c>
       <c r="O320" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L321" t="s">
         <v>39</v>
@@ -9135,7 +9135,7 @@
     </row>
     <row r="336" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -10670,7 +10670,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I406" t="s">
         <v>83</v>
@@ -10689,12 +10689,12 @@
         <v>37</v>
       </c>
       <c r="O406" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="I407" t="s">
         <v>83</v>
@@ -10713,7 +10713,7 @@
         <v>37</v>
       </c>
       <c r="O407" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.25">
@@ -10893,7 +10893,7 @@
     </row>
     <row r="416" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B416" s="36"/>
       <c r="C416" s="36"/>
@@ -11722,7 +11722,7 @@
         <v>363</v>
       </c>
       <c r="D455" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L455" t="s">
         <v>81</v>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="R484" s="48"/>
       <c r="S484" s="49" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="485" spans="1:22" x14ac:dyDescent="0.25">
@@ -12302,7 +12302,7 @@
       <c r="O485" s="5"/>
       <c r="P485" s="5"/>
       <c r="R485" s="45" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="S485" s="51">
         <v>4.2000000000000003E-2</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="486" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -12593,7 +12593,7 @@
         <v>37</v>
       </c>
       <c r="O493" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="P493" t="s">
         <v>88</v>
@@ -12706,7 +12706,7 @@
         <v>37</v>
       </c>
       <c r="O496" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="P496" t="s">
         <v>88</v>
@@ -12716,7 +12716,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="T496" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="497" spans="1:19" x14ac:dyDescent="0.25">
@@ -12759,7 +12759,7 @@
     </row>
     <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" s="38" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B498" s="11"/>
       <c r="C498" s="11"/>
@@ -13001,7 +13001,7 @@
     </row>
     <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" s="38" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B505" s="11"/>
       <c r="C505" s="11"/>
@@ -13163,10 +13163,10 @@
         <v>37</v>
       </c>
       <c r="O510" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P510" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="511" spans="1:19" x14ac:dyDescent="0.25">
@@ -13180,7 +13180,7 @@
         <v>54</v>
       </c>
       <c r="H511" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L511" t="s">
         <v>82</v>
@@ -13210,7 +13210,7 @@
         <v>54</v>
       </c>
       <c r="H512" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L512" t="s">
         <v>82</v>
@@ -13240,7 +13240,7 @@
         <v>54</v>
       </c>
       <c r="H513" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L513" t="s">
         <v>82</v>
@@ -13270,7 +13270,7 @@
         <v>54</v>
       </c>
       <c r="H514" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L514" t="s">
         <v>82</v>
@@ -13283,10 +13283,10 @@
         <v>37</v>
       </c>
       <c r="O514" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="P514" s="42" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.25">
@@ -13300,7 +13300,7 @@
         <v>54</v>
       </c>
       <c r="H515" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L515" t="s">
         <v>82</v>
@@ -13335,10 +13335,10 @@
         <v>37</v>
       </c>
       <c r="O516" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P516" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.25">
@@ -13352,7 +13352,7 @@
         <v>54</v>
       </c>
       <c r="H517" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L517" t="s">
         <v>82</v>
@@ -13382,7 +13382,7 @@
         <v>54</v>
       </c>
       <c r="H518" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L518" t="s">
         <v>82</v>
@@ -13412,7 +13412,7 @@
         <v>54</v>
       </c>
       <c r="H519" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L519" t="s">
         <v>82</v>
@@ -13442,7 +13442,7 @@
         <v>54</v>
       </c>
       <c r="H520" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L520" t="s">
         <v>82</v>
@@ -13455,10 +13455,10 @@
         <v>37</v>
       </c>
       <c r="O520" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="P520" s="42" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.25">
@@ -13472,7 +13472,7 @@
         <v>54</v>
       </c>
       <c r="H521" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L521" t="s">
         <v>82</v>
@@ -13507,10 +13507,10 @@
         <v>37</v>
       </c>
       <c r="O522" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P522" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.25">
@@ -13524,7 +13524,7 @@
         <v>54</v>
       </c>
       <c r="H523" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I523" s="16"/>
       <c r="J523" s="16"/>
@@ -13557,7 +13557,7 @@
         <v>54</v>
       </c>
       <c r="H524" s="16" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L524" t="s">
         <v>82</v>
@@ -13587,7 +13587,7 @@
         <v>54</v>
       </c>
       <c r="H525" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L525" t="s">
         <v>82</v>
@@ -13600,7 +13600,7 @@
         <v>37</v>
       </c>
       <c r="O525" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="P525" s="16"/>
     </row>
@@ -13615,7 +13615,7 @@
         <v>54</v>
       </c>
       <c r="H526" s="16" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L526" t="s">
         <v>82</v>
@@ -13654,10 +13654,10 @@
         <v>37</v>
       </c>
       <c r="O527" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P527" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.25">
@@ -13675,7 +13675,7 @@
         <v>54</v>
       </c>
       <c r="H528" s="16" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L528" t="s">
         <v>82</v>
@@ -13688,10 +13688,10 @@
         <v>37</v>
       </c>
       <c r="O528" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="P528" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.25">
@@ -13709,7 +13709,7 @@
         <v>54</v>
       </c>
       <c r="H529" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="L529" t="s">
         <v>82</v>
@@ -13722,7 +13722,7 @@
         <v>37</v>
       </c>
       <c r="P529" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.25">
@@ -13740,7 +13740,7 @@
         <v>54</v>
       </c>
       <c r="H530" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L530" t="s">
         <v>82</v>
@@ -13753,7 +13753,7 @@
         <v>37</v>
       </c>
       <c r="P530" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.25">
@@ -13768,10 +13768,10 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H532" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L532" t="s">
         <v>81</v>
@@ -13785,10 +13785,10 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H533" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L533" t="s">
         <v>81</v>
@@ -14022,7 +14022,7 @@
       <c r="B546"/>
       <c r="C546"/>
       <c r="D546" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E546"/>
       <c r="F546"/>
@@ -14048,13 +14048,13 @@
       <c r="B547"/>
       <c r="C547"/>
       <c r="D547" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E547"/>
       <c r="F547"/>
       <c r="G547"/>
       <c r="H547" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="I547"/>
       <c r="J547"/>
@@ -14076,7 +14076,7 @@
       <c r="B548"/>
       <c r="C548"/>
       <c r="D548" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E548"/>
       <c r="F548"/>
@@ -14102,13 +14102,13 @@
       <c r="B549"/>
       <c r="C549"/>
       <c r="D549" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E549"/>
       <c r="F549"/>
       <c r="G549"/>
       <c r="H549" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I549"/>
       <c r="J549"/>
@@ -14399,7 +14399,7 @@
         <v>382</v>
       </c>
       <c r="H562" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L562" s="11" t="s">
         <v>82</v>
@@ -14818,7 +14818,7 @@
         <v>37</v>
       </c>
       <c r="O579" s="11" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="P579" s="6"/>
     </row>
@@ -15510,7 +15510,7 @@
     </row>
     <row r="611" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D611" s="16"/>
       <c r="L611" s="11" t="s">
@@ -15523,12 +15523,12 @@
         <v>37</v>
       </c>
       <c r="O611" s="11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="612" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D612" s="16"/>
       <c r="L612" s="11" t="s">
@@ -15543,7 +15543,7 @@
     </row>
     <row r="613" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D613" s="16"/>
       <c r="L613" s="11" t="s">
@@ -15558,7 +15558,7 @@
     </row>
     <row r="614" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D614" s="16"/>
       <c r="L614" s="11" t="s">
@@ -15573,7 +15573,7 @@
     </row>
     <row r="615" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D615" s="16"/>
       <c r="L615" s="11" t="s">
@@ -15588,7 +15588,7 @@
     </row>
     <row r="616" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="16" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D616" s="16"/>
       <c r="L616" s="11" t="s">
@@ -15603,7 +15603,7 @@
     </row>
     <row r="617" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D617" s="16"/>
       <c r="L617" s="11" t="s">
@@ -15618,7 +15618,7 @@
     </row>
     <row r="618" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="16" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D618" s="16"/>
       <c r="L618" s="11" t="s">
@@ -15633,7 +15633,7 @@
     </row>
     <row r="619" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="16" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D619" s="16"/>
       <c r="L619" s="11" t="s">
@@ -15648,7 +15648,7 @@
     </row>
     <row r="620" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D620" s="16"/>
       <c r="L620" s="11" t="s">
@@ -15663,7 +15663,7 @@
     </row>
     <row r="621" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D621" s="16"/>
       <c r="L621" s="11" t="s">
@@ -15678,7 +15678,7 @@
     </row>
     <row r="622" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="16" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D622" s="16"/>
       <c r="L622" s="11" t="s">
@@ -15693,7 +15693,7 @@
     </row>
     <row r="623" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="16" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D623" s="16"/>
       <c r="L623" s="11" t="s">
@@ -15743,7 +15743,7 @@
     </row>
     <row r="626" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="16" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L626" s="11" t="s">
         <v>81</v>
@@ -15757,7 +15757,7 @@
     </row>
     <row r="627" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="16" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="L627" s="11" t="s">
         <v>81</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="628" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="16" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L628" s="11" t="s">
         <v>81</v>
@@ -15785,7 +15785,7 @@
     </row>
     <row r="629" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="L629" s="11" t="s">
         <v>81</v>
@@ -15799,7 +15799,7 @@
     </row>
     <row r="630" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L630" s="11" t="s">
         <v>81</v>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="644" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A644" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -16619,7 +16619,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
